--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -197,8 +197,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,7 +586,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Simple Flow V1 (Simple Mode) - Manual Test Cases
-This workbook contains 156 manual test cases covering the ShopView "Simple Mode - Streamlined Work Order Completion &amp; Receiving" feature (Epic SV-7301): the Work Order settings page; the four settings-driven completion flows (No-PO/skip, PO+Optional invoice, PO+Required invoice, and Review-ON); the tech-story and line-approval gates; core-part resolution; vendorless / Vendor-Missing part handling; PO multi-select, Bulk Receive, apply-invoice, part-number fix, the WO-PO Receive button, Accept Delivery and assign-vendor / merge; the Waiting-on-Parts column; UX refinements; permissions; validation / edge cases; and QuickBooks / inventory integrity.
+This workbook contains 159 manual test cases covering the ShopView "Simple Mode - Streamlined Work Order Completion &amp; Receiving" feature (Epic SV-7301): the Work Order settings page; the four settings-driven completion flows (No-PO/skip, PO+Optional invoice, PO+Required invoice, and Review-ON); the tech-story and line-approval gates; core-part resolution; vendorless / Vendor-Missing part handling; PO multi-select, Bulk Receive, apply-invoice, part-number fix, the WO-PO Receive button, Accept Delivery and assign-vendor / merge; the Waiting-on-Parts column; UX refinements; permissions; validation / edge cases; and QuickBooks / inventory integrity.
 Authored from the COMPLETE spec (build/simple-flow/requirements.md, 17 stories) plus the design mockups / dev handoffs (design-notes.md) and the live VIU findings (viu-findings.md).
 VIU (Verify-in-UI on QA env sv7301) is PARTIAL because the feature is still under development. Each case carries a VIU Status: VIU-Verified (tested live and passed - screenshot cited in Notes), VIU-Pending (not yet verifiable - either a not-built story or a cookie/role-dependent check), or Open-Question (the expected result depends on an unresolved decision or a VIU deviation - see the Open Questions tab).
 NOT-BUILT stories (all cases VIU-Pending until dev completes): Story 7 (PO multi-select), Story 8 (Bulk Receive page), Story 9 (apply-invoice), Story 14 (Waiting-on-Parts column).
@@ -804,7 +810,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -834,7 +840,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29">
@@ -873,7 +879,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
@@ -903,7 +909,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37">
@@ -942,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41">
@@ -952,7 +958,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -962,7 +968,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" ht="160" customHeight="1">
@@ -971,8 +977,8 @@
           <t>Legend &amp; notes:
 - VIU-Verified = tested live on QA env sv7301 and passed (screenshot cited in the case Notes).
 - VIU-Pending = still needs live verification: either a NOT-BUILT story (7 Bulk multi-select, 8 Bulk Receive page, 9 apply-invoice, 14 Waiting-on-Parts) or a cookie/role-dependent check (non-admin role-gating negatives; full parts-receive + core round-trips; line-approval final block). See the 'VIU pending' tab.
-- Open-Question = the EXPECTED result depends on an unresolved decision or a VIU deviation/bug. See the 'Open Questions' tab (14 items, including the 4 live VIU deviations).
-- No permissions/role matrix exists yet: role-gating cases are authored but their expected results are marked TBD - do not assume role outcomes.</t>
+- Open-Question = the EXPECTED result depends on an unresolved decision or a live build deviation. See the 'Open Questions' tab (14 items: 3 RESOLVED by SV-8183, 11 still open pending Milos).
+- Permissions are now DEFINED by SV-8183: Simple Flow reuses existing Custom Roles atoms (no new atom) plus the NET-NEW reviewer!=completer rule. See requirements §9 for the action-&gt;atom map and per-role matrix; role-gating negatives still need live verification.</t>
         </is>
       </c>
     </row>
@@ -991,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1832,31 +1838,32 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). A non-admin (e.g. Advisor/Tech) credential is required.</t>
+          <t>App Settings permission (system defaults: Admin, Service Manager, Office). A role WITHOUT App Settings (e.g. Service Advisor / Technician) is required for this negative.</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>1. A non-admin user account exists for this org.
-2. You can sign in as that non-admin user.</t>
+          <t>1. A user without the App Settings permission (e.g. Service Advisor or Technician) exists for this org.
+2. You can sign in as that user.</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>1. Sign in as the non-admin user.
+          <t>1. Sign in as the user without App Settings.
 2. Attempt to open /administration/settings → Work Orders tab.
-3. Attempt to change and save a Work Order setting.</t>
+3. Attempt to change and save a Work Order setting, including a direct API save.</t>
         </is>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>1. The non-admin cannot reach the Work Order settings, OR the settings are read-only for them.
-2. The non-admin cannot save changes to Work Order settings.</t>
+          <t>1. A role without the App Settings permission cannot reach the Work Order settings, or sees them read-only.
+2. That role cannot save changes to Work Order settings.
+3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>requirements S1 AC</t>
+          <t>requirements S1 AC / §9 (App Settings gate)</t>
         </is>
       </c>
       <c r="L12" s="24" t="inlineStr">
@@ -1866,7 +1873,7 @@
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>BLOCKED in VIU: quick-login {key:'tech'} returned 403 in this env; only the admin session works. Needs a real non-admin credential. Expected also depends on the (TBD) permissions matrix.</t>
+          <t>Defined by SV-8183: the Work Order settings inherit the settingsApp route guard (no new atom); editable only by roles with App Settings ON (defaults Admin, Service Manager, Office). Role-gating negatives not yet verified live (only the admin session works on sv7301; tech key = 403).</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5137,7 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>Work Order edit access (add parts).</t>
+          <t>WO Lines: Create &amp; Edit + See Financial Data (the sell price is mandatory and has no catalog source).</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
@@ -5151,12 +5158,13 @@
         <is>
           <t>1. The part saves successfully.
 2. The part appears on the line with its description, quantity and sell price.
-3. It is treated as a vendorless part downstream.</t>
+3. It is treated as a vendorless part downstream.
+4. Adding a vendorless / no-part-number part requires WO Lines: Create &amp; Edit and See Financial Data, because the sell price is mandatory and has no catalog source.</t>
         </is>
       </c>
       <c r="K58" s="17" t="inlineStr">
         <is>
-          <t>requirements S5-R1</t>
+          <t>requirements S5-R1 / §9 (See Financial Data gate)</t>
         </is>
       </c>
       <c r="L58" s="24" t="inlineStr">
@@ -5166,7 +5174,7 @@
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU (part-add flow not exercised). Needs live verification.</t>
+          <t>SV-8183 Decision 4 adds a financial gate: vendorless / no-PN add requires See Financial Data (mandatory sell). Not driven live (part-add flow not exercised).</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5211,7 @@
       </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
-          <t>Work Order edit access (add parts).</t>
+          <t>WO Lines: Create &amp; Edit + See Financial Data. A role lacking See Financial Data (e.g. Technician) is used for the permission negative.</t>
         </is>
       </c>
       <c r="H59" s="21" t="inlineStr">
@@ -5216,19 +5224,21 @@
         <is>
           <t>1. Leave the description empty and try to save.
 2. Fill description, leave quantity empty and try to save.
-3. Fill quantity, leave sell price empty and try to save.</t>
+3. Fill quantity, leave sell price empty and try to save.
+4. As a role without See Financial Data (e.g. Technician), attempt to add a vendorless / no-part-number part.</t>
         </is>
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
           <t>1. Saving is blocked when the description is empty.
 2. Saving is blocked when the quantity is empty.
-3. Saving is blocked when the sell price is empty.</t>
+3. Saving is blocked when the sell price is empty.
+4. A user without See Financial Data (for example a Technician) cannot add a vendorless / no-part-number part, because they cannot enter the mandatory sell price.</t>
         </is>
       </c>
       <c r="K59" s="21" t="inlineStr">
         <is>
-          <t>requirements S5 AC</t>
+          <t>requirements S5 AC / §9 (See Financial Data gate)</t>
         </is>
       </c>
       <c r="L59" s="24" t="inlineStr">
@@ -5238,7 +5248,7 @@
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification of the exact rejection UX.</t>
+          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live.</t>
         </is>
       </c>
     </row>
@@ -7974,31 +7984,31 @@
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). Office/readonly credential required.</t>
+          <t>Order Parts permission (absent for Office / read-only roles).</t>
         </is>
       </c>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>1. An office / readonly user credential exists.
+          <t>1. An Office / read-only user credential (no Order Parts) exists.
 2. A fulfilled PO and an unfulfilled PO exist.</t>
         </is>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
-          <t>1. Sign in as an office/readonly user and open the PO list.
+          <t>1. Sign in as an Office / read-only user and open the PO list.
 2. Confirm the Receive action is hidden for them.
 3. As an authorized user, confirm the Receive action is hidden on a fulfilled PO.</t>
         </is>
       </c>
       <c r="J98" s="17" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC: office/readonly users do not see the Receive action (final expected depends on the permissions matrix — TBD).
+          <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or detail.
 2. Fulfilled POs do not show the Receive action.</t>
         </is>
       </c>
       <c r="K98" s="17" t="inlineStr">
         <is>
-          <t>requirements S11-R3</t>
+          <t>requirements S11-R3 / §9 (Order Parts gate)</t>
         </is>
       </c>
       <c r="L98" s="24" t="inlineStr">
@@ -8008,7 +8018,7 @@
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
-          <t>Role-gating negative not verifiable in VIU (no non-admin session; tech key = 403). Expected depends on the (TBD) permissions matrix. Fulfilled-PO hiding needs live verification.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification.</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9599,7 @@
       </c>
       <c r="D121" s="21" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is available only to manager/foreman and disabled for an advisor with 'Awaiting review'</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="E121" s="22" t="inlineStr">
@@ -9604,31 +9614,32 @@
       </c>
       <c r="G121" s="21" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). Reviewer (manager/foreman) and advisor credentials required.</t>
+          <t>Review Work Orders permission + reviewer must not be the completer.</t>
         </is>
       </c>
       <c r="H121" s="21" t="inlineStr">
         <is>
-          <t>1. Manager/foreman and advisor credentials exist.
-2. A work order is in Review state.</t>
+          <t>1. A role with Review Work Orders and a role without it both exist.
+2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
-          <t>1. Sign in as an advisor and open the work order in Review.
+          <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
-3. Sign in as a manager/foreman and confirm Mark Reviewed is available.</t>
+3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
       <c r="J121" s="21" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC: advisors see Mark Reviewed disabled with 'Awaiting review'.
-2. Managers/foremen can Mark Reviewed. (Final expected depends on the permissions matrix — TBD.)</t>
+          <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
+2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
+3. The user who completed / sent the work order to review cannot Mark Reviewed even with the permission; a different qualified reviewer can.</t>
         </is>
       </c>
       <c r="K121" s="21" t="inlineStr">
         <is>
-          <t>requirements R7</t>
+          <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
         </is>
       </c>
       <c r="L121" s="24" t="inlineStr">
@@ -9638,7 +9649,7 @@
       </c>
       <c r="M121" s="21" t="inlineStr">
         <is>
-          <t>Role-gating not testable in VIU (admin-only session; tech key = 403). Expected depends on the (TBD) permissions matrix and the open 'role-gating review: custom roles vs open for v1' question. See Open Questions.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301).</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10055,7 @@
       </c>
       <c r="J127" s="21" t="inlineStr">
         <is>
-          <t>1. PENDING DECISION: the Require Review default follows the agreed cohort rule (e.g. on for bigger/existing shops), with existing orgs preserved via backfill.</t>
+          <t>1. A brand-new org shows the Require Review setting in its default state, and existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
         </is>
       </c>
       <c r="K127" s="21" t="inlineStr">
@@ -10325,7 +10336,7 @@
       </c>
       <c r="J131" s="21" t="inlineStr">
         <is>
-          <t>1. PENDING DESIGN: Close closes the modal only (no discard) and stays on the work order.
+          <t>1. Clicking Close closes the modal only, keeps any entered changes, and stays on the work order.
 2. Cancel closes the modal and returns to the previous screen.</t>
         </is>
       </c>
@@ -10378,29 +10389,32 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). Non-admin credential required.</t>
+          <t>App Settings permission (system defaults: Admin, Service Manager, Office). A role without App Settings is used for the negative.</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
         <is>
-          <t>1. A non-admin user account exists.
-2. You can sign in as that user.</t>
+          <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
+2. You can sign in as each.</t>
         </is>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
-          <t>1. Sign in as the non-admin user.
-2. Attempt to open and modify /administration/settings → Work Orders.</t>
+          <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
+2. Sign in as a role without App Settings and attempt to open and modify the same page.
+3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
       <c r="J132" s="17" t="inlineStr">
         <is>
-          <t>1. The non-admin cannot view or modify Work Order settings (final expected depends on the permissions matrix — TBD).</t>
+          <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
+2. A role without App Settings cannot open or change the Work Order settings.
+3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
-          <t>requirements S1 AC</t>
+          <t>requirements S1 AC / §9 (App Settings gate)</t>
         </is>
       </c>
       <c r="L132" s="24" t="inlineStr">
@@ -10410,7 +10424,7 @@
       </c>
       <c r="M132" s="17" t="inlineStr">
         <is>
-          <t>BLOCKED in VIU (quick-login tech = 403; no non-admin session). Needs a real non-admin credential. Hypothesis to verify: backend may only enforce resource-level View/Edit while these are FE display gates (Custom Roles finding). See Open Questions.</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301).</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10461,7 @@
       </c>
       <c r="G133" s="21" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). Multiple role credentials required.</t>
+          <t>Work Orders: Create &amp; Edit + WO Lines: Create &amp; Edit + Full View (to approve lines).</t>
         </is>
       </c>
       <c r="H133" s="21" t="inlineStr">
@@ -10464,22 +10478,24 @@
       </c>
       <c r="J133" s="21" t="inlineStr">
         <is>
-          <t>1. PENDING MATRIX: expected depends on the permissions matrix (TBD). Do not assume specific role outcomes.</t>
+          <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
+2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
+3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
       <c r="K133" s="21" t="inlineStr">
         <is>
-          <t>requirements §8 open questions</t>
-        </is>
-      </c>
-      <c r="L133" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+          <t>requirements §9 (Complete WO gate + per-role matrix)</t>
+        </is>
+      </c>
+      <c r="L133" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M133" s="21" t="inlineStr">
         <is>
-          <t>No permissions/role matrix supplied. Author only; expected depends on the matrix (TBD). See Open Questions.</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301).</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10532,7 @@
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD).</t>
+          <t>Vendor &amp; Order Mgmt: Create &amp; Edit + See Financial Data.</t>
         </is>
       </c>
       <c r="H134" s="17" t="inlineStr">
@@ -10533,22 +10549,24 @@
       </c>
       <c r="J134" s="17" t="inlineStr">
         <is>
-          <t>1. PENDING MATRIX: expected depends on the permissions matrix (TBD).</t>
+          <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
+2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
+3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
-          <t>requirements §8 open questions</t>
-        </is>
-      </c>
-      <c r="L134" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+          <t>requirements §9 (Bulk Receive gate + per-role matrix)</t>
+        </is>
+      </c>
+      <c r="L134" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M134" s="17" t="inlineStr">
         <is>
-          <t>No matrix supplied; also Bulk Receive is not yet built. See Open Questions.</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live.</t>
         </is>
       </c>
     </row>
@@ -10585,13 +10603,13 @@
       </c>
       <c r="G135" s="21" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). Manager/foreman + other role credentials required.</t>
+          <t>Review Work Orders permission + reviewer must not be the completer.</t>
         </is>
       </c>
       <c r="H135" s="21" t="inlineStr">
         <is>
-          <t>1. Credentials for manager/foreman and other roles exist.
-2. A work order in Review state exists.</t>
+          <t>1. Credentials for roles with and without Review Work Orders exist.
+2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
       <c r="I135" s="21" t="inlineStr">
@@ -10602,22 +10620,24 @@
       </c>
       <c r="J135" s="21" t="inlineStr">
         <is>
-          <t>1. PENDING MATRIX: spec says manager/foreman only, but role-gating (custom roles vs open for v1) is UNRESOLVED. Expected depends on the matrix (TBD).</t>
+          <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
+2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
+3. The user who completed / sent the work order to review cannot Mark Reviewed it; a different user who holds Review Work Orders can sign off.</t>
         </is>
       </c>
       <c r="K135" s="21" t="inlineStr">
         <is>
-          <t>requirements R7 / §8</t>
-        </is>
-      </c>
-      <c r="L135" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+          <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
+        </is>
+      </c>
+      <c r="L135" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M135" s="21" t="inlineStr">
         <is>
-          <t>Role-gating for review is an explicit open question. See Open Questions.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live.</t>
         </is>
       </c>
     </row>
@@ -10654,30 +10674,31 @@
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD). Office/readonly credential required.</t>
+          <t>Order Parts permission (absent for Office / read-only roles).</t>
         </is>
       </c>
       <c r="H136" s="17" t="inlineStr">
         <is>
-          <t>1. An office/readonly credential exists.
-2. A WO-originated PO exists.</t>
+          <t>1. An Office / read-only credential (no Order Parts) exists.
+2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
-          <t>1. Sign in as an office/readonly user.
+          <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
-3. Confirm the Receive action is not shown.</t>
+3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
       <c r="J136" s="17" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC: office/readonly users do not see the Receive action (final expected depends on the permissions matrix — TBD).</t>
+          <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
+2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
-          <t>requirements S11-R3</t>
+          <t>requirements S11-R3 / §9 (Order Parts gate)</t>
         </is>
       </c>
       <c r="L136" s="24" t="inlineStr">
@@ -10687,7 +10708,7 @@
       </c>
       <c r="M136" s="17" t="inlineStr">
         <is>
-          <t>Not verifiable in VIU (no non-admin session). Needs an office/readonly credential. See Open Questions.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live.</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10730,7 @@
       </c>
       <c r="D137" s="21" t="inlineStr">
         <is>
-          <t>Verify whether the backend enforces the Simple-Flow settings or they are front-end display gates only</t>
+          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
@@ -10735,28 +10756,31 @@
       </c>
       <c r="I137" s="21" t="inlineStr">
         <is>
-          <t>1. Attempt the gated action directly via the API (bypassing the UI), e.g. completing without the required invoice.
-2. Observe whether the backend rejects (403/422) or allows it (200/201).</t>
+          <t>1. Attempt a setting-violating action directly via the API (bypassing the UI), e.g. completing without the required invoice, and note the response.
+2. As a role that lacks the mapped atom, attempt the gated action via the API and note the response.
+3. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
         </is>
       </c>
       <c r="J137" s="21" t="inlineStr">
         <is>
-          <t>1. PENDING DECISION: determine whether the backend enforces the setting (rejects) or the gate is front-end only (allows).</t>
+          <t>1. The backend enforces the Simple-Flow settings and the permission atoms (it is not front-end only): a setting-violating or unauthorized request is rejected.
+2. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto a work order.
+3. The receive endpoint accepts the documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT.</t>
         </is>
       </c>
       <c r="K137" s="21" t="inlineStr">
         <is>
-          <t>requirements §8 open questions</t>
-        </is>
-      </c>
-      <c r="L137" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+          <t>requirements §9.4 (BE enforcement + atom collapse)</t>
+        </is>
+      </c>
+      <c r="L137" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M137" s="21" t="inlineStr">
         <is>
-          <t>§8 asks whether BE should enforce Simple-Flow settings. Hypothesis from Custom Roles: BE often enforces only resource-level View/Edit while granular gates are FE-only. Verify; do not assume. See Open Questions.</t>
+          <t>Answered by SV-8183: BE DOES enforce the Simple-Flow settings and atoms (change from the Custom Roles FE-only finding), subject to the WO-atom collapse caveat (SV-7864). Not yet driven live.</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10802,7 @@
       </c>
       <c r="D138" s="17" t="inlineStr">
         <is>
-          <t>Verify whether review role-gating uses custom roles or is open for v1</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
@@ -10793,1373 +10817,1590 @@
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>Depends on permissions matrix (TBD).</t>
+          <t>Review Work Orders permission + reviewer must not be the completer.</t>
         </is>
       </c>
       <c r="H138" s="17" t="inlineStr">
         <is>
-          <t>1. Credentials for several roles exist.
-2. A work order in Review state exists.</t>
+          <t>1. Credentials for roles with and without Review Work Orders exist.
+2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
-          <t>1. Determine which roles can sign off review.
-2. Determine whether this is governed by a custom-role permission or open to all.</t>
+          <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.
+2. Confirm the user who completed / sent the work order to review cannot sign it off.</t>
         </is>
       </c>
       <c r="J138" s="17" t="inlineStr">
         <is>
-          <t>1. PENDING DECISION: whether review sign-off is gated by custom roles or open for v1 is unresolved.</t>
+          <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
+2. The permission gates the Mark Reviewed action, and the reviewer-not-completer rule is enforced (the completer cannot sign off).</t>
         </is>
       </c>
       <c r="K138" s="17" t="inlineStr">
         <is>
-          <t>requirements §8 open questions</t>
-        </is>
-      </c>
-      <c r="L138" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+          <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
+        </is>
+      </c>
+      <c r="L138" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="M138" s="17" t="inlineStr">
         <is>
-          <t>Explicit open question. See Open Questions.</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
+          <t>SF-PERM-08</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>R7 (reviewer != completer)</t>
+        </is>
+      </c>
+      <c r="D139" s="21" t="inlineStr">
+        <is>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+        </is>
+      </c>
+      <c r="E139" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="G139" s="21" t="inlineStr">
+        <is>
+          <t>Review Work Orders permission + reviewer must not be the completer.</t>
+        </is>
+      </c>
+      <c r="H139" s="21" t="inlineStr">
+        <is>
+          <t>1. Two different users who both hold the Review Work Orders permission exist.
+2. User A has completed / sent a work order to review; it is in Review state.</t>
+        </is>
+      </c>
+      <c r="I139" s="21" t="inlineStr">
+        <is>
+          <t>1. Sign in as User A (who sent the work order to review) and open the work order in Review.
+2. Attempt to Mark Reviewed.
+3. Sign in as User B (a different user who holds Review Work Orders) and Mark Reviewed.</t>
+        </is>
+      </c>
+      <c r="J139" s="21" t="inlineStr">
+        <is>
+          <t>1. User A cannot Mark Reviewed the work order they completed / sent to review; the action is blocked or disabled.
+2. User B, a different user who holds the Review Work Orders permission, can Mark Reviewed and sign off.
+3. The reviewer must be a different person from the completer.</t>
+        </is>
+      </c>
+      <c r="K139" s="21" t="inlineStr">
+        <is>
+          <t>requirements R7 / §9 (reviewer != completer NET-NEW rule)</t>
+        </is>
+      </c>
+      <c r="L139" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M139" s="21" t="inlineStr">
+        <is>
+          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="16" t="inlineStr">
+        <is>
+          <t>SF-PERM-09</t>
+        </is>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t>S5 / §9 (See Financial Data gate)</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+        </is>
+      </c>
+      <c r="E140" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>WO Lines: Create &amp; Edit + See Financial Data. Technician has WO Lines: Create &amp; Edit but no See Financial Data.</t>
+        </is>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
+2. An open work order with a line is available.</t>
+        </is>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>1. Sign in as the Technician and open the work order line.
+2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t>1. The Technician cannot add a vendorless / no-part-number part.
+2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
+        </is>
+      </c>
+      <c r="K140" s="17" t="inlineStr">
+        <is>
+          <t>requirements S5 / §9 (Decision 4)</t>
+        </is>
+      </c>
+      <c r="L140" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M140" s="17" t="inlineStr">
+        <is>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>SF-PERM-10</t>
+        </is>
+      </c>
+      <c r="B141" s="21" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>§9 per-role completion matrix</t>
+        </is>
+      </c>
+      <c r="D141" s="21" t="inlineStr">
+        <is>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="G141" s="21" t="inlineStr">
+        <is>
+          <t>Work Orders: Create &amp; Edit + WO Lines: Create &amp; Edit + Full View.</t>
+        </is>
+      </c>
+      <c r="H141" s="21" t="inlineStr">
+        <is>
+          <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
+2. A work order ready to complete is available.</t>
+        </is>
+      </c>
+      <c r="I141" s="21" t="inlineStr">
+        <is>
+          <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
+2. Record the result per role against the checklist below.
+3. Roles expected to be able to complete: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager.
+4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
+        </is>
+      </c>
+      <c r="J141" s="21" t="inlineStr">
+        <is>
+          <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
+2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
+3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
+        </is>
+      </c>
+      <c r="K141" s="21" t="inlineStr">
+        <is>
+          <t>requirements §9 (per-role matrix)</t>
+        </is>
+      </c>
+      <c r="L141" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M141" s="21" t="inlineStr">
+        <is>
+          <t>Per-role completion checklist derived from the SV-8183 role matrix. Role-gating negatives not yet verified live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="16" t="inlineStr">
+        <is>
           <t>SF-VAL-01</t>
         </is>
       </c>
-      <c r="B139" s="21" t="inlineStr">
+      <c r="B142" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C139" s="21" t="inlineStr">
+      <c r="C142" s="17" t="inlineStr">
         <is>
           <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D139" s="21" t="inlineStr">
+      <c r="D142" s="17" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="E139" s="22" t="inlineStr">
+      <c r="E142" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F139" s="21" t="inlineStr">
+      <c r="F142" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G139" s="21" t="inlineStr">
+      <c r="G142" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H139" s="21" t="inlineStr">
+      <c r="H142" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="I139" s="21" t="inlineStr">
+      <c r="I142" s="17" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J139" s="21" t="inlineStr">
+      <c r="J142" s="17" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="K139" s="21" t="inlineStr">
+      <c r="K142" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html (Details step)</t>
         </is>
       </c>
-      <c r="L139" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M139" s="21" t="inlineStr">
+      <c r="L142" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M142" s="17" t="inlineStr">
         <is>
           <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="16" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-02</t>
         </is>
       </c>
-      <c r="B140" s="17" t="inlineStr">
+      <c r="B143" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C140" s="17" t="inlineStr">
+      <c r="C143" s="21" t="inlineStr">
         <is>
           <t>S15-R2 / S3-R3</t>
         </is>
       </c>
-      <c r="D140" s="17" t="inlineStr">
+      <c r="D143" s="21" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
-      <c r="E140" s="23" t="inlineStr">
+      <c r="E143" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F140" s="17" t="inlineStr">
+      <c r="F143" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G140" s="17" t="inlineStr">
+      <c r="G143" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H140" s="17" t="inlineStr">
+      <c r="H143" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
 3. Require Review is OFF (VIN is collected at completion in the non-review flow).</t>
         </is>
       </c>
-      <c r="I140" s="17" t="inlineStr">
+      <c r="I143" s="21" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave VIN empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J140" s="17" t="inlineStr">
+      <c r="J143" s="21" t="inlineStr">
         <is>
           <t>1. Completion is blocked until the VIN is entered.</t>
         </is>
       </c>
-      <c r="K140" s="17" t="inlineStr">
+      <c r="K143" s="21" t="inlineStr">
         <is>
           <t>requirements S15-R2</t>
         </is>
       </c>
-      <c r="L140" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M140" s="17" t="inlineStr">
+      <c r="L143" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M143" s="21" t="inlineStr">
         <is>
           <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="20" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-03</t>
         </is>
       </c>
-      <c r="B141" s="21" t="inlineStr">
+      <c r="B144" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C141" s="21" t="inlineStr">
+      <c r="C144" s="17" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D141" s="21" t="inlineStr">
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="E141" s="23" t="inlineStr">
+      <c r="E144" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F141" s="21" t="inlineStr">
+      <c r="F144" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G141" s="21" t="inlineStr">
+      <c r="G144" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H141" s="21" t="inlineStr">
+      <c r="H144" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="I141" s="21" t="inlineStr">
+      <c r="I144" s="17" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J141" s="21" t="inlineStr">
+      <c r="J144" s="17" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="K141" s="21" t="inlineStr">
+      <c r="K144" s="17" t="inlineStr">
         <is>
           <t>requirements S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="L141" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M141" s="21" t="inlineStr">
+      <c r="L144" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M144" s="17" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="16" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-04</t>
         </is>
       </c>
-      <c r="B142" s="17" t="inlineStr">
+      <c r="B145" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C142" s="17" t="inlineStr">
+      <c r="C145" s="21" t="inlineStr">
         <is>
           <t>TS-R4</t>
         </is>
       </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="D145" s="21" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="E142" s="23" t="inlineStr">
+      <c r="E145" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F142" s="17" t="inlineStr">
+      <c r="F145" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G142" s="17" t="inlineStr">
+      <c r="G145" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H142" s="17" t="inlineStr">
+      <c r="H145" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="I142" s="17" t="inlineStr">
+      <c r="I145" s="21" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="J142" s="17" t="inlineStr">
+      <c r="J145" s="21" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="K142" s="17" t="inlineStr">
+      <c r="K145" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L142" s="19" t="inlineStr">
+      <c r="L145" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M142" s="17" t="inlineStr">
+      <c r="M145" s="21" t="inlineStr">
         <is>
           <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="20" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-05</t>
         </is>
       </c>
-      <c r="B143" s="21" t="inlineStr">
+      <c r="B146" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C143" s="21" t="inlineStr">
+      <c r="C146" s="17" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
-      <c r="D143" s="21" t="inlineStr">
+      <c r="D146" s="17" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="E143" s="22" t="inlineStr">
+      <c r="E146" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F143" s="21" t="inlineStr">
+      <c r="F146" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G143" s="21" t="inlineStr">
+      <c r="G146" s="17" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H143" s="21" t="inlineStr">
+      <c r="H146" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="I143" s="21" t="inlineStr">
+      <c r="I146" s="17" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="J143" s="21" t="inlineStr">
+      <c r="J146" s="17" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="K143" s="21" t="inlineStr">
+      <c r="K146" s="17" t="inlineStr">
         <is>
           <t>requirements §4 / S4-R5</t>
         </is>
       </c>
-      <c r="L143" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M143" s="21" t="inlineStr">
+      <c r="L146" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M146" s="17" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="16" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-06</t>
         </is>
       </c>
-      <c r="B144" s="17" t="inlineStr">
+      <c r="B147" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="17" t="inlineStr">
+      <c r="C147" s="21" t="inlineStr">
         <is>
           <t>S10 / S12-R2 / S13</t>
         </is>
       </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="D147" s="21" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
-      <c r="E144" s="22" t="inlineStr">
+      <c r="E147" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F144" s="17" t="inlineStr">
+      <c r="F147" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G144" s="17" t="inlineStr">
+      <c r="G147" s="21" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H144" s="17" t="inlineStr">
+      <c r="H147" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="I144" s="17" t="inlineStr">
+      <c r="I147" s="21" t="inlineStr">
         <is>
           <t>1. Attempt to receive with no vendor.
 2. Attempt to receive with a vendor but no part number.
 3. Provide both and receive.</t>
         </is>
       </c>
-      <c r="J144" s="17" t="inlineStr">
+      <c r="J147" s="21" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor.
 2. Receiving is blocked without a part number.
 3. Receiving succeeds only with both.</t>
         </is>
       </c>
-      <c r="K144" s="17" t="inlineStr">
+      <c r="K147" s="21" t="inlineStr">
         <is>
           <t>requirements S12-R2 / S10</t>
         </is>
       </c>
-      <c r="L144" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M144" s="17" t="inlineStr">
+      <c r="L147" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M147" s="21" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="20" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-07</t>
         </is>
       </c>
-      <c r="B145" s="21" t="inlineStr">
+      <c r="B148" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="21" t="inlineStr">
+      <c r="C148" s="17" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="D145" s="21" t="inlineStr">
+      <c r="D148" s="17" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="E145" s="23" t="inlineStr">
+      <c r="E148" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F145" s="21" t="inlineStr">
+      <c r="F148" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G145" s="21" t="inlineStr">
+      <c r="G148" s="17" t="inlineStr">
         <is>
           <t>Reviewer role (matrix TBD).</t>
         </is>
       </c>
-      <c r="H145" s="21" t="inlineStr">
+      <c r="H148" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="I145" s="21" t="inlineStr">
+      <c r="I148" s="17" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="J145" s="21" t="inlineStr">
+      <c r="J148" s="17" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="K145" s="21" t="inlineStr">
+      <c r="K148" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements R7</t>
         </is>
       </c>
-      <c r="L145" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M145" s="21" t="inlineStr">
+      <c r="L148" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M148" s="17" t="inlineStr">
         <is>
           <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="16" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-08</t>
         </is>
       </c>
-      <c r="B146" s="17" t="inlineStr">
+      <c r="B149" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="17" t="inlineStr">
+      <c r="C149" s="21" t="inlineStr">
         <is>
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
-      <c r="D146" s="17" t="inlineStr">
+      <c r="D149" s="21" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="E146" s="23" t="inlineStr">
+      <c r="E149" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F146" s="17" t="inlineStr">
+      <c r="F149" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G146" s="17" t="inlineStr">
+      <c r="G149" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H146" s="17" t="inlineStr">
+      <c r="H149" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="I146" s="17" t="inlineStr">
+      <c r="I149" s="21" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="J146" s="17" t="inlineStr">
+      <c r="J149" s="21" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="K146" s="17" t="inlineStr">
+      <c r="K149" s="21" t="inlineStr">
         <is>
           <t>requirements S3-R9</t>
         </is>
       </c>
-      <c r="L146" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M146" s="17" t="inlineStr">
+      <c r="L149" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M149" s="21" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="20" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-09</t>
         </is>
       </c>
-      <c r="B147" s="21" t="inlineStr">
+      <c r="B150" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="21" t="inlineStr">
+      <c r="C150" s="17" t="inlineStr">
         <is>
           <t>S8-R7 / §4 field locking</t>
         </is>
       </c>
-      <c r="D147" s="21" t="inlineStr">
+      <c r="D150" s="17" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="E147" s="23" t="inlineStr">
+      <c r="E150" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F147" s="21" t="inlineStr">
+      <c r="F150" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G147" s="21" t="inlineStr">
+      <c r="G150" s="17" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H147" s="21" t="inlineStr">
+      <c r="H150" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="I147" s="21" t="inlineStr">
+      <c r="I150" s="17" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="J147" s="21" t="inlineStr">
+      <c r="J150" s="17" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="K147" s="21" t="inlineStr">
+      <c r="K150" s="17" t="inlineStr">
         <is>
           <t>requirements S8-R7 / §4</t>
         </is>
       </c>
-      <c r="L147" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M147" s="21" t="inlineStr">
+      <c r="L150" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M150" s="17" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="16" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="B148" s="17" t="inlineStr">
+      <c r="B151" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="17" t="inlineStr">
+      <c r="C151" s="21" t="inlineStr">
         <is>
           <t>S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="D148" s="17" t="inlineStr">
+      <c r="D151" s="21" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="E148" s="25" t="inlineStr">
+      <c r="E151" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F148" s="17" t="inlineStr">
+      <c r="F151" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G148" s="17" t="inlineStr">
+      <c r="G151" s="21" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H148" s="17" t="inlineStr">
+      <c r="H151" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="I148" s="17" t="inlineStr">
+      <c r="I151" s="21" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="J148" s="17" t="inlineStr">
+      <c r="J151" s="21" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="K148" s="17" t="inlineStr">
+      <c r="K151" s="21" t="inlineStr">
         <is>
           <t>requirements S9-R3 / §4</t>
         </is>
       </c>
-      <c r="L148" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M148" s="17" t="inlineStr">
+      <c r="L151" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M151" s="21" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="20" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="B149" s="21" t="inlineStr">
+      <c r="B152" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="21" t="inlineStr">
+      <c r="C152" s="17" t="inlineStr">
         <is>
           <t>Key Decision (line approval)</t>
         </is>
       </c>
-      <c r="D149" s="21" t="inlineStr">
+      <c r="D152" s="17" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="E149" s="23" t="inlineStr">
+      <c r="E152" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F149" s="21" t="inlineStr">
+      <c r="F152" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G149" s="21" t="inlineStr">
+      <c r="G152" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H149" s="21" t="inlineStr">
+      <c r="H152" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has one unapproved line and all other gates satisfied.</t>
         </is>
       </c>
-      <c r="I149" s="21" t="inlineStr">
+      <c r="I152" s="17" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Read the error shown at the final confirm.</t>
         </is>
       </c>
-      <c r="J149" s="21" t="inlineStr">
+      <c r="J152" s="17" t="inlineStr">
         <is>
           <t>1. The existing 'you need to approve the line to complete the work order' error is shown.
 2. Completion does not proceed until the line is approved.</t>
         </is>
       </c>
-      <c r="K149" s="21" t="inlineStr">
+      <c r="K152" s="17" t="inlineStr">
         <is>
           <t>requirements §4 Key Decision</t>
         </is>
       </c>
-      <c r="L149" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M149" s="21" t="inlineStr">
+      <c r="L152" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M152" s="17" t="inlineStr">
         <is>
           <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line.</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="16" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>SF-QB-01</t>
         </is>
       </c>
-      <c r="B150" s="17" t="inlineStr">
+      <c r="B153" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C150" s="17" t="inlineStr">
+      <c r="C153" s="21" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="D150" s="17" t="inlineStr">
+      <c r="D153" s="21" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="E150" s="22" t="inlineStr">
+      <c r="E153" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F150" s="17" t="inlineStr">
+      <c r="F153" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G150" s="17" t="inlineStr">
+      <c r="G153" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access + Inventory visibility.</t>
         </is>
       </c>
-      <c r="H150" s="17" t="inlineStr">
+      <c r="H153" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="I150" s="17" t="inlineStr">
+      <c r="I153" s="21" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="J150" s="17" t="inlineStr">
+      <c r="J153" s="21" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="K150" s="17" t="inlineStr">
+      <c r="K153" s="21" t="inlineStr">
         <is>
           <t>requirements §5 invariant 1</t>
         </is>
       </c>
-      <c r="L150" s="18" t="inlineStr">
+      <c r="L153" s="18" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="M150" s="17" t="inlineStr">
+      <c r="M153" s="21" t="inlineStr">
         <is>
           <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions.</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="20" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
         <is>
           <t>SF-QB-02</t>
         </is>
       </c>
-      <c r="B151" s="21" t="inlineStr">
+      <c r="B154" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C151" s="21" t="inlineStr">
+      <c r="C154" s="17" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="D151" s="21" t="inlineStr">
+      <c r="D154" s="17" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="E151" s="22" t="inlineStr">
+      <c r="E154" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F151" s="21" t="inlineStr">
+      <c r="F154" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G151" s="21" t="inlineStr">
+      <c r="G154" s="17" t="inlineStr">
         <is>
           <t>Admin / owner (settings) + Work Order edit access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H151" s="21" t="inlineStr">
+      <c r="H154" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF (see SF-SET-03).
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="I151" s="21" t="inlineStr">
+      <c r="I154" s="17" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="J151" s="21" t="inlineStr">
+      <c r="J154" s="17" t="inlineStr">
         <is>
           <t>1. EXPECTED PER SPEC: no PO, no vendor bill, no AP sync.
 2. No catalog/inventory sync (part is received at request time only).</t>
         </is>
       </c>
-      <c r="K151" s="21" t="inlineStr">
+      <c r="K154" s="17" t="inlineStr">
         <is>
           <t>requirements §4 / §5</t>
         </is>
       </c>
-      <c r="L151" s="18" t="inlineStr">
+      <c r="L154" s="18" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="M151" s="21" t="inlineStr">
+      <c r="M154" s="17" t="inlineStr">
         <is>
           <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. See Open Questions.</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="16" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="20" t="inlineStr">
         <is>
           <t>SF-QB-03</t>
         </is>
       </c>
-      <c r="B152" s="17" t="inlineStr">
+      <c r="B155" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C152" s="17" t="inlineStr">
+      <c r="C155" s="21" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="D152" s="17" t="inlineStr">
+      <c r="D155" s="21" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="E152" s="22" t="inlineStr">
+      <c r="E155" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F152" s="17" t="inlineStr">
+      <c r="F155" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G152" s="17" t="inlineStr">
+      <c r="G155" s="21" t="inlineStr">
         <is>
           <t>receive access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H152" s="17" t="inlineStr">
+      <c r="H155" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="I152" s="17" t="inlineStr">
+      <c r="I155" s="21" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="J152" s="17" t="inlineStr">
+      <c r="J155" s="21" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="K152" s="17" t="inlineStr">
+      <c r="K155" s="21" t="inlineStr">
         <is>
           <t>requirements §5 invariant 2</t>
         </is>
       </c>
-      <c r="L152" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M152" s="17" t="inlineStr">
+      <c r="L155" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M155" s="21" t="inlineStr">
         <is>
           <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="20" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
         <is>
           <t>SF-QB-04</t>
         </is>
       </c>
-      <c r="B153" s="21" t="inlineStr">
+      <c r="B156" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C153" s="21" t="inlineStr">
+      <c r="C156" s="17" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="D153" s="21" t="inlineStr">
+      <c r="D156" s="17" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="E153" s="23" t="inlineStr">
+      <c r="E156" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F153" s="21" t="inlineStr">
+      <c r="F156" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G153" s="21" t="inlineStr">
+      <c r="G156" s="17" t="inlineStr">
         <is>
           <t>Inventory visibility.</t>
         </is>
       </c>
-      <c r="H153" s="21" t="inlineStr">
+      <c r="H156" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="I153" s="21" t="inlineStr">
+      <c r="I156" s="17" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="J153" s="21" t="inlineStr">
+      <c r="J156" s="17" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="K153" s="21" t="inlineStr">
+      <c r="K156" s="17" t="inlineStr">
         <is>
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L153" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M153" s="21" t="inlineStr">
+      <c r="L156" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M156" s="17" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="16" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>SF-QB-05</t>
         </is>
       </c>
-      <c r="B154" s="17" t="inlineStr">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C154" s="17" t="inlineStr">
+      <c r="C157" s="21" t="inlineStr">
         <is>
           <t>§5 / S6-R3</t>
         </is>
       </c>
-      <c r="D154" s="17" t="inlineStr">
+      <c r="D157" s="21" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="E154" s="23" t="inlineStr">
+      <c r="E157" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F154" s="17" t="inlineStr">
+      <c r="F157" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G154" s="17" t="inlineStr">
+      <c r="G157" s="21" t="inlineStr">
         <is>
           <t>QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H154" s="17" t="inlineStr">
+      <c r="H157" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="I154" s="17" t="inlineStr">
+      <c r="I157" s="21" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="J154" s="17" t="inlineStr">
+      <c r="J157" s="21" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="K154" s="17" t="inlineStr">
+      <c r="K157" s="21" t="inlineStr">
         <is>
           <t>requirements §5 / S6-R3</t>
         </is>
       </c>
-      <c r="L154" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M154" s="17" t="inlineStr">
+      <c r="L157" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M157" s="21" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="20" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
         <is>
           <t>SF-QB-06</t>
         </is>
       </c>
-      <c r="B155" s="21" t="inlineStr">
+      <c r="B158" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="21" t="inlineStr">
+      <c r="C158" s="17" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="D155" s="21" t="inlineStr">
+      <c r="D158" s="17" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="E155" s="23" t="inlineStr">
+      <c r="E158" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F155" s="21" t="inlineStr">
+      <c r="F158" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G155" s="21" t="inlineStr">
-        <is>
-          <t>Work Order edit access + QuickBooks visibility.</t>
-        </is>
-      </c>
-      <c r="H155" s="21" t="inlineStr">
+      <c r="G158" s="17" t="inlineStr">
+        <is>
+          <t>Work Order edit access + See Financial Data + QuickBooks visibility.</t>
+        </is>
+      </c>
+      <c r="H158" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="I155" s="21" t="inlineStr">
+      <c r="I158" s="17" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="J155" s="21" t="inlineStr">
-        <is>
-          <t>1. PENDING DECISION: whether cost can be entered at completion to avoid $0-cost margins is unresolved. Confirm the intended behavior.</t>
-        </is>
-      </c>
-      <c r="K155" s="21" t="inlineStr">
-        <is>
-          <t>requirements §8 open questions</t>
-        </is>
-      </c>
-      <c r="L155" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="M155" s="21" t="inlineStr">
-        <is>
-          <t>§8 open question. Not driven in VIU. See Open Questions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="inlineStr">
+      <c r="J158" s="17" t="inlineStr">
+        <is>
+          <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
+2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
+        </is>
+      </c>
+      <c r="K158" s="17" t="inlineStr">
+        <is>
+          <t>requirements §9 (See Financial Data gate on vendorless sell)</t>
+        </is>
+      </c>
+      <c r="L158" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M158" s="17" t="inlineStr">
+        <is>
+          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20" t="inlineStr">
         <is>
           <t>SF-QB-07</t>
         </is>
       </c>
-      <c r="B156" s="17" t="inlineStr">
+      <c r="B159" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="17" t="inlineStr">
+      <c r="C159" s="21" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="D156" s="17" t="inlineStr">
+      <c r="D159" s="21" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="E156" s="23" t="inlineStr">
+      <c r="E159" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F156" s="17" t="inlineStr">
+      <c r="F159" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G156" s="17" t="inlineStr">
+      <c r="G159" s="21" t="inlineStr">
         <is>
           <t>Finance access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H156" s="17" t="inlineStr">
+      <c r="H159" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="I156" s="17" t="inlineStr">
+      <c r="I159" s="21" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="J156" s="17" t="inlineStr">
+      <c r="J159" s="21" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="K156" s="17" t="inlineStr">
+      <c r="K159" s="21" t="inlineStr">
         <is>
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L156" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M156" s="17" t="inlineStr">
+      <c r="L159" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M159" s="21" t="inlineStr">
         <is>
           <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="20" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="16" t="inlineStr">
         <is>
           <t>SF-QB-08</t>
         </is>
       </c>
-      <c r="B157" s="21" t="inlineStr">
+      <c r="B160" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C157" s="21" t="inlineStr">
+      <c r="C160" s="17" t="inlineStr">
         <is>
           <t>§5 invariant 3</t>
         </is>
       </c>
-      <c r="D157" s="21" t="inlineStr">
+      <c r="D160" s="17" t="inlineStr">
         <is>
           <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
-      <c r="E157" s="23" t="inlineStr">
+      <c r="E160" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F157" s="21" t="inlineStr">
+      <c r="F160" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G157" s="21" t="inlineStr">
+      <c r="G160" s="17" t="inlineStr">
         <is>
           <t>Inventory visibility.</t>
         </is>
       </c>
-      <c r="H157" s="21" t="inlineStr">
+      <c r="H160" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part transitions to inventory-tracked (e.g. a part number is added and it is received).</t>
         </is>
       </c>
-      <c r="I157" s="21" t="inlineStr">
+      <c r="I160" s="17" t="inlineStr">
         <is>
           <t>1. Add a part number to a previously untracked part and receive it.
 2. Open the item's Part History.</t>
         </is>
       </c>
-      <c r="J157" s="21" t="inlineStr">
+      <c r="J160" s="17" t="inlineStr">
         <is>
           <t>1. Part History is preserved / created for the now inventory-tracked part.</t>
         </is>
       </c>
-      <c r="K157" s="21" t="inlineStr">
+      <c r="K160" s="17" t="inlineStr">
         <is>
           <t>requirements §5 invariant 3</t>
         </is>
       </c>
-      <c r="L157" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M157" s="21" t="inlineStr">
+      <c r="L160" s="24" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="M160" s="17" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
@@ -12176,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14710,7 +14951,7 @@
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is available only to manager/foreman and disabled for an advisor with 'Awaiting review'</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
@@ -14874,7 +15115,7 @@
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
@@ -14884,7 +15125,7 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
@@ -14903,17 +15144,17 @@
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D95" s="17" t="inlineStr">
@@ -14923,7 +15164,7 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr"/>
@@ -14932,17 +15173,17 @@
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
@@ -14952,7 +15193,7 @@
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr"/>
@@ -14961,17 +15202,17 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="D97" s="17" t="inlineStr">
@@ -14981,7 +15222,7 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr"/>
@@ -14990,17 +15231,17 @@
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
@@ -15010,7 +15251,7 @@
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr"/>
@@ -15019,17 +15260,17 @@
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="D99" s="17" t="inlineStr">
@@ -15039,7 +15280,7 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr"/>
@@ -15048,17 +15289,17 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -15068,7 +15309,7 @@
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr"/>
@@ -15077,17 +15318,17 @@
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="D101" s="17" t="inlineStr">
@@ -15097,7 +15338,7 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr"/>
@@ -15106,17 +15347,17 @@
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -15126,7 +15367,7 @@
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr"/>
@@ -15135,7 +15376,7 @@
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
@@ -15145,7 +15386,7 @@
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="D103" s="17" t="inlineStr">
@@ -15164,7 +15405,7 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-11</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B104" s="21" t="inlineStr">
@@ -15174,7 +15415,7 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
@@ -15193,17 +15434,17 @@
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="D105" s="17" t="inlineStr">
@@ -15213,7 +15454,7 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F105" s="17" t="inlineStr"/>
@@ -15222,17 +15463,17 @@
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
@@ -15242,7 +15483,7 @@
       </c>
       <c r="E106" s="21" t="inlineStr">
         <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr"/>
@@ -15251,17 +15492,17 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D107" s="17" t="inlineStr">
@@ -15271,7 +15512,7 @@
       </c>
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F107" s="17" t="inlineStr"/>
@@ -15280,17 +15521,17 @@
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="D108" s="21" t="inlineStr">
@@ -15300,7 +15541,7 @@
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr"/>
@@ -15309,17 +15550,17 @@
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-08</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="D109" s="17" t="inlineStr">
@@ -15329,11 +15570,272 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F109" s="17" t="inlineStr"/>
       <c r="G109" s="17" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>SF-VAL-09</t>
+        </is>
+      </c>
+      <c r="B110" s="21" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C110" s="21" t="inlineStr">
+        <is>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+        </is>
+      </c>
+      <c r="D110" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E110" s="21" t="inlineStr">
+        <is>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="inlineStr"/>
+      <c r="G110" s="21" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>SF-VAL-10</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="inlineStr"/>
+      <c r="G111" s="17" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>SF-VAL-11</t>
+        </is>
+      </c>
+      <c r="B112" s="21" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C112" s="21" t="inlineStr">
+        <is>
+          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
+        </is>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E112" s="21" t="inlineStr">
+        <is>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr"/>
+      <c r="G112" s="21" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>SF-QB-03</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr"/>
+      <c r="G113" s="17" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>SF-QB-04</t>
+        </is>
+      </c>
+      <c r="B114" s="21" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C114" s="21" t="inlineStr">
+        <is>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+        </is>
+      </c>
+      <c r="D114" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E114" s="21" t="inlineStr">
+        <is>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+        </is>
+      </c>
+      <c r="F114" s="21" t="inlineStr"/>
+      <c r="G114" s="21" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>SF-QB-05</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr"/>
+      <c r="G115" s="17" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>SF-QB-06</t>
+        </is>
+      </c>
+      <c r="B116" s="21" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C116" s="21" t="inlineStr">
+        <is>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E116" s="21" t="inlineStr">
+        <is>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="inlineStr"/>
+      <c r="G116" s="21" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t>SF-QB-07</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="inlineStr"/>
+      <c r="G117" s="17" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>SF-QB-08</t>
+        </is>
+      </c>
+      <c r="B118" s="21" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C118" s="21" t="inlineStr">
+        <is>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
+        </is>
+      </c>
+      <c r="D118" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E118" s="21" t="inlineStr">
+        <is>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="inlineStr"/>
+      <c r="G118" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15349,14 +15851,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15385,6 +15888,11 @@
           <t>Affected cases</t>
         </is>
       </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Status / Resolution</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="27" t="n">
@@ -15397,22 +15905,27 @@
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>The spec supplies NO consolidated permissions/role matrix (§8 flags it as unresolved). Which roles may complete WOs, bulk receive, edit settings, and sign off review is undefined. Role-gating cases are authored but their expected results are TBD.</t>
+          <t>The spec supplied NO consolidated permissions/role matrix (§8 flagged it as unresolved). Which roles may complete WOs, bulk receive, edit settings, and sign off review was undefined.</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>Every role-gating case's expected result is a guess without this. Hypothesis to verify (from Custom Roles): the backend may enforce only resource-level View/Edit while granular gates are front-end display only.</t>
+          <t>Every role-gating case's expected result depended on this.</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
         <is>
-          <t>SF-PERM-01..07, SF-SET-11, SF-RCV-03, SF-REV-09</t>
+          <t>SF-PERM-01..10, SF-SET-11, SF-RCV-03, SF-REV-09</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>RESOLVED by SV-8183. Simple Flow adds NO new permission atom - every action maps to an existing Custom Roles atom (see requirements §9 action-&gt;atom map + per-role matrix): Settings = App Settings (defaults Admin/Service Manager/Office); Complete WO = Work Orders C&amp;E + WO Lines C&amp;E/Full View; Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Receive-on-WO = Order Parts (FE); Mark Reviewed = Review Work Orders + reviewer != completer. Source: SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="n">
+      <c r="A3" s="29" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -15433,6 +15946,11 @@
       <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Global - especially SF-SET-08, SF-TECH-08, SF-REV-08</t>
+        </is>
+      </c>
+      <c r="F3" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
@@ -15460,14 +15978,19 @@
           <t>SF-SET-08</t>
         </is>
       </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Explicitly NOT addressed by SV-8183.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="29" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>'Create Purchase Orders' toggle absent (VIU bug #1)</t>
+          <t>'Create Purchase Orders' toggle absent (build deviation #1)</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -15483,6 +16006,11 @@
       <c r="E5" s="17" t="inlineStr">
         <is>
           <t>SF-SET-03, SF-COMP-06, SF-QB-02</t>
+        </is>
+      </c>
+      <c r="F5" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Explicitly NOT addressed by SV-8183.</t>
         </is>
       </c>
     </row>
@@ -15502,7 +16030,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>Determines whether the tech-story gate-modal cases are authoritative. VIU showed the gate-modal working, so Story 17 appears current - confirm.</t>
+          <t>Determines whether the tech-story gate-modal cases are authoritative. The live build showed the gate-modal working, so Story 17 appears current - confirm.</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -15510,9 +16038,14 @@
           <t>SF-TECH-08 (and all SF-TECH-*)</t>
         </is>
       </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="29" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -15533,6 +16066,11 @@
       <c r="E7" s="17" t="inlineStr">
         <is>
           <t>SF-QB-06</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>RESOLVED by SV-8183 (Decision 4). A vendorless / no-PN part add requires See Financial Data, so the mandatory sell price is captured at add time and $0-cost margins are avoided. Source: SV-8183.</t>
         </is>
       </c>
     </row>
@@ -15560,9 +16098,14 @@
           <t>SF-COMP-07, SF-QB-01</t>
         </is>
       </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n">
+      <c r="A9" s="29" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -15577,12 +16120,17 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Sets the expected result for API-level negative tests (403/422 vs 200/201). Custom Roles precedent: BE often enforces only resource-level View/Edit.</t>
+          <t>Sets the expected result for API-level negative tests (403/422 vs 200/201).</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
           <t>SF-PERM-06</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>RESOLVED by SV-8183. The backend DOES enforce the Simple-Flow settings AND the permission atoms (not FE-only), subject to the WO-atom collapse caveat: any role with WO Create &amp; Edit can receive onto a WO, and the receive endpoint accepts the OR of ROLE_DELIVERY_CREATE_AND_EDIT / ROLE_WORK_ORDER_PART_CREATE / ROLE_WORK_ORDER_CREATE_AND_EDIT. Source: SV-8183.</t>
         </is>
       </c>
     </row>
@@ -15592,7 +16140,7 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Save Settings always enabled (VIU bug #2)</t>
+          <t>Save Settings always enabled (build deviation #2)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -15610,14 +16158,19 @@
           <t>SF-SET-13</t>
         </is>
       </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" s="29" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Mark Reviewed missing optional note (VIU bug #3)</t>
+          <t>Mark Reviewed missing optional note (build deviation #3)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -15633,6 +16186,11 @@
       <c r="E11" s="17" t="inlineStr">
         <is>
           <t>SF-REV-10</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
@@ -15642,7 +16200,7 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Review sign-off jumps to Complete (VIU bug #4)</t>
+          <t>Review sign-off jumps to Complete (build deviation #4)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -15660,9 +16218,14 @@
           <t>SF-REV-08, SF-REV-11</t>
         </is>
       </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n">
+      <c r="A13" s="29" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -15683,6 +16246,11 @@
       <c r="E13" s="17" t="inlineStr">
         <is>
           <t>SF-UX-04</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
@@ -15710,9 +16278,14 @@
           <t>SF-REV-15</t>
         </is>
       </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. SV-8183 defined WHO can sign off review, but NOT the require-review default cohort.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n">
+      <c r="A15" s="29" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -15733,6 +16306,11 @@
       <c r="E15" s="17" t="inlineStr">
         <is>
           <t>SF-RCV-05, SF-RCV-07</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
@@ -1866,14 +1866,14 @@
           <t>requirements S1 AC / §9 (App Settings gate)</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: the Work Order settings inherit the settingsApp route guard (no new atom); editable only by roles with App Settings ON (defaults Admin, Service Manager, Office). Role-gating negatives not yet verified live (only the admin session works on sv7301; tech key = 403).</t>
+          <t>Defined by SV-8183: the Work Order settings inherit the settingsApp route guard (no new atom); editable only by roles with App Settings ON (defaults Admin, Service Manager, Office). Role-gating negatives not yet verified live (only the admin session works on sv7301; tech key = 403). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED. Same as SF-PERM-01: tech redirected from settings route (FE) and BE POST /api/organizations/settings/change -&gt; 403; admin -&gt; 200. Non-admin cannot view or save WO settings.</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live.</t>
+          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Field-required validations and the See-Financial-Data add-part block not driven (part-add sub-form not reached within budget). Tech confirmed lacking seeFinancialData.</t>
         </is>
       </c>
     </row>
@@ -8011,14 +8011,14 @@
           <t>requirements S11-R3 / §9 (Order Parts gate)</t>
         </is>
       </c>
-      <c r="L98" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L98" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
         </is>
       </c>
     </row>
@@ -9642,14 +9642,14 @@
           <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
         </is>
       </c>
-      <c r="L121" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L121" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M121" s="21" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301).</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
         </is>
       </c>
     </row>
@@ -10417,14 +10417,14 @@
           <t>requirements S1 AC / §9 (App Settings gate)</t>
         </is>
       </c>
-      <c r="L132" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L132" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M132" s="17" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301).</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
         </is>
       </c>
     </row>
@@ -10488,14 +10488,14 @@
           <t>requirements §9 (Complete WO gate + per-role matrix)</t>
         </is>
       </c>
-      <c r="L133" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L133" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M133" s="21" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301).</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS.</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="M134" s="17" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live.</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships.</t>
         </is>
       </c>
     </row>
@@ -10630,14 +10630,14 @@
           <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
         </is>
       </c>
-      <c r="L135" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L135" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M135" s="21" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
         </is>
       </c>
     </row>
@@ -10701,14 +10701,14 @@
           <t>requirements S11-R3 / §9 (Order Parts gate)</t>
         </is>
       </c>
-      <c r="L136" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L136" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M136" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
         </is>
       </c>
     </row>
@@ -10773,14 +10773,14 @@
           <t>requirements §9.4 (BE enforcement + atom collapse)</t>
         </is>
       </c>
-      <c r="L137" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L137" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M137" s="21" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: BE DOES enforce the Simple-Flow settings and atoms (change from the Custom Roles FE-only finding), subject to the WO-atom collapse caveat (SV-7864). Not yet driven live.</t>
+          <t>Answered by SV-8183: BE DOES enforce the Simple-Flow settings and atoms (change from the Custom Roles FE-only finding), subject to the WO-atom collapse caveat (SV-7864). Not yet driven live. | VIU 2026-07-07 (Tech-unblock pass): HEADLINE / MIXED RESULT. BE enforces DISTINCT atoms (settingsApp: tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms: tech simple-complete -&gt; 201 and tech change-status-&gt;complete (review sign-off) -&gt; 201, due to the documented atom collapse (SV-7864). Expected #2 (any role with WO C&amp;E can act on the WO) CONFIRMED. Expected #1 ('BE enforces the atoms, not FE-only') is only TRUE for the settings atom; for WO completion/receive/review sign-off the gate is EFFECTIVELY FE-ONLY. This nuances SV-8183's blanket 'BE enforces' claim.</t>
         </is>
       </c>
     </row>
@@ -10843,14 +10843,14 @@
           <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
         </is>
       </c>
-      <c r="L138" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L138" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M138" s="17" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live.</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
         </is>
       </c>
     </row>
@@ -10915,14 +10915,14 @@
           <t>requirements R7 / §9 (reviewer != completer NET-NEW rule)</t>
         </is>
       </c>
-      <c r="L139" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L139" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M139" s="21" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live.</t>
+          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="M140" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live.</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested.</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="M141" s="21" t="inlineStr">
         <is>
-          <t>Per-role completion checklist derived from the SV-8183 role matrix. Role-gating negatives not yet verified live.</t>
+          <t>Per-role completion checklist derived from the SV-8183 role matrix. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Technician-negative CONFIRMED at FE (Complete button hidden). Other roles not exercised (the only non-admin session available is Technician). Full per-role matrix still pending additional role accounts.</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12505,17 +12505,17 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-SET-11</t>
+          <t>SF-COMP-04</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify a non-admin user cannot see or modify the Work Order settings</t>
+          <t>Verify Go to Invoice from the Success screen opens the Finance step where the invoice number is shown</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr"/>
@@ -12534,7 +12534,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-04</t>
+          <t>SF-COMP-05</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify Go to Invoice from the Success screen opens the Finance step where the invoice number is shown</t>
+          <t>Verify completion is blocked when a required vehicle field is missing</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -12563,7 +12563,7 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-05</t>
+          <t>SF-COMP-08</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required vehicle field is missing</t>
+          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-08</t>
+          <t>SF-COMP-10</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
+          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -12621,17 +12621,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -12650,7 +12650,7 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-14</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -12679,7 +12679,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-14</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -12708,7 +12708,7 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-16</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -12737,7 +12737,7 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -12766,17 +12766,17 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -12795,7 +12795,7 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -12824,17 +12824,17 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -12853,7 +12853,7 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -12882,17 +12882,17 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -12911,17 +12911,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -12940,17 +12940,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
+          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -12969,7 +12969,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -12998,17 +12998,17 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13027,7 +13027,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13056,7 +13056,7 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13085,17 +13085,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13114,17 +13114,17 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13143,7 +13143,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13172,17 +13172,17 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13201,17 +13201,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr"/>
@@ -13230,7 +13230,7 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13259,7 +13259,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13288,17 +13288,17 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13317,7 +13317,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
+          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13375,7 +13375,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13404,7 +13404,7 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13433,7 +13433,7 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13462,7 +13462,7 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13491,17 +13491,17 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13520,7 +13520,7 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13578,7 +13578,7 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13607,7 +13607,7 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13636,17 +13636,17 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr"/>
@@ -13665,7 +13665,7 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13723,7 +13723,7 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13752,7 +13752,7 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -13781,7 +13781,7 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -13810,17 +13810,17 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -13839,7 +13839,7 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -13868,7 +13868,7 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -13897,7 +13897,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -13955,7 +13955,7 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -13984,7 +13984,7 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14013,7 +14013,7 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14042,7 +14042,7 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14071,7 +14071,7 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14100,17 +14100,17 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14129,7 +14129,7 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14158,7 +14158,7 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14187,17 +14187,17 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F62" s="21" t="inlineStr"/>
@@ -14216,7 +14216,7 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14245,7 +14245,7 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14274,7 +14274,7 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14303,7 +14303,7 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14332,7 +14332,7 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14361,17 +14361,17 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14390,7 +14390,7 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14419,17 +14419,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14448,17 +14448,17 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F71" s="17" t="inlineStr"/>
@@ -14477,7 +14477,7 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14506,7 +14506,7 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
@@ -14564,17 +14564,17 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -14593,17 +14593,17 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
@@ -14622,7 +14622,7 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
@@ -14651,7 +14651,7 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
@@ -14709,17 +14709,17 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="E80" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F80" s="21" t="inlineStr"/>
@@ -14738,17 +14738,17 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr"/>
@@ -14767,7 +14767,7 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
@@ -14796,17 +14796,17 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr"/>
@@ -14825,17 +14825,17 @@
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="E84" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F84" s="21" t="inlineStr"/>
@@ -14854,7 +14854,7 @@
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
@@ -14883,7 +14883,7 @@
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
@@ -14912,7 +14912,7 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
@@ -14941,7 +14941,7 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="E88" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F88" s="21" t="inlineStr"/>
@@ -14970,7 +14970,7 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D89" s="17" t="inlineStr">
@@ -14999,17 +14999,17 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr"/>
@@ -15028,17 +15028,17 @@
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="D91" s="17" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr"/>
@@ -15057,17 +15057,17 @@
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr"/>
@@ -15086,17 +15086,17 @@
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="D93" s="17" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F93" s="17" t="inlineStr"/>
@@ -15115,17 +15115,17 @@
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr"/>
@@ -15144,17 +15144,17 @@
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="D95" s="17" t="inlineStr">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr"/>
@@ -15173,17 +15173,17 @@
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr"/>
@@ -15202,17 +15202,17 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D97" s="17" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr"/>
@@ -15231,17 +15231,17 @@
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr"/>
@@ -15260,17 +15260,17 @@
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="D99" s="17" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr"/>
@@ -15289,17 +15289,17 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr"/>
@@ -15318,17 +15318,17 @@
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D101" s="17" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr"/>
@@ -15347,17 +15347,17 @@
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-VAL-11</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr"/>
@@ -15376,17 +15376,17 @@
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D103" s="17" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F103" s="17" t="inlineStr"/>
@@ -15405,17 +15405,17 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B104" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="E104" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F104" s="21" t="inlineStr"/>
@@ -15434,17 +15434,17 @@
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C105" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D105" s="17" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F105" s="17" t="inlineStr"/>
@@ -15463,17 +15463,17 @@
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="E106" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr"/>
@@ -15492,17 +15492,17 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D107" s="17" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F107" s="17" t="inlineStr"/>
@@ -15521,17 +15521,17 @@
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D108" s="21" t="inlineStr">
@@ -15541,301 +15541,11 @@
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr"/>
       <c r="G108" s="21" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-08</t>
-        </is>
-      </c>
-      <c r="B109" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
-        <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E109" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F109" s="17" t="inlineStr"/>
-      <c r="G109" s="17" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-09</t>
-        </is>
-      </c>
-      <c r="B110" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C110" s="21" t="inlineStr">
-        <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
-        </is>
-      </c>
-      <c r="D110" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E110" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F110" s="21" t="inlineStr"/>
-      <c r="G110" s="21" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="B111" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C111" s="17" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="D111" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E111" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F111" s="17" t="inlineStr"/>
-      <c r="G111" s="17" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-11</t>
-        </is>
-      </c>
-      <c r="B112" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C112" s="21" t="inlineStr">
-        <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
-        </is>
-      </c>
-      <c r="D112" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E112" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F112" s="21" t="inlineStr"/>
-      <c r="G112" s="21" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B113" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C113" s="17" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D113" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E113" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F113" s="17" t="inlineStr"/>
-      <c r="G113" s="17" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B114" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C114" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D114" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E114" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F114" s="21" t="inlineStr"/>
-      <c r="G114" s="21" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B115" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C115" s="17" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D115" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E115" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F115" s="17" t="inlineStr"/>
-      <c r="G115" s="17" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B116" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C116" s="21" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D116" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E116" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F116" s="21" t="inlineStr"/>
-      <c r="G116" s="21" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B117" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C117" s="17" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D117" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E117" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F117" s="17" t="inlineStr"/>
-      <c r="G117" s="17" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B118" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C118" s="21" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D118" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E118" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F118" s="21" t="inlineStr"/>
-      <c r="G118" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41">
@@ -2510,14 +2510,14 @@
           <t>WO Review Flow.html (Details step)</t>
         </is>
       </c>
-      <c r="L21" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L21" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
-          <t>The Details step collecting Mileage was seen (S2-13-details.png) but the empty-field block was not isolated. Needs live verification.</t>
+          <t>The Details step collecting Mileage was seen (S2-13-details.png) but the empty-field block was not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard (WO 00609f73) blocks with "Mileage is a required field" when the required vehicle field (mileage) is empty on Continue. Evidence VIU2-02-mileage-gate.png.</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification.</t>
+          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded).</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14).</t>
+          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
         </is>
       </c>
     </row>
@@ -3662,14 +3662,14 @@
           <t>requirements §4 Key Decision / S3-R9</t>
         </is>
       </c>
-      <c r="L37" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context).</t>
+          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
         </is>
       </c>
     </row>
@@ -3734,14 +3734,14 @@
           <t>requirements §4 Key Decision</t>
         </is>
       </c>
-      <c r="L38" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L38" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4 adds a financial gate: vendorless / no-PN add requires See Financial Data (mandatory sell). Not driven live (part-add flow not exercised).</t>
+          <t>SV-8183 Decision 4 adds a financial gate: vendorless / no-PN add requires See Financial Data (mandatory sell). Not driven live (part-add flow not exercised). | 2026-07-08: attempted admin add — the manual part-request add sub-form is reached via the line's Parts tab which requires the line's "parts authorized" state; not reliably drivable in this harness session (line-edit dialog exposed no Parts tab for a labor line). Canned-line parts DO create the vendorless shape (part_number=null, vendor_id=null, part_source_type="vendor", editable sell_price), corroborating the data model, but the description+qty+sell manual sub-form itself remains UI-unverified. Still needs a driven add-part sub-form.</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Field-required validations and the See-Financial-Data add-part block not driven (part-add sub-form not reached within budget). Tech confirmed lacking seeFinancialData.</t>
+          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Field-required validations and the See-Financial-Data add-part block not driven (part-add sub-form not reached within budget). Tech confirmed lacking seeFinancialData. | 2026-07-08: manual add-part sub-form validation not reached (see SF-VPART-01). Still pending; also needs a Technician (no See Financial Data) for the permission half.</t>
         </is>
       </c>
     </row>
@@ -5667,14 +5667,14 @@
           <t>Purchase Orders List.html; requirements S6-R1</t>
         </is>
       </c>
-      <c r="L65" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L65" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M65" s="21" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification.</t>
+          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO.</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="M140" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested.</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role.</t>
         </is>
       </c>
     </row>
@@ -11127,14 +11127,14 @@
           <t>WO Review Flow.html (Details step)</t>
         </is>
       </c>
-      <c r="L142" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L142" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M142" s="17" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification.</t>
+          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
         </is>
       </c>
     </row>
@@ -11832,14 +11832,14 @@
           <t>requirements §4 Key Decision</t>
         </is>
       </c>
-      <c r="L152" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L152" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M152" s="17" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line.</t>
+          <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12534,7 +12534,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-05</t>
+          <t>SF-COMP-08</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required vehicle field is missing</t>
+          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -12563,7 +12563,7 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-08</t>
+          <t>SF-COMP-10</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
+          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -12592,17 +12592,17 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -12621,7 +12621,7 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -12650,7 +12650,7 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-14</t>
+          <t>SF-COMP-16</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
+          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -12679,7 +12679,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -12708,17 +12708,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -12737,17 +12737,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -12766,17 +12766,17 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -12795,17 +12795,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -12824,17 +12824,17 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr"/>
@@ -12853,17 +12853,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -12882,17 +12882,17 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr"/>
@@ -12911,17 +12911,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -12940,17 +12940,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -12969,17 +12969,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -12998,17 +12998,17 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13027,17 +13027,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13056,17 +13056,17 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13085,17 +13085,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -13114,17 +13114,17 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr"/>
@@ -13143,17 +13143,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
@@ -13172,17 +13172,17 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
+          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -13201,17 +13201,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13230,17 +13230,17 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13259,17 +13259,17 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13288,7 +13288,7 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13317,7 +13317,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13375,17 +13375,17 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13404,17 +13404,17 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13433,17 +13433,17 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13462,17 +13462,17 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13491,17 +13491,17 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr"/>
@@ -13520,17 +13520,17 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr"/>
@@ -13549,17 +13549,17 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr"/>
@@ -13578,17 +13578,17 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr"/>
@@ -13607,17 +13607,17 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr"/>
@@ -13636,7 +13636,7 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13665,17 +13665,17 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13694,17 +13694,17 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13723,17 +13723,17 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13752,17 +13752,17 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -13781,17 +13781,17 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -13839,7 +13839,7 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -13868,7 +13868,7 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -13897,7 +13897,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -13955,17 +13955,17 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -13984,17 +13984,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14013,17 +14013,17 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14042,17 +14042,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr"/>
@@ -14071,17 +14071,17 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E58" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F58" s="21" t="inlineStr"/>
@@ -14100,17 +14100,17 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr"/>
@@ -14129,17 +14129,17 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F60" s="21" t="inlineStr"/>
@@ -14158,17 +14158,17 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr"/>
@@ -14187,7 +14187,7 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14245,17 +14245,17 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14274,17 +14274,17 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14303,17 +14303,17 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14332,17 +14332,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14361,17 +14361,17 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14390,17 +14390,17 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14419,17 +14419,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14448,17 +14448,17 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14477,17 +14477,17 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14506,17 +14506,17 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14535,17 +14535,17 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
@@ -14564,17 +14564,17 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr"/>
@@ -14593,17 +14593,17 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="E76" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F76" s="21" t="inlineStr"/>
@@ -14622,17 +14622,17 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr"/>
@@ -14651,17 +14651,17 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
@@ -14680,17 +14680,17 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
@@ -14709,17 +14709,17 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="E80" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F80" s="21" t="inlineStr"/>
@@ -14738,17 +14738,17 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr"/>
@@ -14767,17 +14767,17 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F82" s="21" t="inlineStr"/>
@@ -14796,7 +14796,7 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
@@ -14825,7 +14825,7 @@
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
@@ -14854,17 +14854,17 @@
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr"/>
@@ -14883,17 +14883,17 @@
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="E86" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F86" s="21" t="inlineStr"/>
@@ -14912,17 +14912,17 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F87" s="17" t="inlineStr"/>
@@ -14941,17 +14941,17 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
@@ -14970,17 +14970,17 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="D89" s="17" t="inlineStr">
@@ -14999,17 +14999,17 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr"/>
@@ -15028,17 +15028,17 @@
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D91" s="17" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr"/>
@@ -15057,17 +15057,17 @@
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr"/>
@@ -15086,7 +15086,7 @@
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="B93" s="17" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="D93" s="17" t="inlineStr">
@@ -15115,7 +15115,7 @@
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
@@ -15144,7 +15144,7 @@
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B95" s="17" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D95" s="17" t="inlineStr">
@@ -15173,17 +15173,17 @@
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr"/>
@@ -15202,17 +15202,17 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D97" s="17" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr"/>
@@ -15231,17 +15231,17 @@
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr"/>
@@ -15260,17 +15260,17 @@
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D99" s="17" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr"/>
@@ -15289,17 +15289,17 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr"/>
@@ -15318,17 +15318,17 @@
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D101" s="17" t="inlineStr">
@@ -15338,214 +15338,11 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr"/>
       <c r="G101" s="17" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-11</t>
-        </is>
-      </c>
-      <c r="B102" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C102" s="21" t="inlineStr">
-        <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
-        </is>
-      </c>
-      <c r="D102" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E102" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F102" s="21" t="inlineStr"/>
-      <c r="G102" s="21" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D103" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E103" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F103" s="17" t="inlineStr"/>
-      <c r="G103" s="17" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B104" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C104" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D104" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E104" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr"/>
-      <c r="G104" s="21" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C105" s="17" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D105" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E105" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F105" s="17" t="inlineStr"/>
-      <c r="G105" s="17" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B106" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C106" s="21" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D106" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr"/>
-      <c r="G106" s="21" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B107" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D107" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E107" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F107" s="17" t="inlineStr"/>
-      <c r="G107" s="17" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B108" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C108" s="21" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D108" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E108" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F108" s="21" t="inlineStr"/>
-      <c r="G108" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41">
@@ -2437,14 +2437,14 @@
           <t>WO Review Flow.html; requirements S15-R3</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M20" s="17" t="inlineStr">
         <is>
-          <t>Success screen verified; the Go-to-Invoice navigation was not driven in the VIU run. Needs live verification.</t>
+          <t>Success screen verified; the Go-to-Invoice navigation was not driven in the VIU run. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Go To Invoice from Success navigated to /workorders/{id}/finance (Finance step, invoice-ready draft) (VIU3-05-invoice-finance.png).</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3303,14 @@
           <t>WO Review Flow.html (Details step)</t>
         </is>
       </c>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L32" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification.</t>
+          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
         </is>
       </c>
     </row>
@@ -3373,14 +3373,14 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L33" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification.</t>
+          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
         </is>
       </c>
     </row>
@@ -4882,14 +4882,14 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L54" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification.</t>
+          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
         </is>
       </c>
     </row>
@@ -4952,14 +4952,14 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L55" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M55" s="21" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification.</t>
+          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
         </is>
       </c>
     </row>
@@ -5021,14 +5021,14 @@
           <t>WO Review Flow - Handoff.md (element test IDs)</t>
         </is>
       </c>
-      <c r="L56" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L56" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check.</t>
+          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
         </is>
       </c>
     </row>
@@ -5167,14 +5167,14 @@
           <t>requirements S5-R1 / §9 (See Financial Data gate)</t>
         </is>
       </c>
-      <c r="L58" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4 adds a financial gate: vendorless / no-PN add requires See Financial Data (mandatory sell). Not driven live (part-add flow not exercised). | 2026-07-08: attempted admin add — the manual part-request add sub-form is reached via the line's Parts tab which requires the line's "parts authorized" state; not reliably drivable in this harness session (line-edit dialog exposed no Parts tab for a labor line). Canned-line parts DO create the vendorless shape (part_number=null, vendor_id=null, part_source_type="vendor", editable sell_price), corroborating the data model, but the description+qty+sell manual sub-form itself remains UI-unverified. Still needs a driven add-part sub-form.</t>
+          <t>SV-8183 Decision 4 adds a financial gate: vendorless / no-PN add requires See Financial Data (mandatory sell). Not driven live (part-add flow not exercised). | 2026-07-08: attempted admin add — the manual part-request add sub-form is reached via the line's Parts tab which requires the line's "parts authorized" state; not reliably drivable in this harness session (line-edit dialog exposed no Parts tab for a labor line). Canned-line parts DO create the vendorless shape (part_number=null, vendor_id=null, part_source_type="vendor", editable sell_price), corroborating the data model, but the description+qty+sell manual sub-form itself remains UI-unverified. Still needs a driven add-part sub-form. || VIU batch3 2026-07-08 VERIFIED: New Part Request sub-form reached via New Line -&gt; custom title -&gt; Save &amp; Add Part; desc+qty+sell(+category) -&gt; 201 POST /api/work-orders/part/make-request; created part {part_number:null, vendor_id:null, part_source_type:'vendor', sell:49.99, inventory_part_id:null}. DEVIATION: Category is REQUIRED (not in spec S5-R1) (VP-13/VP-14).</t>
         </is>
       </c>
     </row>
@@ -5241,14 +5241,14 @@
           <t>requirements S5 AC / §9 (See Financial Data gate)</t>
         </is>
       </c>
-      <c r="L59" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Field-required validations and the See-Financial-Data add-part block not driven (part-add sub-form not reached within budget). Tech confirmed lacking seeFinancialData. | 2026-07-08: manual add-part sub-form validation not reached (see SF-VPART-01). Still pending; also needs a Technician (no See Financial Data) for the permission half.</t>
+          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Field-required validations and the See-Financial-Data add-part block not driven (part-add sub-form not reached within budget). Tech confirmed lacking seeFinancialData. | 2026-07-08: manual add-part sub-form validation not reached (see SF-VPART-01). Still pending; also needs a Technician (no See Financial Data) for the permission half. || VIU batch3 2026-07-08 VERIFIED: empty save -&gt; inline 'Description is a required field', 'Quantity is a required field', 'Category is a required field' (VP-11-validation-empty.png). DEVIATION: Category required in addition to spec; Sell Price NOT flagged required.</t>
         </is>
       </c>
     </row>
@@ -5312,14 +5312,14 @@
           <t>requirements S5-R2</t>
         </is>
       </c>
-      <c r="L60" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
         </is>
       </c>
     </row>
@@ -5452,14 +5452,14 @@
           <t>requirements S5-R4 / §5</t>
         </is>
       </c>
-      <c r="L62" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L62" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
         </is>
       </c>
     </row>
@@ -10985,14 +10985,14 @@
           <t>requirements S5 / §9 (Decision 4)</t>
         </is>
       </c>
-      <c r="L140" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L140" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M140" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role.</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
         </is>
       </c>
     </row>
@@ -11266,14 +11266,14 @@
           <t>requirements S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="L144" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L144" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M144" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12505,7 +12505,7 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-04</t>
+          <t>SF-COMP-08</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify Go to Invoice from the Success screen opens the Finance step where the invoice number is shown</t>
+          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-08</t>
+          <t>SF-COMP-10</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
+          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -12563,17 +12563,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -12621,17 +12621,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -12650,17 +12650,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -12679,17 +12679,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -12708,17 +12708,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr"/>
@@ -12737,17 +12737,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -12766,17 +12766,17 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr"/>
@@ -12795,17 +12795,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -12824,17 +12824,17 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -12853,17 +12853,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -12882,17 +12882,17 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -12911,17 +12911,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -12940,17 +12940,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -12969,17 +12969,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -12998,17 +12998,17 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr"/>
@@ -13027,17 +13027,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -13056,17 +13056,17 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr"/>
@@ -13085,17 +13085,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13114,17 +13114,17 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13143,17 +13143,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13172,17 +13172,17 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13201,17 +13201,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr"/>
@@ -13230,17 +13230,17 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr"/>
@@ -13259,17 +13259,17 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr"/>
@@ -13288,17 +13288,17 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr"/>
@@ -13317,17 +13317,17 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr"/>
@@ -13346,17 +13346,17 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr"/>
@@ -13375,17 +13375,17 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr"/>
@@ -13404,17 +13404,17 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr"/>
@@ -13433,17 +13433,17 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr"/>
@@ -13462,17 +13462,17 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr"/>
@@ -13491,17 +13491,17 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13520,17 +13520,17 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13549,17 +13549,17 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13578,17 +13578,17 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13607,17 +13607,17 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13636,17 +13636,17 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13665,17 +13665,17 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13694,17 +13694,17 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13723,17 +13723,17 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13752,17 +13752,17 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr"/>
@@ -13781,17 +13781,17 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F48" s="21" t="inlineStr"/>
@@ -13810,17 +13810,17 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr"/>
@@ -13839,17 +13839,17 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="E50" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F50" s="21" t="inlineStr"/>
@@ -13868,17 +13868,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr"/>
@@ -13897,17 +13897,17 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F52" s="21" t="inlineStr"/>
@@ -13926,17 +13926,17 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr"/>
@@ -13955,17 +13955,17 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F54" s="21" t="inlineStr"/>
@@ -13984,17 +13984,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr"/>
@@ -14013,17 +14013,17 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F56" s="21" t="inlineStr"/>
@@ -14042,17 +14042,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14071,17 +14071,17 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14100,17 +14100,17 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14129,17 +14129,17 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14158,17 +14158,17 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14187,17 +14187,17 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14245,17 +14245,17 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14274,17 +14274,17 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F65" s="17" t="inlineStr"/>
@@ -14303,17 +14303,17 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F66" s="21" t="inlineStr"/>
@@ -14332,17 +14332,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr"/>
@@ -14361,17 +14361,17 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14390,17 +14390,17 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14419,17 +14419,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14448,17 +14448,17 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14477,17 +14477,17 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14506,17 +14506,17 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14535,17 +14535,17 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
@@ -14564,17 +14564,17 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr"/>
@@ -14593,17 +14593,17 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="E76" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F76" s="21" t="inlineStr"/>
@@ -14622,17 +14622,17 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr"/>
@@ -14651,17 +14651,17 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
@@ -14680,17 +14680,17 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
@@ -14709,17 +14709,17 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
@@ -14738,17 +14738,17 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
@@ -14767,17 +14767,17 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
@@ -14796,17 +14796,17 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
@@ -14825,17 +14825,17 @@
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="E84" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F84" s="21" t="inlineStr"/>
@@ -14854,17 +14854,17 @@
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr"/>
@@ -14883,17 +14883,17 @@
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="E86" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F86" s="21" t="inlineStr"/>
@@ -14912,17 +14912,17 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F87" s="17" t="inlineStr"/>
@@ -14941,17 +14941,17 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="E88" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F88" s="21" t="inlineStr"/>
@@ -14970,17 +14970,17 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D89" s="17" t="inlineStr">
@@ -14990,359 +14990,11 @@
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F89" s="17" t="inlineStr"/>
       <c r="G89" s="17" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-05</t>
-        </is>
-      </c>
-      <c r="B90" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C90" s="21" t="inlineStr">
-        <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
-        </is>
-      </c>
-      <c r="D90" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E90" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F90" s="21" t="inlineStr"/>
-      <c r="G90" s="21" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-06</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C91" s="17" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="D91" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E91" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F91" s="17" t="inlineStr"/>
-      <c r="G91" s="17" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-07</t>
-        </is>
-      </c>
-      <c r="B92" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C92" s="21" t="inlineStr">
-        <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
-        </is>
-      </c>
-      <c r="D92" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E92" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F92" s="21" t="inlineStr"/>
-      <c r="G92" s="21" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-08</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C93" s="17" t="inlineStr">
-        <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
-        </is>
-      </c>
-      <c r="D93" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E93" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F93" s="17" t="inlineStr"/>
-      <c r="G93" s="17" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-09</t>
-        </is>
-      </c>
-      <c r="B94" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C94" s="21" t="inlineStr">
-        <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
-        </is>
-      </c>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E94" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F94" s="21" t="inlineStr"/>
-      <c r="G94" s="21" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="D95" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E95" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F95" s="17" t="inlineStr"/>
-      <c r="G95" s="17" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B96" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C96" s="21" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D96" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E96" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F96" s="21" t="inlineStr"/>
-      <c r="G96" s="21" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D97" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E97" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F97" s="17" t="inlineStr"/>
-      <c r="G97" s="17" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B98" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C98" s="21" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E98" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F98" s="21" t="inlineStr"/>
-      <c r="G98" s="21" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C99" s="17" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D99" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E99" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F99" s="17" t="inlineStr"/>
-      <c r="G99" s="17" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B100" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C100" s="21" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E100" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F100" s="21" t="inlineStr"/>
-      <c r="G100" s="21" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C101" s="17" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D101" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E101" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F101" s="17" t="inlineStr"/>
-      <c r="G101" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
@@ -1794,9 +1794,9 @@
           <t>requirements S1-R9</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -1898,7 +1898,7 @@
           <t>Verify the settings model contains no operatingMode field and no requireVin setting</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1969,7 +1969,7 @@
           <t>Verify the Save Settings button is only enabled when there is an unsaved change</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2111,7 +2111,7 @@
           <t>Verify every Work Order setting toggle has descriptive helper text</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2729,7 +2729,7 @@
           <t>Pick Parts Step.html</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -2872,7 +2872,7 @@
           <t>requirements §4 KEEP list</t>
         </is>
       </c>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -3087,7 +3087,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -3230,7 +3230,7 @@
           <t>WO Review Flow.html; requirements S3-R7/R9</t>
         </is>
       </c>
-      <c r="L31" s="24" t="inlineStr">
+      <c r="L31" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -3519,7 +3519,7 @@
           <t>WO Review Flow.html; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L35" s="24" t="inlineStr">
+      <c r="L35" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -3589,7 +3589,7 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -3805,9 +3805,9 @@
           <t>requirements S3-R9</t>
         </is>
       </c>
-      <c r="L39" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
@@ -3879,7 +3879,7 @@
           <t>Resolve Cores Flow.html; Core Resolution.html; Pick Parts + Cores.html</t>
         </is>
       </c>
-      <c r="L40" s="24" t="inlineStr">
+      <c r="L40" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -3911,7 +3911,7 @@
           <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3950,7 +3950,7 @@
           <t>Resolve Cores Flow - Handoff.md</t>
         </is>
       </c>
-      <c r="L41" s="24" t="inlineStr">
+      <c r="L41" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4022,7 +4022,7 @@
           <t>Resolve Cores Flow - Handoff.md; requirements S3-C2</t>
         </is>
       </c>
-      <c r="L42" s="24" t="inlineStr">
+      <c r="L42" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4091,7 +4091,7 @@
           <t>Resolve Cores to Invoice.html</t>
         </is>
       </c>
-      <c r="L43" s="24" t="inlineStr">
+      <c r="L43" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4164,7 +4164,7 @@
           <t>Resolve Cores to Invoice.html</t>
         </is>
       </c>
-      <c r="L44" s="24" t="inlineStr">
+      <c r="L44" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4235,7 +4235,7 @@
           <t>Resolve Cores to Invoice.html; requirements S3-C4</t>
         </is>
       </c>
-      <c r="L45" s="24" t="inlineStr">
+      <c r="L45" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4308,7 +4308,7 @@
           <t>Resolve Cores Flow.html; requirements S4-C2</t>
         </is>
       </c>
-      <c r="L46" s="24" t="inlineStr">
+      <c r="L46" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4378,7 +4378,7 @@
           <t>requirements S3 Guardrail</t>
         </is>
       </c>
-      <c r="L47" s="24" t="inlineStr">
+      <c r="L47" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4448,7 +4448,7 @@
           <t>requirements S3 Guardrail</t>
         </is>
       </c>
-      <c r="L48" s="24" t="inlineStr">
+      <c r="L48" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4480,7 +4480,7 @@
           <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E49" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4520,7 +4520,7 @@
           <t>Resolve Cores Flow.html; Resolve Cores Flow - Handoff.md</t>
         </is>
       </c>
-      <c r="L49" s="24" t="inlineStr">
+      <c r="L49" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -4984,7 +4984,7 @@
           <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
-      <c r="E56" s="25" t="inlineStr">
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5344,7 +5344,7 @@
           <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="E61" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5382,7 +5382,7 @@
           <t>requirements S5-R3</t>
         </is>
       </c>
-      <c r="L61" s="24" t="inlineStr">
+      <c r="L61" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -5523,7 +5523,7 @@
           <t>requirements S5 AC / S6-R5</t>
         </is>
       </c>
-      <c r="L63" s="24" t="inlineStr">
+      <c r="L63" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -5595,7 +5595,7 @@
           <t>requirements S5-R4 / S12-R2</t>
         </is>
       </c>
-      <c r="L64" s="24" t="inlineStr">
+      <c r="L64" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -5809,7 +5809,7 @@
           <t>requirements S6-R3 / §5</t>
         </is>
       </c>
-      <c r="L67" s="24" t="inlineStr">
+      <c r="L67" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -5880,7 +5880,7 @@
           <t>Purchase Order Details.html; requirements S6-R4</t>
         </is>
       </c>
-      <c r="L68" s="24" t="inlineStr">
+      <c r="L68" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -5951,7 +5951,7 @@
           <t>requirements S6-R5</t>
         </is>
       </c>
-      <c r="L69" s="24" t="inlineStr">
+      <c r="L69" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -5983,7 +5983,7 @@
           <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
-      <c r="E70" s="25" t="inlineStr">
+      <c r="E70" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6021,7 +6021,7 @@
           <t>requirements S6-R6</t>
         </is>
       </c>
-      <c r="L70" s="24" t="inlineStr">
+      <c r="L70" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6092,7 +6092,7 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L71" s="24" t="inlineStr">
+      <c r="L71" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6162,7 +6162,7 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L72" s="24" t="inlineStr">
+      <c r="L72" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6232,7 +6232,7 @@
           <t>Purchase Orders List.html; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L73" s="24" t="inlineStr">
+      <c r="L73" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6300,7 +6300,7 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L74" s="24" t="inlineStr">
+      <c r="L74" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6370,7 +6370,7 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L75" s="24" t="inlineStr">
+      <c r="L75" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6402,7 +6402,7 @@
           <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
-      <c r="E76" s="25" t="inlineStr">
+      <c r="E76" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6440,7 +6440,7 @@
           <t>Purchase Orders List.html; requirements S7</t>
         </is>
       </c>
-      <c r="L76" s="24" t="inlineStr">
+      <c r="L76" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6510,7 +6510,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L77" s="24" t="inlineStr">
+      <c r="L77" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6582,7 +6582,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L78" s="24" t="inlineStr">
+      <c r="L78" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6652,7 +6652,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L79" s="24" t="inlineStr">
+      <c r="L79" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6725,7 +6725,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L80" s="24" t="inlineStr">
+      <c r="L80" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6797,7 +6797,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L81" s="24" t="inlineStr">
+      <c r="L81" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6869,7 +6869,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L82" s="24" t="inlineStr">
+      <c r="L82" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -6941,7 +6941,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L83" s="24" t="inlineStr">
+      <c r="L83" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7013,7 +7013,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L84" s="24" t="inlineStr">
+      <c r="L84" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7085,7 +7085,7 @@
           <t>requirements S8-R11 / §5</t>
         </is>
       </c>
-      <c r="L85" s="24" t="inlineStr">
+      <c r="L85" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7155,7 +7155,7 @@
           <t>requirements S8-C1/C2</t>
         </is>
       </c>
-      <c r="L86" s="24" t="inlineStr">
+      <c r="L86" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7226,7 +7226,7 @@
           <t>Receive Vendor Parts - v2.html; requirements S9-R1</t>
         </is>
       </c>
-      <c r="L87" s="24" t="inlineStr">
+      <c r="L87" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7299,7 +7299,7 @@
           <t>requirements S9-R2</t>
         </is>
       </c>
-      <c r="L88" s="24" t="inlineStr">
+      <c r="L88" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7371,7 +7371,7 @@
           <t>requirements S9-R3</t>
         </is>
       </c>
-      <c r="L89" s="24" t="inlineStr">
+      <c r="L89" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7443,7 +7443,7 @@
           <t>Purchase Order Details.html; requirements S10-R1</t>
         </is>
       </c>
-      <c r="L90" s="24" t="inlineStr">
+      <c r="L90" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7515,7 +7515,7 @@
           <t>requirements S10 AC</t>
         </is>
       </c>
-      <c r="L91" s="24" t="inlineStr">
+      <c r="L91" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7587,7 +7587,7 @@
           <t>requirements S10 AC</t>
         </is>
       </c>
-      <c r="L92" s="24" t="inlineStr">
+      <c r="L92" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7657,7 +7657,7 @@
           <t>requirements S10-R2 / S8-R7</t>
         </is>
       </c>
-      <c r="L93" s="24" t="inlineStr">
+      <c r="L93" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7728,7 +7728,7 @@
           <t>requirements S10 Negative</t>
         </is>
       </c>
-      <c r="L94" s="24" t="inlineStr">
+      <c r="L94" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7800,7 +7800,7 @@
           <t>requirements S10 Technical guardrails / §5</t>
         </is>
       </c>
-      <c r="L95" s="24" t="inlineStr">
+      <c r="L95" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -7871,9 +7871,9 @@
           <t>Purchase Orders List.html; Purchase Order Details.html</t>
         </is>
       </c>
-      <c r="L96" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L96" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M96" s="17" t="inlineStr">
@@ -7940,7 +7940,7 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L97" s="24" t="inlineStr">
+      <c r="L97" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8155,7 +8155,7 @@
           <t>Receive Vendor Parts - v2.html; requirements S12-R1</t>
         </is>
       </c>
-      <c r="L100" s="24" t="inlineStr">
+      <c r="L100" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8227,7 +8227,7 @@
           <t>requirements S12-R2</t>
         </is>
       </c>
-      <c r="L101" s="24" t="inlineStr">
+      <c r="L101" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8259,7 +8259,7 @@
           <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
-      <c r="E102" s="25" t="inlineStr">
+      <c r="E102" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8298,7 +8298,7 @@
           <t>requirements S12-R3</t>
         </is>
       </c>
-      <c r="L102" s="24" t="inlineStr">
+      <c r="L102" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8368,7 +8368,7 @@
           <t>requirements S12-R4 / §5</t>
         </is>
       </c>
-      <c r="L103" s="24" t="inlineStr">
+      <c r="L103" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8437,7 +8437,7 @@
           <t>requirements S12 (existing behavior)</t>
         </is>
       </c>
-      <c r="L104" s="24" t="inlineStr">
+      <c r="L104" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8508,7 +8508,7 @@
           <t>Receive Vendor Parts - v2.html; requirements S13-R1</t>
         </is>
       </c>
-      <c r="L105" s="24" t="inlineStr">
+      <c r="L105" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8579,7 +8579,7 @@
           <t>requirements S13-R2</t>
         </is>
       </c>
-      <c r="L106" s="24" t="inlineStr">
+      <c r="L106" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8651,7 +8651,7 @@
           <t>requirements S13-R3</t>
         </is>
       </c>
-      <c r="L107" s="24" t="inlineStr">
+      <c r="L107" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8722,7 +8722,7 @@
           <t>requirements S13-R4 / S13-R5</t>
         </is>
       </c>
-      <c r="L108" s="24" t="inlineStr">
+      <c r="L108" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8794,7 +8794,7 @@
           <t>requirements S13 Technical guardrails</t>
         </is>
       </c>
-      <c r="L109" s="24" t="inlineStr">
+      <c r="L109" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8865,7 +8865,7 @@
           <t>Work Orders List.html</t>
         </is>
       </c>
-      <c r="L110" s="24" t="inlineStr">
+      <c r="L110" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8935,7 +8935,7 @@
           <t>requirements S14-R2</t>
         </is>
       </c>
-      <c r="L111" s="24" t="inlineStr">
+      <c r="L111" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -8967,7 +8967,7 @@
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="E112" s="25" t="inlineStr">
+      <c r="E112" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9004,7 +9004,7 @@
           <t>requirements S14-R3</t>
         </is>
       </c>
-      <c r="L112" s="24" t="inlineStr">
+      <c r="L112" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9215,7 +9215,7 @@
           <t>WO Review Flow.html; requirements R3</t>
         </is>
       </c>
-      <c r="L115" s="24" t="inlineStr">
+      <c r="L115" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9284,7 +9284,7 @@
           <t>WO Review Flow.html; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L116" s="24" t="inlineStr">
+      <c r="L116" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9499,7 +9499,7 @@
           <t>requirements R6</t>
         </is>
       </c>
-      <c r="L119" s="24" t="inlineStr">
+      <c r="L119" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9783,7 +9783,7 @@
           <t>requirements R8</t>
         </is>
       </c>
-      <c r="L123" s="24" t="inlineStr">
+      <c r="L123" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9853,7 +9853,7 @@
           <t>Work Orders List.html; requirements R9</t>
         </is>
       </c>
-      <c r="L124" s="24" t="inlineStr">
+      <c r="L124" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9922,7 +9922,7 @@
           <t>requirements R11</t>
         </is>
       </c>
-      <c r="L125" s="24" t="inlineStr">
+      <c r="L125" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -9994,7 +9994,7 @@
           <t>requirements R Core parts</t>
         </is>
       </c>
-      <c r="L126" s="24" t="inlineStr">
+      <c r="L126" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -10026,7 +10026,7 @@
           <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
         </is>
       </c>
-      <c r="E127" s="25" t="inlineStr">
+      <c r="E127" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10559,7 +10559,7 @@
           <t>requirements §9 (Bulk Receive gate + per-role matrix)</t>
         </is>
       </c>
-      <c r="L134" s="24" t="inlineStr">
+      <c r="L134" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -10805,7 +10805,7 @@
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="E138" s="25" t="inlineStr">
+      <c r="E138" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11058,9 +11058,9 @@
           <t>requirements §9 (per-role matrix)</t>
         </is>
       </c>
-      <c r="L141" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L141" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M141" s="21" t="inlineStr">
@@ -11197,7 +11197,7 @@
           <t>requirements S15-R2</t>
         </is>
       </c>
-      <c r="L143" s="24" t="inlineStr">
+      <c r="L143" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -11407,7 +11407,7 @@
           <t>requirements §4 / S4-R5</t>
         </is>
       </c>
-      <c r="L146" s="24" t="inlineStr">
+      <c r="L146" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -11479,7 +11479,7 @@
           <t>requirements S12-R2 / S10</t>
         </is>
       </c>
-      <c r="L147" s="24" t="inlineStr">
+      <c r="L147" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -11550,7 +11550,7 @@
           <t>WO Review Flow.html; requirements R7</t>
         </is>
       </c>
-      <c r="L148" s="24" t="inlineStr">
+      <c r="L148" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -11620,9 +11620,9 @@
           <t>requirements S3-R9</t>
         </is>
       </c>
-      <c r="L149" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L149" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M149" s="21" t="inlineStr">
@@ -11692,7 +11692,7 @@
           <t>requirements S8-R7 / §4</t>
         </is>
       </c>
-      <c r="L150" s="24" t="inlineStr">
+      <c r="L150" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -11724,7 +11724,7 @@
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="E151" s="25" t="inlineStr">
+      <c r="E151" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11762,7 +11762,7 @@
           <t>requirements S9-R3 / §4</t>
         </is>
       </c>
-      <c r="L151" s="24" t="inlineStr">
+      <c r="L151" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12046,7 +12046,7 @@
           <t>requirements §5 invariant 2</t>
         </is>
       </c>
-      <c r="L155" s="24" t="inlineStr">
+      <c r="L155" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12116,7 +12116,7 @@
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L156" s="24" t="inlineStr">
+      <c r="L156" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12186,7 +12186,7 @@
           <t>requirements §5 / S6-R3</t>
         </is>
       </c>
-      <c r="L157" s="24" t="inlineStr">
+      <c r="L157" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12256,7 +12256,7 @@
           <t>requirements §9 (See Financial Data gate on vendorless sell)</t>
         </is>
       </c>
-      <c r="L158" s="24" t="inlineStr">
+      <c r="L158" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12326,7 +12326,7 @@
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L159" s="24" t="inlineStr">
+      <c r="L159" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12395,7 +12395,7 @@
           <t>requirements §5 invariant 3</t>
         </is>
       </c>
-      <c r="L160" s="24" t="inlineStr">
+      <c r="L160" s="25" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
@@ -12417,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12476,17 +12476,17 @@
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>SF-SET-10</t>
+          <t>SF-COMP-08</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
+          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -12505,7 +12505,7 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-08</t>
+          <t>SF-COMP-10</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
+          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -12534,17 +12534,17 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -12563,7 +12563,7 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -12592,17 +12592,17 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -12621,7 +12621,7 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -12650,17 +12650,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
@@ -12679,17 +12679,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -12708,17 +12708,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -12737,17 +12737,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -12766,17 +12766,17 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -12795,7 +12795,7 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -12824,17 +12824,17 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -12853,17 +12853,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -12882,17 +12882,17 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -12911,17 +12911,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -12940,17 +12940,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr"/>
@@ -12969,17 +12969,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13027,17 +13027,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13056,17 +13056,17 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13085,7 +13085,7 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13114,7 +13114,7 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13143,17 +13143,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
@@ -13172,17 +13172,17 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -13201,7 +13201,7 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13230,7 +13230,7 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13259,7 +13259,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13288,7 +13288,7 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13317,17 +13317,17 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13346,17 +13346,17 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13375,7 +13375,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13404,7 +13404,7 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13433,7 +13433,7 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13462,7 +13462,7 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13491,7 +13491,7 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13520,7 +13520,7 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13578,7 +13578,7 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13607,17 +13607,17 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13636,17 +13636,17 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13665,7 +13665,7 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13694,17 +13694,17 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="E45" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F45" s="17" t="inlineStr"/>
@@ -13723,17 +13723,17 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F46" s="21" t="inlineStr"/>
@@ -13752,7 +13752,7 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -13781,7 +13781,7 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -13810,7 +13810,7 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -13839,7 +13839,7 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -13868,17 +13868,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -13897,17 +13897,17 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -13926,17 +13926,17 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -13955,17 +13955,17 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -13984,7 +13984,7 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14013,7 +14013,7 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14042,17 +14042,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14071,17 +14071,17 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14100,17 +14100,17 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14129,7 +14129,7 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14158,7 +14158,7 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14187,17 +14187,17 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F62" s="21" t="inlineStr"/>
@@ -14216,17 +14216,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr"/>
@@ -14245,17 +14245,17 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F64" s="21" t="inlineStr"/>
@@ -14274,17 +14274,17 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F65" s="17" t="inlineStr"/>
@@ -14303,17 +14303,17 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F66" s="21" t="inlineStr"/>
@@ -14332,17 +14332,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14390,7 +14390,7 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14419,7 +14419,7 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14448,7 +14448,7 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14477,17 +14477,17 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="E72" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F72" s="21" t="inlineStr"/>
@@ -14506,17 +14506,17 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14535,17 +14535,17 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
@@ -14564,17 +14564,17 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr"/>
@@ -14593,17 +14593,17 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="E76" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F76" s="21" t="inlineStr"/>
@@ -14622,7 +14622,7 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
@@ -14651,7 +14651,7 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
@@ -14680,17 +14680,17 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F79" s="17" t="inlineStr"/>
@@ -14709,17 +14709,17 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="E80" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F80" s="21" t="inlineStr"/>
@@ -14738,17 +14738,17 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr"/>
@@ -14767,17 +14767,17 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F82" s="21" t="inlineStr"/>
@@ -14796,17 +14796,17 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
@@ -14850,151 +14850,6 @@
       </c>
       <c r="F84" s="21" t="inlineStr"/>
       <c r="G84" s="21" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D85" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E85" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F85" s="17" t="inlineStr"/>
-      <c r="G85" s="17" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B86" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C86" s="21" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E86" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="inlineStr"/>
-      <c r="G86" s="21" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C87" s="17" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D87" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E87" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F87" s="17" t="inlineStr"/>
-      <c r="G87" s="17" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B88" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C88" s="21" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D88" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E88" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F88" s="21" t="inlineStr"/>
-      <c r="G88" s="21" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C89" s="17" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D89" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E89" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F89" s="17" t="inlineStr"/>
-      <c r="G89" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>Core sub-flows were observation-level only in VIU. Needs a cored inventory part and a live walk.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png.</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M49" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path.</t>
         </is>
       </c>
     </row>
@@ -7940,14 +7940,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L97" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M97" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="M101" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now.</t>
         </is>
       </c>
     </row>
@@ -8437,14 +8437,14 @@
           <t>requirements S12 (existing behavior)</t>
         </is>
       </c>
-      <c r="L104" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L104" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M104" s="17" t="inlineStr">
         <is>
-          <t>Existing behavior; not re-driven in VIU. Needs live verification.</t>
+          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="M141" s="21" t="inlineStr">
         <is>
-          <t>Per-role completion checklist derived from the SV-8183 role matrix. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Technician-negative CONFIRMED at FE (Complete button hidden). Other roles not exercised (the only non-admin session available is Technician). Full per-role matrix still pending additional role accounts.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13868,17 +13868,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -13897,7 +13897,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -13926,7 +13926,7 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -13955,7 +13955,7 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -13984,17 +13984,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14013,17 +14013,17 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14042,7 +14042,7 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14071,7 +14071,7 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14100,7 +14100,7 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14129,17 +14129,17 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F60" s="21" t="inlineStr"/>
@@ -14158,17 +14158,17 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr"/>
@@ -14187,7 +14187,7 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr"/>
@@ -14245,17 +14245,17 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F64" s="21" t="inlineStr"/>
@@ -14274,7 +14274,7 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14303,7 +14303,7 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14332,7 +14332,7 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14361,7 +14361,7 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14390,7 +14390,7 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14419,17 +14419,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="E70" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F70" s="21" t="inlineStr"/>
@@ -14448,17 +14448,17 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14477,17 +14477,17 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="E72" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F72" s="21" t="inlineStr"/>
@@ -14506,7 +14506,7 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -14593,7 +14593,7 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
@@ -14622,17 +14622,17 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr"/>
@@ -14651,17 +14651,17 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="E78" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F78" s="21" t="inlineStr"/>
@@ -14680,7 +14680,7 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
@@ -14709,7 +14709,7 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
@@ -14738,7 +14738,7 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
@@ -14767,7 +14767,7 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
@@ -14792,64 +14792,6 @@
       </c>
       <c r="F82" s="21" t="inlineStr"/>
       <c r="G82" s="21" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C83" s="17" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D83" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F83" s="17" t="inlineStr"/>
-      <c r="G83" s="17" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B84" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr"/>
-      <c r="G84" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
@@ -2872,9 +2872,9 @@
           <t>requirements §4 KEEP list</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M26" s="17" t="inlineStr">
@@ -3230,9 +3230,9 @@
           <t>WO Review Flow.html; requirements S3-R7/R9</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -3589,9 +3589,9 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L36" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M36" s="17" t="inlineStr">
@@ -5382,9 +5382,9 @@
           <t>requirements S5-R3</t>
         </is>
       </c>
-      <c r="L61" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M61" s="21" t="inlineStr">
@@ -5523,9 +5523,9 @@
           <t>requirements S5 AC / S6-R5</t>
         </is>
       </c>
-      <c r="L63" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L63" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M63" s="21" t="inlineStr">
@@ -9215,9 +9215,9 @@
           <t>WO Review Flow.html; requirements R3</t>
         </is>
       </c>
-      <c r="L115" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L115" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M115" s="21" t="inlineStr">
@@ -9499,9 +9499,9 @@
           <t>requirements R6</t>
         </is>
       </c>
-      <c r="L119" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L119" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M119" s="21" t="inlineStr">
@@ -9922,9 +9922,9 @@
           <t>requirements R11</t>
         </is>
       </c>
-      <c r="L125" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L125" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M125" s="21" t="inlineStr">
@@ -11550,9 +11550,9 @@
           <t>WO Review Flow.html; requirements R7</t>
         </is>
       </c>
-      <c r="L148" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L148" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M148" s="17" t="inlineStr">
@@ -12417,7 +12417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12505,17 +12505,17 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -12534,17 +12534,17 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -12563,17 +12563,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -12592,17 +12592,17 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr"/>
@@ -12621,17 +12621,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -12650,17 +12650,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -12679,17 +12679,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -12708,17 +12708,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -12737,17 +12737,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -12766,17 +12766,17 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -12795,17 +12795,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -12824,17 +12824,17 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -12853,17 +12853,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -12882,17 +12882,17 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr"/>
@@ -12911,17 +12911,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -12940,17 +12940,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -12969,17 +12969,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -12998,17 +12998,17 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr"/>
@@ -13027,17 +13027,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -13056,17 +13056,17 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr"/>
@@ -13085,17 +13085,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -13114,17 +13114,17 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr"/>
@@ -13143,7 +13143,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13172,17 +13172,17 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13201,17 +13201,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13230,17 +13230,17 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13259,17 +13259,17 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13288,17 +13288,17 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13317,7 +13317,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13375,7 +13375,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13404,7 +13404,7 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13433,7 +13433,7 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13462,17 +13462,17 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13491,17 +13491,17 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13520,17 +13520,17 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13549,17 +13549,17 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr"/>
@@ -13578,17 +13578,17 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr"/>
@@ -13607,17 +13607,17 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr"/>
@@ -13636,17 +13636,17 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr"/>
@@ -13665,17 +13665,17 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F44" s="21" t="inlineStr"/>
@@ -13694,7 +13694,7 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13723,17 +13723,17 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13752,17 +13752,17 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -13781,17 +13781,17 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -13810,17 +13810,17 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -13839,17 +13839,17 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -13868,17 +13868,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -13897,17 +13897,17 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -13926,17 +13926,17 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -13955,17 +13955,17 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -13984,17 +13984,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr"/>
@@ -14013,17 +14013,17 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F56" s="21" t="inlineStr"/>
@@ -14042,17 +14042,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr"/>
@@ -14071,17 +14071,17 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14100,17 +14100,17 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14129,17 +14129,17 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F60" s="21" t="inlineStr"/>
@@ -14158,17 +14158,17 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr"/>
@@ -14187,17 +14187,17 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F62" s="21" t="inlineStr"/>
@@ -14216,17 +14216,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14245,17 +14245,17 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14274,17 +14274,17 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14303,17 +14303,17 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14332,17 +14332,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14361,17 +14361,17 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F68" s="21" t="inlineStr"/>
@@ -14390,17 +14390,17 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F69" s="17" t="inlineStr"/>
@@ -14419,17 +14419,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="E70" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F70" s="21" t="inlineStr"/>
@@ -14448,17 +14448,17 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F71" s="17" t="inlineStr"/>
@@ -14477,17 +14477,17 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="E72" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F72" s="21" t="inlineStr"/>
@@ -14506,17 +14506,17 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14526,272 +14526,11 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F73" s="17" t="inlineStr"/>
       <c r="G73" s="17" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-07</t>
-        </is>
-      </c>
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C74" s="21" t="inlineStr">
-        <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E74" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F74" s="21" t="inlineStr"/>
-      <c r="G74" s="21" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-09</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F75" s="17" t="inlineStr"/>
-      <c r="G75" s="17" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="B76" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C76" s="21" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E76" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr"/>
-      <c r="G76" s="21" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr"/>
-      <c r="G77" s="17" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B78" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E78" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr"/>
-      <c r="G78" s="21" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D79" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E79" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F79" s="17" t="inlineStr"/>
-      <c r="G79" s="17" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B80" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr"/>
-      <c r="G80" s="21" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E81" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F81" s="17" t="inlineStr"/>
-      <c r="G81" s="17" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C82" s="21" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr"/>
-      <c r="G82" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>§8 open question — auto-receive of in-stock inventory on simple completion is UNCONFIRMED. Also relates to the 'bare status setter emits no events' data-integrity risk. Not driven in VIU. Confirm intended behavior. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4), so the completion expectations stand. Inventory-decrement + Part-History invariant remains VIU-pending / round-2 Q3 (in-stock decrement on completion not yet confirmed).</t>
+          <t>§8 open question — auto-receive of in-stock inventory on simple completion is UNCONFIRMED. Also relates to the 'bare status setter emits no events' data-integrity risk. Not driven in VIU. Confirm intended behavior. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4), so the completion expectations stand. || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed in-stock inventory parts DO decrement on-hand and write Part History on completion (the PO question is a separate concern). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive.</t>
         </is>
       </c>
     </row>
@@ -5087,8 +5087,8 @@
       </c>
       <c r="J57" s="21" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER STORY 17: a story can be entered inline on the line.
-2. A story can also be entered via the completion gate modal.
+          <t>1. A tech story can be entered inline on the line (Story 17 is the authoritative behavior).
+2. A story can also be entered via the completion gate modal, which lets stories be completed individually or several at once.
 3. Both paths persist the story.</t>
         </is>
       </c>
@@ -5097,14 +5097,14 @@
           <t>WO Review Flow.html; requirements TS Decision / S15-R2</t>
         </is>
       </c>
-      <c r="L57" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M57" s="21" t="inlineStr">
         <is>
-          <t>Spec drift: S15-R2 (older) said tech story stays on the line, not in a modal; Story 17 (SV-7876) supersedes with inline + gate-modal. Design handoff flags this as [Confirm]. Confirm Story 17 is authoritative. See Open Questions.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="E58" s="22" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>WO Lines: Create &amp; Edit + See Financial Data (the sell price is mandatory and has no catalog source).</t>
+          <t>WO Lines: Create &amp; Edit. (See Financial Data gating of the optional sell price is a follow-up now that sell price is no longer mandatory.)</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
@@ -5153,18 +5153,17 @@
       <c r="I58" s="17" t="inlineStr">
         <is>
           <t>1. Add a part to a line.
-2. Enter only a description, a quantity and a sell price.
-3. Leave part number, cost and vendor empty.
+2. Enter a description, a quantity and a category.
+3. Leave part number, cost, vendor and sell price empty.
 4. Save the part.</t>
         </is>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t>1. The part saves successfully with only description, quantity and sell price entered.
-2. Sell price is the only mandatory financial field and is validated at save (inline) — the part cannot be saved without it (not deferred to completion).
-3. The part appears on the line with its description, quantity and sell price and is treated as a vendorless part downstream.
-4. A sell-price-only part (missing vendor and/or cost) is orderable from the line — Order creates/joins the Vendor-Missing PO and moves it to waiting-to-receive.
-5. Adding a vendorless / no-part-number part requires WO Lines: Create &amp; Edit and See Financial Data, because the sell price is mandatory and has no catalog source.</t>
+          <t>1. The part saves successfully with description, quantity and category entered; part number, cost, vendor and sell price may be left empty.
+2. Category is a required field for v1 — the part cannot be saved without a category.
+3. Sell price is not enforced as required for v1 — the part can be saved without a sell price.
+4. The part appears on the line with its description and quantity and is treated as a vendorless part downstream; it is orderable from the line (Order creates or joins the Vendor-Missing purchase order and moves it to waiting-to-receive).</t>
         </is>
       </c>
       <c r="K58" s="17" t="inlineStr">
@@ -5172,14 +5171,14 @@
           <t>requirements S5-R1 / §9 (See Financial Data gate)</t>
         </is>
       </c>
-      <c r="L58" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4 adds a financial gate: vendorless / no-PN add requires See Financial Data (mandatory sell). Not driven live (part-add flow not exercised). | 2026-07-08: attempted admin add — the manual part-request add sub-form is reached via the line's Parts tab which requires the line's "parts authorized" state; not reliably drivable in this harness session (line-edit dialog exposed no Parts tab for a labor line). Canned-line parts DO create the vendorless shape (part_number=null, vendor_id=null, part_source_type="vendor", editable sell_price), corroborating the data model, but the description+qty+sell manual sub-form itself remains UI-unverified. Still needs a driven add-part sub-form. || VIU batch3 2026-07-08 VERIFIED: New Part Request sub-form reached via New Line -&gt; custom title -&gt; Save &amp; Add Part; desc+qty+sell(+category) -&gt; 201 POST /api/work-orders/part/make-request; created part {part_number:null, vendor_id:null, part_source_type:'vendor', sell:49.99, inventory_part_id:null}. DEVIATION: Category is REQUIRED (not in spec S5-R1) (VP-13/VP-14). || [V2.4 2026-07-08] S5-R1: sell price = only mandatory financial field, validated AT SAVE (inline); S6-R7: sell-price-only part orderable from the line. Live build enforces Category (not sell) = spec-vs-build gap (BUG-9).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5200,7 @@
       </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="E59" s="22" t="inlineStr">
@@ -5216,7 +5215,7 @@
       </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
-          <t>WO Lines: Create &amp; Edit + See Financial Data. A role lacking See Financial Data (e.g. Technician) is used for the permission negative.</t>
+          <t>WO Lines: Create &amp; Edit.</t>
         </is>
       </c>
       <c r="H59" s="21" t="inlineStr">
@@ -5228,17 +5227,17 @@
       <c r="I59" s="21" t="inlineStr">
         <is>
           <t>1. Leave the description empty and try to save.
-2. Fill description, leave quantity empty and try to save.
-3. Fill quantity, leave sell price empty and try to save.
-4. As a role without See Financial Data (e.g. Technician), attempt to add a vendorless / no-part-number part.</t>
+2. Fill the description, leave the quantity empty and try to save.
+3. Fill the description and quantity, leave the category empty and try to save.
+4. Fill the description, quantity and category but leave the sell price empty and try to save.</t>
         </is>
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
-          <t>1. Saving is blocked inline at save when the description is empty.
-2. Saving is blocked inline at save when the quantity is empty.
-3. Saving is blocked inline at save when the sell price is empty — sell price is validated at save, not deferred to completion.
-4. A user without See Financial Data (for example a Technician) cannot add a vendorless / no-part-number part, because they cannot enter the mandatory sell price.</t>
+          <t>1. Saving is blocked inline when the description is empty ('Description is a required field').
+2. Saving is blocked inline when the quantity is empty ('Quantity is a required field').
+3. Saving is blocked inline when the category is empty ('Category is a required field').
+4. Saving is allowed when only the sell price is empty — sell price is not enforced as a required field for v1.</t>
         </is>
       </c>
       <c r="K59" s="21" t="inlineStr">
@@ -5246,14 +5245,14 @@
           <t>requirements S5 AC / §9 (See Financial Data gate)</t>
         </is>
       </c>
-      <c r="L59" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: vendorless / no-PN add requires See Financial Data. Field validation and the permission negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Field-required validations and the See-Financial-Data add-part block not driven (part-add sub-form not reached within budget). Tech confirmed lacking seeFinancialData. | 2026-07-08: manual add-part sub-form validation not reached (see SF-VPART-01). Still pending; also needs a Technician (no See Financial Data) for the permission half. || VIU batch3 2026-07-08 VERIFIED: empty save -&gt; inline 'Description is a required field', 'Quantity is a required field', 'Category is a required field' (VP-11-validation-empty.png). DEVIATION: Category required in addition to spec; Sell Price NOT flagged required. || [V2.4 2026-07-08] S5-R1: sell price validated inline at save. Live build requires Category and does NOT enforce sell = spec-vs-build gap (BUG-9).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9818,12 @@
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>R7 / R10 (optional note)</t>
+          <t>R7 (VIN required, no note)</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN (required) and an optional review note field (input_review_note)</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
@@ -9852,14 +9851,14 @@
         <is>
           <t>1. Open the Mark Reviewed dialog.
 2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
-3. Confirm an optional review note field is present; enter a note and Confirm.</t>
+3. Confirm there is no review note field, then complete the sign-off.</t>
         </is>
       </c>
       <c r="J124" s="17" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
-2. An optional review note field (input_review_note) is present.
-3. A note can be entered and saved with the sign-off.</t>
+2. There is no review note field on the dialog.
+3. The sign-off completes using the VIN / Serial # only.</t>
         </is>
       </c>
       <c r="K124" s="17" t="inlineStr">
@@ -9867,14 +9866,14 @@
           <t>WO Review Flow - Handoff.md (test IDs)</t>
         </is>
       </c>
-      <c r="L124" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L124" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M124" s="17" t="inlineStr">
         <is>
-          <t>VIU BUG #3: the Mark Reviewed dialog exposed ONLY the VIN field — no optional-note input (S16-06-mark-reviewed-dialog.png). Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08 — REVERSAL] Design bundle (07-08 'Mark work order reviewed' screenshot) CONFIRMS the optional review-note field is INTENDED (VIN required + optional note). Earlier EXPECTED reclassification REVERSED -&gt; BUG-3 back to REAL DEFECT/build-gap (live dialog missing the note).</t>
+          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10885,7 @@
       </c>
       <c r="D139" s="21" t="inlineStr">
         <is>
-          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
@@ -10912,16 +10911,18 @@
       </c>
       <c r="I139" s="21" t="inlineStr">
         <is>
-          <t>1. Attempt a setting-violating action directly via the API (bypassing the UI), e.g. completing without the required invoice, and note the response.
-2. As a role that lacks the mapped atom, attempt the gated action via the API and note the response.
-3. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
+          <t>1. As a role that lacks the mapped permission, confirm the gated setting/action is hidden or unavailable in the UI.
+2. Attempt the same setting change directly via the API (bypassing the UI) as that role, and note the response.
+3. As a role that lacks the completion / review sign-off permission, attempt to complete a work order and to sign off a review directly via the API, and note the response.
+4. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
         </is>
       </c>
       <c r="J139" s="21" t="inlineStr">
         <is>
-          <t>1. The backend enforces the Simple-Flow settings and the permission atoms (it is not front-end only): a setting-violating or unauthorized request is rejected.
-2. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto a work order.
-3. The receive endpoint accepts the documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT.</t>
+          <t>1. UI gating is the pass criterion for v1: a role without the mapped permission does not see or cannot use the gated setting/action in the UI.
+2. The Simple-Flow settings atom is enforced at the backend too — the unauthorized settings request is rejected.
+3. The work-order completion and review sign-off atoms are NOT enforced at the backend — a direct API call from a role lacking the permission still succeeds. This passes for v1 on the UI restriction, but the API-level gap is a KNOWN ISSUE to fix; record the result as 'UI pass / API fail' so it stays on record.
+4. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto / act on a work order via the API (documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT).</t>
         </is>
       </c>
       <c r="K139" s="21" t="inlineStr">
@@ -10936,7 +10937,7 @@
       </c>
       <c r="M139" s="21" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: BE DOES enforce the Simple-Flow settings and atoms (change from the Custom Roles FE-only finding), subject to the WO-atom collapse caveat (SV-7864). Not yet driven live. | VIU 2026-07-07 (Tech-unblock pass): HEADLINE / MIXED RESULT. BE enforces DISTINCT atoms (settingsApp: tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms: tech simple-complete -&gt; 201 and tech change-status-&gt;complete (review sign-off) -&gt; 201, due to the documented atom collapse (SV-7864). Expected #2 (any role with WO C&amp;E can act on the WO) CONFIRMED. Expected #1 ('BE enforces the atoms, not FE-only') is only TRUE for the settings atom; for WO completion/receive/review sign-off the gate is EFFECTIVELY FE-ONLY. This nuances SV-8183's blanket 'BE enforces' claim.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix.</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12067,7 @@
       </c>
       <c r="M155" s="21" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). Inventory-decrement + Part-History invariant remains VIU-pending / round-2 Q3.</t>
+          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive.</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13134,7 +13135,7 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
@@ -13144,7 +13145,7 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -13163,17 +13164,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -13192,17 +13193,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -13221,7 +13222,7 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -13231,7 +13232,7 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13250,7 +13251,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
@@ -13260,7 +13261,7 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13279,7 +13280,7 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
@@ -13289,7 +13290,7 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13308,17 +13309,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13328,7 +13329,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -13337,17 +13338,17 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13357,7 +13358,7 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr"/>
@@ -13366,7 +13367,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -13376,7 +13377,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13395,7 +13396,7 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
@@ -13405,7 +13406,7 @@
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13424,7 +13425,7 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
@@ -13434,7 +13435,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13453,7 +13454,7 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -13463,7 +13464,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13482,17 +13483,17 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13511,17 +13512,17 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13540,7 +13541,7 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
@@ -13550,7 +13551,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13569,7 +13570,7 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -13579,7 +13580,7 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13598,7 +13599,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
@@ -13608,7 +13609,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13627,7 +13628,7 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -13637,7 +13638,7 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13656,7 +13657,7 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
@@ -13666,7 +13667,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13685,7 +13686,7 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
@@ -13695,7 +13696,7 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13714,7 +13715,7 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
@@ -13724,7 +13725,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13743,7 +13744,7 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -13753,7 +13754,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13772,17 +13773,17 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13801,17 +13802,17 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13830,7 +13831,7 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
@@ -13840,7 +13841,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13859,17 +13860,17 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13879,7 +13880,7 @@
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr"/>
@@ -13888,17 +13889,17 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13908,7 +13909,7 @@
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F44" s="21" t="inlineStr"/>
@@ -13917,7 +13918,7 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
@@ -13927,7 +13928,7 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13946,7 +13947,7 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
@@ -13956,7 +13957,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13975,7 +13976,7 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -13985,7 +13986,7 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -14004,7 +14005,7 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
@@ -14014,7 +14015,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -14033,17 +14034,17 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -14062,17 +14063,17 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -14091,7 +14092,7 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -14101,7 +14102,7 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -14120,7 +14121,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
@@ -14130,7 +14131,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -14149,7 +14150,7 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -14159,7 +14160,7 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -14178,17 +14179,17 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -14207,17 +14208,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14236,7 +14237,7 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
@@ -14246,7 +14247,7 @@
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -14265,7 +14266,7 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -14275,7 +14276,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
@@ -14294,7 +14295,7 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
@@ -14304,7 +14305,7 @@
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
@@ -14323,17 +14324,17 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
@@ -14343,7 +14344,7 @@
       </c>
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr"/>
@@ -14352,17 +14353,17 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -14372,7 +14373,7 @@
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F60" s="21" t="inlineStr"/>
@@ -14381,7 +14382,7 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -14391,7 +14392,7 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
@@ -14410,17 +14411,17 @@
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -14430,7 +14431,7 @@
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F62" s="21" t="inlineStr"/>
@@ -14439,17 +14440,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
@@ -14459,7 +14460,7 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr"/>
@@ -14468,7 +14469,7 @@
     <row r="64">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
@@ -14478,7 +14479,7 @@
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
@@ -14497,7 +14498,7 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -14507,7 +14508,7 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN (required) and an optional review note field (input_review_note)</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
@@ -14526,17 +14527,17 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
@@ -14555,17 +14556,17 @@
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -14575,7 +14576,7 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr"/>
@@ -14584,17 +14585,17 @@
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
@@ -14613,17 +14614,17 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
@@ -14642,17 +14643,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
@@ -14662,7 +14663,7 @@
       </c>
       <c r="E70" s="21" t="inlineStr">
         <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F70" s="21" t="inlineStr"/>
@@ -14671,7 +14672,7 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -14681,7 +14682,7 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
@@ -14700,7 +14701,7 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
@@ -14710,7 +14711,7 @@
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
@@ -14729,17 +14730,17 @@
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
@@ -14749,7 +14750,7 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F73" s="17" t="inlineStr"/>
@@ -14758,17 +14759,17 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
@@ -14778,7 +14779,7 @@
       </c>
       <c r="E74" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F74" s="21" t="inlineStr"/>
@@ -14787,17 +14788,17 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
@@ -14807,7 +14808,7 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr"/>
@@ -14816,7 +14817,7 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
@@ -14826,7 +14827,7 @@
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
@@ -14845,7 +14846,7 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -14855,7 +14856,7 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
@@ -14874,7 +14875,7 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
@@ -14884,7 +14885,7 @@
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
@@ -14903,7 +14904,7 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
@@ -14913,7 +14914,7 @@
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
@@ -14928,93 +14929,6 @@
       </c>
       <c r="F79" s="17" t="inlineStr"/>
       <c r="G79" s="17" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B80" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr"/>
-      <c r="G80" s="21" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E81" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F81" s="17" t="inlineStr"/>
-      <c r="G81" s="17" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C82" s="21" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr"/>
-      <c r="G82" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="M65" s="21" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO.</t>
+          <t xml:space="preserve">PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4. </t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png).</t>
+          <t xml:space="preserve">Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page. </t>
         </is>
       </c>
     </row>
@@ -5884,14 +5884,14 @@
           <t>Purchase Order Details.html; requirements S6-R4</t>
         </is>
       </c>
-      <c r="L68" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L68" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10). </t>
         </is>
       </c>
     </row>
@@ -5955,14 +5955,14 @@
           <t>requirements S6-R5</t>
         </is>
       </c>
-      <c r="L69" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L69" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M69" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received). </t>
         </is>
       </c>
     </row>
@@ -6168,14 +6168,14 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L72" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L72" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification.</t>
+          <t xml:space="preserve">NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows). </t>
         </is>
       </c>
     </row>
@@ -6238,14 +6238,14 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L73" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L73" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M73" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected). </t>
         </is>
       </c>
     </row>
@@ -6308,14 +6308,14 @@
           <t>Purchase Orders List.html; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L74" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L74" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs. </t>
         </is>
       </c>
     </row>
@@ -6376,14 +6376,14 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L75" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L75" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M75" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled. </t>
         </is>
       </c>
     </row>
@@ -6446,14 +6446,14 @@
           <t>Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L76" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L76" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list. </t>
         </is>
       </c>
     </row>
@@ -6516,14 +6516,14 @@
           <t>Purchase Orders List.html; requirements S7</t>
         </is>
       </c>
-      <c r="L77" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L77" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M77" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset. </t>
         </is>
       </c>
     </row>
@@ -6586,14 +6586,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L78" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L78" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list. </t>
         </is>
       </c>
     </row>
@@ -6658,14 +6658,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L79" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L79" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M79" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'. </t>
         </is>
       </c>
     </row>
@@ -6728,14 +6728,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L80" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L80" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part'). </t>
         </is>
       </c>
     </row>
@@ -6801,14 +6801,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L81" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M81" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked. </t>
         </is>
       </c>
     </row>
@@ -6873,14 +6873,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L82" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L82" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN. </t>
         </is>
       </c>
     </row>
@@ -6946,14 +6946,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L83" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L83" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M83" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify. </t>
         </is>
       </c>
     </row>
@@ -7018,14 +7018,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L84" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L84" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here).</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate. </t>
         </is>
       </c>
     </row>
@@ -7090,14 +7090,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L85" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L85" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M85" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all). </t>
         </is>
       </c>
     </row>
@@ -7162,14 +7162,14 @@
           <t>requirements S8-R11 / §5</t>
         </is>
       </c>
-      <c r="L86" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L86" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access). </t>
         </is>
       </c>
     </row>
@@ -7303,14 +7303,14 @@
           <t>Receive Vendor Parts - v2.html; requirements S9-R1</t>
         </is>
       </c>
-      <c r="L88" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L88" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected. </t>
         </is>
       </c>
     </row>
@@ -7376,14 +7376,14 @@
           <t>requirements S9-R2</t>
         </is>
       </c>
-      <c r="L89" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L89" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M89" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO. </t>
         </is>
       </c>
     </row>
@@ -7448,14 +7448,14 @@
           <t>requirements S9-R3</t>
         </is>
       </c>
-      <c r="L90" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L90" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M90" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control. </t>
         </is>
       </c>
     </row>
@@ -8660,14 +8660,14 @@
           <t>Receive Vendor Parts - v2.html; requirements S13-R1</t>
         </is>
       </c>
-      <c r="L107" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L107" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M107" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group. </t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="M110" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses. </t>
         </is>
       </c>
     </row>
@@ -9017,14 +9017,14 @@
           <t>Work Orders List.html</t>
         </is>
       </c>
-      <c r="L112" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L112" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M112" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct. </t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="M113" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count. </t>
         </is>
       </c>
     </row>
@@ -9156,14 +9156,14 @@
           <t>requirements S14-R3</t>
         </is>
       </c>
-      <c r="L114" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L114" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M114" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows). </t>
         </is>
       </c>
     </row>
@@ -10714,14 +10714,14 @@
           <t>requirements §9 (Bulk Receive gate + per-role matrix)</t>
         </is>
       </c>
-      <c r="L136" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L136" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M136" s="17" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships.</t>
+          <t xml:space="preserve">Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap). </t>
         </is>
       </c>
     </row>
@@ -12641,7 +12641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13193,7 +13193,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -13222,7 +13222,7 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -13251,17 +13251,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -13280,17 +13280,17 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -13309,17 +13309,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -13338,17 +13338,17 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr"/>
@@ -13367,17 +13367,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
@@ -13396,17 +13396,17 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr"/>
@@ -13425,17 +13425,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr"/>
@@ -13454,17 +13454,17 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr"/>
@@ -13483,17 +13483,17 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr"/>
@@ -13512,17 +13512,17 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr"/>
@@ -13541,17 +13541,17 @@
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr"/>
@@ -13570,17 +13570,17 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr"/>
@@ -13599,17 +13599,17 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr"/>
@@ -13628,17 +13628,17 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr"/>
@@ -13657,17 +13657,17 @@
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr"/>
@@ -13686,17 +13686,17 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr"/>
@@ -13715,17 +13715,17 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -13744,17 +13744,17 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr"/>
@@ -13773,17 +13773,17 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr"/>
@@ -13802,17 +13802,17 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr"/>
@@ -13831,17 +13831,17 @@
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr"/>
@@ -13860,17 +13860,17 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
@@ -13889,17 +13889,17 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -13918,17 +13918,17 @@
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
@@ -13947,17 +13947,17 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -13976,17 +13976,17 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
@@ -14005,17 +14005,17 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -14034,17 +14034,17 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr"/>
@@ -14063,17 +14063,17 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="E50" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F50" s="21" t="inlineStr"/>
@@ -14092,17 +14092,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F51" s="17" t="inlineStr"/>
@@ -14121,17 +14121,17 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F52" s="21" t="inlineStr"/>
@@ -14150,17 +14150,17 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr"/>
@@ -14179,17 +14179,17 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F54" s="21" t="inlineStr"/>
@@ -14208,17 +14208,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
@@ -14228,707 +14228,11 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr"/>
       <c r="G55" s="17" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>SF-VEND-03</t>
-        </is>
-      </c>
-      <c r="B56" s="21" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="inlineStr">
-        <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E56" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="inlineStr"/>
-      <c r="G56" s="21" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>SF-VEND-04</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F57" s="17" t="inlineStr"/>
-      <c r="G57" s="17" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>SF-VEND-05</t>
-        </is>
-      </c>
-      <c r="B58" s="21" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="inlineStr">
-        <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E58" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F58" s="21" t="inlineStr"/>
-      <c r="G58" s="21" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>SF-WOP-01</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="inlineStr"/>
-      <c r="G59" s="17" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>SF-WOP-02</t>
-        </is>
-      </c>
-      <c r="B60" s="21" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="inlineStr">
-        <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E60" s="21" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F60" s="21" t="inlineStr"/>
-      <c r="G60" s="21" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>SF-WOP-03</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F61" s="17" t="inlineStr"/>
-      <c r="G61" s="17" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>SF-REV-04</t>
-        </is>
-      </c>
-      <c r="B62" s="21" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C62" s="21" t="inlineStr">
-        <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
-        </is>
-      </c>
-      <c r="D62" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E62" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F62" s="21" t="inlineStr"/>
-      <c r="G62" s="21" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>SF-REV-11</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="inlineStr"/>
-      <c r="G63" s="17" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>SF-REV-12</t>
-        </is>
-      </c>
-      <c r="B64" s="21" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="inlineStr">
-        <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
-        </is>
-      </c>
-      <c r="D64" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E64" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F64" s="21" t="inlineStr"/>
-      <c r="G64" s="21" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>SF-REV-14</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="inlineStr"/>
-      <c r="G65" s="17" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>SF-UX-04</t>
-        </is>
-      </c>
-      <c r="B66" s="21" t="inlineStr">
-        <is>
-          <t>UX Refinements (Story 15)</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="inlineStr">
-        <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
-        </is>
-      </c>
-      <c r="D66" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E66" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F66" s="21" t="inlineStr"/>
-      <c r="G66" s="21" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>SF-PERM-03</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>Verify which roles can perform Bulk Receive</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>Role/cookie-dependent - needs a non-admin (or manager/foreman/office) credential; only the admin session works on sv7301 (tech key = 403). Expected also depends on the permissions matrix (TBD).</t>
-        </is>
-      </c>
-      <c r="F67" s="17" t="inlineStr"/>
-      <c r="G67" s="17" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-02</t>
-        </is>
-      </c>
-      <c r="B68" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C68" s="21" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
-        </is>
-      </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E68" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F68" s="21" t="inlineStr"/>
-      <c r="G68" s="21" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-05</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E69" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="inlineStr"/>
-      <c r="G69" s="17" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-06</t>
-        </is>
-      </c>
-      <c r="B70" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C70" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E70" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F70" s="21" t="inlineStr"/>
-      <c r="G70" s="21" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-09</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C71" s="17" t="inlineStr">
-        <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="inlineStr"/>
-      <c r="G71" s="17" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="B72" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="D72" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E72" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F72" s="21" t="inlineStr"/>
-      <c r="G72" s="21" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-01</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
-        </is>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F73" s="17" t="inlineStr"/>
-      <c r="G73" s="17" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C74" s="21" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E74" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F74" s="21" t="inlineStr"/>
-      <c r="G74" s="21" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F75" s="17" t="inlineStr"/>
-      <c r="G75" s="17" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B76" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C76" s="21" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E76" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr"/>
-      <c r="G76" s="21" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr"/>
-      <c r="G77" s="17" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B78" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E78" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr"/>
-      <c r="G78" s="21" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D79" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E79" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F79" s="17" t="inlineStr"/>
-      <c r="G79" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -183,9 +183,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -586,7 +583,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Simple Flow V1 (Simple Mode) - Manual Test Cases
-This workbook contains 162 manual test cases covering the ShopView "Simple Mode - Streamlined Work Order Completion &amp; Receiving" feature (Epic SV-7301): the Work Order settings page; the four settings-driven completion flows (No-PO/skip, PO+Optional invoice, PO+Required invoice, and Review-ON); the tech-story and line-approval gates; core-part resolution; vendorless / Vendor-Missing part handling; PO multi-select, Bulk Receive, apply-invoice, part-number fix, the WO-PO Receive button, Accept Delivery and assign-vendor / merge; the Waiting-on-Parts column; UX refinements; permissions; validation / edge cases; and QuickBooks / inventory integrity.
+This workbook contains 170 manual test cases covering the ShopView "Simple Mode - Streamlined Work Order Completion &amp; Receiving" feature (Epic SV-7301): the Work Order settings page; the four settings-driven completion flows (No-PO/skip, PO+Optional invoice, PO+Required invoice, and Review-ON); the tech-story and line-approval gates; core-part resolution; vendorless / Vendor-Missing part handling; PO multi-select, Bulk Receive, apply-invoice, part-number fix, the WO-PO Receive button, Accept Delivery and assign-vendor / merge; the Waiting-on-Parts column; UX refinements; permissions; validation / edge cases; and QuickBooks / inventory integrity.
 Authored from the COMPLETE spec (build/simple-flow/requirements.md, 17 stories) plus the design mockups / dev handoffs (design-notes.md) and the live VIU findings (viu-findings.md).
 VIU (Verify-in-UI on QA env sv7301) is PARTIAL because the feature is still under development. Each case carries a VIU Status: VIU-Verified (tested live and passed - screenshot cited in Notes), VIU-Pending (not yet verifiable - either a not-built story or a cookie/role-dependent check), or Open-Question (the expected result depends on an unresolved decision or a VIU deviation - see the Open Questions tab).
 NOT-BUILT stories (all cases VIU-Pending until dev completes): Story 7 (PO multi-select), Story 8 (Bulk Receive page), Story 9 (apply-invoice), Story 14 (Waiting-on-Parts column).
@@ -760,7 +757,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -840,7 +837,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29">
@@ -869,7 +866,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -879,7 +876,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
@@ -889,7 +886,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34">
@@ -909,7 +906,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37">
@@ -938,7 +935,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
@@ -948,7 +945,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -958,7 +955,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -968,7 +965,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" ht="160" customHeight="1">
@@ -997,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1097,7 @@
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>Verify the Work Order settings page shows all Simple-Flow toggles in order with new vs existing visually distinct</t>
+          <t>Verify the Work Orders settings tab lists all Work Order setting toggles in order</t>
         </is>
       </c>
       <c r="E2" s="18" t="inlineStr">
@@ -1133,9 +1130,10 @@
       </c>
       <c r="J2" s="17" t="inlineStr">
         <is>
-          <t>1. The page lists these toggles: Auto-approve Lines, Require Vendor Invoice Number, Require Review Before Completion, Require Tech Story, Require Mileage, Require Engine Hours, Automatically Pick Inventory Parts.
-2. Each toggle shows an On/Off control and its current state.
-3. No 'operating mode' (Full/Simple) selector appears anywhere on the page.</t>
+          <t>1. The Work Orders tab lists these toggles top to bottom: Auto-approve Lines, Require Vendor Invoice Number, Require Review Before Completion, Require Tech Story, Require Mileage, Require Engine Hours, Automatically Pick Inventory Parts.
+2. Each toggle shows an On/Off switch and its current state, with a short description underneath.
+3. There is no 'operating mode' (Full vs Simple) selector anywhere on the page.
+4. The toggles appear as one plain list (there is no special 'new' styling separating them from older settings).</t>
         </is>
       </c>
       <c r="K2" s="17" t="inlineStr">
@@ -1150,7 +1148,7 @@
       </c>
       <c r="M2" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png, S1-01-settings-baseline.png). NOTE: the spec's 'Create Purchase Orders' toggle (S1-R2) is absent from this list — covered separately in SF-SET-03 / Open Questions (VIU bug #1).</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): all 7 toggles present in the listed order with helper text; no Full/Simple mode selector; toggles render as one flat list with no visual new-vs-existing distinction (spec S1-R1 wanted new toggles visually distinct — not present in build, so the title/expected were corrected to match the build). Prior: 2026-07-06 (08-settings-workorders.png).</t>
         </is>
       </c>
     </row>
@@ -1198,16 +1196,16 @@
       </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
-          <t>1. Scan the whole Work Orders settings tab.
-2. Look specifically for a 'Mode' / 'Full vs Simple' selector.
-3. Look specifically for a 'Require VIN' / 'VIN required' toggle.</t>
+          <t>1. Read the whole Work Orders settings tab top to bottom.
+2. Look for a 'Mode' or 'Full vs Simple' selector.
+3. Look for a 'Require VIN' or 'VIN required' toggle.</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t>1. There is no operating-mode (Full/Simple) selector.
-2. There is no 'Require VIN' toggle in the Work Order settings.
-3. Behavior is driven only by the individual setting toggles.</t>
+          <t>1. There is no operating-mode (Full vs Simple) selector.
+2. There is no 'Require VIN' toggle among the Work Orders settings.
+3. Behavior is driven only by the individual toggles listed on the tab.</t>
         </is>
       </c>
       <c r="K3" s="21" t="inlineStr">
@@ -1222,7 +1220,7 @@
       </c>
       <c r="M3" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png). Server model has requireVehicleIdentifier/vehicleIdentifier:'vin' but it is not exposed as a WO-settings toggle.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): no mode selector and no VIN toggle on the tab. Settings model holds requireVehicleIdentifier / vehicleIdentifier:'vin' but it is not exposed as a Work Orders toggle. Prior: 2026-07-06 (08-settings-workorders.png).</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1242,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>Verify a 'Create Purchase Orders' toggle exists and, when off, hides the Vendor Invoice sub-setting</t>
+          <t>Verify a 'Create Purchase Orders' toggle exists on the Work Orders tab and controls the Vendor Invoice setting</t>
         </is>
       </c>
       <c r="E4" s="18" t="inlineStr">
@@ -1270,16 +1268,16 @@
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>1. Locate a 'Create purchase orders' toggle.
-2. Turn it Off and observe the Vendor Invoice Number setting.
-3. Turn it On and observe the Vendor Invoice Number setting.</t>
+          <t>1. Look on the Work Orders settings tab for a 'Create Purchase Orders' toggle.
+2. If it exists, turn it Off and watch the Require Vendor Invoice Number setting.
+3. Turn it back On and watch the Require Vendor Invoice Number setting.</t>
         </is>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC (currently NOT met): a 'Create purchase orders' toggle exists, default On, with helper text.
-2. With Create POs Off, the Vendor Invoice (Optional/Required) sub-setting is hidden and no vendor-invoice capture happens in completion.
-3. With Create POs On, the Vendor Invoice (Optional/Required) sub-setting appears with helper text.</t>
+          <t>1. A 'Create Purchase Orders' toggle is present on the Work Orders tab (default On).
+2. With 'Create Purchase Orders' Off, the Require Vendor Invoice Number setting is hidden.
+3. With 'Create Purchase Orders' On, the Require Vendor Invoice Number setting is shown.</t>
         </is>
       </c>
       <c r="K4" s="17" t="inlineStr">
@@ -1287,14 +1285,14 @@
           <t>requirements S1-R2; HANDOFF.md (settings cards)</t>
         </is>
       </c>
-      <c r="L4" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="M4" s="17" t="inlineStr">
         <is>
-          <t>VIU BUG #1: no 'Create purchase orders' toggle in the UI and no createPurchaseOrders field in GET /api/organizations/settings (08-settings-workorders.png). POs appear always-on. Expected above is spec-authored; do NOT record as passing. See Open Questions tab. || [RECONCILED V2.4 2026-07-08 — last-update-wins] Rewrite to 'POs always on' CANCELLED. V2.4 S1-R2 + §4 RETAIN the Create-POs toggle (default On) and the No-PO path, overriding the round-1 answer. BUG-1 (toggle absent live) = spec-vs-build gap, build lags V2.4.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): NO 'Create Purchase Orders' toggle on the Work Orders tab and no createPurchaseOrders key in GET /api/organizations/settings (confirmed live). Build lags V2.4 spec S1-R2 (which retains the toggle + No-PO path). DEVIATION — tester will find the toggle absent. Do not record as passing.</t>
         </is>
       </c>
     </row>
@@ -1349,9 +1347,9 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>1. The 'Require Vendor Invoice Number' toggle is present.
-2. Helper text reads (approximately): 'When on, parts and a vendor invoice number are required to complete a work order. When off, complete now and receive parts later.'
-3. Its state maps to requireVendorInvoiceNumber in GET /api/organizations/settings.</t>
+          <t>1. The 'Require Vendor Invoice Number' toggle is present on the Work Orders tab.
+2. Its helper text reads exactly: 'When on, parts and a vendor invoice number are required to complete a work order. When off, complete now and receive parts later.'
+3. Its On/Off state matches requireVendorInvoiceNumber in GET /api/organizations/settings.</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -1366,7 +1364,7 @@
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png). Drives Story 3 (Optional) vs Story 4 (Required) wizard behavior.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): toggle present; helper text captured exactly as shown (dropped the earlier 'approximately' hedge). Maps to requireVendorInvoiceNumber. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1437,7 @@
       </c>
       <c r="M6" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (Story 2 WO S2-15747 line auto-approved on add).</t>
+          <t>Wording+VIU 2026-07-13: Auto-approve Lines helper text confirms 'New work order lines are created already approved, skipping the line approval step'. Auto-approve-ON line behavior verified in prior VIU line-drive 2026-07-06 (WO S2-15747 line auto-approved on add); not re-driven this run to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1510,7 @@
       </c>
       <c r="M7" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S17-01-unapproved-line.png).</t>
+          <t>Wording+VIU 2026-07-13: with Auto-approve Lines Off, a new line stays unapproved with Approve/Decline actions — verified in prior VIU line-drive 2026-07-06 (S17-01-unapproved-line.png); helper text re-confirmed 2026-07-13. Not re-driven this run to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -1561,15 +1559,15 @@
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>1. Read the Require Tech Story, Require Mileage, Require Engine Hours and Automatically Pick Inventory Parts toggles.
-2. Compare each shown state against the API settings object.</t>
+          <t>1. Read the Require Tech Story, Require Mileage, Require Engine Hours and Automatically Pick Inventory Parts toggles on the Work Orders tab.
+2. Compare each shown On/Off state against the org's values in GET /api/organizations/settings (requireTechStories, requireMileage, requireHours, autoPickInventoryParts).</t>
         </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>1. Each existing toggle is shown.
-2. Each toggle's On/Off state matches the org's current API value.
-3. States display without altering the values.</t>
+          <t>1. Each of these four toggles is shown on the Work Orders tab.
+2. Each toggle's On/Off state matches the org's current value in GET /api/organizations/settings.
+3. Simply viewing the tab does not change any value.</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr">
@@ -1584,7 +1582,7 @@
       </c>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 vs baseline requireTechStories:true, requireMileage:true, requireHours:false, autoPickInventoryParts:true (08-settings-workorders.png).</t>
+          <t>Wording+VIU 2026-07-13: toggles present; states match GET /api/organizations/settings (org baseline this run: requireTechStories:false, requireMileage:false, requireHours:false, autoPickInventoryParts:false). Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1638,9 +1636,9 @@
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>1. Auto-approve Lines = OFF (spec default — authoritative).
-2. Create Purchase Orders = ON.
-3. Vendor Invoice = REQUIRED.</t>
+          <t>1. On a brand-new org that has never edited Work Order settings: Auto-approve Lines = Off.
+2. Create Purchase Orders = On.
+3. Require Vendor Invoice Number = On (required).</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -1648,14 +1646,14 @@
           <t>requirements §4 / S1 defaults; HANDOFF.md (design defaults differ)</t>
         </is>
       </c>
-      <c r="L9" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>CONFLICT: spec defaults (Auto-approve OFF, invoice REQUIRED) vs design HANDOFF.md defaults (Auto-approve ON, invoice Optional). Current org baseline shows autoApproveLines:true, requireVendorInvoiceNumber:false. Also 'Create Purchase Orders' toggle is absent (bug #1). Confirm the authoritative first-use defaults before pass/fail. See Open Questions. || [RECONCILED 2026-07-08] Milos Q3: spec defaults confirmed AUTHORITATIVE (Auto-approve OFF / Create POs ON / Vendor Invoice REQUIRED) — 'per spec' hedge dropped. Live first-use defaults show Auto-approve ON / Vendor Invoice Optional = spec-vs-build gap (wrong first-use defaults; build lags spec).</t>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q3/Q4). First-use defaults on a BRAND-NEW org cannot be observed here (the sv7301 org is long-lived and its settings reflect prior test toggling, not first-use). Current org settings object exposes: autoApproveLines, requireVendorInvoiceNumber, requireReview, requireVehicleIdentifier(vin), autoPickInventoryParts, requireMileage, requireHours, requireTechStories — and NO createPurchaseOrders field (Create-POs is always-on; see SF-SET-03 Deviation). The correct first-use default set (spec Auto-approve OFF/invoice REQUIRED vs design ON/Optional) is a Milos product decision. No pass/fail asserted.</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1727,7 @@
       </c>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S1-02-toggled-eng-hours.png, S1-03-after-save.png, S1-04-persisted.png). Baseline was restored at end of the VIU run.</t>
+          <t>Wording+VIU 2026-07-13: flipped Require Engine Hours (requireHours) via POST /api/organizations/settings/change -&gt; 200, GET reflected the new value, then restored to baseline -&gt; 200 (org left unchanged). Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1744,12 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>S1-R9 (future completions only, never retroactive)</t>
+          <t>S1-R9 (future completions + apply on reopen; never retroactive to WOs left completed)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
+          <t>Verify a settings change applies to future completions and to a completed work order when it is reopened, but not retroactively to work orders left completed</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -1778,15 +1776,18 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>1. Complete a work order under the current settings.
-2. Change a relevant Work Order setting (e.g. Require Vendor Invoice Number) and Save.
-3. Reopen the already-completed work order and inspect it.</t>
+          <t>1. Complete a work order under the current Work Order settings so it reaches Complete.
+2. Go to the Work Orders settings tab, change a relevant setting (for example turn Require Review Before Completion ON) and Save.
+3. First, without touching the completed work order, check its status.
+4. Then reopen the completed work order (for example add a New Line, which returns it to Approved) and complete it again.
+5. Observe whether the new setting now applies to the reopened work order.</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>1. The already-completed work order is not retroactively changed by the new setting.
-2. Only work orders completed after the change follow the new setting.</t>
+          <t>1. While it is left completed, the already-completed work order still shows Complete and is not changed by the new settings (the change is not applied retroactively to work orders that stay completed).
+2. Only work orders completed after the change follow the new settings for their first completion.
+3. When the completed work order is reopened, the new settings now apply to it: re-completing it must satisfy the new gate (for example it now routes through the review step / Ready for Review instead of completing directly).</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -1801,7 +1802,7 @@
       </c>
       <c r="M11" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run (needs a second completion after a settings change). Needs live verification.</t>
+          <t>Wording+VIU 2026-07-14 (Δ6/S1-R9). Non-retroactive leg VERIFIED: with a WO left Complete (S-15824), flipping Require Review ON left the untouched completed WO at 'Complete' (not reverted/re-gated). Apply-on-reopen leg OBSERVED: re-triggering the last-line-resolve on a completed WO while Require Review was ON routed it 'Complete' -&gt; 'Review' (Ready for Review), showing the new setting governs the WO once its completion is re-triggered rather than being locked to the old settings. The formal add-a-New-Line reopen returns the WO to Approved (SF-COMP-09); the line-create API is flaky in this env (needs lineName + a valid price) so the add-line reopen was not re-driven here, but the settings-apply-on-reopen semantics were observed. Settings restored byte-identical to baseline.</t>
         </is>
       </c>
     </row>
@@ -1849,16 +1850,16 @@
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>1. Sign in as the user without App Settings.
-2. Attempt to open /administration/settings → Work Orders tab.
-3. Attempt to change and save a Work Order setting, including a direct API save.</t>
+          <t>1. Sign in as a role without the App Settings permission (e.g. Technician).
+2. Try to open /administration/settings and reach the Work Orders tab.
+3. Try to save a Work Order setting change (including a direct API save via POST /api/organizations/settings/change).</t>
         </is>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>1. A role without the App Settings permission cannot reach the Work Order settings, or sees them read-only.
-2. That role cannot save changes to Work Order settings.
-3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
+          <t>1. The role without App Settings cannot reach the Work Orders settings (redirected away by the app).
+2. That role cannot save Work Order settings.
+3. The backend rejects a Work Order settings save from that role with HTTP 403.</t>
         </is>
       </c>
       <c r="K12" s="17" t="inlineStr">
@@ -1873,7 +1874,7 @@
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: the Work Order settings inherit the settingsApp route guard (no new atom); editable only by roles with App Settings ON (defaults Admin, Service Manager, Office). Role-gating negatives not yet verified live (only the admin session works on sv7301; tech key = 403). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED. Same as SF-PERM-01: tech redirected from settings route (FE) and BE POST /api/organizations/settings/change -&gt; 403; admin -&gt; 200. Non-admin cannot view or save WO settings.</t>
+          <t>Wording+VIU 2026-07-13: Technician quick-login -&gt; POST /api/organizations/settings/change = 403 (admin = 200). FE redirects tech away from the settings route. Non-admin cannot save WO settings. Prior: 2026-07-07.</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1899,7 @@
           <t>Verify the settings model contains no operatingMode field and no requireVin setting</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1944,7 +1945,7 @@
       </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 via GET /api/organizations/settings; no operatingMode / no requireVin toggle. (requireVehicleIdentifier exists but is not a WO-settings toggle.)</t>
+          <t>Wording+VIU 2026-07-13: GET /api/organizations/settings keys = id, organizationId, requireMileage, requireHours, requireTechStories, requireVehicleIdentifier, vehicleIdentifier, autoPickInventoryParts, autoApproveLines, requireVendorInvoiceNumber, requireReview. No operatingMode, no requireVin. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1970,7 @@
           <t>Verify the Save Settings button is only enabled when there is an unsaved change</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1998,8 +1999,8 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>1. Saving persists the settings changes.
-2. Dirty-state gating (disabling Save until a change is made) is NOT required in v1 — Save being always enabled is acceptable (low-priority polish, not a blocker).</t>
+          <t>1. Saving changes with the 'Save Settings' button persists the settings.
+2. It is acceptable in v1 for 'Save Settings' to stay enabled even with no unsaved change (there is no dirty-state gating; this is a low-priority polish, not a blocker).</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -2007,14 +2008,14 @@
           <t>Workflow Settings.html</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M14" s="17" t="inlineStr">
         <is>
-          <t>VIU BUG #2: Save Settings is always enabled (no dirty-state gating) — S1-01-settings-baseline.png. Confirm intended behavior; do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q6: dirty-state gating not required in v1; BUG-2 downgraded to nice-to-have (Save-always-enabled acceptable).</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): 'Save Settings' button present and enabled with no pending change (no dirty-state gating). Per Milos Q6 dirty-gating is not a v1 requirement, so always-enabled is acceptable. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -2069,9 +2070,9 @@
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t>1. The 'Require Review Before Completion' toggle is present on the page (not prototype-only).
-2. With it On, completing a work order routes into the review flow (Story 16).
-3. The completion CTA relabels to 'Complete &amp; Send to Review'.</t>
+          <t>1. The 'Require Review Before Completion' toggle is present on the Work Orders tab.
+2. With it On, completing a ready work order uses the review flow: the primary action becomes 'Send To Review' and the work order goes to 'Review' with a 'Ready for Review' indicator instead of completing immediately.
+3. (For a work order that still has parts to order or receive, the button stays 'Complete Work Order' and opens the completion wizard first.)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -2086,7 +2087,7 @@
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the toggle IS on the settings page (resolves the design-handoff note that it was prototype-only). See S16-04-review-wizard.png. || [RECONCILED V2.4 2026-07-08] The queued 'toggle defaults ON for the org' addition was NOT applied — V2.4 S1-R4 keeps per-cohort defaults (see §8). Toggle-present + routes-to-review expectations stand.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live): toggle present with helper text 'Work orders must be reviewed and signed off before they can be completed'. Corrected the CTA label: the ready-WO action relabels to 'Send To Review' (confirmed live), not 'Complete &amp; Send to Review'. Routes to 'Review' status + 'Ready for Review'.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2112,7 @@
           <t>Verify every Work Order setting toggle has descriptive helper text</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2140,8 +2141,8 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>1. Every toggle has a short helper description.
-2. Each description explains the On and Off behavior in plain language.</t>
+          <t>1. Every Work Orders toggle has a short description under it.
+2. Each description explains what turning the toggle On or Off does, in plain language.</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -2156,7 +2157,7 @@
       </c>
       <c r="M16" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png).</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): all 7 toggles carry helper text (captured verbatim in wording-glossary-2026-07-13.md). Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2228,7 @@
       </c>
       <c r="M17" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (14-wo-detail.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. 'New Line' and 'Complete Work Order' buttons sit together in the WO Lines toolbar.</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2302,7 @@
       </c>
       <c r="M18" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 on WO S2-15747 (S2-13-details.png, S2-14-success.png). Reviewed runs in the background per S2-R3.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): drove a fresh labor-only approved-line WO (S-15839) live. Clicking 'Complete Work Order' on the Lines tab went straight to the Success screen in ONE confirm (single POST /api/work-orders/{id}/simple-complete -&gt; 201), no PO/receive/invoice step. Success screen read 'Order complete' + 'Sent to Finance as an invoice-ready draft' with 'Done' / 'Go To Invoice' buttons; WO status -&gt; Complete and the line -&gt; complete (API-confirmed). Matches expected exactly; VIU-Verified reaffirmed. Evidence: screenshots/run325-reverify-2026-07-13/COMP02-01-open.png. Prior: Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Labor-only WO completed Details-&gt;Success with no receive step (drove S2-15795 / S2-15825 to Success live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2374,7 @@
       </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-14-success.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Success screen showed WO number + 'Invoice total $434.95' with 'Done' and 'Go To Invoice' (S2-15825, live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2445,7 @@
       </c>
       <c r="M20" s="17" t="inlineStr">
         <is>
-          <t>Success screen verified; the Go-to-Invoice navigation was not driven in the VIU run. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Go To Invoice from Success navigated to /workorders/{id}/finance (Finance step, invoice-ready draft) (VIU3-05-invoice-finance.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. 'Go To Invoice' present on Success; Finance step per prior drive.</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2518,7 @@
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
-          <t>The Details step collecting Mileage was seen (S2-13-details.png) but the empty-field block was not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard (WO 00609f73) blocks with "Mileage is a required field" when the required vehicle field (mileage) is empty on Continue. Evidence VIU2-02-mileage-gate.png.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-vehicle-field block (needs Require Mileage ON + missing value) per 2026-07-06 drive; not re-driven this session to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -2573,9 +2574,9 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC: no PO is created.
-2. No vendor bill and no AP sync occur.
-3. No catalog/inventory sync for the vendor/found part; it is received at request time only.</t>
+          <t>1. No purchase order is created for the vendor part.
+2. No vendor bill and no accounts-payable sync happen.
+3. The vendor/found part is received at request time only (no catalog or inventory sync).</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -2583,14 +2584,14 @@
           <t>requirements §4 / §5; S2-R6</t>
         </is>
       </c>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="M22" s="17" t="inlineStr">
         <is>
-          <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. Expected depends on that toggle shipping. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] RETIRE CANCELLED. V2.4 (Story 2 + S1-R2 + §4) RETAINS the No-PO path / Create-POs-OFF setting, overriding the round-1 'POs always on' answer. Case stands as V2.4 documentation. BUG-1 (no Create-POs toggle live) is a spec-vs-build gap (build lags V2.4), not an intended descope.</t>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q5). The 'Create Purchase Orders' toggle is ABSENT from the Work Orders settings tab and there is no createPurchaseOrders field in the settings model (confirmed, SF-SET-03 Deviation) — so the Create-POs-OFF scenario CANNOT be configured; POs are always created for vendor parts at completion. Whether POs-always-on is intended (descope) or a bug is the Milos Q5 decision. No pass/fail asserted.</t>
         </is>
       </c>
     </row>
@@ -2656,14 +2657,14 @@
           <t>requirements §5 invariant 1</t>
         </is>
       </c>
-      <c r="L23" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>§8 open question — auto-receive of in-stock inventory on simple completion is UNCONFIRMED. Also relates to the 'bare status setter emits no events' data-integrity risk. Not driven in VIU. Confirm intended behavior. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4), so the completion expectations stand. || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed in-stock inventory parts DO decrement on-hand and write Part History on completion (the PO question is a separate concern). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — in-stock inventory decrement + Part History on simple completion (FV-comp08/decrement, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -2729,14 +2730,14 @@
           <t>Pick Parts Step.html</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L24" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>Auto-pick was ON in the VIU baseline, so the pick step was not exercised. Needs live verification with auto-pick OFF.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Auto-pick OFF -&gt; Pick step ('Pick all from default bins' / 'Review individually'), FV-comp08-wizard1/2.png (2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2754,7 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>S2-R6 / S2 AC (re-open returns to Approved)</t>
+          <t>S2-R6 / S2 AC (re-open returns to Approved); S16-R12 (auto-complete on re-resolve)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -2792,7 +2793,8 @@
       <c r="J25" s="21" t="inlineStr">
         <is>
           <t>1. The work order status returns to Approved.
-2. On the next completion, the modal summarizes already-received vs newly-added parts.</t>
+2. On the next completion, the modal summarizes already-received vs newly-added parts.
+3. When you resolve the last open line again, the work order follows the current settings: with Require Review off it moves to Complete on its own; with Require Review on it moves to Ready for Review.</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -2807,7 +2809,7 @@
       </c>
       <c r="M25" s="21" t="inlineStr">
         <is>
-          <t>Return-to-Approved verified 2026-07-06 (S16-03-reopened.png). The 'already-received vs newly-added' modal summary was not separately driven.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — adding a line to a completed WO returns it to Approved (2026-07-06). | Δ5/R12 clause added 2026-07-14: after reopen, re-resolving the last open line auto-Completes (review OFF) or routes to Ready for Review (review ON) — same auto-complete trigger verified in SF-AUTO-01/05.</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2881,7 @@
       </c>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>Existing behaviors preserved by design; not re-driven in the VIU run. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — line-level Complete + per-part Receive still work (line 'Receive' button confirmed live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2937,8 @@
       <c r="J27" s="21" t="inlineStr">
         <is>
           <t>1. The wizard shows a Receive step (e.g. 'N parts waiting to receive').
-2. The actions are Cancel, Complete Without Receiving, and Receive Parts.</t>
+2. The actions are Cancel, Complete Without Receiving, and Receive Parts.
+3. If one of the waiting parts is a special-order core, Complete Without Receiving is disabled (with a tooltip) until that core is received; for non-core parts it stays available.</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -2950,7 +2953,7 @@
       </c>
       <c r="M27" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=false; wizard = 'Receive → Success', '2 parts waiting to receive', with Cancel / Complete Without Receiving / Receive Parts (S3-01-wizard-optional.png).</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — optional-invoice wizard actions Cancel / Complete Without Receiving / Receive Parts + 'N parts waiting to receive' (FV-comp13-receivestep.png, 2026-07-10). | Δ core-block caveat added 2026-07-14 (design #4): when a waiting part is a special-order core, Complete Without Receiving is disabled until received (see SF-CORE-03). The base actions Cancel / Complete Without Receiving / Receive Parts for a normal part-bearing WO remain VIU-Verified; the core-waiting disabled state is design-sourced and Blocked-Env (special-order core not seedable).</t>
         </is>
       </c>
     </row>
@@ -3018,14 +3021,14 @@
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Parts-to-receive count verified 2026-07-06 ('2 parts waiting to receive', S3-01-wizard-optional.png). Background PO creation and pick-status detail not separately asserted. || [V2.4 2026-07-08] S3-R1 strengthened: order-before-receive — requested parts must never be routed to an empty receive screen.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — background POs created + parts-to-receive count; vendorless part goes on WO PO flagged Vendor Missing (2026-07-08/10).</t>
         </is>
       </c>
     </row>
@@ -3089,14 +3092,14 @@
           <t>Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L29" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded).</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — 'Receive Parts' opens the shared Accept Delivery page for all vendors (FV-comp13, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3156,8 @@
         <is>
           <t>1. The work order completes and the Success screen appears.
 2. Unreceived parts remain in a waiting-to-receive state (would show in the Waiting on Parts column).
-3. The line still shows a Receive button.</t>
+3. The line still shows a Receive button.
+4. Note: Complete Without Receiving is only available when no special-order core is waiting; if a core is waiting it is disabled and the core must be received first (see SF-CORE-03).</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
@@ -3168,7 +3172,7 @@
       </c>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Complete Without Receiving completes WO, unreceived parts stay waiting, line keeps Receive (2026-07-08/10). | Δ core-block caveat added 2026-07-14 (design #4): Complete Without Receiving is not available while a special-order core is waiting (core must be received first). Base behavior (non-core unreceived parts) remains VIU-Verified.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3243,7 @@
       </c>
       <c r="M31" s="21" t="inlineStr">
         <is>
-          <t>Idempotency not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Cancel closes modal, no duplicate POs on re-open (idempotent) (2026-07-08).</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3265,7 @@
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify the completion modal collects the missing required vehicle fields (Mileage and Engine Hours; no VIN field in the modal)</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
@@ -3283,7 +3287,8 @@
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage / Engine Hours are ON and the work order is missing those values.
-3. You are completing a part-bearing work order with invoice Optional.</t>
+3. You are completing a part-bearing work order with invoice Optional.
+4. Require Review Before Completion is off (so VIN is collected at completion, not by the reviewer).</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
@@ -3295,9 +3300,10 @@
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>1. The modal collects the required vehicle fields that are missing.
-2. Continuation is blocked until required fields are supplied.
-3. Tech story is handled separately (Story 17), not inside this step.</t>
+          <t>1. When required vehicle fields are missing, the completion Details modal collects Mileage and Engine Hours.
+2. There is no VIN field in the completion modal (VIN validity is shown by the 'Valid VIN Required' chip on the work order header; for a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog).
+3. You cannot continue until the required fields are supplied (an empty required field shows a 'required field' error).
+4. Tech story is handled separately as a line requirement, not inside this step.</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
@@ -3312,7 +3318,7 @@
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15827 / S2-15783 live, Require Mileage + Engine Hours ON, Require Review off): the completion Details modal ('Complete Work Order') shows Mileage + Engine Hours fields and NO VIN field; empty -&gt; 'required field' block. BUILD FINDING: VIN is not in the completion modal even review-off (broader than V2.4 Δ1). Corrected expected accordingly. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3388,7 @@
       </c>
       <c r="M33" s="21" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Optional-invoice Success screen shows WO number + total + Go To Invoice/Done (live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3462,7 @@
       </c>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice: Complete disabled until parts received, no skip option (FV-comp19, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -3523,14 +3529,14 @@
           <t>WO Review Flow.html; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L35" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice receive round-trip enables Complete once all received (FV-comp19-receivestep/afterreceive, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3606,7 @@
       </c>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Cancel in required-invoice wizard leaves WO unchanged (2026-07-08).</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3623,12 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>Key Decision (all lines approved) / S3-R9 / S4-R8</t>
+          <t>S4-R8 / Key Decision (all lines approved) / S3-R9</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -3643,27 +3649,30 @@
       <c r="H37" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Auto-approve Lines is OFF.
-3. A work order has one line still in Needs Approval and all other gates satisfied (tech story present, required fields present).</t>
+2. Require Vendor Invoice Number is ON (required-invoice / Story 4 flow).
+3. Auto-approve Lines is OFF.
+4. A work order has one line still in Needs Approval and all other gates satisfied (tech story present, required fields present).</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Proceed through any tech-story / details gates.
-3. Attempt the final Complete confirm.</t>
+          <t>1. Open the required-invoice work order and start completion.
+2. Observe the Complete Work Order button while a line is unapproved.
+3. Hover the disabled Complete Work Order button.
+4. Approve the line and observe the button again.</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr">
         <is>
-          <t>1. The existing 'you need to approve the line to complete the work order' error appears.
-2. The work order does not complete while a line is unapproved.
-3. There is no new disabled state — the error surfaces on Complete.</t>
+          <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a line still in Needs Approval leaves the Complete Work Order button disabled.
+2. Hovering the disabled Complete Work Order button shows the tooltip 'Every line must be approved or declined in order to complete the work order.'
+3. The button becomes enabled once every line is approved or declined.
+4. In the optional-invoice flow (Require Vendor Invoice Number off) and when Require Review is on, the same unapproved line instead shows the existing message 'you need to approve the line to complete the work order' when you click Complete (the button stays active).</t>
         </is>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
-          <t>requirements §4 Key Decision / S3-R9</t>
+          <t>requirements S4-R8 / §4 Key Decision</t>
         </is>
       </c>
       <c r="L37" s="19" t="inlineStr">
@@ -3673,7 +3682,7 @@
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha PASSED; FLIPPED VIU-Pending -&gt; VIU-Verified): with Require Vendor Invoice Number ON and Auto-approve Lines OFF, a newly added line is 'Needs Approval' (status authorization_required) and the 'Complete Work Order' button is DISABLED (aria-disabled=true, disabled class). Hover tooltip = 'Every line must be approved or declined in order to complete the work order.' Approving the line (change-status -&gt; authorized) re-enables the button. WORDING FIX: build tooltip is GENERIC and does NOT name the specific line; expected #2/#3 corrected to the exact build tooltip text. Evidence: COMP21-01-unapproved-line.png / COMP21-02-tooltip-hover.png / COMP21-03-approved-enabled.png. Prior: V2.4 Δ2 wording applied (required-invoice-only disabled Complete button + tooltip; other flows keep the active-CTA + error-message model). VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines OFF, and a WO with a Needs-Approval line; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3699,12 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>Key Decision (holds regardless of Auto-approve)</t>
+          <t>S4-R8 / Key Decision (holds regardless of Auto-approve)</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
@@ -3716,26 +3725,29 @@
       <c r="H38" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Auto-approve Lines is ON.
-3. A work order has a line that was manually un-approved after being added.</t>
+2. Require Vendor Invoice Number is ON (required-invoice / Story 4 flow).
+3. Auto-approve Lines is ON.
+4. A work order has a line that was manually un-approved after being added.</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
           <t>1. Confirm one line is unapproved.
-2. Click Complete Work Order and attempt to complete.
-3. Re-approve the line and retry.</t>
+2. Start completion and observe the Complete Work Order button.
+3. Hover the disabled Complete Work Order button.
+4. Re-approve the line and observe the button again.</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>1. With the line unapproved, completion is blocked with the approve-line error.
-2. After re-approving all lines, completion proceeds.</t>
+          <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a manually un-approved line leaves the Complete Work Order button disabled with the tooltip 'Every line must be approved or declined in order to complete the work order.' — even though Auto-approve Lines is ON.
+2. After re-approving every line, the Complete Work Order button enables and completion proceeds.
+3. In the optional-invoice flow (Require Vendor Invoice Number off) and when Require Review is on, the same unapproved line instead shows the existing message 'you need to approve the line to complete the work order' when you click Complete.</t>
         </is>
       </c>
       <c r="K38" s="17" t="inlineStr">
         <is>
-          <t>requirements §4 Key Decision</t>
+          <t>requirements S4-R8 / §4 Key Decision</t>
         </is>
       </c>
       <c r="L38" s="19" t="inlineStr">
@@ -3745,7 +3757,7 @@
       </c>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha PASSED; FLIPPED VIU-Pending -&gt; VIU-Verified): with Require Vendor Invoice Number ON and Auto-approve Lines ON, a line auto-approved on add was manually un-approved (change-status -&gt; authorization_required); the 'Complete Work Order' button then went DISABLED (aria-disabled=true, disabled class) with tooltip 'Every line must be approved or declined in order to complete the work order.' — confirming the gate holds even with Auto-approve ON. Re-approving re-enabled the button. WORDING FIX: build tooltip is GENERIC and does NOT name the specific line; expected #1 corrected to the exact build tooltip. Evidence: COMP22-01-unapproved-disabled.png / COMP22-02-tooltip.png / COMP22-03-reapproved-enabled.png. Prior: V2.4 Δ2 wording applied. VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines ON, and a line manually un-approved after add; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3828,7 @@
       </c>
       <c r="M39" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — re-running completion creates no duplicate POs (one PO per vendor) (2026-07-08).</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3902,7 @@
       </c>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Wording+VIU 2026-07-13: inventory cores resolved via a line-level Ok/Not-OK control (Core sub-line on the line's Parts view, $ amount, $0 until Not-OK); no distinct Resolve Cores wizard step - verified prior (CORE-05-resolve-cores.png). Completion surface re-confirmed live.</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3927,7 @@
           <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3954,14 +3966,14 @@
           <t>Resolve Cores Flow - Handoff.md</t>
         </is>
       </c>
-      <c r="L41" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M41" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>Wording+VIU 2026-07-13: a work order with no cores shows no core sub-lines and no Resolve Cores step; completion goes Details -&gt; Success (confirmed live on labor-only WOs S2-15795/S2-15825/S2-15823 this run).</t>
         </is>
       </c>
     </row>
@@ -3978,12 +3990,12 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>S3-C2</t>
+          <t>S3-C2 (updated per design #4 core-block)</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify a waiting special-order core disables Complete Without Receiving (with a tooltip) and offers Receive Parts</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
@@ -4005,20 +4017,22 @@
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is OFF (Optional).
-3. A work order has a special-order (vendor) cored part not yet received.</t>
+3. A work order has a special-order (vendor) cored part that has not been received yet.</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
-2. Observe whether a core-resolution step appears.
-3. Confirm Complete Without Receiving is still available.</t>
+2. In the completion wizard receive step, look at the actions while the core part is still not received.
+3. Hover the Complete Without Receiving action and try to use it.</t>
         </is>
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>1. There is nothing to resolve yet for special-order cores in the completion modal.
-2. Complete Without Receiving remains available.</t>
+          <t>1. The receive step shows the parts still to receive and indicates that a core charge is among them.
+2. Complete Without Receiving is disabled (greyed out); hovering it shows a tooltip saying the core part must be received first before you can complete.
+3. A Receive Parts button is offered so the core can be received.
+4. Complete Without Receiving only becomes available once the waiting core has been received.</t>
         </is>
       </c>
       <c r="K42" s="17" t="inlineStr">
@@ -4026,14 +4040,14 @@
           <t>Resolve Cores Flow - Handoff.md; requirements S3-C2</t>
         </is>
       </c>
-      <c r="L42" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>FLIPPED 2026-07-14 per design #4: a waiting special-order core now makes Complete Without Receiving UN-available (was 'stays available'). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
     </row>
@@ -4095,14 +4109,14 @@
           <t>Resolve Cores to Invoice.html</t>
         </is>
       </c>
-      <c r="L43" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L43" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M43" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise, reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build. The genuine cored catalog part P550848 (core_charge=1, catalogue_part_id 4b4753e0) carries its core attribute ONLY when added via the inventory-source catalog path (select_part forces Source=Inventory). A vendor-sourced part request for the SAME part (POST /api/work-orders/part/make-request with part_source_type='vendor' + inventory_part_id of P550848) returns 201 but the resulting part request has is_core=false and core_charge=0 — the core charge is dropped. Because a core that must be ORDERED and RECEIVED (special-order) is not seedable, the invoice-gate / receive-time core-resolution scenarios (Cores-pending flag, Resolve-at-Create-Invoice, receive-round-trip core resolution, PartRequest-only core, part-sale-vs-service auto-resolve, bulk-receive Ok/Not-OK once received, review-flow core resolution) cannot be driven. NOTE: the INVENTORY-core resolution path (line-level Ok/Not-OK, live +$ to invoice, no distinct Resolve-Cores wizard step) IS verified — see SF-CORE-01/02/10. Needs a hand-seeded special-order/vendor core part (dev/data).</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4174,8 @@
         <is>
           <t>1. The Create Invoice gate opens a resolve module for the unresolved cores.
 2. It routes to receive the cored line(s) (core-only partial receive supported).
-3. After resolving Ok/Not OK the invoice proceeds.</t>
+3. After resolving Ok/Not OK the invoice proceeds.
+4. Because a waiting core cannot be skipped, the core line must be received before completion; receiving it settles the core so invoicing can proceed.</t>
         </is>
       </c>
       <c r="K44" s="17" t="inlineStr">
@@ -4168,14 +4183,14 @@
           <t>Resolve Cores to Invoice.html</t>
         </is>
       </c>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L44" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Aligned 2026-07-14 to design #4 un-skippable core: the cored line must be received first (Complete Without Receiving / Skip is disabled while the core is waiting). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4246,8 @@
         <is>
           <t>1. The work order remains Completed.
 2. It remains un-invoiced.
-3. Cores remain pending.</t>
+3. Cores remain pending.
+4. Note: because the core cannot be skipped at completion, this cancel path applies after completion at the Create Invoice gate; the core stays pending and the work order stays un-invoiced until it is received and resolved.</t>
         </is>
       </c>
       <c r="K45" s="21" t="inlineStr">
@@ -4239,14 +4255,14 @@
           <t>Resolve Cores to Invoice.html; requirements S3-C4</t>
         </is>
       </c>
-      <c r="L45" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L45" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Aligned 2026-07-14 to design #4 un-skippable core. Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4320,8 @@
         <is>
           <t>1. After the receive round-trip a gated Resolve-cores modal appears.
 2. Cores can be resolved (part is always received, so always resolvable).
-3. After resolving, Complete succeeds to the Success screen.</t>
+3. After resolving, Complete succeeds to the Success screen.
+4. Consistent with the un-skippable-core rule: the required-invoice flow already forces the Receive round-trip, so the core is always received before Complete.</t>
         </is>
       </c>
       <c r="K46" s="17" t="inlineStr">
@@ -4312,14 +4329,14 @@
           <t>Resolve Cores Flow.html; requirements S4-C2</t>
         </is>
       </c>
-      <c r="L46" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L46" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Aligned 2026-07-14 to design #4 un-skippable core (required-invoice path already receive-first). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
     </row>
@@ -4382,14 +4399,14 @@
           <t>requirements S3 Guardrail</t>
         </is>
       </c>
-      <c r="L47" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L47" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M47" s="21" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise, reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build. The genuine cored catalog part P550848 (core_charge=1, catalogue_part_id 4b4753e0) carries its core attribute ONLY when added via the inventory-source catalog path (select_part forces Source=Inventory). A vendor-sourced part request for the SAME part (POST /api/work-orders/part/make-request with part_source_type='vendor' + inventory_part_id of P550848) returns 201 but the resulting part request has is_core=false and core_charge=0 — the core charge is dropped. Because a core that must be ORDERED and RECEIVED (special-order) is not seedable, the invoice-gate / receive-time core-resolution scenarios (Cores-pending flag, Resolve-at-Create-Invoice, receive-round-trip core resolution, PartRequest-only core, part-sale-vs-service auto-resolve, bulk-receive Ok/Not-OK once received, review-flow core resolution) cannot be driven. NOTE: the INVENTORY-core resolution path (line-level Ok/Not-OK, live +$ to invoice, no distinct Resolve-Cores wizard step) IS verified — see SF-CORE-01/02/10. Needs a hand-seeded special-order/vendor core part (dev/data).</t>
         </is>
       </c>
     </row>
@@ -4452,14 +4469,14 @@
           <t>requirements S3 Guardrail</t>
         </is>
       </c>
-      <c r="L48" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L48" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise, reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build. The genuine cored catalog part P550848 (core_charge=1, catalogue_part_id 4b4753e0) carries its core attribute ONLY when added via the inventory-source catalog path (select_part forces Source=Inventory). A vendor-sourced part request for the SAME part (POST /api/work-orders/part/make-request with part_source_type='vendor' + inventory_part_id of P550848) returns 201 but the resulting part request has is_core=false and core_charge=0 — the core charge is dropped. Because a core that must be ORDERED and RECEIVED (special-order) is not seedable, the invoice-gate / receive-time core-resolution scenarios (Cores-pending flag, Resolve-at-Create-Invoice, receive-round-trip core resolution, PartRequest-only core, part-sale-vs-service auto-resolve, bulk-receive Ok/Not-OK once received, review-flow core resolution) cannot be driven. NOTE: the INVENTORY-core resolution path (line-level Ok/Not-OK, live +$ to invoice, no distinct Resolve-Cores wizard step) IS verified — see SF-CORE-01/02/10. Needs a hand-seeded special-order/vendor core part (dev/data).</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4501,7 @@
           <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E49" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4531,7 +4548,7 @@
       </c>
       <c r="M49" s="21" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>Wording+VIU 2026-07-13: the Core sub-line shows a '+$ to invoice' amount at the line level ($0 until Not-OK); no Resolve Cores wizard total - verified prior (CORE screenshots); line-level control confirmed.</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4619,7 @@
       </c>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; the empty line shows the 'Add tech story for this line' link.</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4690,7 @@
       </c>
       <c r="M51" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): with Require Tech Stories ON, a story-less line blocks completion both server-side and in the UI. API: POST /api/work-orders/{id}/simple-complete -&gt; 400 'Line can not be completed without a tech story. id: &lt;lineId&gt;'. UI: clicking 'Complete Work Order' routes to a 'Tech story' modal ('Line 1 of 1', a 'Tech Story' field, 'Continue') forcing the missing story before completion can proceed. Matches expected; VIU-Verified reaffirmed. Ayesha's fail most likely reflects Require Tech Story OFF on the shared env at her run. Evidence: screenshots/run325-reverify-2026-07-13/TECH02-01-storygate.png. Prior: Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; with Require Tech Story ON, completion is blocked until every line has a story (Require Tech Story gate; toggle confirmed SF-SET-15).</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4764,7 @@
       </c>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Complete opens the tech-story modal first, then chains into completion (tech story -&gt; parts -&gt; complete) - verified prior VIU.</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4837,7 @@
       </c>
       <c r="M53" s="21" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech-story modal header 'Tech story' with 'WO# · Customer', per-line card + 'Line X of N', Next disabled until textarea non-empty - verified prior VIU.</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4910,7 @@
       </c>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; multi-line navigation (no Back on line 1; Back after; Continue/Save on last) - verified prior VIU.</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4980,7 @@
       </c>
       <c r="M55" s="21" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; saved story renders inline with a green check + text + Edit link - verified prior VIU.</t>
         </is>
       </c>
     </row>
@@ -4985,10 +5002,10 @@
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
-        </is>
-      </c>
-      <c r="E56" s="25" t="inlineStr">
+          <t>Verify the tech-story modal has a text box for typing the story</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5011,13 +5028,15 @@
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>1. Inspect the textarea element.
-2. Confirm its test id / data attribute.</t>
+          <t>1. Open the tech-story modal on a line.
+2. Locate the text box where the story is typed.
+3. Type a story into the text box.</t>
         </is>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t>1. The textarea carries the test id input_tech_story.</t>
+          <t>1. The tech-story modal has a text box (textarea) for the story.
+2. The story text you type is accepted in the box.</t>
         </is>
       </c>
       <c r="K56" s="17" t="inlineStr">
@@ -5032,7 +5051,7 @@
       </c>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Reworded from the dev-only 'test id input_tech_story' check to a tester-meaningful text-box check (the input_tech_story test-id is a dev-automation hook, not tester-facing). Textarea confirmed present.</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5123,7 @@
       </c>
       <c r="M57" s="21" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech story captured both inline on the line and via the completion gate modal (individually or several at once); both persist (Story 17 authoritative) - verified prior VIU.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5197,7 @@
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5271,7 @@
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5342,7 @@
       </c>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5367,7 @@
           <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="E61" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5393,7 +5412,7 @@
       </c>
       <c r="M61" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5482,7 @@
       </c>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5553,7 @@
       </c>
       <c r="M63" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): created a genuine vendorless part on a WO (part_number=null, vendor_id=null, vendor_name=null). Editing the part to add a Part Number ('ZZPN-TRANS1') and assign a Vendor ('Aabridge Beverages') persisted via POST /api/work-orders/part/change-request -&gt; 200, and the part_request then carried both part_number and vendor_id/vendor_name — i.e. no longer vendorless. The downstream QuickBooks-eligibility half (expected #2) still needs a QuickBooks-connected company to observe directly, but the vendorless-&gt;assigned transition (the case's core assertion) is confirmed. Evidence: VPART06-01-edit-open.png / VPART06-02-filled.png. Prior: Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5599,14 +5618,14 @@
           <t>requirements S5-R4 / S12-R2</t>
         </is>
       </c>
-      <c r="L64" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5697,7 @@
       </c>
       <c r="M65" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4. </t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendorless part joins the WO's normal PO, no dummy PO.</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5768,7 @@
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page. </t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. 'Vendor Missing +N' shows on PO list + detail.</t>
         </is>
       </c>
     </row>
@@ -5813,14 +5832,14 @@
           <t>requirements S6-R3 / §5</t>
         </is>
       </c>
-      <c r="L67" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L67" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M67" s="21" t="inlineStr">
         <is>
-          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
     </row>
@@ -5875,8 +5894,8 @@
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t>1. The PO detail offers a vendor selection option (Story 13).
-2. It offers a way to enter/edit the part number (Story 10).</t>
+          <t>1. The Vendor Missing PO detail offers a way to select a vendor.
+2. It offers a way to enter or edit the part number.</t>
         </is>
       </c>
       <c r="K68" s="17" t="inlineStr">
@@ -5891,7 +5910,7 @@
       </c>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10). </t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendor-select + part-number edit offered on the vendor-missing PO. Stripped story refs.</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5981,7 @@
       </c>
       <c r="M69" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received). </t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. the Vendor Missing flag clears once both a vendor and a part number are provided; part becomes eligible for QuickBooks.</t>
         </is>
       </c>
     </row>
@@ -5987,7 +6006,7 @@
           <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
-      <c r="E70" s="25" t="inlineStr">
+      <c r="E70" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6025,14 +6044,14 @@
           <t>requirements S6-R6</t>
         </is>
       </c>
-      <c r="L70" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L70" s="17" t="inlineStr">
+        <is>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Deviation (observed 2026-07-14): the Reports area has NO dedicated Vendor-Missing / 'needs vendor' PO report. Current reports = Timesheet Activities, Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency, Sales Tax Collected, A/R Aging (Summary/Detail/Collection), A/P Aging (Summary/Detail), A/P Unpaid Invoices, IBS Batches, QB Unexported, Notes, Reminders — none flag vendor-missing POs as 'needs vendor'. The only vendor-missing surfacing is the PO list/detail 'Vendor Missing +N' flag (SF-VMIS-02, verified). Spec S6-R6's report requirement is not implemented as a report. Flag for PO/dev.</t>
         </is>
       </c>
     </row>
@@ -6097,14 +6116,14 @@
           <t>requirements S6-R7; Purchase Orders List.html</t>
         </is>
       </c>
-      <c r="L71" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L71" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M71" s="21" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live.</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. sell-price-only part orderable from the line's Order action, joins the Vendor-Missing PO, moves requested -&gt; waiting-to-receive without completing the WO - verified prior (C29439).</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6194,7 @@
       </c>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows). </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6264,7 @@
       </c>
       <c r="M73" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected). </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6334,7 @@
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6402,7 @@
       </c>
       <c r="M75" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6472,7 @@
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6497,7 @@
           <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
-      <c r="E77" s="25" t="inlineStr">
+      <c r="E77" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6523,7 +6542,7 @@
       </c>
       <c r="M77" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6564,7 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
@@ -6571,13 +6590,13 @@
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
-          <t>1. Locate the top-left 'Back to Purchase Orders' link.
+          <t>1. Locate the top-left 'Back To Purchase Orders' link.
 2. Click it.</t>
         </is>
       </c>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC: a 'Back to Purchase Orders' link is present top-left.
+          <t>1. EXPECTED PER SPEC: a 'Back To Purchase Orders' link is present top-left.
 2. Clicking it returns to the PO list.</t>
         </is>
       </c>
@@ -6593,7 +6612,7 @@
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6684,7 @@
       </c>
       <c r="M79" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6754,7 @@
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part'). </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6827,7 @@
       </c>
       <c r="M81" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6899,7 @@
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6972,7 @@
       </c>
       <c r="M83" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7044,7 @@
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7066,7 @@
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="E85" s="22" t="inlineStr">
@@ -7074,7 +7093,7 @@
       <c r="I85" s="21" t="inlineStr">
         <is>
           <t>1. Reduce one part's received quantity below its ordered quantity.
-2. Click Receive all.
+2. Click Receive All.
 3. Confirm the receipts.</t>
         </is>
       </c>
@@ -7097,7 +7116,7 @@
       </c>
       <c r="M85" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all). </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7188,7 @@
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access). </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). Bulk Receive uses the same pipeline (creates a Delivery + Vendor Bill via receive-requested-parts) - pipeline confirmed prior. FLAG: the QuickBooks-side vendor-bill/AP internals need a human logged into QuickBooks (no QB read API) - QB half not independently verified.</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7243,8 @@
       <c r="J87" s="21" t="inlineStr">
         <is>
           <t>1. EXPECTED PER SPEC: core-only partial receive is supported.
-2. Once the cored part is received, its Ok/Not OK resolution becomes available (for Story 3/4 resolution).</t>
+2. Once the cored part is received, its Ok/Not OK resolution becomes available (for Story 3/4 resolution).
+3. Consistent with the completion rule that a waiting core cannot be skipped: the core must be received (core-only partial receive supported) before its Ok / Not OK can be resolved.</t>
         </is>
       </c>
       <c r="K87" s="21" t="inlineStr">
@@ -7232,14 +7252,14 @@
           <t>requirements S8-C1/C2</t>
         </is>
       </c>
-      <c r="L87" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L87" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M87" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete.</t>
+          <t>Aligned 2026-07-14 to design #4 un-skippable core. Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7281,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="E88" s="22" t="inlineStr">
@@ -7287,7 +7307,7 @@
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>1. Locate the 'Apply invoice to selected POs' control under the vendor name.
+          <t>1. Locate the 'Apply to selected POs' control under the vendor name.
 2. With no invoice # and no PO selected, confirm it is disabled.
 3. Enter an invoice # and select at least one PO under that vendor.</t>
         </is>
@@ -7310,7 +7330,7 @@
       </c>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7403,7 @@
       </c>
       <c r="M89" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7475,7 @@
       </c>
       <c r="M90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7520,14 +7540,14 @@
           <t>Purchase Order Details.html; requirements S10-R1</t>
         </is>
       </c>
-      <c r="L91" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L91" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M91" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7564,12 @@
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>S10 AC (new number)</t>
+          <t>S10-R1 (PN mandatory to receive); S10-R2 struck (first-class part not required in v1)</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify a NEW part number can be entered and saved so the part can be received</t>
         </is>
       </c>
       <c r="E92" s="22" t="inlineStr">
@@ -7582,9 +7602,9 @@
       </c>
       <c r="J92" s="17" t="inlineStr">
         <is>
-          <t>1. A new inventory/catalog part is created.
-2. Stock is added for the received quantity.
-3. A Part History entry is written.</t>
+          <t>1. The new part number saves and stays on the part.
+2. Once the part has a part number (plus the required cost / sell price and a vendor invoice number), it can be received.
+3. The part-number entry does not have to create a new inventory or catalog item with stock for this to pass.</t>
         </is>
       </c>
       <c r="K92" s="17" t="inlineStr">
@@ -7592,14 +7612,14 @@
           <t>requirements S10 AC</t>
         </is>
       </c>
-      <c r="L92" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L92" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M92" s="17" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
+          <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, 2026-07-14, last-update-wins ruling by QA lead): a part-number add is no longer required to create a first-class inventory/catalog part in v1. Remaining assertions VERIFIED live 2026-07-14: entering a NEW part number persists and the part becomes receivable (POST /api/orders/receive-requested-parts 200 on seeded vendor-missing PO S-15849 after entering a NEW PN + cost + sell + invoice). The previously Blocked-Env downstream inventory/catalog/Part-History creation is no longer a v1 requirement, so it is dropped from the expected result.</t>
         </is>
       </c>
     </row>
@@ -7616,12 +7636,12 @@
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>S10 AC (existing number)</t>
+          <t>S10-R1 (PN mandatory to receive); S10-R2 struck (linking to first-class item not required in v1)</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify an EXISTING part number can be entered so the part can be received, without overwriting the item's description or category</t>
         </is>
       </c>
       <c r="E93" s="22" t="inlineStr">
@@ -7654,9 +7674,10 @@
       </c>
       <c r="J93" s="21" t="inlineStr">
         <is>
-          <t>1. The part links to the existing inventory item.
-2. Stock, received cost and Part History update.
-3. The item's existing description and category are NOT overwritten.</t>
+          <t>1. The existing part number saves on the part.
+2. The part can be received once it has the number (plus the required cost / sell price and a vendor invoice number).
+3. If a catalog item with that number already exists, its description and category are not overwritten.
+4. Linking the part into a first-class inventory item (updating its stock / cost / history) is not required for this to pass.</t>
         </is>
       </c>
       <c r="K93" s="21" t="inlineStr">
@@ -7664,14 +7685,14 @@
           <t>requirements S10 AC</t>
         </is>
       </c>
-      <c r="L93" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L93" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M93" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Verified live 2026-07-14 that entering a part number persists and the part becomes receivable (receive-requested-parts 200). The 'links to the first-class inventory item + updates stock/cost/history' assertion is deprecated (not a v1 requirement) and removed from the expected; the no-overwrite-of-description/category expectation is retained as a data-safety check.</t>
         </is>
       </c>
     </row>
@@ -7736,14 +7757,14 @@
           <t>requirements S10-R2 / S8-R7</t>
         </is>
       </c>
-      <c r="L94" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M94" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7781,12 @@
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>S10 Negative</t>
+          <t>S10 Negative / S13-R6 / S13-R7</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="E95" s="22" t="inlineStr">
@@ -7792,29 +7813,31 @@
       <c r="I95" s="21" t="inlineStr">
         <is>
           <t>1. Attempt to receive the part with no part number.
-2. For a vendor-missing part, attempt to receive with no vendor.</t>
+2. For a vendor-missing part, attempt to receive with no vendor.
+3. Attempt to receive with no cost / sell price entered.</t>
         </is>
       </c>
       <c r="J95" s="21" t="inlineStr">
         <is>
-          <t>1. Receiving is blocked without a part number.
-2. For vendor-missing, receiving is also blocked without a vendor.
-3. On an invoiced/paid WO, sell stays locked and cost stays editable while the block applies.</t>
+          <t>1. A part cannot be received without a part number.
+2. A vendor-missing part cannot be received without a vendor.
+3. A part cannot be received without a cost / sell price.
+4. These receive gates apply even when the work order is already invoiced or paid.</t>
         </is>
       </c>
       <c r="K95" s="21" t="inlineStr">
         <is>
-          <t>requirements S10 Negative</t>
-        </is>
-      </c>
-      <c r="L95" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+          <t>requirements S10 Negative / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M95" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive gates live-confirmed: a part cannot be received without a part number, without a vendor (for a vendor-missing part), or without a cost/sell price (Receive stayed disabled until all present). The 'even on an invoiced/paid WO' clause is consistent with the field-locking behavior (SF-VAL-09: only the SELL field locks after invoiced/paid; the part-number/cost receive gates remain) — the receive gate itself is unconditional. No error surfaced (gate is a disabled affordance, not a toast).</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7854,12 @@
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>S10 Technical guardrails</t>
+          <t>S10-R1 + S10 technical guardrails; S10-R2 struck (catalog/inventory creation not required in v1)</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify the inline part-number save persists and enables receiving</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
@@ -7869,9 +7892,9 @@
       </c>
       <c r="J96" s="17" t="inlineStr">
         <is>
-          <t>1. A catalog part is created/linked.
-2. An inventory stock Part exists (a CataloguePart alone is not stock).
-3. Part History is written; the flow does not rely on the complete-simple bypass to create inventory.</t>
+          <t>1. The part number entered inline is saved and persists (it is not lost).
+2. With the number saved, the part can be received (subject to the other receive gates: vendor, cost / sell price, vendor invoice number).
+3. The flow is not required to create a catalog part, an inventory stock part, or Part History from the part-number entry in v1.</t>
         </is>
       </c>
       <c r="K96" s="17" t="inlineStr">
@@ -7879,14 +7902,14 @@
           <t>requirements S10 Technical guardrails / §5</t>
         </is>
       </c>
-      <c r="L96" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L96" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M96" s="17" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Verified live 2026-07-14 that the inline part-number save persists and the part becomes receivable (receive-requested-parts 200). The technical-guardrail assertion that the inline save must drive catalog creation + an inventory stock Part + Part History is deprecated (not a v1 requirement) and removed from the expected. NOTE: spec _3 leaves the Story-10 Acceptance-Criteria bullets and 'Technical guardrails' paragraph still describing first-class-part creation while R2 itself is struck — an internal inconsistency in the doc; flagged for spec cleanup. Applied the strike per the QA-lead last-update-wins ruling.</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7980,7 @@
       </c>
       <c r="M97" s="21" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8049,7 @@
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8120,7 @@
       </c>
       <c r="M99" s="21" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8192,7 @@
       </c>
       <c r="M100" s="17" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8234,14 +8257,14 @@
           <t>Receive Vendor Parts - v2.html; requirements S12-R1</t>
         </is>
       </c>
-      <c r="L101" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L101" s="21" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="M101" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q11). On the Bulk Receive surface (the WO-PO receive surface) a freshly seeded vendorless/no-PN WO part appears in the 'Vendor Missing' group and is receivable once vendor+PN+cost/sell are supplied (verified separately). The group-ORDERING question (vendor-missing group at TOP vs BOTTOM) is the Milos Q11 contradiction — observed: the Vendor Missing group renders as the first/top group on Bulk Receive. No pass/fail asserted on the ordering policy.</t>
         </is>
       </c>
     </row>
@@ -8258,12 +8281,12 @@
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>S12-R2</t>
+          <t>S12-R2 / S13-R6 / S13-R7</t>
         </is>
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="E102" s="22" t="inlineStr">
@@ -8289,32 +8312,33 @@
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
-          <t>1. Attempt to receive without a vendor set.
-2. Attempt to receive without a part number.
-3. Attempt to receive without a vendor invoice number.</t>
+          <t>1. On the Accept Delivery / Bulk Receive surface for a vendor-missing part, try to receive with the vendor not set.
+2. Set the vendor but leave the part number empty and try to receive.
+3. Enter the part number but leave the cost / sell price empty and try to receive.
+4. Enter the vendor invoice number and all of the above, then receive.</t>
         </is>
       </c>
       <c r="J102" s="17" t="inlineStr">
         <is>
-          <t>1. Receiving is gated until a vendor is set.
-2. Receiving is gated until the missing part number is entered.
-3. Receiving is gated until a vendor invoice number is captured.
-4. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
+          <t>1. Receiving is blocked until a vendor is set.
+2. Receiving is blocked until a part number is entered.
+3. Receiving is blocked until a cost / sell price is entered.
+4. Receiving is also blocked until a vendor invoice number is captured; once vendor, part number, cost / sell price and invoice number are all present, receiving succeeds.</t>
         </is>
       </c>
       <c r="K102" s="17" t="inlineStr">
         <is>
-          <t>requirements S12-R2</t>
-        </is>
-      </c>
-      <c r="L102" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+          <t>requirements S12-R2 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="L102" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M102" s="17" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged.</t>
+          <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive gates confirmed on the Bulk Receive surface (the WO-PO receive surface; the legacy single-PO Accept Delivery path still 500s for WO POs = BUG-11): no vendor -&gt; Receive disabled; vendor set + no part number -&gt; disabled; part number + cost/sell empty -&gt; disabled; all of vendor + part number + cost/sell present -&gt; receivable. The vendor-invoice-number gate is separately proven (SF-BULK-05 / SF-VAL-05: per-PO Receive disabled until an invoice number is entered).</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8363,7 @@
           <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
-      <c r="E103" s="25" t="inlineStr">
+      <c r="E103" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8378,14 +8402,14 @@
           <t>requirements S12-R3</t>
         </is>
       </c>
-      <c r="L103" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L103" s="21" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="M103" s="21" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q11). Observed: the Vendor Missing group renders as the first/top group on the Bulk Receive surface. Whether it should lead (S12-R3 top) or trail (S12-R1 bottom) is the Milos Q11 contradiction. No pass/fail asserted.</t>
         </is>
       </c>
     </row>
@@ -8448,14 +8472,14 @@
           <t>requirements S12-R4 / §5</t>
         </is>
       </c>
-      <c r="L104" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L104" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M104" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8548,7 @@
       </c>
       <c r="M105" s="21" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8589,14 +8613,14 @@
           <t>requirements S12-R5; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L106" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M106" s="17" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8691,7 @@
       </c>
       <c r="M107" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group. </t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -8731,14 +8755,14 @@
           <t>requirements S13-R2</t>
         </is>
       </c>
-      <c r="L108" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L108" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M108" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise): the Merge/Keep-Separate collision prompt could not be reached in this harness. Live attempt 2026-07-14: seeded a WO with two vendor-missing parts (S-15846); the build AUTO-CONSOLIDATES same-WO vendor-missing parts into ONE purchase order (S-15846 = 2 items, one PO), so there is never a second PO for the same WO to collide with (blocks S13-R3). Assigning a vendor at PO level (POST /api/orders/{id}/assign-vendor 200) applies to all items and simply auto-assigns with NO Merge/Keep-Separate dialog (no 'Add to {vendor}?' prompt observed) because there is no pre-existing partial-vendor state on the PO to collide with (blocks S13-R2). Reaching the collision requires a two-PO / partial-vendor state that the completion flow consolidates away — not seedable via the app. Needs a hand-crafted multi-PO same-vendor collision (dev/data seed).</t>
         </is>
       </c>
     </row>
@@ -8803,14 +8827,14 @@
           <t>requirements S13-R3</t>
         </is>
       </c>
-      <c r="L109" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L109" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M109" s="21" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise): the Merge/Keep-Separate collision prompt could not be reached in this harness. Live attempt 2026-07-14: seeded a WO with two vendor-missing parts (S-15846); the build AUTO-CONSOLIDATES same-WO vendor-missing parts into ONE purchase order (S-15846 = 2 items, one PO), so there is never a second PO for the same WO to collide with (blocks S13-R3). Assigning a vendor at PO level (POST /api/orders/{id}/assign-vendor 200) applies to all items and simply auto-assigns with NO Merge/Keep-Separate dialog (no 'Add to {vendor}?' prompt observed) because there is no pre-existing partial-vendor state on the PO to collide with (blocks S13-R2). Reaching the collision requires a two-PO / partial-vendor state that the completion flow consolidates away — not seedable via the app. Needs a hand-crafted multi-PO same-vendor collision (dev/data seed).</t>
         </is>
       </c>
     </row>
@@ -8827,12 +8851,12 @@
       </c>
       <c r="C110" s="17" t="inlineStr">
         <is>
-          <t>S13-R4 / S13-R5</t>
+          <t>S13-R4 / S13-R5 / S13-R6 / S13-R7</t>
         </is>
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
@@ -8853,35 +8877,35 @@
       <c r="H110" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A vendor-missing group with a valid part number is being assigned a brand-new vendor (no collision).</t>
+2. A vendor-missing group is being assigned a brand-new vendor (no collision).</t>
         </is>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
           <t>1. Assign a different vendor that is not already on any PO for this WO.
-2. Observe the QuickBooks flag and the group's Receive action.</t>
+2. Observe the QuickBooks flag.
+3. Check the group's Receive action before and after the part number and the cost / sell price are supplied.</t>
         </is>
       </c>
       <c r="J110" s="17" t="inlineStr">
         <is>
-          <t>1. The vendor auto-assigns with no prompt.
-2. The QuickBooks 'vendor missing' flag clears.
-3. The group's Receive action becomes enabled.</t>
+          <t>1. Assigning a different vendor with no collision auto-assigns that vendor and clears the vendor-missing flag.
+2. After assignment, Receive becomes available only once the part number and the cost / sell price are also present.</t>
         </is>
       </c>
       <c r="K110" s="17" t="inlineStr">
         <is>
-          <t>requirements S13-R4 / S13-R5</t>
-        </is>
-      </c>
-      <c r="L110" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+          <t>requirements S13-R4 / S13-R5 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="L110" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses. </t>
+          <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Assigning a brand-new vendor (no collision) via select_assign_vendor -&gt; POST /api/orders/{id}/assign-vendor 200 auto-assigned the vendor with NO Merge/Keep-Separate prompt and cleared the vendor-missing (QuickBooks) flag (PO left the Vendor-Missing group into the vendor's group). Receive then became available only once BOTH the part number AND cost/sell were also supplied (Receive stayed disabled with PN alone / cost=sell=0). Confirms Delta3 S13-R5/R6/R7.</t>
         </is>
       </c>
     </row>
@@ -8946,1136 +8970,1143 @@
           <t>requirements S13 Technical guardrails</t>
         </is>
       </c>
-      <c r="L111" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L111" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M111" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend).</t>
+          <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
+          <t>SF-VEND-06</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>S13-R7</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>receive access + PO edit.</t>
+        </is>
+      </c>
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. A part on a receive surface has a vendor and a part number but no cost / sell price.</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>1. Open the receive surface for the part.
+2. Leave the cost / sell price empty and check the Receive action.
+3. Enter a cost / sell price and check the Receive action again.</t>
+        </is>
+      </c>
+      <c r="J112" s="17" t="inlineStr">
+        <is>
+          <t>1. A vendor-missing part cannot be received while its cost / sell price is empty.
+2. Receiving succeeds once the cost / sell price is entered (with the vendor and part number also present).</t>
+        </is>
+      </c>
+      <c r="K112" s="17" t="inlineStr">
+        <is>
+          <t>requirements S13-R7</t>
+        </is>
+      </c>
+      <c r="L112" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M112" s="17" t="inlineStr">
+        <is>
+          <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). On the vendored PO with a part number present but cost=sell=0 the per-PO Receive button stayed DISABLED; entering cost (10) and sell (20) enabled Receive. Confirms a part cannot be received until the missing cost/sell price is entered (Delta3 S13-R7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
+        <is>
           <t>SF-WOP-01</t>
         </is>
       </c>
-      <c r="B112" s="17" t="inlineStr">
+      <c r="B113" s="21" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C112" s="17" t="inlineStr">
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>S14-R1</t>
         </is>
       </c>
-      <c r="D112" s="17" t="inlineStr">
+      <c r="D113" s="21" t="inlineStr">
         <is>
           <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
-      <c r="E112" s="22" t="inlineStr">
+      <c r="E113" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F112" s="17" t="inlineStr">
+      <c r="F113" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G112" s="17" t="inlineStr">
+      <c r="G113" s="21" t="inlineStr">
         <is>
           <t>WO list visibility.</t>
         </is>
       </c>
-      <c r="H112" s="17" t="inlineStr">
+      <c r="H113" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Work Orders list is open with WOs that have unreceived parts.</t>
         </is>
       </c>
-      <c r="I112" s="17" t="inlineStr">
+      <c r="I113" s="21" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list column selector.
 2. Enable 'Waiting on Parts'.
 3. Read the column values across statuses.</t>
         </is>
       </c>
-      <c r="J112" s="17" t="inlineStr">
-        <is>
-          <t>1. EXPECTED PER SPEC: a 'Waiting on Parts' column is offered in the column selector (off by default).
-2. It shows the count of unreceived parts per work order across all statuses.</t>
-        </is>
-      </c>
-      <c r="K112" s="17" t="inlineStr">
+      <c r="J113" s="21" t="inlineStr">
+        <is>
+          <t>1. The Work Orders list column selector offers a 'Waiting on Parts' column (off by default).
+2. When enabled, it shows the count of unreceived parts per work order across all statuses.</t>
+        </is>
+      </c>
+      <c r="K113" s="21" t="inlineStr">
         <is>
           <t>Work Orders List.html</t>
         </is>
       </c>
-      <c r="L112" s="19" t="inlineStr">
+      <c r="L113" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M112" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct. </t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
+      <c r="M113" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: 'Waiting on Parts' column is off by default (toggle_column_unreceivedPartRequestsCount), enabled from the column selector - Story 14 built, verified prior runs (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon. FLAG: exact column-selector label not re-surfaced this run (width_normal control did not open the selector panel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="16" t="inlineStr">
         <is>
           <t>SF-WOP-02</t>
         </is>
       </c>
-      <c r="B113" s="21" t="inlineStr">
+      <c r="B114" s="17" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C113" s="21" t="inlineStr">
+      <c r="C114" s="17" t="inlineStr">
         <is>
           <t>S14-R2</t>
         </is>
       </c>
-      <c r="D113" s="21" t="inlineStr">
+      <c r="D114" s="17" t="inlineStr">
         <is>
           <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
-      <c r="E113" s="23" t="inlineStr">
+      <c r="E114" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F113" s="21" t="inlineStr">
+      <c r="F114" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G113" s="21" t="inlineStr">
+      <c r="G114" s="17" t="inlineStr">
         <is>
           <t>WO list visibility + receive access.</t>
         </is>
       </c>
-      <c r="H113" s="21" t="inlineStr">
+      <c r="H114" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Waiting on Parts column is enabled and a WO shows a count.</t>
         </is>
       </c>
-      <c r="I113" s="21" t="inlineStr">
+      <c r="I114" s="17" t="inlineStr">
         <is>
           <t>1. Click the count on a work order row.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="J113" s="21" t="inlineStr">
-        <is>
-          <t>1. EXPECTED PER SPEC: Accept Delivery opens for the work order's first unreceived PO.
-2. Receiving behaves as it does today from there.</t>
-        </is>
-      </c>
-      <c r="K113" s="21" t="inlineStr">
+      <c r="J114" s="17" t="inlineStr">
+        <is>
+          <t>1. Clicking the count opens the receiving surface for the work order's first unreceived purchase order. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
+2. Receiving from there behaves as it does on the Bulk Receive page.</t>
+        </is>
+      </c>
+      <c r="K114" s="17" t="inlineStr">
         <is>
           <t>requirements S14-R2</t>
         </is>
       </c>
-      <c r="L113" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M113" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count. </t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
+      <c r="L114" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M114" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: clicking the Waiting on Parts count opens the Bulk Receive page for the WO's first unreceived PO - verified prior (case 29384 pushed 2026-07-09/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
         <is>
           <t>SF-WOP-03</t>
         </is>
       </c>
-      <c r="B114" s="17" t="inlineStr">
+      <c r="B115" s="21" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C114" s="17" t="inlineStr">
+      <c r="C115" s="21" t="inlineStr">
         <is>
           <t>S14-R3</t>
         </is>
       </c>
-      <c r="D114" s="17" t="inlineStr">
+      <c r="D115" s="21" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="E114" s="25" t="inlineStr">
+      <c r="E115" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F114" s="17" t="inlineStr">
+      <c r="F115" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G114" s="17" t="inlineStr">
+      <c r="G115" s="21" t="inlineStr">
         <is>
           <t>WO list visibility.</t>
         </is>
       </c>
-      <c r="H114" s="17" t="inlineStr">
+      <c r="H115" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO with nothing to receive (or POs off) is in the list with the column enabled.</t>
         </is>
       </c>
-      <c r="I114" s="17" t="inlineStr">
+      <c r="I115" s="21" t="inlineStr">
         <is>
           <t>1. Find a WO with nothing waiting to receive.
 2. Read its Waiting on Parts cell.</t>
         </is>
       </c>
-      <c r="J114" s="17" t="inlineStr">
-        <is>
-          <t>1. EXPECTED PER SPEC: the cell shows '—' with no clickable link.</t>
-        </is>
-      </c>
-      <c r="K114" s="17" t="inlineStr">
+      <c r="J115" s="21" t="inlineStr">
+        <is>
+          <t>1. A work order with nothing to receive shows an em dash ('—') in the Waiting on Parts column, with no clickable link.</t>
+        </is>
+      </c>
+      <c r="K115" s="21" t="inlineStr">
         <is>
           <t>requirements S14-R3</t>
         </is>
       </c>
-      <c r="L114" s="19" t="inlineStr">
+      <c r="L115" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M114" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows). </t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
+      <c r="M115" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: WO with nothing to receive shows '—' (no link) - verified prior (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="16" t="inlineStr">
         <is>
           <t>SF-REV-01</t>
         </is>
       </c>
-      <c r="B115" s="21" t="inlineStr">
+      <c r="B116" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C115" s="21" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D115" s="21" t="inlineStr">
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>R1 + S16-R12</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
         <is>
           <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
-      <c r="E115" s="22" t="inlineStr">
+      <c r="E116" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F115" s="21" t="inlineStr">
+      <c r="F116" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G115" s="21" t="inlineStr">
+      <c r="G116" s="17" t="inlineStr">
         <is>
           <t>Admin / owner (settings) + Work Order edit access.</t>
         </is>
       </c>
-      <c r="H115" s="21" t="inlineStr">
+      <c r="H116" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is ON and saved.</t>
         </is>
       </c>
-      <c r="I115" s="21" t="inlineStr">
+      <c r="I116" s="17" t="inlineStr">
         <is>
           <t>1. Open a work order with approved lines.
 2. Start completion.
 3. Observe that the review flow is used.</t>
         </is>
       </c>
-      <c r="J115" s="21" t="inlineStr">
-        <is>
-          <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.</t>
-        </is>
-      </c>
-      <c r="K115" s="21" t="inlineStr">
+      <c r="J116" s="17" t="inlineStr">
+        <is>
+          <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.
+2. When the last open line is resolved (by any path) while Require Review is on, the work order routes to Ready for Review — it never auto-completes.</t>
+        </is>
+      </c>
+      <c r="K116" s="17" t="inlineStr">
         <is>
           <t>Workflow Settings.html; WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L115" s="19" t="inlineStr">
+      <c r="L116" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M115" s="21" t="inlineStr">
-        <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="16" t="inlineStr">
+      <c r="M116" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): with Require Review ON, completing routes into the review flow (Send To Review), not a direct complete. | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>SF-REV-02</t>
         </is>
       </c>
-      <c r="B116" s="17" t="inlineStr">
+      <c r="B117" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C116" s="17" t="inlineStr">
+      <c r="C117" s="21" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D116" s="17" t="inlineStr">
-        <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
-        </is>
-      </c>
-      <c r="E116" s="22" t="inlineStr">
+      <c r="D117" s="21" t="inlineStr">
+        <is>
+          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
+        </is>
+      </c>
+      <c r="E117" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F116" s="17" t="inlineStr">
+      <c r="F117" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G116" s="17" t="inlineStr">
+      <c r="G117" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H116" s="17" t="inlineStr">
+      <c r="H117" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order with approved lines is ready to complete.</t>
         </is>
       </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>1. Click Complete Work Order.
-2. Read the wizard's primary CTA label.</t>
-        </is>
-      </c>
-      <c r="J116" s="17" t="inlineStr">
-        <is>
-          <t>1. The primary CTA reads 'Complete &amp; Send to Review' (Send to Review).</t>
-        </is>
-      </c>
-      <c r="K116" s="17" t="inlineStr">
+      <c r="I117" s="21" t="inlineStr">
+        <is>
+          <t>1. Open a work order that is ready to complete, with Require Review Before Completion turned on.
+2. Read the primary action button on the work order (and, for a work order that still has parts to receive, the heading of the dialog that opens).</t>
+        </is>
+      </c>
+      <c r="J117" s="21" t="inlineStr">
+        <is>
+          <t>1. With Require Review Before Completion ON, a ready work order's primary action button reads 'Send To Review' (it replaces 'Complete Work Order').
+2. For a work order that still has parts waiting to receive, clicking 'Send To Review' opens a dialog headed 'Complete &amp; Send to Review' that shows how many parts are waiting to receive and offers 'Receive Parts' and 'Send To Review'.</t>
+        </is>
+      </c>
+      <c r="K117" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L116" s="19" t="inlineStr">
+      <c r="L117" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M116" s="17" t="inlineStr">
-        <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
+      <c r="M117" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15827/S2-15783 live, Require Review ON): the primary action button = 'Send To Review' on BOTH ready and part-bearing WOs (it replaces 'Complete Work Order'). For a part-bearing WO, clicking 'Send To Review' opens a dialog HEADED 'Complete &amp; Send to Review' (body 'N part waiting to receive'; buttons Cancel / Receive Parts / Send To Review). So 'Complete &amp; Send to Review' is the review-dialog HEADER, not the button; the clickable CTA is 'Send To Review'. Title corrected + expected #2 corrected (a part-bearing WO does NOT read 'Complete Work Order'). Evidence: screenshots/relevance-fix-2026-07-13/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
         <is>
           <t>SF-REV-03</t>
         </is>
       </c>
-      <c r="B117" s="21" t="inlineStr">
+      <c r="B118" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C117" s="21" t="inlineStr">
+      <c r="C118" s="17" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="D117" s="21" t="inlineStr">
+      <c r="D118" s="17" t="inlineStr">
         <is>
           <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
-      <c r="E117" s="23" t="inlineStr">
+      <c r="E118" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F117" s="21" t="inlineStr">
+      <c r="F118" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G117" s="21" t="inlineStr">
+      <c r="G118" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H117" s="21" t="inlineStr">
+      <c r="H118" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order missing mileage/hours/VIN is ready to complete.</t>
         </is>
       </c>
-      <c r="I117" s="21" t="inlineStr">
+      <c r="I118" s="17" t="inlineStr">
         <is>
           <t>1. Start completion and reach the Details step.
 2. Note which vehicle fields are collected.</t>
         </is>
       </c>
-      <c r="J117" s="21" t="inlineStr">
-        <is>
-          <t>1. The Details step collects mileage and engine hours only.
-2. VIN is NOT collected here; it is captured later by the reviewer in the Mark Reviewed dialog.</t>
-        </is>
-      </c>
-      <c r="K117" s="21" t="inlineStr">
+      <c r="J118" s="17" t="inlineStr">
+        <is>
+          <t>1. When Require Review is on, the completion Details step collects Mileage and Engine Hours only.
+2. There is no VIN field in the completion modal; VIN is captured later by the reviewer in the Mark Reviewed dialog.</t>
+        </is>
+      </c>
+      <c r="K118" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements R3</t>
         </is>
       </c>
-      <c r="L117" s="19" t="inlineStr">
+      <c r="L118" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M117" s="21" t="inlineStr">
-        <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+      <c r="M118" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: the completion Details modal shows Mileage + Engine Hours and no VIN field (confirmed live on the review-off modal S2-15827; review-on captures VIN in Mark Reviewed per SF-REV-06). Upgraded from Pending - the field set is now confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>SF-REV-04</t>
         </is>
       </c>
-      <c r="B118" s="17" t="inlineStr">
+      <c r="B119" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C118" s="17" t="inlineStr">
+      <c r="C119" s="21" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="D118" s="17" t="inlineStr">
+      <c r="D119" s="21" t="inlineStr">
         <is>
           <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
-      <c r="E118" s="23" t="inlineStr">
+      <c r="E119" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F118" s="17" t="inlineStr">
+      <c r="F119" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G118" s="17" t="inlineStr">
+      <c r="G119" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access + receive access.</t>
         </is>
       </c>
-      <c r="H118" s="17" t="inlineStr">
+      <c r="H119" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON with a part-bearing work order.</t>
         </is>
       </c>
-      <c r="I118" s="17" t="inlineStr">
+      <c r="I119" s="21" t="inlineStr">
         <is>
           <t>1. Start completion and click Receive Parts.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="J118" s="17" t="inlineStr">
+      <c r="J119" s="21" t="inlineStr">
         <is>
           <t>1. Receive Parts opens the shared receive page (not an inline modal).</t>
         </is>
       </c>
-      <c r="K118" s="17" t="inlineStr">
+      <c r="K119" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Receive Vendor Parts - v2.html</t>
         </is>
       </c>
-      <c r="L118" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M118" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
+      <c r="L119" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M119" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: 'Receive Parts' opens the shared receive page (not an inline modal) in the review flow — verified prior drive (FV-rev04-receivestep/afterreceive.png, 2026-07-10); review flow re-confirmed live this run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
         <is>
           <t>SF-REV-05</t>
         </is>
       </c>
-      <c r="B119" s="21" t="inlineStr">
+      <c r="B120" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C119" s="21" t="inlineStr">
-        <is>
-          <t>R5 / R6</t>
-        </is>
-      </c>
-      <c r="D119" s="21" t="inlineStr">
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>R5 / R6 + S16-R12</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
         <is>
           <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
-      <c r="E119" s="18" t="inlineStr">
+      <c r="E120" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F119" s="21" t="inlineStr">
+      <c r="F120" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G119" s="21" t="inlineStr">
+      <c r="G120" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H119" s="21" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Review is ON and a work order with approved lines is in the completion wizard.</t>
-        </is>
-      </c>
-      <c r="I119" s="21" t="inlineStr">
-        <is>
-          <t>1. Click Complete &amp; Send to Review.
+      <c r="H120" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review is ON and a work order with approved lines is ready to send to review (for a work order with parts still to receive, the 'Complete &amp; Send to Review' dialog is open).</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>1. Click Send To Review (the primary action button, or the 'Send To Review' button in the 'Complete &amp; Send to Review' dialog for a part-bearing work order).
 2. Observe the work order status and banner.
 3. Check the lines state and inventory pick state.</t>
         </is>
       </c>
-      <c r="J119" s="21" t="inlineStr">
+      <c r="J120" s="17" t="inlineStr">
         <is>
           <t>1. The work order status becomes Review (amber).
 2. A 'Ready for Review' / 'Sent for review' indication is shown.
-3. Lines lock to Complete and inventory is auto-picked.</t>
-        </is>
-      </c>
-      <c r="K119" s="21" t="inlineStr">
+3. Lines lock to Complete and inventory is auto-picked.
+4. The same Review / Ready-for-Review end state is reached when the last open line auto-resolves under Require Review on, not only when Send To Review is clicked explicitly.</t>
+        </is>
+      </c>
+      <c r="K120" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L119" s="19" t="inlineStr">
+      <c r="L120" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M119" s="21" t="inlineStr">
-        <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="16" t="inlineStr">
+      <c r="M120" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15823/S2-15827 live, Require Review ON): the confirm button is 'Send To Review' (NOT 'Complete &amp; Send to Review' - that is the dialog HEADER for a part-bearing WO). Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.) Step 1 label corrected. Evidence: screenshots/relevance-fix-2026-07-13/. | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>SF-REV-06</t>
         </is>
       </c>
-      <c r="B120" s="17" t="inlineStr">
+      <c r="B121" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C120" s="17" t="inlineStr">
+      <c r="C121" s="21" t="inlineStr">
         <is>
           <t>R7 / R10</t>
         </is>
       </c>
-      <c r="D120" s="17" t="inlineStr">
+      <c r="D121" s="21" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
-      <c r="E120" s="18" t="inlineStr">
+      <c r="E121" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F120" s="17" t="inlineStr">
+      <c r="F121" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G120" s="17" t="inlineStr">
+      <c r="G121" s="21" t="inlineStr">
         <is>
           <t>Reviewer role (manager/foreman) — matrix TBD. Verified here as admin.</t>
         </is>
       </c>
-      <c r="H120" s="17" t="inlineStr">
+      <c r="H121" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review state.</t>
         </is>
       </c>
-      <c r="I120" s="17" t="inlineStr">
+      <c r="I121" s="21" t="inlineStr">
         <is>
           <t>1. Click Mark Reviewed.
 2. Observe the VIN field.
 3. Clear the VIN and check the Confirm Review button, then enter a VIN.</t>
         </is>
       </c>
-      <c r="J120" s="17" t="inlineStr">
-        <is>
-          <t>1. The Mark Reviewed dialog exposes a VIN field (input_review_vin), required if missing.
+      <c r="J121" s="21" t="inlineStr">
+        <is>
+          <t>1. The Mark Reviewed dialog shows a VIN / Serial # field, required if the work order is missing a valid VIN.
 2. Confirm Review is disabled until a VIN is present.
-3. With a VIN, Confirm Review is enabled.</t>
-        </is>
-      </c>
-      <c r="K120" s="17" t="inlineStr">
+3. Once a VIN is entered, Confirm Review is enabled.</t>
+        </is>
+      </c>
+      <c r="K121" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; WO Review Flow - Handoff.md (test IDs)</t>
         </is>
       </c>
-      <c r="L120" s="19" t="inlineStr">
+      <c r="L121" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M120" s="17" t="inlineStr">
-        <is>
-          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
+      <c r="M121" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed action confirmed live (S2-15823). The VIN-required dialog surfaces only when the WO lacks a valid VIN; every test WO this run had a VIN (so Mark Reviewed completed directly - see SF-REV-08). VIN-required dialog verified prior run 2026-07-06 (S16-04-review-wizard.png). Stripped dev test-id 'input_review_vin' from tester wording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="16" t="inlineStr">
         <is>
           <t>SF-REV-07</t>
         </is>
       </c>
-      <c r="B121" s="21" t="inlineStr">
+      <c r="B122" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C121" s="21" t="inlineStr">
+      <c r="C122" s="17" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="D121" s="21" t="inlineStr">
+      <c r="D122" s="17" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="E121" s="23" t="inlineStr">
+      <c r="E122" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F121" s="21" t="inlineStr">
+      <c r="F122" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G121" s="21" t="inlineStr">
+      <c r="G122" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H121" s="21" t="inlineStr">
+      <c r="H122" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order with an inventory line just went to Review.</t>
         </is>
       </c>
-      <c r="I121" s="21" t="inlineStr">
+      <c r="I122" s="17" t="inlineStr">
         <is>
           <t>1. Open the work order in Review state.
 2. Check the line states.
 3. Check whether inventory was auto-picked.</t>
         </is>
       </c>
-      <c r="J121" s="21" t="inlineStr">
+      <c r="J122" s="17" t="inlineStr">
         <is>
           <t>1. Lines are locked to Complete.
 2. Inventory has been auto-picked.</t>
         </is>
       </c>
-      <c r="K121" s="21" t="inlineStr">
+      <c r="K122" s="17" t="inlineStr">
         <is>
           <t>requirements R6</t>
         </is>
       </c>
-      <c r="L121" s="19" t="inlineStr">
+      <c r="L122" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M121" s="21" t="inlineStr">
-        <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="16" t="inlineStr">
+      <c r="M122" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): on Send To Review the lines lock to Complete and inventory is auto-picked (design; review state confirmed live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>SF-REV-08</t>
         </is>
       </c>
-      <c r="B122" s="17" t="inlineStr">
+      <c r="B123" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>R5 / R8 (distinct Reviewed state)</t>
-        </is>
-      </c>
-      <c r="D122" s="17" t="inlineStr">
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>R5 / R8 (direct sign-off, no separate Complete) + S16-R12</t>
+        </is>
+      </c>
+      <c r="D123" s="21" t="inlineStr">
         <is>
           <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
-      <c r="E122" s="22" t="inlineStr">
+      <c r="E123" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F122" s="17" t="inlineStr">
+      <c r="F123" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G122" s="17" t="inlineStr">
+      <c r="G123" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H122" s="17" t="inlineStr">
+      <c r="H123" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review with the Mark Reviewed dialog filled (VIN present).</t>
         </is>
       </c>
-      <c r="I122" s="17" t="inlineStr">
+      <c r="I123" s="21" t="inlineStr">
         <is>
           <t>1. Click Confirm Review.
 2. Observe the resulting work order state.
 3. Look for a separate final 'Complete Work Order' action.</t>
         </is>
       </c>
-      <c r="J122" s="17" t="inlineStr">
+      <c r="J123" s="21" t="inlineStr">
         <is>
           <t>1. After Confirm Review the sign-off completes and the work order moves directly Review -&gt; Complete.
-2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.</t>
-        </is>
-      </c>
-      <c r="K122" s="17" t="inlineStr">
+2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.
+3. Note: with Require Review on, resolving the last open line first routes the work order to Ready for Review; sign-off (Confirm Review) then moves it to Complete.</t>
+        </is>
+      </c>
+      <c r="K123" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements R5/R8</t>
         </is>
       </c>
-      <c r="L122" s="19" t="inlineStr">
+      <c r="L123" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M122" s="17" t="inlineStr">
-        <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
+      <c r="M123" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Mark Reviewed (VIN present) signs off and moves the WO directly Review -&gt; Complete; no distinct 'Reviewed' holding state and no separate final Complete click (S2-15823 went Review-&gt;Complete). | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="16" t="inlineStr">
         <is>
           <t>SF-REV-09</t>
         </is>
       </c>
-      <c r="B123" s="21" t="inlineStr">
+      <c r="B124" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="21" t="inlineStr">
+      <c r="C124" s="17" t="inlineStr">
         <is>
           <t>R7 (role-gating)</t>
         </is>
       </c>
-      <c r="D123" s="21" t="inlineStr">
+      <c r="D124" s="17" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="E123" s="22" t="inlineStr">
+      <c r="E124" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F123" s="21" t="inlineStr">
+      <c r="F124" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G123" s="21" t="inlineStr">
-        <is>
-          <t>Review Work Orders permission + reviewer must not be the completer.</t>
-        </is>
-      </c>
-      <c r="H123" s="21" t="inlineStr">
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>Review Work Orders permission.</t>
+        </is>
+      </c>
+      <c r="H124" s="17" t="inlineStr">
         <is>
           <t>1. A role with Review Work Orders and a role without it both exist.
 2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="I123" s="21" t="inlineStr">
+      <c r="I124" s="17" t="inlineStr">
         <is>
           <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
 3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
-      <c r="J123" s="21" t="inlineStr">
+      <c r="J124" s="17" t="inlineStr">
         <is>
           <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
-3. The user who completed / sent the work order to review cannot Mark Reviewed even with the permission; a different qualified reviewer can.</t>
-        </is>
-      </c>
-      <c r="K123" s="21" t="inlineStr">
-        <is>
-          <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
-        </is>
-      </c>
-      <c r="L123" s="19" t="inlineStr">
+3. A user who holds the Review Work Orders permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
+        </is>
+      </c>
+      <c r="K124" s="17" t="inlineStr">
+        <is>
+          <t>requirements R7 / §9 (Review Work Orders permission gate)</t>
+        </is>
+      </c>
+      <c r="L124" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M123" s="21" t="inlineStr">
-        <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="16" t="inlineStr">
+      <c r="M124" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed gated by Review Work Orders (woReviewWorkOrders) per fresh roles matrix (roles-matrix-2026-07-13.md); role without it sees Mark Reviewed disabled + 'Awaiting review'; self-review allowed when the role holds the permission (Milos ruling). Review flow re-confirmed live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>SF-REV-10</t>
         </is>
       </c>
-      <c r="B124" s="17" t="inlineStr">
+      <c r="B125" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C124" s="17" t="inlineStr">
+      <c r="C125" s="21" t="inlineStr">
         <is>
           <t>R7 (VIN required, no note)</t>
         </is>
       </c>
-      <c r="D124" s="17" t="inlineStr">
+      <c r="D125" s="21" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
-      <c r="E124" s="23" t="inlineStr">
+      <c r="E125" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F124" s="17" t="inlineStr">
+      <c r="F125" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G124" s="17" t="inlineStr">
+      <c r="G125" s="21" t="inlineStr">
         <is>
           <t>Reviewer role (matrix TBD).</t>
         </is>
       </c>
-      <c r="H124" s="17" t="inlineStr">
+      <c r="H125" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open.</t>
         </is>
       </c>
-      <c r="I124" s="17" t="inlineStr">
+      <c r="I125" s="21" t="inlineStr">
         <is>
           <t>1. Open the Mark Reviewed dialog.
 2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
 3. Confirm there is no review note field, then complete the sign-off.</t>
         </is>
       </c>
-      <c r="J124" s="17" t="inlineStr">
+      <c r="J125" s="21" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
 2. There is no review note field on the dialog.
 3. The sign-off completes using the VIN / Serial # only.</t>
         </is>
       </c>
-      <c r="K124" s="17" t="inlineStr">
+      <c r="K125" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow - Handoff.md (test IDs)</t>
         </is>
       </c>
-      <c r="L124" s="19" t="inlineStr">
+      <c r="L125" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M124" s="17" t="inlineStr">
-        <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
+      <c r="M125" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed uses VIN / Serial # only, no review note field (V2.4 Δ4 confirmed; SF-REV-06/10 were already note-free). Dialog surfaces when VIN missing (verified prior 2026-07-06); Mark Reviewed action re-confirmed live this run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
         <is>
           <t>SF-REV-11</t>
         </is>
       </c>
-      <c r="B125" s="21" t="inlineStr">
+      <c r="B126" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C125" s="21" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="D125" s="21" t="inlineStr">
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>R8 + S16-R12</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
         <is>
           <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
-      <c r="E125" s="22" t="inlineStr">
+      <c r="E126" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F125" s="21" t="inlineStr">
+      <c r="F126" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G125" s="21" t="inlineStr">
+      <c r="G126" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access + Finance access.</t>
         </is>
       </c>
-      <c r="H125" s="21" t="inlineStr">
+      <c r="H126" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Reviewed state (or a Review state before sign-off for the invoicing-block check).</t>
         </is>
       </c>
-      <c r="I125" s="21" t="inlineStr">
+      <c r="I126" s="17" t="inlineStr">
         <is>
           <t>1. Before sign-off, attempt to invoice the work order.
 2. Complete the review sign-off (Confirm Review).
 3. Confirm the work order becomes Complete (invoice-ready).</t>
         </is>
       </c>
-      <c r="J125" s="21" t="inlineStr">
+      <c r="J126" s="17" t="inlineStr">
         <is>
           <t>1. Invoicing is blocked until the work order is reviewed.
-2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.</t>
-        </is>
-      </c>
-      <c r="K125" s="21" t="inlineStr">
+2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.
+3. With Require Review on the work order never auto-completes on last-line-resolve; it routes to Ready for Review and invoicing stays blocked until it is reviewed.</t>
+        </is>
+      </c>
+      <c r="K126" s="17" t="inlineStr">
         <is>
           <t>requirements R8</t>
         </is>
       </c>
-      <c r="L125" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M125" s="21" t="inlineStr">
-        <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="16" t="inlineStr">
+      <c r="L126" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
+        </is>
+      </c>
+      <c r="M126" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q8). The direct-sign-off behavior is observed: Confirm Review signs off and completes the WO directly with no distinct 'Reviewed' holding state (see SF-REV-08). The 'invoicing blocked until reviewed' leg depends on the Q8 ruling about whether a separate Reviewed state should exist. No pass/fail asserted on the undecided policy. | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>SF-REV-12</t>
         </is>
       </c>
-      <c r="B126" s="17" t="inlineStr">
+      <c r="B127" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C126" s="17" t="inlineStr">
+      <c r="C127" s="21" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="D126" s="17" t="inlineStr">
+      <c r="D127" s="21" t="inlineStr">
         <is>
           <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
-      <c r="E126" s="23" t="inlineStr">
+      <c r="E127" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F126" s="17" t="inlineStr">
+      <c r="F127" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G126" s="17" t="inlineStr">
+      <c r="G127" s="21" t="inlineStr">
         <is>
           <t>WO list visibility.</t>
         </is>
       </c>
-      <c r="H126" s="17" t="inlineStr">
+      <c r="H127" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. At least one work order is in Review state.</t>
         </is>
       </c>
-      <c r="I126" s="17" t="inlineStr">
+      <c r="I127" s="21" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list.
 2. Look for a 'Ready for Review' filter or column.
 3. Confirm work orders in Review appear in it.</t>
         </is>
       </c>
-      <c r="J126" s="17" t="inlineStr">
+      <c r="J127" s="21" t="inlineStr">
         <is>
           <t>1. EXPECTED PER SPEC: a 'Ready for Review' filter/column lists work orders awaiting review.</t>
         </is>
       </c>
-      <c r="K126" s="17" t="inlineStr">
+      <c r="K127" s="21" t="inlineStr">
         <is>
           <t>Work Orders List.html; requirements R9</t>
         </is>
       </c>
-      <c r="L126" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M126" s="17" t="inlineStr">
-        <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>SF-REV-13</t>
-        </is>
-      </c>
-      <c r="B127" s="21" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C127" s="21" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="D127" s="21" t="inlineStr">
-        <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
-        </is>
-      </c>
-      <c r="E127" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F127" s="21" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G127" s="21" t="inlineStr">
-        <is>
-          <t>Work Order edit access.</t>
-        </is>
-      </c>
-      <c r="H127" s="21" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Review is ON and a work order has one unapproved line.</t>
-        </is>
-      </c>
-      <c r="I127" s="21" t="inlineStr">
-        <is>
-          <t>1. Click Complete &amp; Send to Review.
-2. Attempt to send with an unapproved line.</t>
-        </is>
-      </c>
-      <c r="J127" s="21" t="inlineStr">
-        <is>
-          <t>1. Send to Review is blocked with the existing approve-line error while any line is unapproved.</t>
-        </is>
-      </c>
-      <c r="K127" s="21" t="inlineStr">
-        <is>
-          <t>requirements R11</t>
-        </is>
-      </c>
       <c r="L127" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
@@ -10083,1119 +10114,1190 @@
       </c>
       <c r="M127" s="21" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: 'Ready for Review' indicator confirmed on a WO in Review (S2-15823). Reviewer-queue surfacing on the WO list per design; the 'Ready for Review' label is build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
+          <t>SF-REV-13</t>
+        </is>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
+        </is>
+      </c>
+      <c r="E128" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>Work Order edit access.</t>
+        </is>
+      </c>
+      <c r="H128" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review is ON and a work order has one unapproved line.</t>
+        </is>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>1. Open the work order and locate the 'Send To Review' action while a line is still unapproved.
+2. Attempt to use Send To Review with the unapproved line.</t>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
+        <is>
+          <t>1. The 'Send To Review' action cannot be used while any line is unapproved - the 'Send To Review' button is disabled until every line has been approved.</t>
+        </is>
+      </c>
+      <c r="K128" s="17" t="inlineStr">
+        <is>
+          <t>requirements R11</t>
+        </is>
+      </c>
+      <c r="L128" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M128" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15783 live, Require Review ON, one unapproved line): the 'Send To Review' button is DISABLED (isDisabled=true) while a line is unapproved; it becomes usable only after every line is approved. Step label corrected ('Complete &amp; Send to Review' -&gt; 'Send To Review'; the clickable action is 'Send To Review') and expected made build-accurate (the button is disabled rather than showing an error message). Evidence: screenshots/relevance-fix-2026-07-13/neg-5b653a02-sendtoreview-blocked.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
           <t>SF-REV-14</t>
         </is>
       </c>
-      <c r="B128" s="17" t="inlineStr">
+      <c r="B129" s="21" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C128" s="17" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>R Core parts / invoicing block</t>
         </is>
       </c>
-      <c r="D128" s="17" t="inlineStr">
+      <c r="D129" s="21" t="inlineStr">
         <is>
           <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
-      <c r="E128" s="23" t="inlineStr">
+      <c r="E129" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F128" s="17" t="inlineStr">
+      <c r="F129" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G128" s="17" t="inlineStr">
+      <c r="G129" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access + Finance access.</t>
         </is>
       </c>
-      <c r="H128" s="17" t="inlineStr">
+      <c r="H129" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has inventory and special-order cores.</t>
         </is>
       </c>
-      <c r="I128" s="17" t="inlineStr">
+      <c r="I129" s="21" t="inlineStr">
         <is>
           <t>1. Resolve inventory cores in the completion modal (after Pick) before Send to Review.
 2. For required-invoice, resolve special-order cores after the Receive round-trip before Send to Review; for optional-invoice, resolve at the Create Invoice gate after sign-off.
 3. Attempt to invoice before both Reviewed and cores are resolved.</t>
         </is>
       </c>
-      <c r="J128" s="17" t="inlineStr">
+      <c r="J129" s="21" t="inlineStr">
         <is>
           <t>1. Inventory cores are resolved before Send to Review.
 2. Special-order cores follow the vendor-invoice rules.
-3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.</t>
-        </is>
-      </c>
-      <c r="K128" s="17" t="inlineStr">
+3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.
+4. In the review flow too, a waiting special-order core cannot be skipped: Send to Review / completion is blocked until the core is received and resolved, and invoicing stays blocked until both Reviewed and all cores resolved.</t>
+        </is>
+      </c>
+      <c r="K129" s="21" t="inlineStr">
         <is>
           <t>requirements R Core parts</t>
         </is>
       </c>
-      <c r="L128" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M128" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
+      <c r="L129" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M129" s="21" t="inlineStr">
+        <is>
+          <t>Aligned 2026-07-14 to design #4 un-skippable core (review flow). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
         <is>
           <t>SF-REV-15</t>
         </is>
       </c>
-      <c r="B129" s="21" t="inlineStr">
+      <c r="B130" s="17" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C129" s="21" t="inlineStr">
+      <c r="C130" s="17" t="inlineStr">
         <is>
           <t>R Open (default)</t>
         </is>
       </c>
-      <c r="D129" s="21" t="inlineStr">
+      <c r="D130" s="17" t="inlineStr">
         <is>
           <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
         </is>
       </c>
-      <c r="E129" s="25" t="inlineStr">
+      <c r="E130" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F129" s="21" t="inlineStr">
+      <c r="F130" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G129" s="21" t="inlineStr">
+      <c r="G130" s="17" t="inlineStr">
         <is>
           <t>Admin / owner (settings).</t>
         </is>
       </c>
-      <c r="H129" s="21" t="inlineStr">
+      <c r="H130" s="17" t="inlineStr">
         <is>
           <t>1. A newly-created org and an existing org are available.
 2. Signed in as Admin for each.</t>
         </is>
       </c>
-      <c r="I129" s="21" t="inlineStr">
+      <c r="I130" s="17" t="inlineStr">
         <is>
           <t>1. Check the Require Review default on a brand-new org.
 2. Check that existing orgs keep today's behavior (backfilled).</t>
         </is>
       </c>
-      <c r="J129" s="21" t="inlineStr">
-        <is>
-          <t>1. A brand-new org shows the Require Review setting in its default state, and existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
-        </is>
-      </c>
-      <c r="K129" s="21" t="inlineStr">
+      <c r="J130" s="17" t="inlineStr">
+        <is>
+          <t>1. On a brand-new org the Require Review Before Completion setting shows its default state.
+2. Existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
+        </is>
+      </c>
+      <c r="K130" s="17" t="inlineStr">
         <is>
           <t>requirements §8 open questions / R Open</t>
         </is>
       </c>
-      <c r="L129" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="M129" s="21" t="inlineStr">
-        <is>
-          <t>Spec §8 marks the require-review default as UNRESOLVED. Confirm the intended default before pass/fail. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] Round-1 answer sheet said 'Require Review ON for ALL orgs'; V2.4 S1-R4 (latest) keeps 'Default per cohort (see §8)' -&gt; per-cohort RETAINED; the 'ON for all' rewrite was NOT applied. §8 still marks which cohorts default ON as unresolved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="16" t="inlineStr">
+      <c r="L130" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
+        </is>
+      </c>
+      <c r="M130" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q1). The Require-Review default for NEW vs EXISTING orgs cannot be observed on the long-lived sv7301 org (Require Review is currently a normal toggle, default reflects prior toggling). The cohort default rule is a Milos product decision (Q1). No pass/fail asserted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="inlineStr">
         <is>
           <t>SF-UX-01</t>
         </is>
       </c>
-      <c r="B130" s="17" t="inlineStr">
+      <c r="B131" s="21" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C130" s="17" t="inlineStr">
+      <c r="C131" s="21" t="inlineStr">
         <is>
           <t>S15-R1</t>
         </is>
       </c>
-      <c r="D130" s="17" t="inlineStr">
+      <c r="D131" s="21" t="inlineStr">
         <is>
           <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
-      <c r="E130" s="23" t="inlineStr">
+      <c r="E131" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F130" s="17" t="inlineStr">
+      <c r="F131" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G130" s="17" t="inlineStr">
+      <c r="G131" s="21" t="inlineStr">
         <is>
           <t>Work Order create access.</t>
         </is>
       </c>
-      <c r="H130" s="17" t="inlineStr">
+      <c r="H131" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are on the Create Work Order form (/workorders → Create).</t>
         </is>
       </c>
-      <c r="I130" s="17" t="inlineStr">
+      <c r="I131" s="21" t="inlineStr">
         <is>
           <t>1. Open the Create Work Order form.
 2. Read the primary button label.</t>
         </is>
       </c>
-      <c r="J130" s="17" t="inlineStr">
+      <c r="J131" s="21" t="inlineStr">
         <is>
           <t>1. The primary button reads 'Create Work Order'.</t>
         </is>
       </c>
-      <c r="K130" s="17" t="inlineStr">
+      <c r="K131" s="21" t="inlineStr">
         <is>
           <t>Work Orders List.html; requirements S15-R1</t>
         </is>
       </c>
-      <c r="L130" s="19" t="inlineStr">
+      <c r="L131" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M130" s="17" t="inlineStr">
-        <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20" t="inlineStr">
+      <c r="M131" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 (UX-workorders-list.png): the Work Orders create form's primary button reads 'Create Work Order' (confirmed on /workorders list Create Work Order button).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
         <is>
           <t>SF-UX-02</t>
         </is>
       </c>
-      <c r="B131" s="21" t="inlineStr">
+      <c r="B132" s="17" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C131" s="21" t="inlineStr">
+      <c r="C132" s="17" t="inlineStr">
         <is>
           <t>S15-R2</t>
         </is>
       </c>
-      <c r="D131" s="21" t="inlineStr">
+      <c r="D132" s="17" t="inlineStr">
         <is>
           <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
-      <c r="E131" s="23" t="inlineStr">
+      <c r="E132" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F131" s="21" t="inlineStr">
+      <c r="F132" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G131" s="21" t="inlineStr">
+      <c r="G132" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H131" s="21" t="inlineStr">
+      <c r="H132" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order requiring mileage/VIN is being completed.</t>
         </is>
       </c>
-      <c r="I131" s="21" t="inlineStr">
+      <c r="I132" s="17" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Observe where required fields are collected.
 3. Confirm the tech story is handled by its own flow, not inside this modal.</t>
         </is>
       </c>
-      <c r="J131" s="21" t="inlineStr">
-        <is>
-          <t>1. Required fields (mileage / VIN when required) are collected in a centralized center modal.
-2. The tech story is NOT part of this modal (Story 17 handles it separately).</t>
-        </is>
-      </c>
-      <c r="K131" s="21" t="inlineStr">
+      <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t>1. The required vehicle fields (Mileage and Engine Hours) are collected in a centralized center modal titled 'Complete Work Order'.
+2. The tech story is NOT part of this modal (it is handled by its own line-level flow).</t>
+        </is>
+      </c>
+      <c r="K132" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements S15-R2</t>
         </is>
       </c>
-      <c r="L131" s="19" t="inlineStr">
+      <c r="L132" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M131" s="21" t="inlineStr">
-        <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="16" t="inlineStr">
+      <c r="M132" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: required fields collected in the centralized 'Complete Work Order' modal (Mileage + Engine Hours; no VIN field in the modal - see SF-COMP-16/SF-VAL-02 build finding); tech story handled separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="inlineStr">
         <is>
           <t>SF-UX-03</t>
         </is>
       </c>
-      <c r="B132" s="17" t="inlineStr">
+      <c r="B133" s="21" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C132" s="17" t="inlineStr">
+      <c r="C133" s="21" t="inlineStr">
         <is>
           <t>S15-R3</t>
         </is>
       </c>
-      <c r="D132" s="17" t="inlineStr">
+      <c r="D133" s="21" t="inlineStr">
         <is>
           <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
-      <c r="E132" s="23" t="inlineStr">
+      <c r="E133" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F132" s="17" t="inlineStr">
+      <c r="F133" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G132" s="17" t="inlineStr">
+      <c r="G133" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H132" s="17" t="inlineStr">
+      <c r="H133" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has just been completed.</t>
         </is>
       </c>
-      <c r="I132" s="17" t="inlineStr">
+      <c r="I133" s="21" t="inlineStr">
         <is>
           <t>1. Read the success screen.
 2. Confirm WO number, total, Done and Go to Invoice.
 3. Confirm the invoice number is shown on the Finance step, not the success screen.</t>
         </is>
       </c>
-      <c r="J132" s="17" t="inlineStr">
+      <c r="J133" s="21" t="inlineStr">
         <is>
           <t>1. The success screen shows the WO number and total with Done and Go to Invoice.
 2. The invoice number appears on the Finance step, not on the success screen.</t>
         </is>
       </c>
-      <c r="K132" s="17" t="inlineStr">
+      <c r="K133" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements S15-R3</t>
         </is>
       </c>
-      <c r="L132" s="19" t="inlineStr">
+      <c r="L133" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M132" s="17" t="inlineStr">
-        <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="20" t="inlineStr">
+      <c r="M133" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: success screen shows WO number + total with 'Done' and 'Go To Invoice'; invoice number appears on the Finance step (confirmed live via SF-COMP drives S2-15825 'Invoice total $434.95').</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t>SF-UX-04</t>
         </is>
       </c>
-      <c r="B133" s="21" t="inlineStr">
+      <c r="B134" s="17" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C133" s="21" t="inlineStr">
+      <c r="C134" s="17" t="inlineStr">
         <is>
           <t>S15-R4</t>
         </is>
       </c>
-      <c r="D133" s="21" t="inlineStr">
+      <c r="D134" s="17" t="inlineStr">
         <is>
           <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
-      <c r="E133" s="23" t="inlineStr">
+      <c r="E134" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F133" s="21" t="inlineStr">
+      <c r="F134" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G133" s="21" t="inlineStr">
+      <c r="G134" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H133" s="21" t="inlineStr">
+      <c r="H134" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completion modal is open.</t>
         </is>
       </c>
-      <c r="I133" s="21" t="inlineStr">
+      <c r="I134" s="17" t="inlineStr">
         <is>
           <t>1. Trigger the close-confirmation modal.
 2. Click Close (prominent/red) and observe.
 3. Trigger it again and click Cancel (text link, far left) and observe.</t>
         </is>
       </c>
-      <c r="J133" s="21" t="inlineStr">
+      <c r="J134" s="17" t="inlineStr">
         <is>
           <t>1. Close (prominent/red button) closes the confirmation modal only, discards nothing (no discard warning), and stays on the work order.
 2. Cancel (text link, far left) closes the modal and returns to the previous screen.
 3. Other consumers of the shared confirmation dialog keep their existing action labels.</t>
         </is>
       </c>
-      <c r="K133" s="21" t="inlineStr">
+      <c r="K134" s="17" t="inlineStr">
         <is>
           <t>requirements S15-R4 (design pending)</t>
         </is>
       </c>
-      <c r="L133" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M133" s="21" t="inlineStr">
-        <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="16" t="inlineStr">
+      <c r="L134" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
+        </is>
+      </c>
+      <c r="M134" s="17" t="inlineStr">
+        <is>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q10). The close-vs-cancel confirmation modal (Close = closes modal only; Cancel = closes modal + returns to previous screen) is per the design 'still to be added'; no distinct close/cancel confirmation modal behavior is defined/finalized. Milos Q10 decision. No pass/fail asserted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
         <is>
           <t>SF-PERM-01</t>
         </is>
       </c>
-      <c r="B134" s="17" t="inlineStr">
+      <c r="B135" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C134" s="17" t="inlineStr">
+      <c r="C135" s="21" t="inlineStr">
         <is>
           <t>S1 AC / §8 Permissions</t>
         </is>
       </c>
-      <c r="D134" s="17" t="inlineStr">
+      <c r="D135" s="21" t="inlineStr">
         <is>
           <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
-      <c r="E134" s="22" t="inlineStr">
+      <c r="E135" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F134" s="17" t="inlineStr">
+      <c r="F135" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G134" s="17" t="inlineStr">
+      <c r="G135" s="21" t="inlineStr">
         <is>
           <t>App Settings permission (system defaults: Admin, Service Manager, Office). A role without App Settings is used for the negative.</t>
         </is>
       </c>
-      <c r="H134" s="17" t="inlineStr">
+      <c r="H135" s="21" t="inlineStr">
         <is>
           <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
 2. You can sign in as each.</t>
         </is>
       </c>
-      <c r="I134" s="17" t="inlineStr">
+      <c r="I135" s="21" t="inlineStr">
         <is>
           <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
 2. Sign in as a role without App Settings and attempt to open and modify the same page.
 3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
-      <c r="J134" s="17" t="inlineStr">
+      <c r="J135" s="21" t="inlineStr">
         <is>
           <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
 2. A role without App Settings cannot open or change the Work Order settings.
 3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
-      <c r="K134" s="17" t="inlineStr">
+      <c r="K135" s="21" t="inlineStr">
         <is>
           <t>requirements S1 AC / §9 (App Settings gate)</t>
         </is>
       </c>
-      <c r="L134" s="19" t="inlineStr">
+      <c r="L135" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M134" s="17" t="inlineStr">
-        <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20" t="inlineStr">
+      <c r="M135" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
         <is>
           <t>SF-PERM-02</t>
         </is>
       </c>
-      <c r="B135" s="21" t="inlineStr">
+      <c r="B136" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C135" s="21" t="inlineStr">
+      <c r="C136" s="17" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="D135" s="21" t="inlineStr">
+      <c r="D136" s="17" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="E135" s="23" t="inlineStr">
+      <c r="E136" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F135" s="21" t="inlineStr">
+      <c r="F136" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G135" s="21" t="inlineStr">
+      <c r="G136" s="17" t="inlineStr">
         <is>
           <t>Work Orders: Create &amp; Edit + WO Lines: Create &amp; Edit + Full View (to approve lines).</t>
         </is>
       </c>
-      <c r="H135" s="21" t="inlineStr">
+      <c r="H136" s="17" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. A work order ready to complete exists.</t>
         </is>
       </c>
-      <c r="I135" s="21" t="inlineStr">
+      <c r="I136" s="17" t="inlineStr">
         <is>
           <t>1. For each role, attempt to complete a work order.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="J135" s="21" t="inlineStr">
+      <c r="J136" s="17" t="inlineStr">
         <is>
           <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
 3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
-      <c r="K135" s="21" t="inlineStr">
+      <c r="K136" s="17" t="inlineStr">
         <is>
           <t>requirements §9 (Complete WO gate + per-role matrix)</t>
         </is>
       </c>
-      <c r="L135" s="19" t="inlineStr">
+      <c r="L136" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M135" s="21" t="inlineStr">
-        <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="16" t="inlineStr">
+      <c r="M136" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
         <is>
           <t>SF-PERM-03</t>
         </is>
       </c>
-      <c r="B136" s="17" t="inlineStr">
+      <c r="B137" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C136" s="17" t="inlineStr">
+      <c r="C137" s="21" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="D136" s="17" t="inlineStr">
+      <c r="D137" s="21" t="inlineStr">
         <is>
           <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
-      <c r="E136" s="23" t="inlineStr">
+      <c r="E137" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F136" s="17" t="inlineStr">
+      <c r="F137" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G136" s="17" t="inlineStr">
+      <c r="G137" s="21" t="inlineStr">
         <is>
           <t>Vendor &amp; Order Mgmt: Create &amp; Edit + See Financial Data.</t>
         </is>
       </c>
-      <c r="H136" s="17" t="inlineStr">
+      <c r="H137" s="21" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. The Bulk Receive flow is available (Story 7/8 built).</t>
         </is>
       </c>
-      <c r="I136" s="17" t="inlineStr">
+      <c r="I137" s="21" t="inlineStr">
         <is>
           <t>1. For each role, attempt to reach and use Bulk Receive.
 2. Record the outcomes.</t>
         </is>
       </c>
-      <c r="J136" s="17" t="inlineStr">
+      <c r="J137" s="21" t="inlineStr">
         <is>
           <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
 2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
-      <c r="K136" s="17" t="inlineStr">
+      <c r="K137" s="21" t="inlineStr">
         <is>
           <t>requirements §9 (Bulk Receive gate + per-role matrix)</t>
         </is>
       </c>
-      <c r="L136" s="19" t="inlineStr">
+      <c r="L137" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M136" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap). </t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20" t="inlineStr">
+      <c r="M137" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
         <is>
           <t>SF-PERM-04</t>
         </is>
       </c>
-      <c r="B137" s="21" t="inlineStr">
+      <c r="B138" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C137" s="21" t="inlineStr">
+      <c r="C138" s="17" t="inlineStr">
         <is>
           <t>R7 / §8 role-gating review</t>
         </is>
       </c>
-      <c r="D137" s="21" t="inlineStr">
+      <c r="D138" s="17" t="inlineStr">
         <is>
           <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
-      <c r="E137" s="23" t="inlineStr">
+      <c r="E138" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F137" s="21" t="inlineStr">
+      <c r="F138" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G137" s="21" t="inlineStr">
-        <is>
-          <t>Review Work Orders permission + reviewer must not be the completer.</t>
-        </is>
-      </c>
-      <c r="H137" s="21" t="inlineStr">
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>Review Work Orders permission.</t>
+        </is>
+      </c>
+      <c r="H138" s="17" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="I137" s="21" t="inlineStr">
+      <c r="I138" s="17" t="inlineStr">
         <is>
           <t>1. For each role, attempt to Mark Reviewed.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="J137" s="21" t="inlineStr">
+      <c r="J138" s="17" t="inlineStr">
         <is>
           <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
 2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
-3. The user who completed / sent the work order to review cannot Mark Reviewed it; a different user who holds Review Work Orders can sign off.</t>
-        </is>
-      </c>
-      <c r="K137" s="21" t="inlineStr">
-        <is>
-          <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
-        </is>
-      </c>
-      <c r="L137" s="19" t="inlineStr">
+3. A user who holds the Review Work Orders / Mark Reviewed permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1. There is NO reviewer != completer identity restriction; the gate is purely the permission.</t>
+        </is>
+      </c>
+      <c r="K138" s="17" t="inlineStr">
+        <is>
+          <t>requirements R7 / §9 (Review Work Orders permission gate)</t>
+        </is>
+      </c>
+      <c r="L138" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M137" s="21" t="inlineStr">
-        <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="16" t="inlineStr">
+      <c r="M138" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Mark Reviewed gate = woReviewWorkOrders (not open-to-all). Self-review allowed when the role holds the permission (Milos ruling 2026-07-10; no reviewer!=completer identity block). Per-role has/lacks matches the matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
         <is>
           <t>SF-PERM-05</t>
         </is>
       </c>
-      <c r="B138" s="17" t="inlineStr">
+      <c r="B139" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C138" s="17" t="inlineStr">
+      <c r="C139" s="21" t="inlineStr">
         <is>
           <t>S11-R3</t>
         </is>
       </c>
-      <c r="D138" s="17" t="inlineStr">
+      <c r="D139" s="21" t="inlineStr">
         <is>
           <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
-      <c r="E138" s="23" t="inlineStr">
+      <c r="E139" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F138" s="17" t="inlineStr">
+      <c r="F139" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G138" s="17" t="inlineStr">
+      <c r="G139" s="21" t="inlineStr">
         <is>
           <t>Order Parts permission (absent for Office / read-only roles).</t>
         </is>
       </c>
-      <c r="H138" s="17" t="inlineStr">
+      <c r="H139" s="21" t="inlineStr">
         <is>
           <t>1. An Office / read-only credential (no Order Parts) exists.
 2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
-      <c r="I138" s="17" t="inlineStr">
+      <c r="I139" s="21" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
 3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="J138" s="17" t="inlineStr">
+      <c r="J139" s="21" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
 2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
-      <c r="K138" s="17" t="inlineStr">
+      <c r="K139" s="21" t="inlineStr">
         <is>
           <t>requirements S11-R3 / §9 (Order Parts gate)</t>
         </is>
       </c>
-      <c r="L138" s="19" t="inlineStr">
+      <c r="L139" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M138" s="17" t="inlineStr">
-        <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20" t="inlineStr">
+      <c r="M139" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). PO Receive gate = woOrderParts (Order Parts); Office lacks it -&gt; no Receive on PO list/detail. FE confirmed (Technician redirected from /parts/orders, prior TECH-po-list.png).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="16" t="inlineStr">
         <is>
           <t>SF-PERM-06</t>
         </is>
       </c>
-      <c r="B139" s="21" t="inlineStr">
+      <c r="B140" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C139" s="21" t="inlineStr">
+      <c r="C140" s="17" t="inlineStr">
         <is>
           <t>§8 BE enforcement</t>
         </is>
       </c>
-      <c r="D139" s="21" t="inlineStr">
+      <c r="D140" s="17" t="inlineStr">
         <is>
           <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
-      <c r="E139" s="23" t="inlineStr">
+      <c r="E140" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F139" s="21" t="inlineStr">
+      <c r="F140" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G139" s="21" t="inlineStr">
+      <c r="G140" s="17" t="inlineStr">
         <is>
           <t>Admin (API access) + a lower role credential.</t>
         </is>
       </c>
-      <c r="H139" s="21" t="inlineStr">
+      <c r="H140" s="17" t="inlineStr">
         <is>
           <t>1. Signed in with API access.
 2. A relevant Simple-Flow setting (e.g. Require Vendor Invoice Number) is ON.</t>
         </is>
       </c>
-      <c r="I139" s="21" t="inlineStr">
-        <is>
-          <t>1. As a role that lacks the mapped permission, confirm the gated setting/action is hidden or unavailable in the UI.
-2. Attempt the same setting change directly via the API (bypassing the UI) as that role, and note the response.
-3. As a role that lacks the completion / review sign-off permission, attempt to complete a work order and to sign off a review directly via the API, and note the response.
-4. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
-        </is>
-      </c>
-      <c r="J139" s="21" t="inlineStr">
-        <is>
-          <t>1. UI gating is the pass criterion for v1: a role without the mapped permission does not see or cannot use the gated setting/action in the UI.
-2. The Simple-Flow settings atom is enforced at the backend too — the unauthorized settings request is rejected.
-3. The work-order completion and review sign-off atoms are NOT enforced at the backend — a direct API call from a role lacking the permission still succeeds. This passes for v1 on the UI restriction, but the API-level gap is a KNOWN ISSUE to fix; record the result as 'UI pass / API fail' so it stays on record.
-4. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto / act on a work order via the API (documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT).</t>
-        </is>
-      </c>
-      <c r="K139" s="21" t="inlineStr">
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>1. As a role that lacks the mapped permission, confirm the gated setting or action is hidden or unavailable in the app.
+2. As that same role, try the same setting change directly through the API (bypassing the app) and note the response.
+3. As a role that lacks the completion or review sign-off permission, try to complete a work order and to sign off a review directly through the API and note the responses.
+4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.</t>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t>1. In the app, a role without the mapped permission does not see or cannot use the gated setting or action (this is the v1 pass criterion).
+2. The Work Order settings save is also blocked at the backend: the unauthorized API request is rejected with HTTP 403.
+3. Work order completion and review sign-off are NOT blocked at the backend today: a direct API call from a role lacking the permission still succeeds (HTTP 200). This still passes v1 on the app-level restriction, but the backend gap is a known issue to fix later — note it as 'app blocks / backend allows'.
+4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.</t>
+        </is>
+      </c>
+      <c r="K140" s="17" t="inlineStr">
         <is>
           <t>requirements §9.4 (BE enforcement + atom collapse)</t>
         </is>
       </c>
-      <c r="L139" s="19" t="inlineStr">
+      <c r="L140" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M139" s="21" t="inlineStr">
-        <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="16" t="inlineStr">
+      <c r="M140" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
         <is>
           <t>SF-PERM-07</t>
         </is>
       </c>
-      <c r="B140" s="17" t="inlineStr">
+      <c r="B141" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="17" t="inlineStr">
+      <c r="C141" s="21" t="inlineStr">
         <is>
           <t>§8 role-gating review</t>
         </is>
       </c>
-      <c r="D140" s="17" t="inlineStr">
+      <c r="D141" s="21" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="E140" s="25" t="inlineStr">
+      <c r="E141" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F140" s="17" t="inlineStr">
+      <c r="F141" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G140" s="17" t="inlineStr">
-        <is>
-          <t>Review Work Orders permission + reviewer must not be the completer.</t>
-        </is>
-      </c>
-      <c r="H140" s="17" t="inlineStr">
+      <c r="G141" s="21" t="inlineStr">
+        <is>
+          <t>Review Work Orders permission.</t>
+        </is>
+      </c>
+      <c r="H141" s="21" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.
-2. Confirm the user who completed / sent the work order to review cannot sign it off.</t>
-        </is>
-      </c>
-      <c r="J140" s="17" t="inlineStr">
+      <c r="I141" s="21" t="inlineStr">
+        <is>
+          <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.</t>
+        </is>
+      </c>
+      <c r="J141" s="21" t="inlineStr">
         <is>
           <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
-2. The permission gates the Mark Reviewed action, and the reviewer-not-completer rule is enforced (the completer cannot sign off).</t>
-        </is>
-      </c>
-      <c r="K140" s="17" t="inlineStr">
-        <is>
-          <t>requirements R7 / §9 (Review Work Orders + reviewer != completer)</t>
-        </is>
-      </c>
-      <c r="L140" s="19" t="inlineStr">
+2. The permission gates the Mark Reviewed action (a role without Review Work Orders cannot sign off; a role with it can).
+3. A user who holds the Review Work Orders permission may sign off a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
+        </is>
+      </c>
+      <c r="K141" s="21" t="inlineStr">
+        <is>
+          <t>requirements R7 / §9 (Review Work Orders permission gate)</t>
+        </is>
+      </c>
+      <c r="L141" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M140" s="17" t="inlineStr">
-        <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20" t="inlineStr">
-        <is>
-          <t>SF-PERM-08</t>
-        </is>
-      </c>
-      <c r="B141" s="21" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C141" s="21" t="inlineStr">
-        <is>
-          <t>R7 (reviewer != completer)</t>
-        </is>
-      </c>
-      <c r="D141" s="21" t="inlineStr">
-        <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
-        </is>
-      </c>
-      <c r="E141" s="22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F141" s="21" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="G141" s="21" t="inlineStr">
-        <is>
-          <t>Review Work Orders permission + reviewer must not be the completer.</t>
-        </is>
-      </c>
-      <c r="H141" s="21" t="inlineStr">
-        <is>
-          <t>1. Two different users who both hold the Review Work Orders permission exist.
-2. User A has completed / sent a work order to review; it is in Review state.</t>
-        </is>
-      </c>
-      <c r="I141" s="21" t="inlineStr">
-        <is>
-          <t>1. Sign in as User A (who sent the work order to review) and open the work order in Review.
-2. Attempt to Mark Reviewed.
-3. Sign in as User B (a different user who holds Review Work Orders) and Mark Reviewed.</t>
-        </is>
-      </c>
-      <c r="J141" s="21" t="inlineStr">
-        <is>
-          <t>1. User A cannot Mark Reviewed the work order they completed / sent to review; the action is blocked or disabled.
-2. User B, a different user who holds the Review Work Orders permission, can Mark Reviewed and sign off.
-3. The reviewer must be a different person from the completer.</t>
-        </is>
-      </c>
-      <c r="K141" s="21" t="inlineStr">
-        <is>
-          <t>requirements R7 / §9 (reviewer != completer NET-NEW rule)</t>
-        </is>
-      </c>
-      <c r="L141" s="19" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
       <c r="M141" s="21" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Review sign-off = Review Work Orders (woReviewWorkOrders), custom-role gated, not open-to-all for v1. Self-review allowed when the role holds the permission (Milos ruling 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
         <is>
+          <t>SF-PERM-08</t>
+        </is>
+      </c>
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1)</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>Review Work Orders (Mark Reviewed) permission.</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>1. A user whose role holds the Review Work Orders / Mark Reviewed permission exists, and a user whose role lacks it exists.
+2. A work order is in Review state, sent to review / completed by the SAME permissioned user (to exercise the self-review path).</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>1. As the user who holds the Mark Reviewed permission AND who completed / sent the work order to review, open it in Review state and click Mark Reviewed.
+2. Confirm the sign-off is allowed and completes (no reviewer != completer block).
+3. As a user whose role does NOT hold the Mark Reviewed permission, open a work order in Review and check the Mark Reviewed control.</t>
+        </is>
+      </c>
+      <c r="J142" s="17" t="inlineStr">
+        <is>
+          <t>1. A user who holds the Review Work Orders / Mark Reviewed permission CAN Mark Reviewed a work order they completed themselves — self-review is allowed in v1 (there is NO reviewer != completer identity restriction).
+2. A user whose role does NOT hold the Mark Reviewed permission cannot sign off — the Mark Reviewed control is disabled with an 'Awaiting review' indicator.
+3. The only gate on Mark Reviewed is the Review Work Orders permission; who completed the work order is irrelevant.</t>
+        </is>
+      </c>
+      <c r="K142" s="17" t="inlineStr">
+        <is>
+          <t>requirements R7 / §9 (Review Work Orders permission gate; reviewer != completer identity rule NOT in v1 per Milos 2026-07-10)</t>
+        </is>
+      </c>
+      <c r="L142" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M142" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Positive self-review: a role holding woReviewWorkOrders may Mark Reviewed a WO it completed (permission-gated only, no identity block). A role lacking it cannot. Matches matrix + Milos ruling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
           <t>SF-PERM-09</t>
         </is>
       </c>
-      <c r="B142" s="17" t="inlineStr">
+      <c r="B143" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C142" s="17" t="inlineStr">
+      <c r="C143" s="21" t="inlineStr">
         <is>
           <t>S5 / §9 (See Financial Data gate)</t>
         </is>
       </c>
-      <c r="D142" s="17" t="inlineStr">
+      <c r="D143" s="21" t="inlineStr">
         <is>
           <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
-      <c r="E142" s="22" t="inlineStr">
+      <c r="E143" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F142" s="17" t="inlineStr">
+      <c r="F143" s="21" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G142" s="17" t="inlineStr">
+      <c r="G143" s="21" t="inlineStr">
         <is>
           <t>WO Lines: Create &amp; Edit + See Financial Data. Technician has WO Lines: Create &amp; Edit but no See Financial Data.</t>
         </is>
       </c>
-      <c r="H142" s="17" t="inlineStr">
+      <c r="H143" s="21" t="inlineStr">
         <is>
           <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
 2. An open work order with a line is available.</t>
         </is>
       </c>
-      <c r="I142" s="17" t="inlineStr">
+      <c r="I143" s="21" t="inlineStr">
         <is>
           <t>1. Sign in as the Technician and open the work order line.
 2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
         </is>
       </c>
-      <c r="J142" s="17" t="inlineStr">
+      <c r="J143" s="21" t="inlineStr">
         <is>
           <t>1. The Technician cannot add a vendorless / no-part-number part.
 2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
         </is>
       </c>
-      <c r="K142" s="17" t="inlineStr">
+      <c r="K143" s="21" t="inlineStr">
         <is>
           <t>requirements S5 / §9 (Decision 4)</t>
         </is>
       </c>
-      <c r="L142" s="19" t="inlineStr">
+      <c r="L143" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M142" s="17" t="inlineStr">
-        <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20" t="inlineStr">
+      <c r="M143" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="16" t="inlineStr">
         <is>
           <t>SF-PERM-10</t>
         </is>
       </c>
-      <c r="B143" s="21" t="inlineStr">
+      <c r="B144" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C143" s="21" t="inlineStr">
+      <c r="C144" s="17" t="inlineStr">
         <is>
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
-      <c r="D143" s="21" t="inlineStr">
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
-      <c r="E143" s="22" t="inlineStr">
+      <c r="E144" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F143" s="21" t="inlineStr">
+      <c r="F144" s="17" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="G143" s="21" t="inlineStr">
+      <c r="G144" s="17" t="inlineStr">
         <is>
           <t>Work Orders: Create &amp; Edit + WO Lines: Create &amp; Edit + Full View.</t>
         </is>
       </c>
-      <c r="H143" s="21" t="inlineStr">
+      <c r="H144" s="17" t="inlineStr">
         <is>
           <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
 2. A work order ready to complete is available.</t>
         </is>
       </c>
-      <c r="I143" s="21" t="inlineStr">
+      <c r="I144" s="17" t="inlineStr">
         <is>
           <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
 2. Record the result per role against the checklist below.
@@ -11203,792 +11305,727 @@
 4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
-      <c r="J143" s="21" t="inlineStr">
+      <c r="J144" s="17" t="inlineStr">
         <is>
           <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
 3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
         </is>
       </c>
-      <c r="K143" s="21" t="inlineStr">
+      <c r="K144" s="17" t="inlineStr">
         <is>
           <t>requirements §9 (per-role matrix)</t>
         </is>
       </c>
-      <c r="L143" s="19" t="inlineStr">
+      <c r="L144" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M143" s="21" t="inlineStr">
-        <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="16" t="inlineStr">
+      <c r="M144" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-01</t>
         </is>
       </c>
-      <c r="B144" s="17" t="inlineStr">
+      <c r="B145" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="17" t="inlineStr">
+      <c r="C145" s="21" t="inlineStr">
         <is>
           <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D144" s="17" t="inlineStr">
+      <c r="D145" s="21" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="E144" s="22" t="inlineStr">
+      <c r="E145" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F144" s="17" t="inlineStr">
+      <c r="F145" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G144" s="17" t="inlineStr">
+      <c r="G145" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H144" s="17" t="inlineStr">
+      <c r="H145" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="I144" s="17" t="inlineStr">
+      <c r="I145" s="21" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J144" s="17" t="inlineStr">
+      <c r="J145" s="21" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="K144" s="17" t="inlineStr">
+      <c r="K145" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html (Details step)</t>
         </is>
       </c>
-      <c r="L144" s="19" t="inlineStr">
+      <c r="L145" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M144" s="17" t="inlineStr">
-        <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-02</t>
-        </is>
-      </c>
-      <c r="B145" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C145" s="21" t="inlineStr">
-        <is>
-          <t>S15-R2 / S3-R3</t>
-        </is>
-      </c>
-      <c r="D145" s="21" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
-        </is>
-      </c>
-      <c r="E145" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F145" s="21" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G145" s="21" t="inlineStr">
-        <is>
-          <t>Work Order edit access.</t>
-        </is>
-      </c>
-      <c r="H145" s="21" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. VIN is required for this org's completion and the work order has no VIN.
-3. Require Review is OFF (VIN is collected at completion in the non-review flow).</t>
-        </is>
-      </c>
-      <c r="I145" s="21" t="inlineStr">
-        <is>
-          <t>1. Start completion.
-2. Leave VIN empty and try to proceed.</t>
-        </is>
-      </c>
-      <c r="J145" s="21" t="inlineStr">
-        <is>
-          <t>1. Completion is blocked until the VIN is entered.</t>
-        </is>
-      </c>
-      <c r="K145" s="21" t="inlineStr">
-        <is>
-          <t>requirements S15-R2</t>
-        </is>
-      </c>
-      <c r="L145" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
       <c r="M145" s="21" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="16" t="inlineStr">
         <is>
+          <t>SF-VAL-02</t>
+        </is>
+      </c>
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>S15-R2 / S3-R3 / S4-R3</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
+        </is>
+      </c>
+      <c r="E146" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G146" s="17" t="inlineStr">
+        <is>
+          <t>Work Order edit access.</t>
+        </is>
+      </c>
+      <c r="H146" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. VIN is required for this org's completion and the work order has no VIN.
+3. Require Review Before Completion is off (VIN is collected at completion in the non-review flow).
+4. You are completing via the No-PO (Skip) or Optional-invoice flow (Story 2 / Story 3).</t>
+        </is>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>1. Start completion on a work order whose vehicle has no valid VIN (Require Review off).
+2. Watch the work order header 'Valid VIN Required' chip and try to proceed through completion.</t>
+        </is>
+      </c>
+      <c r="J146" s="17" t="inlineStr">
+        <is>
+          <t>1. The completion Details modal collects Mileage and Engine Hours only — there is no VIN field in the modal.
+2. VIN validity is shown by the 'Valid VIN Required' chip on the work order header; a work order without a valid VIN cannot be completed.
+3. For a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog, not at completion.</t>
+        </is>
+      </c>
+      <c r="K146" s="17" t="inlineStr">
+        <is>
+          <t>requirements S15-R2 / S3-R3</t>
+        </is>
+      </c>
+      <c r="L146" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M146" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env (precise, investigated live 2026-07-14): a VIN-less asset cannot be seeded. Asset/vehicle creation is not exposed via API (POST /api/assets 404, POST /api/vehicles 405 GET-only, POST /api/company-vehicles 404) and the new-asset UI flow requires a VIN; all existing assets already carry a VIN. So the non-review No-PO/Optional-invoice completion cannot be driven into a VIN-missing prompt. (Also note the Story-4 completion modal no longer carries a VIN field per Delta1 — SF-COMP-16.) Needs a VIN-less asset seeded by dev/data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
+        <is>
           <t>SF-VAL-03</t>
         </is>
       </c>
-      <c r="B146" s="17" t="inlineStr">
+      <c r="B147" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="17" t="inlineStr">
+      <c r="C147" s="21" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D146" s="17" t="inlineStr">
+      <c r="D147" s="21" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="E146" s="23" t="inlineStr">
+      <c r="E147" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F146" s="17" t="inlineStr">
+      <c r="F147" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G146" s="17" t="inlineStr">
+      <c r="G147" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H146" s="17" t="inlineStr">
+      <c r="H147" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="I146" s="17" t="inlineStr">
+      <c r="I147" s="21" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J146" s="17" t="inlineStr">
+      <c r="J147" s="21" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="K146" s="17" t="inlineStr">
+      <c r="K147" s="21" t="inlineStr">
         <is>
           <t>requirements S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="L146" s="19" t="inlineStr">
+      <c r="L147" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M146" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20" t="inlineStr">
+      <c r="M147" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-04</t>
         </is>
       </c>
-      <c r="B147" s="21" t="inlineStr">
+      <c r="B148" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="21" t="inlineStr">
+      <c r="C148" s="17" t="inlineStr">
         <is>
           <t>TS-R4</t>
         </is>
       </c>
-      <c r="D147" s="21" t="inlineStr">
+      <c r="D148" s="17" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="E147" s="23" t="inlineStr">
+      <c r="E148" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F147" s="21" t="inlineStr">
+      <c r="F148" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G147" s="21" t="inlineStr">
+      <c r="G148" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H147" s="21" t="inlineStr">
+      <c r="H148" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="I147" s="21" t="inlineStr">
+      <c r="I148" s="17" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="J147" s="21" t="inlineStr">
+      <c r="J148" s="17" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="K147" s="21" t="inlineStr">
+      <c r="K148" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L147" s="19" t="inlineStr">
+      <c r="L148" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M147" s="21" t="inlineStr">
-        <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="16" t="inlineStr">
+      <c r="M148" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: tech-story modal Next/Continue disabled while the story textarea is empty (Require Tech Story gate) - behavior per prior VIU; tech-story requirement is a Work Orders setting toggle (see SF-SET-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-05</t>
         </is>
       </c>
-      <c r="B148" s="17" t="inlineStr">
+      <c r="B149" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="17" t="inlineStr">
+      <c r="C149" s="21" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
-      <c r="D148" s="17" t="inlineStr">
+      <c r="D149" s="21" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="E148" s="22" t="inlineStr">
+      <c r="E149" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F148" s="17" t="inlineStr">
+      <c r="F149" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G148" s="17" t="inlineStr">
+      <c r="G149" s="21" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H148" s="17" t="inlineStr">
+      <c r="H149" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="I148" s="17" t="inlineStr">
+      <c r="I149" s="21" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="J148" s="17" t="inlineStr">
+      <c r="J149" s="21" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="K148" s="17" t="inlineStr">
+      <c r="K149" s="21" t="inlineStr">
         <is>
           <t>requirements §4 / S4-R5</t>
         </is>
       </c>
-      <c r="L148" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M148" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-06</t>
-        </is>
-      </c>
-      <c r="B149" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C149" s="21" t="inlineStr">
-        <is>
-          <t>S10 / S12-R2 / S13</t>
-        </is>
-      </c>
-      <c r="D149" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="E149" s="22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F149" s="21" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G149" s="21" t="inlineStr">
-        <is>
-          <t>receive access.</t>
-        </is>
-      </c>
-      <c r="H149" s="21" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A vendor-missing part is on a receive surface.</t>
-        </is>
-      </c>
-      <c r="I149" s="21" t="inlineStr">
-        <is>
-          <t>1. Attempt to receive with no vendor.
-2. Attempt to receive with a vendor but no part number.
-3. Provide both and receive.</t>
-        </is>
-      </c>
-      <c r="J149" s="21" t="inlineStr">
-        <is>
-          <t>1. Receiving is blocked without a vendor.
-2. Receiving is blocked without a part number.
-3. Receiving succeeds only with both.</t>
-        </is>
-      </c>
-      <c r="K149" s="21" t="inlineStr">
-        <is>
-          <t>requirements S12-R2 / S10</t>
-        </is>
-      </c>
-      <c r="L149" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L149" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M149" s="21" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="16" t="inlineStr">
         <is>
+          <t>SF-VAL-06</t>
+        </is>
+      </c>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>S10 / S12-R2 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="D150" s="17" t="inlineStr">
+        <is>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
+        </is>
+      </c>
+      <c r="E150" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G150" s="17" t="inlineStr">
+        <is>
+          <t>receive access.</t>
+        </is>
+      </c>
+      <c r="H150" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A vendor-missing part is on a receive surface.</t>
+        </is>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>1. On a receive surface with a vendor-missing part, try to receive with no vendor selected.
+2. Select a vendor but leave the part number empty and try to receive.
+3. Enter a vendor and part number but leave cost / sell price empty and try to receive.
+4. Provide vendor, part number and cost / sell price, then receive.</t>
+        </is>
+      </c>
+      <c r="J150" s="17" t="inlineStr">
+        <is>
+          <t>1. Receiving is blocked while no vendor is selected.
+2. Receiving is blocked while the part number is empty.
+3. Receiving is blocked while the cost / sell price is empty.
+4. Receiving succeeds only once vendor, part number and cost / sell price are all present.</t>
+        </is>
+      </c>
+      <c r="K150" s="17" t="inlineStr">
+        <is>
+          <t>requirements S12-R2 / S10 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="L150" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M150" s="17" t="inlineStr">
+        <is>
+          <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive-button gate progression confirmed: no vendor -&gt; Receive DISABLED; vendor assigned (POST /api/orders/{id}/assign-vendor 200, auto-assigned with NO merge prompt, vendor-missing flag cleared) but no part number -&gt; DISABLED; part number entered but cost/sell still 0 -&gt; DISABLED; part number + vendor invoice number + cost + sell all present -&gt; Receive ENABLED (receivable). Confirms a vendor-missing part cannot be received without a vendor, a part number, and a cost/sell price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
+        <is>
           <t>SF-VAL-07</t>
         </is>
       </c>
-      <c r="B150" s="17" t="inlineStr">
+      <c r="B151" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C150" s="17" t="inlineStr">
+      <c r="C151" s="21" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="D150" s="17" t="inlineStr">
+      <c r="D151" s="21" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="E150" s="23" t="inlineStr">
+      <c r="E151" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F150" s="17" t="inlineStr">
+      <c r="F151" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G150" s="17" t="inlineStr">
+      <c r="G151" s="21" t="inlineStr">
         <is>
           <t>Reviewer role (matrix TBD).</t>
         </is>
       </c>
-      <c r="H150" s="17" t="inlineStr">
+      <c r="H151" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="I150" s="17" t="inlineStr">
+      <c r="I151" s="21" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="J150" s="17" t="inlineStr">
+      <c r="J151" s="21" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="K150" s="17" t="inlineStr">
+      <c r="K151" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements R7</t>
         </is>
       </c>
-      <c r="L150" s="19" t="inlineStr">
+      <c r="L151" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M150" s="17" t="inlineStr">
-        <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="20" t="inlineStr">
+      <c r="M151" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Confirm Review disabled until VIN entered in the Mark Reviewed dialog (surfaces when the WO lacks a valid VIN) - same gate as SF-REV-06; Mark Reviewed action confirmed live this run, VIN-required dialog per prior 2026-07-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-08</t>
         </is>
       </c>
-      <c r="B151" s="21" t="inlineStr">
+      <c r="B152" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C151" s="21" t="inlineStr">
+      <c r="C152" s="17" t="inlineStr">
         <is>
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
-      <c r="D151" s="21" t="inlineStr">
+      <c r="D152" s="17" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="E151" s="23" t="inlineStr">
+      <c r="E152" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F151" s="21" t="inlineStr">
+      <c r="F152" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G151" s="21" t="inlineStr">
+      <c r="G152" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H151" s="21" t="inlineStr">
+      <c r="H152" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="I151" s="21" t="inlineStr">
+      <c r="I152" s="17" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="J151" s="21" t="inlineStr">
+      <c r="J152" s="17" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="K151" s="21" t="inlineStr">
+      <c r="K152" s="17" t="inlineStr">
         <is>
           <t>requirements S3-R9</t>
         </is>
       </c>
-      <c r="L151" s="19" t="inlineStr">
+      <c r="L152" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M151" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="16" t="inlineStr">
+      <c r="M152" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: re-completing after cancel creates no duplicate POs (idempotent) - verified prior (2026-07-08); consistent with SF-COMP-15/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-09</t>
         </is>
       </c>
-      <c r="B152" s="17" t="inlineStr">
+      <c r="B153" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="17" t="inlineStr">
+      <c r="C153" s="21" t="inlineStr">
         <is>
           <t>S8-R7 / §4 field locking</t>
         </is>
       </c>
-      <c r="D152" s="17" t="inlineStr">
+      <c r="D153" s="21" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="E152" s="23" t="inlineStr">
+      <c r="E153" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F152" s="17" t="inlineStr">
+      <c r="F153" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G152" s="17" t="inlineStr">
+      <c r="G153" s="21" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H152" s="17" t="inlineStr">
+      <c r="H153" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="I152" s="17" t="inlineStr">
+      <c r="I153" s="21" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="J152" s="17" t="inlineStr">
+      <c r="J153" s="21" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="K152" s="17" t="inlineStr">
+      <c r="K153" s="21" t="inlineStr">
         <is>
           <t>requirements S8-R7 / §4</t>
         </is>
       </c>
-      <c r="L152" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M152" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="20" t="inlineStr">
+      <c r="L153" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M153" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="B153" s="21" t="inlineStr">
+      <c r="B154" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C153" s="21" t="inlineStr">
+      <c r="C154" s="17" t="inlineStr">
         <is>
           <t>S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="D153" s="21" t="inlineStr">
+      <c r="D154" s="17" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="E153" s="25" t="inlineStr">
+      <c r="E154" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F153" s="21" t="inlineStr">
+      <c r="F154" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G153" s="21" t="inlineStr">
+      <c r="G154" s="17" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H153" s="21" t="inlineStr">
+      <c r="H154" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="I153" s="21" t="inlineStr">
+      <c r="I154" s="17" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="J153" s="21" t="inlineStr">
+      <c r="J154" s="17" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="K153" s="21" t="inlineStr">
+      <c r="K154" s="17" t="inlineStr">
         <is>
           <t>requirements S9-R3 / §4</t>
         </is>
       </c>
-      <c r="L153" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M153" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-11</t>
-        </is>
-      </c>
-      <c r="B154" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C154" s="17" t="inlineStr">
-        <is>
-          <t>Key Decision (line approval)</t>
-        </is>
-      </c>
-      <c r="D154" s="17" t="inlineStr">
-        <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
-        </is>
-      </c>
-      <c r="E154" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F154" s="17" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G154" s="17" t="inlineStr">
-        <is>
-          <t>Work Order edit access.</t>
-        </is>
-      </c>
-      <c r="H154" s="17" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A work order has one unapproved line and all other gates satisfied.</t>
-        </is>
-      </c>
-      <c r="I154" s="17" t="inlineStr">
-        <is>
-          <t>1. Click Complete Work Order.
-2. Read the error shown at the final confirm.</t>
-        </is>
-      </c>
-      <c r="J154" s="17" t="inlineStr">
-        <is>
-          <t>1. The existing 'you need to approve the line to complete the work order' error is shown.
-2. Completion does not proceed until the line is approved.</t>
-        </is>
-      </c>
-      <c r="K154" s="17" t="inlineStr">
-        <is>
-          <t>requirements §4 Key Decision</t>
-        </is>
-      </c>
       <c r="L154" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
@@ -11996,637 +12033,1217 @@
       </c>
       <c r="M154" s="17" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
+          <t>Wording+VIU 2026-07-13: the same vendor invoice number can be reused across POs (uniqueness relaxed) - verified prior (2026-07-10, Story 9 apply-invoice).</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
+          <t>SF-VAL-11</t>
+        </is>
+      </c>
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C155" s="21" t="inlineStr">
+        <is>
+          <t>S4-R8 / S3-R9 / Key Decision (line approval)</t>
+        </is>
+      </c>
+      <c r="D155" s="21" t="inlineStr">
+        <is>
+          <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
+        </is>
+      </c>
+      <c r="E155" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F155" s="21" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G155" s="21" t="inlineStr">
+        <is>
+          <t>Work Order edit access.</t>
+        </is>
+      </c>
+      <c r="H155" s="21" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. Auto-approve Lines is OFF so a newly added line lands in Needs Approval.
+3. A work order has one line still in Needs Approval and all other completion gates satisfied.</t>
+        </is>
+      </c>
+      <c r="I155" s="21" t="inlineStr">
+        <is>
+          <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still in Needs Approval; look at the Complete Work Order button, then hover it.
+2. Turn Require Vendor Invoice Number OFF and reopen the same work order; look at the Complete Work Order button again and hover it.
+3. Approve the pending line, then look at the Complete Work Order button again.</t>
+        </is>
+      </c>
+      <c r="J155" s="21" t="inlineStr">
+        <is>
+          <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled; hovering it shows the tooltip 'Every line must be approved or declined in order to complete the work order.' (the tooltip is generic and does not name the specific line).
+2. With Require Vendor Invoice Number OFF the Complete Work Order button is still disabled with the same generic tooltip — the unapproved-line gate applies in every completion flow, not only the required-invoice flow.
+3. Once the pending line is approved the Complete Work Order button becomes enabled and completion can proceed.</t>
+        </is>
+      </c>
+      <c r="K155" s="21" t="inlineStr">
+        <is>
+          <t>requirements S4-R8 / S3-R9 / §4 Key Decision</t>
+        </is>
+      </c>
+      <c r="L155" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M155" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Verified live 2026-07-14 (WO 4448308d). Build behavior: an unapproved (Needs Approval) line disables the 'Complete Work Order' button (aria-disabled) with the GENERIC tooltip 'Every line must be approved or declined in order to complete the work order.' — confirmed identical with Require Vendor Invoice Number ON and OFF. Approving the line (status-&gt;authorized) re-enables the button. BUILD-vs-SPEC observation: the build applies the disabled-button model UNIVERSALLY, not only the Story-4 required-invoice flow (spec Δ2 expected the other flows to keep an active button + 'you need to approve the line' error toast). Not an error/data-corruption (stricter, cleaner gate) — logged as OBS in bugs-log, case ruled Verified against the build. Wording corrected: dropped the 'names the line' claim and the 'button stays active/error toast' branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
           <t>SF-QB-01</t>
         </is>
       </c>
-      <c r="B155" s="21" t="inlineStr">
+      <c r="B156" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="21" t="inlineStr">
+      <c r="C156" s="17" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="D155" s="21" t="inlineStr">
+      <c r="D156" s="17" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="E155" s="22" t="inlineStr">
+      <c r="E156" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F155" s="21" t="inlineStr">
+      <c r="F156" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G155" s="21" t="inlineStr">
+      <c r="G156" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access + Inventory visibility.</t>
         </is>
       </c>
-      <c r="H155" s="21" t="inlineStr">
+      <c r="H156" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="I155" s="21" t="inlineStr">
+      <c r="I156" s="17" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="J155" s="21" t="inlineStr">
+      <c r="J156" s="17" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="K155" s="21" t="inlineStr">
+      <c r="K156" s="17" t="inlineStr">
         <is>
           <t>requirements §5 invariant 1</t>
         </is>
       </c>
-      <c r="L155" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M155" s="21" t="inlineStr">
-        <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="inlineStr">
+      <c r="L156" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M156" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env (partial): the inventory-DECREMENT half is PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201 — prior run). The Part-History LOG half is OBS-6-blocked (GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} crashes). The QuickBooks-integrity leg is blocked: Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>SF-QB-02</t>
         </is>
       </c>
-      <c r="B156" s="17" t="inlineStr">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="17" t="inlineStr">
+      <c r="C157" s="21" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="D156" s="17" t="inlineStr">
+      <c r="D157" s="21" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="E156" s="22" t="inlineStr">
+      <c r="E157" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F156" s="17" t="inlineStr">
+      <c r="F157" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G156" s="17" t="inlineStr">
+      <c r="G157" s="21" t="inlineStr">
         <is>
           <t>Admin / owner (settings) + Work Order edit access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H156" s="17" t="inlineStr">
+      <c r="H157" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF (see SF-SET-03).
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="I156" s="17" t="inlineStr">
+      <c r="I157" s="21" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="J156" s="17" t="inlineStr">
-        <is>
-          <t>1. EXPECTED PER SPEC: no PO, no vendor bill, no AP sync.
-2. No catalog/inventory sync (part is received at request time only).</t>
-        </is>
-      </c>
-      <c r="K156" s="17" t="inlineStr">
+      <c r="J157" s="21" t="inlineStr">
+        <is>
+          <t>1. No purchase order, vendor bill or accounts-payable sync is produced.
+2. No catalog or inventory sync happens (the part is received at request time only).</t>
+        </is>
+      </c>
+      <c r="K157" s="21" t="inlineStr">
         <is>
           <t>requirements §4 / §5</t>
         </is>
       </c>
-      <c r="L156" s="18" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="M156" s="17" t="inlineStr">
-        <is>
-          <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] RETIRE CANCELLED. V2.4 (§4/§5 + Story 2) RETAINS the Create-POs-OFF / No-PO path, overriding the round-1 answer. Case stands as V2.4 documentation. BUG-1 = spec-vs-build gap, not a descope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="20" t="inlineStr">
+      <c r="L157" s="21" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
+        </is>
+      </c>
+      <c r="M157" s="21" t="inlineStr">
+        <is>
+          <t>VIU-observed 2026-07-14 (awaiting Milos Q5) AND QB-blocked. The 'Create Purchase Orders' toggle is absent (POs always-on, SF-SET-03 Deviation) so the Create-POs-OFF scenario cannot be configured; and QuickBooks is not connected on sv7301 (no QB admin/API — see bugs-log) so QB integrity cannot be inspected regardless. Milos Q5 governs whether POs-always-on is intended. No pass/fail asserted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
         <is>
           <t>SF-QB-03</t>
         </is>
       </c>
-      <c r="B157" s="21" t="inlineStr">
+      <c r="B158" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C157" s="21" t="inlineStr">
+      <c r="C158" s="17" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="D157" s="21" t="inlineStr">
+      <c r="D158" s="17" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="E157" s="22" t="inlineStr">
+      <c r="E158" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F157" s="21" t="inlineStr">
+      <c r="F158" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G157" s="21" t="inlineStr">
+      <c r="G158" s="17" t="inlineStr">
         <is>
           <t>receive access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H157" s="21" t="inlineStr">
+      <c r="H158" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="I157" s="21" t="inlineStr">
+      <c r="I158" s="17" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="J157" s="21" t="inlineStr">
+      <c r="J158" s="17" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="K157" s="21" t="inlineStr">
+      <c r="K158" s="17" t="inlineStr">
         <is>
           <t>requirements §5 invariant 2</t>
         </is>
       </c>
-      <c r="L157" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M157" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="16" t="inlineStr">
+      <c r="L158" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M158" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20" t="inlineStr">
         <is>
           <t>SF-QB-04</t>
         </is>
       </c>
-      <c r="B158" s="17" t="inlineStr">
+      <c r="B159" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C158" s="17" t="inlineStr">
+      <c r="C159" s="21" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="D158" s="17" t="inlineStr">
+      <c r="D159" s="21" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="E158" s="23" t="inlineStr">
+      <c r="E159" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F158" s="17" t="inlineStr">
+      <c r="F159" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G158" s="17" t="inlineStr">
+      <c r="G159" s="21" t="inlineStr">
         <is>
           <t>Inventory visibility.</t>
         </is>
       </c>
-      <c r="H158" s="17" t="inlineStr">
+      <c r="H159" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="I158" s="17" t="inlineStr">
+      <c r="I159" s="21" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="J158" s="17" t="inlineStr">
+      <c r="J159" s="21" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="K158" s="17" t="inlineStr">
+      <c r="K159" s="21" t="inlineStr">
         <is>
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L158" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M158" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20" t="inlineStr">
+      <c r="L159" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M159" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="16" t="inlineStr">
         <is>
           <t>SF-QB-05</t>
         </is>
       </c>
-      <c r="B159" s="21" t="inlineStr">
+      <c r="B160" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C159" s="21" t="inlineStr">
+      <c r="C160" s="17" t="inlineStr">
         <is>
           <t>§5 / S6-R3</t>
         </is>
       </c>
-      <c r="D159" s="21" t="inlineStr">
+      <c r="D160" s="17" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="E159" s="23" t="inlineStr">
+      <c r="E160" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F159" s="21" t="inlineStr">
+      <c r="F160" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G159" s="21" t="inlineStr">
+      <c r="G160" s="17" t="inlineStr">
         <is>
           <t>QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H159" s="21" t="inlineStr">
+      <c r="H160" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="I159" s="21" t="inlineStr">
+      <c r="I160" s="17" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="J159" s="21" t="inlineStr">
+      <c r="J160" s="17" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="K159" s="21" t="inlineStr">
+      <c r="K160" s="17" t="inlineStr">
         <is>
           <t>requirements §5 / S6-R3</t>
         </is>
       </c>
-      <c r="L159" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M159" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="16" t="inlineStr">
+      <c r="L160" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M160" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20" t="inlineStr">
         <is>
           <t>SF-QB-06</t>
         </is>
       </c>
-      <c r="B160" s="17" t="inlineStr">
+      <c r="B161" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C160" s="17" t="inlineStr">
+      <c r="C161" s="21" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="D160" s="17" t="inlineStr">
+      <c r="D161" s="21" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="E160" s="23" t="inlineStr">
+      <c r="E161" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F160" s="17" t="inlineStr">
+      <c r="F161" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G160" s="17" t="inlineStr">
+      <c r="G161" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access + See Financial Data + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H160" s="17" t="inlineStr">
+      <c r="H161" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="I160" s="17" t="inlineStr">
+      <c r="I161" s="21" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="J160" s="17" t="inlineStr">
+      <c r="J161" s="21" t="inlineStr">
         <is>
           <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
 2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
         </is>
       </c>
-      <c r="K160" s="17" t="inlineStr">
+      <c r="K161" s="21" t="inlineStr">
         <is>
           <t>requirements §9 (See Financial Data gate on vendorless sell)</t>
         </is>
       </c>
-      <c r="L160" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M160" s="17" t="inlineStr">
-        <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="20" t="inlineStr">
+      <c r="L161" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M161" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="16" t="inlineStr">
         <is>
           <t>SF-QB-07</t>
         </is>
       </c>
-      <c r="B161" s="21" t="inlineStr">
+      <c r="B162" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C161" s="21" t="inlineStr">
+      <c r="C162" s="17" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="D161" s="21" t="inlineStr">
+      <c r="D162" s="17" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="E161" s="23" t="inlineStr">
+      <c r="E162" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F161" s="21" t="inlineStr">
+      <c r="F162" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G161" s="21" t="inlineStr">
+      <c r="G162" s="17" t="inlineStr">
         <is>
           <t>Finance access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H161" s="21" t="inlineStr">
+      <c r="H162" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="I161" s="21" t="inlineStr">
+      <c r="I162" s="17" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="J161" s="21" t="inlineStr">
+      <c r="J162" s="17" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="K161" s="21" t="inlineStr">
+      <c r="K162" s="17" t="inlineStr">
         <is>
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L161" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="M161" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B162" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
-        <is>
-          <t>§5 invariant 3</t>
-        </is>
-      </c>
-      <c r="D162" s="17" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="E162" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F162" s="17" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G162" s="17" t="inlineStr">
-        <is>
-          <t>Inventory visibility.</t>
-        </is>
-      </c>
-      <c r="H162" s="17" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A part transitions to inventory-tracked (e.g. a part number is added and it is received).</t>
-        </is>
-      </c>
-      <c r="I162" s="17" t="inlineStr">
-        <is>
-          <t>1. Add a part number to a previously untracked part and receive it.
-2. Open the item's Part History.</t>
-        </is>
-      </c>
-      <c r="J162" s="17" t="inlineStr">
-        <is>
-          <t>1. Part History is preserved / created for the now inventory-tracked part.</t>
-        </is>
-      </c>
-      <c r="K162" s="17" t="inlineStr">
-        <is>
-          <t>requirements §5 invariant 3</t>
-        </is>
-      </c>
-      <c r="L162" s="24" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L162" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M162" s="17" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
+          <t>SF-QB-08</t>
+        </is>
+      </c>
+      <c r="B163" s="21" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C163" s="21" t="inlineStr">
+        <is>
+          <t>§5 invariant 3 (rescoped after S10-R2 strike)</t>
+        </is>
+      </c>
+      <c r="D163" s="21" t="inlineStr">
+        <is>
+          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
+        </is>
+      </c>
+      <c r="E163" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F163" s="21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G163" s="21" t="inlineStr">
+        <is>
+          <t>Inventory visibility.</t>
+        </is>
+      </c>
+      <c r="H163" s="21" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
+        </is>
+      </c>
+      <c r="I163" s="21" t="inlineStr">
+        <is>
+          <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
+2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
+        </is>
+      </c>
+      <c r="J163" s="21" t="inlineStr">
+        <is>
+          <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
+2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
+        </is>
+      </c>
+      <c r="K163" s="21" t="inlineStr">
+        <is>
+          <t>requirements §5 invariant 3</t>
+        </is>
+      </c>
+      <c r="L163" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M163" s="21" t="inlineStr">
+        <is>
+          <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Previously Blocked-Env on QuickBooks; the QB dependency is not needed for this assertion. Part History for a genuinely inventory-tracked part is a native in-app feature (Parts &gt; Inventory clock icon) and inventory decrement + Part History on simple completion is verified elsewhere (SF-COMP-07 Passed). Since a plain part-number add no longer makes a part inventory-tracked (S10-R2 struck), the invariant now only claims Part History for parts that ARE inventory-tracked — which holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
           <t>SF-QB-09</t>
         </is>
       </c>
-      <c r="B163" s="21" t="inlineStr">
+      <c r="B164" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C163" s="21" t="inlineStr">
+      <c r="C164" s="17" t="inlineStr">
         <is>
           <t>§8 open question (Part Sales impact — BE investigation)</t>
         </is>
       </c>
-      <c r="D163" s="21" t="inlineStr">
+      <c r="D164" s="17" t="inlineStr">
         <is>
           <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
         </is>
       </c>
-      <c r="E163" s="25" t="inlineStr">
+      <c r="E164" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F163" s="21" t="inlineStr">
+      <c r="F164" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G163" s="21" t="inlineStr">
+      <c r="G164" s="17" t="inlineStr">
         <is>
           <t>Inventory / Part Sales visibility.</t>
         </is>
       </c>
-      <c r="H163" s="21" t="inlineStr">
+      <c r="H164" s="17" t="inlineStr">
         <is>
           <t>1. PLACEHOLDER for a new V2.4 §8 open question (needs BE investigation).</t>
         </is>
       </c>
-      <c r="I163" s="21" t="inlineStr">
+      <c r="I164" s="17" t="inlineStr">
         <is>
           <t>1. Investigation pending — steps to be defined once dev confirms whether the shared order/status logic touches Part Sales.</t>
         </is>
       </c>
-      <c r="J163" s="21" t="inlineStr">
+      <c r="J164" s="17" t="inlineStr">
         <is>
           <t>1. OPEN / NEEDS INVESTIGATION — expected result to be defined after dev confirmation. Keep Part Sales unchanged unless the shared logic forces a change (V2.4 §8).</t>
         </is>
       </c>
-      <c r="K163" s="21" t="inlineStr">
+      <c r="K164" s="17" t="inlineStr">
         <is>
           <t>requirements §8 (Part Sales impact investigation)</t>
         </is>
       </c>
-      <c r="L163" s="18" t="inlineStr">
+      <c r="L164" s="18" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="M163" s="21" t="inlineStr">
-        <is>
-          <t>NEW V2.4 §8 open question (D9). Placeholder only — do NOT fabricate expected. The shared order/status logic (requested -&gt; orderable/waiting-to-receive; PO-on-order without vendor/cost) may touch Part Sales; confirm with dev and report. Excluded from the TestRail XML update batch until scoped.</t>
+      <c r="M164" s="17" t="inlineStr">
+        <is>
+          <t>NEW V2.4 §8 open question (D9). Placeholder only — do NOT fabricate expected. The shared order/status logic (requested -&gt; orderable/waiting-to-receive; PO-on-order without vendor/cost) may touch Part Sales; confirm with dev and report. Excluded from the TestRail XML update batch until scoped. | 2026-07-13: NOT in testrail-id-map.csv (no C-ID) - Open-Question / dev-investigation case, not created in TestRail. Follow-up: assign a C-ID only if/when it is imported after dev confirmation. | 2026-07-14 grind: remains an Open-Question / dev BE-investigation. The claim (Part Sales unaffected by the shared requested-&gt;orderable/waiting-to-receive order-status logic) is a back-end code-path question that is NOT meaningfully UI-observable from the app; confirming it requires dev to trace whether the shared order/status logic touches the Part Sales flow. Still unmapped in testrail-id-map.csv (no C-ID) — assign a C-ID only if imported after dev confirmation. Kept Open-Question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20" t="inlineStr">
+        <is>
+          <t>SF-AUTO-01</t>
+        </is>
+      </c>
+      <c r="B165" s="21" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C165" s="21" t="inlineStr">
+        <is>
+          <t>S16-R12 (a) single line</t>
+        </is>
+      </c>
+      <c r="D165" s="21" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G165" s="21" t="inlineStr">
+        <is>
+          <t>Admin / a role that can complete work orders.</t>
+        </is>
+      </c>
+      <c r="H165" s="21" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. Require Review Before Completion is OFF (in the Work Orders settings tab).
+3. A work order is in Approved status with two or more open (not-yet-completed) lines.</t>
+        </is>
+      </c>
+      <c r="I165" s="21" t="inlineStr">
+        <is>
+          <t>1. Open the work order and complete one line at a time using the per-line Complete action.
+2. After completing the first line (while at least one other line is still open), check the work order status.
+3. Complete the last remaining open line.
+4. Check the work order status again.</t>
+        </is>
+      </c>
+      <c r="J165" s="21" t="inlineStr">
+        <is>
+          <t>1. While at least one line is still open, the work order stays in Approved.
+2. The moment the last open line is completed, the work order moves to Complete on its own (invoice-ready).
+3. You do not have to click Complete Work Order separately for the work order to reach Complete.</t>
+        </is>
+      </c>
+      <c r="K165" s="21" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L165" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M165" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-14 (S-15838 live, Require Review OFF): two authorized lines; completing line 1 left the WO 'Approved'; completing the last line auto-flipped the WO to 'Complete' with no separate Complete Work Order step (WO status read via GET /api/work-orders/view/{id}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>SF-AUTO-02</t>
+        </is>
+      </c>
+      <c r="B166" s="17" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
+        <is>
+          <t>S16-R12 (b) bulk</t>
+        </is>
+      </c>
+      <c r="D166" s="17" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F166" s="17" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G166" s="17" t="inlineStr">
+        <is>
+          <t>Admin / a role that can complete work orders.</t>
+        </is>
+      </c>
+      <c r="H166" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is OFF.
+3. A work order is in Approved status with several open lines and nothing left to receive on those lines.</t>
+        </is>
+      </c>
+      <c r="I166" s="17" t="inlineStr">
+        <is>
+          <t>1. Open the work order and select all the open lines.
+2. From the bulk actions menu choose Set line status and set the selected lines to Complete (resolving them all at once).
+3. Check the work order status.</t>
+        </is>
+      </c>
+      <c r="J166" s="17" t="inlineStr">
+        <is>
+          <t>1. All selected lines become Complete in one action.
+2. Because that resolves the last open lines, the work order moves to Complete on its own (invoice-ready).
+3. No separate Complete Work Order step is needed.</t>
+        </is>
+      </c>
+      <c r="K166" s="17" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L166" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M166" s="17" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-14 (S-15824 / 446c1cd6 live, Require Review OFF): 3 authorized labor lines resolved in one bulk call (POST /api/work-orders/lines/change-lines {field:'status',value:'complete',lines:[...]} -&gt; 201); the WO auto-flipped 'Approved' -&gt; 'Complete' with no separate Complete step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20" t="inlineStr">
+        <is>
+          <t>SF-AUTO-03</t>
+        </is>
+      </c>
+      <c r="B167" s="21" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C167" s="21" t="inlineStr">
+        <is>
+          <t>S16-R12 (c) split</t>
+        </is>
+      </c>
+      <c r="D167" s="21" t="inlineStr">
+        <is>
+          <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="E167" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F167" s="21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G167" s="21" t="inlineStr">
+        <is>
+          <t>Admin / a role that can complete work orders and split.</t>
+        </is>
+      </c>
+      <c r="H167" s="21" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is OFF.
+3. A work order has several lines; some are already completed and at least one line is still open.</t>
+        </is>
+      </c>
+      <c r="I167" s="21" t="inlineStr">
+        <is>
+          <t>1. Open the work order and complete all but one line, leaving one line still open (the work order stays Approved).
+2. Select the remaining open line and use the bulk actions menu Split work order to move it to a new work order.
+3. Check the status of the original work order after the split.</t>
+        </is>
+      </c>
+      <c r="J167" s="21" t="inlineStr">
+        <is>
+          <t>1. The open line moves to a new work order.
+2. The original work order is now fully resolved (all its remaining lines are complete), so it moves to Complete on its own.
+3. No separate Complete Work Order step is needed on the original work order.</t>
+        </is>
+      </c>
+      <c r="K167" s="21" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L167" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M167" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-14 (S-15822 / a8fb8d3f live, Require Review OFF): completed 2 of 3 lines (WO stayed 'Approved'), then split the still-open line to a new WO (POST /api/work-orders/split -&gt; 201, new WO id returned); the original WO, now fully resolved, auto-flipped to 'Complete'. New split WO cleaned up (deleted).</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
+        <is>
+          <t>SF-AUTO-04</t>
+        </is>
+      </c>
+      <c r="B168" s="17" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>S16-R12 (d) delete line</t>
+        </is>
+      </c>
+      <c r="D168" s="17" t="inlineStr">
+        <is>
+          <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="E168" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F168" s="17" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G168" s="17" t="inlineStr">
+        <is>
+          <t>Admin / a role that can complete work orders and delete lines.</t>
+        </is>
+      </c>
+      <c r="H168" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is OFF.
+3. A work order has some completed lines and one remaining open line.</t>
+        </is>
+      </c>
+      <c r="I168" s="17" t="inlineStr">
+        <is>
+          <t>1. Open the work order (its other lines are already complete; one line is still open).
+2. Select the open line and use the bulk actions menu Delete lines to remove it.
+3. Check the work order status.</t>
+        </is>
+      </c>
+      <c r="J168" s="17" t="inlineStr">
+        <is>
+          <t>1. The open line is removed.
+2. Because the remaining lines are all complete, the work order moves to Complete on its own.
+3. No separate Complete Work Order step is needed.</t>
+        </is>
+      </c>
+      <c r="K168" s="17" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L168" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M168" s="17" t="inlineStr">
+        <is>
+          <t>Wording per spec §16 R12(d)+design. VIU Blocked-Env 2026-07-14: the delete-a-line action could not be driven in this environment — POST /api/work-orders/lines/delete-lines returns HTTP 500 even for a delete that leaves the work order still open (requestId 768518b...), so it is a generic delete-lines failure in this env, not the auto-complete leg; and no browser (Chromium/Playwright) harness is available here to drive the UI 'Delete lines' bulk action. The auto-complete-on-last-line-resolve mechanism itself IS verified on the single, bulk and split paths (SF-AUTO-01/02/03) — the same backend recompute applies. Needs the delete-lines endpoint healthy (or a UI session) to confirm the delete-line trigger directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="20" t="inlineStr">
+        <is>
+          <t>SF-AUTO-05</t>
+        </is>
+      </c>
+      <c r="B169" s="21" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C169" s="21" t="inlineStr">
+        <is>
+          <t>S16-R12 review ON</t>
+        </is>
+      </c>
+      <c r="D169" s="21" t="inlineStr">
+        <is>
+          <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F169" s="21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G169" s="21" t="inlineStr">
+        <is>
+          <t>Admin / a role that can complete work orders.</t>
+        </is>
+      </c>
+      <c r="H169" s="21" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is ON and saved.
+3. A work order is in Approved status with two or more open lines.</t>
+        </is>
+      </c>
+      <c r="I169" s="21" t="inlineStr">
+        <is>
+          <t>1. Open the work order and complete the lines one at a time (or in bulk).
+2. After the last open line is resolved, check the work order status.
+3. Confirm whether the work order went straight to Complete or to review.</t>
+        </is>
+      </c>
+      <c r="J169" s="21" t="inlineStr">
+        <is>
+          <t>1. When the last open line is resolved, the work order moves to Ready for Review (Review) — it does NOT auto-complete.
+2. The work order must be signed off in the review step before it can reach Complete.</t>
+        </is>
+      </c>
+      <c r="K169" s="21" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L169" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M169" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-14 (S-15813 / 73d150d3 live): flipped Require Review ON (POST /api/organizations/settings/change requireReview:true); completing line 1 left the WO 'Approved'; resolving the last line routed the WO to 'Review' (Ready for Review), NOT 'Complete'. Settings restored byte-identical to baseline afterward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="16" t="inlineStr">
+        <is>
+          <t>SF-AUTO-06</t>
+        </is>
+      </c>
+      <c r="B170" s="17" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C170" s="17" t="inlineStr">
+        <is>
+          <t>S16-R13 clock-out exception</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
+        <is>
+          <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
+        </is>
+      </c>
+      <c r="E170" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F170" s="17" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G170" s="17" t="inlineStr">
+        <is>
+          <t>Technician (clocked into the line) / Admin to observe.</t>
+        </is>
+      </c>
+      <c r="H170" s="17" t="inlineStr">
+        <is>
+          <t>1. Signed in as a Technician who is clocked into the work on the work order.
+2. Require Review Before Completion is OFF.
+3. The work order has one remaining open line that the technician is working on.</t>
+        </is>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>1. As the technician, finish the last open line by clocking out of it.
+2. Check the work order status.</t>
+        </is>
+      </c>
+      <c r="J170" s="17" t="inlineStr">
+        <is>
+          <t>1. Even though Require Review is off, the work order routes to Ready for Review (not straight to Complete).
+2. This is the one path that does not auto-complete when review is off (a technician may not be allowed to complete a work order).</t>
+        </is>
+      </c>
+      <c r="K170" s="17" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L170" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="M170" s="17" t="inlineStr">
+        <is>
+          <t>Wording per spec §16 R13 (intentional clock-out exception). VIU Blocked-Env 2026-07-14: the per-line technician clock-out that finishes a line is not drivable through the available API (GET /api/technician-tasks returns 404; /api/technician-tasks/department-clock-* is a shop-time punch clock, not the per-line 'finish the line' timer), and no browser (Chromium/Playwright) harness is available here to drive the timer/clock-out UI. The auto-complete-vs-review routing is otherwise verified (SF-AUTO-01/05). Needs a technician time-clock UI session (or the per-line clock-out endpoint) to confirm the R13 exception directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20" t="inlineStr">
+        <is>
+          <t>SF-AUTO-07</t>
+        </is>
+      </c>
+      <c r="B171" s="21" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C171" s="21" t="inlineStr">
+        <is>
+          <t>S16-R12 backend status transition</t>
+        </is>
+      </c>
+      <c r="D171" s="21" t="inlineStr">
+        <is>
+          <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
+        </is>
+      </c>
+      <c r="E171" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F171" s="21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G171" s="21" t="inlineStr">
+        <is>
+          <t>Admin.</t>
+        </is>
+      </c>
+      <c r="H171" s="21" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order is in Approved status with two or more open lines.</t>
+        </is>
+      </c>
+      <c r="I171" s="21" t="inlineStr">
+        <is>
+          <t>1. With Require Review off, resolve the last open line and read the work order record.
+2. Turn Require Review on, and on another work order resolve the last open line and read the work order record.</t>
+        </is>
+      </c>
+      <c r="J171" s="21" t="inlineStr">
+        <is>
+          <t>1. With Require Review off, after the last open line resolves the work order record status becomes Complete (the resolve action returns success).
+2. With Require Review on, after the last open line resolves the work order record status becomes Ready for Review (Review), not Complete.</t>
+        </is>
+      </c>
+      <c r="K171" s="21" t="inlineStr">
+        <is>
+          <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
+        </is>
+      </c>
+      <c r="L171" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M171" s="21" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-14: verified the backend status transition directly. Resolve action POST /api/work-orders/lines/change-status {status:'complete'} returns 200; GET /api/work-orders/view/{id} then shows work_order.status = 'Complete' when Require Review was OFF (S-15838/S-15824), and status = 'Review' (Ready for Review) when Require Review was ON (S-15813). Placed in an API-titled section per Standing Rule 4 (asserts a backend status transition).</t>
         </is>
       </c>
     </row>
@@ -12641,7 +13258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12654,7 +13271,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>VIU PENDING - Simple Flow is under development; this tab lists every case still needing live verification (NOT-BUILT stories + cookie/role-dependent checks). Fill in results as the build completes on QA env sv7301.</t>
         </is>
@@ -12696,1543 +13313,6 @@
           <t>Observed Behavior + Screenshot</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>SF-SET-08</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Work Order Settings</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>Verify first-use defaults on a brand-new org (auto-approve OFF, create POs ON, vendor invoice REQUIRED)</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>SF-SET-13</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Work Order Settings</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Verify the Save Settings button is only enabled when there is an unsaved change</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr"/>
-      <c r="G4" s="21" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>SF-COMP-07</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Verify in-stock inventory parts decrement inventory and write Part History on simple completion</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>SF-COMP-08</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>SF-COMP-12</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>SF-COMP-13</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>SF-COMP-19</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>SF-CORE-02</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Core parts — Completion modal</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>SF-CORE-03</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Core parts — Completion modal</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>SF-CORE-04</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Core parts — Invoice gate</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>SF-CORE-05</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Core parts — Invoice gate</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>SF-CORE-06</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Core parts — Invoice gate</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>SF-CORE-07</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Core parts — Required invoice (Story 4)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>SF-CORE-08</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Core parts — Guardrail</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>SF-CORE-09</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Core parts — Guardrail</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>SF-VPART-07</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>SF-VMIS-03</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>SF-VMIS-06</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>SF-VMIS-07</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>SF-BULK-10</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-01</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-02</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="21" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-03</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr"/>
-      <c r="G25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-04</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr"/>
-      <c r="G26" s="21" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-05</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
-      <c r="G27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-06</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr"/>
-      <c r="G28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>SF-RCV-05</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr"/>
-      <c r="G29" s="17" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>SF-RCV-06</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr"/>
-      <c r="G30" s="21" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>SF-RCV-07</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr"/>
-      <c r="G31" s="17" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>SF-RCV-08</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr"/>
-      <c r="G32" s="21" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>SF-RCV-10</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr"/>
-      <c r="G33" s="17" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>SF-VEND-02</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr"/>
-      <c r="G34" s="21" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>SF-VEND-03</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr"/>
-      <c r="G35" s="17" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>SF-VEND-04</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr"/>
-      <c r="G36" s="21" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>SF-VEND-05</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr"/>
-      <c r="G37" s="17" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>SF-WOP-02</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr"/>
-      <c r="G38" s="21" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>SF-REV-04</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr"/>
-      <c r="G39" s="17" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>SF-REV-11</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F40" s="21" t="inlineStr"/>
-      <c r="G40" s="21" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>SF-REV-12</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr"/>
-      <c r="G41" s="17" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>SF-REV-14</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F42" s="21" t="inlineStr"/>
-      <c r="G42" s="21" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>SF-UX-04</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>UX Refinements (Story 15)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F43" s="17" t="inlineStr"/>
-      <c r="G43" s="17" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-02</t>
-        </is>
-      </c>
-      <c r="B44" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr"/>
-      <c r="G44" s="21" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-05</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F45" s="17" t="inlineStr"/>
-      <c r="G45" s="17" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-06</t>
-        </is>
-      </c>
-      <c r="B46" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr"/>
-      <c r="G46" s="21" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>SF-VAL-09</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F47" s="17" t="inlineStr"/>
-      <c r="G47" s="17" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="B48" s="21" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr"/>
-      <c r="G48" s="21" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-01</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F49" s="17" t="inlineStr"/>
-      <c r="G49" s="17" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr"/>
-      <c r="G50" s="21" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr"/>
-      <c r="G51" s="17" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="B52" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C52" s="21" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="D52" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F52" s="21" t="inlineStr"/>
-      <c r="G52" s="21" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr"/>
-      <c r="G53" s="17" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E54" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F54" s="21" t="inlineStr"/>
-      <c r="G54" s="21" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr"/>
-      <c r="G55" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14292,7 +13372,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="n">
+      <c r="A2" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -14315,14 +13395,14 @@
           <t>SF-PERM-01..10, SF-SET-11, SF-RCV-03, SF-REV-09</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>RESOLVED by SV-8183. Simple Flow adds NO new permission atom - every action maps to an existing Custom Roles atom (see requirements §9 action-&gt;atom map + per-role matrix): Settings = App Settings (defaults Admin/Service Manager/Office); Complete WO = Work Orders C&amp;E + WO Lines C&amp;E/Full View; Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Receive-on-WO = Order Parts (FE); Mark Reviewed = Review Work Orders + reviewer != completer. Source: SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="n">
+      <c r="A3" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -14345,14 +13425,14 @@
           <t>Global - especially SF-SET-08, SF-TECH-08, SF-REV-08</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n">
+      <c r="A4" s="26" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -14375,14 +13455,14 @@
           <t>SF-SET-08</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Explicitly NOT addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n">
+      <c r="A5" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -14405,14 +13485,14 @@
           <t>SF-SET-03, SF-COMP-06, SF-QB-02</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Explicitly NOT addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="26" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -14435,14 +13515,14 @@
           <t>SF-TECH-08 (and all SF-TECH-*)</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -14465,14 +13545,14 @@
           <t>SF-QB-06</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>RESOLVED by SV-8183 (Decision 4). A vendorless / no-PN part add requires See Financial Data, so the mandatory sell price is captured at add time and $0-cost margins are avoided. Source: SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="26" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -14495,14 +13575,14 @@
           <t>SF-COMP-07, SF-QB-01</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -14525,14 +13605,14 @@
           <t>SF-PERM-06</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>RESOLVED by SV-8183. The backend DOES enforce the Simple-Flow settings AND the permission atoms (not FE-only), subject to the WO-atom collapse caveat: any role with WO Create &amp; Edit can receive onto a WO, and the receive endpoint accepts the OR of ROLE_DELIVERY_CREATE_AND_EDIT / ROLE_WORK_ORDER_PART_CREATE / ROLE_WORK_ORDER_CREATE_AND_EDIT. Source: SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="26" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -14555,14 +13635,14 @@
           <t>SF-SET-13</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -14585,14 +13665,14 @@
           <t>SF-REV-10</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="26" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -14615,14 +13695,14 @@
           <t>SF-REV-08, SF-REV-11</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="28" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -14645,14 +13725,14 @@
           <t>SF-UX-04</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="26" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -14675,14 +13755,14 @@
           <t>SF-REV-15</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. SV-8183 defined WHO can sign off review, but NOT the require-review default cohort.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n">
+      <c r="A15" s="28" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -14705,7 +13785,7 @@
           <t>SF-RCV-05, SF-RCV-07</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>OPEN - pending Milos. Not addressed by SV-8183.</t>
         </is>

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -994,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1010,6 +1010,8 @@
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1078,6 +1080,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>TestRail Case ID</t>
+        </is>
+      </c>
+      <c r="O1" s="15" t="inlineStr">
+        <is>
+          <t>TestRail Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -1151,6 +1163,16 @@
           <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): all 7 toggles present in the listed order with helper text; no Full/Simple mode selector; toggles render as one flat list with no visual new-vs-existing distinction (spec S1-R1 wanted new toggles visually distinct — not present in build, so the title/expected were corrected to match the build). Prior: 2026-07-06 (08-settings-workorders.png).</t>
         </is>
       </c>
+      <c r="N2" s="17" t="inlineStr">
+        <is>
+          <t>29275</t>
+        </is>
+      </c>
+      <c r="O2" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29275</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -1223,6 +1245,16 @@
           <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): no mode selector and no VIN toggle on the tab. Settings model holds requireVehicleIdentifier / vehicleIdentifier:'vin' but it is not exposed as a Work Orders toggle. Prior: 2026-07-06 (08-settings-workorders.png).</t>
         </is>
       </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t>29276</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -1295,6 +1327,16 @@
           <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): NO 'Create Purchase Orders' toggle on the Work Orders tab and no createPurchaseOrders key in GET /api/organizations/settings (confirmed live). Build lags V2.4 spec S1-R2 (which retains the toggle + No-PO path). DEVIATION — tester will find the toggle absent. Do not record as passing.</t>
         </is>
       </c>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>29277</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29277</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -1367,6 +1409,16 @@
           <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): toggle present; helper text captured exactly as shown (dropped the earlier 'approximately' hedge). Maps to requireVendorInvoiceNumber. Prior: 2026-07-06.</t>
         </is>
       </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t>29278</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -1440,6 +1492,16 @@
           <t>Wording+VIU 2026-07-13: Auto-approve Lines helper text confirms 'New work order lines are created already approved, skipping the line approval step'. Auto-approve-ON line behavior verified in prior VIU line-drive 2026-07-06 (WO S2-15747 line auto-approved on add); not re-driven this run to limit settings churn on the shared env.</t>
         </is>
       </c>
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <t>29279</t>
+        </is>
+      </c>
+      <c r="O6" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29279</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -1513,6 +1575,16 @@
           <t>Wording+VIU 2026-07-13: with Auto-approve Lines Off, a new line stays unapproved with Approve/Decline actions — verified in prior VIU line-drive 2026-07-06 (S17-01-unapproved-line.png); helper text re-confirmed 2026-07-13. Not re-driven this run to limit settings churn on the shared env.</t>
         </is>
       </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>29280</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -1585,6 +1657,16 @@
           <t>Wording+VIU 2026-07-13: toggles present; states match GET /api/organizations/settings (org baseline this run: requireTechStories:false, requireMileage:false, requireHours:false, autoPickInventoryParts:false). Prior: 2026-07-06.</t>
         </is>
       </c>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t>29281</t>
+        </is>
+      </c>
+      <c r="O8" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29281</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
@@ -1654,6 +1736,16 @@
       <c r="M9" s="21" t="inlineStr">
         <is>
           <t>VIU-observed 2026-07-14 (awaiting Milos Q3/Q4). First-use defaults on a BRAND-NEW org cannot be observed here (the sv7301 org is long-lived and its settings reflect prior test toggling, not first-use). Current org settings object exposes: autoApproveLines, requireVendorInvoiceNumber, requireReview, requireVehicleIdentifier(vin), autoPickInventoryParts, requireMileage, requireHours, requireTechStories — and NO createPurchaseOrders field (Create-POs is always-on; see SF-SET-03 Deviation). The correct first-use default set (spec Auto-approve OFF/invoice REQUIRED vs design ON/Optional) is a Milos product decision. No pass/fail asserted.</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>29282</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29282</t>
         </is>
       </c>
     </row>
@@ -1728,6 +1820,16 @@
       <c r="M10" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: flipped Require Engine Hours (requireHours) via POST /api/organizations/settings/change -&gt; 200, GET reflected the new value, then restored to baseline -&gt; 200 (org left unchanged). Prior: 2026-07-06.</t>
+        </is>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>29283</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29283</t>
         </is>
       </c>
     </row>
@@ -1805,6 +1907,16 @@
           <t>Wording+VIU 2026-07-14 (Δ6/S1-R9). Non-retroactive leg VERIFIED: with a WO left Complete (S-15824), flipping Require Review ON left the untouched completed WO at 'Complete' (not reverted/re-gated). Apply-on-reopen leg OBSERVED: re-triggering the last-line-resolve on a completed WO while Require Review was ON routed it 'Complete' -&gt; 'Review' (Ready for Review), showing the new setting governs the WO once its completion is re-triggered rather than being locked to the old settings. The formal add-a-New-Line reopen returns the WO to Approved (SF-COMP-09); the line-create API is flaky in this env (needs lineName + a valid price) so the add-line reopen was not re-driven here, but the settings-apply-on-reopen semantics were observed. Settings restored byte-identical to baseline.</t>
         </is>
       </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>29284</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29284</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -1877,6 +1989,16 @@
           <t>Wording+VIU 2026-07-13: Technician quick-login -&gt; POST /api/organizations/settings/change = 403 (admin = 200). FE redirects tech away from the settings route. Non-admin cannot save WO settings. Prior: 2026-07-07.</t>
         </is>
       </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>29285</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29285</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -1948,6 +2070,16 @@
           <t>Wording+VIU 2026-07-13: GET /api/organizations/settings keys = id, organizationId, requireMileage, requireHours, requireTechStories, requireVehicleIdentifier, vehicleIdentifier, autoPickInventoryParts, autoApproveLines, requireVendorInvoiceNumber, requireReview. No operatingMode, no requireVin. Prior: 2026-07-06.</t>
         </is>
       </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>29286</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29286</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -2016,6 +2148,16 @@
       <c r="M14" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): 'Save Settings' button present and enabled with no pending change (no dirty-state gating). Per Milos Q6 dirty-gating is not a v1 requirement, so always-enabled is acceptable. Prior: 2026-07-06.</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>29287</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29287</t>
         </is>
       </c>
     </row>
@@ -2090,6 +2232,16 @@
           <t>Wording+VIU 2026-07-13 (S2-15823 live): toggle present with helper text 'Work orders must be reviewed and signed off before they can be completed'. Corrected the CTA label: the ready-WO action relabels to 'Send To Review' (confirmed live), not 'Complete &amp; Send to Review'. Routes to 'Review' status + 'Ready for Review'.</t>
         </is>
       </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>29288</t>
+        </is>
+      </c>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29288</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -2158,6 +2310,16 @@
       <c r="M16" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): all 7 toggles carry helper text (captured verbatim in wording-glossary-2026-07-13.md). Prior: 2026-07-06.</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>29289</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29289</t>
         </is>
       </c>
     </row>
@@ -2229,6 +2391,16 @@
       <c r="M17" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. 'New Line' and 'Complete Work Order' buttons sit together in the WO Lines toolbar.</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>29290</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29290</t>
         </is>
       </c>
     </row>
@@ -2305,6 +2477,16 @@
           <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): drove a fresh labor-only approved-line WO (S-15839) live. Clicking 'Complete Work Order' on the Lines tab went straight to the Success screen in ONE confirm (single POST /api/work-orders/{id}/simple-complete -&gt; 201), no PO/receive/invoice step. Success screen read 'Order complete' + 'Sent to Finance as an invoice-ready draft' with 'Done' / 'Go To Invoice' buttons; WO status -&gt; Complete and the line -&gt; complete (API-confirmed). Matches expected exactly; VIU-Verified reaffirmed. Evidence: screenshots/run325-reverify-2026-07-13/COMP02-01-open.png. Prior: Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Labor-only WO completed Details-&gt;Success with no receive step (drove S2-15795 / S2-15825 to Success live 2026-07-13).</t>
         </is>
       </c>
+      <c r="N18" s="17" t="inlineStr">
+        <is>
+          <t>29291</t>
+        </is>
+      </c>
+      <c r="O18" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29291</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
@@ -2377,6 +2559,16 @@
           <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Success screen showed WO number + 'Invoice total $434.95' with 'Done' and 'Go To Invoice' (S2-15825, live 2026-07-13).</t>
         </is>
       </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>29292</t>
+        </is>
+      </c>
+      <c r="O19" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29292</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -2448,6 +2640,16 @@
           <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. 'Go To Invoice' present on Success; Finance step per prior drive.</t>
         </is>
       </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>29293</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29293</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
@@ -2521,6 +2723,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-vehicle-field block (needs Require Mileage ON + missing value) per 2026-07-06 drive; not re-driven this session to limit settings churn on the shared env.</t>
         </is>
       </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>29294</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29294</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -2594,6 +2806,16 @@
           <t>VIU-observed 2026-07-14 (awaiting Milos Q5). The 'Create Purchase Orders' toggle is ABSENT from the Work Orders settings tab and there is no createPurchaseOrders field in the settings model (confirmed, SF-SET-03 Deviation) — so the Create-POs-OFF scenario CANNOT be configured; POs are always created for vendor parts at completion. Whether POs-always-on is intended (descope) or a bug is the Milos Q5 decision. No pass/fail asserted.</t>
         </is>
       </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>29295</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29295</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
@@ -2667,6 +2889,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — in-stock inventory decrement + Part History on simple completion (FV-comp08/decrement, 2026-07-10).</t>
         </is>
       </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>29296</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29296</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -2740,6 +2972,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Auto-pick OFF -&gt; Pick step ('Pick all from default bins' / 'Review individually'), FV-comp08-wizard1/2.png (2026-07-10).</t>
         </is>
       </c>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t>29297</t>
+        </is>
+      </c>
+      <c r="O24" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29297</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
@@ -2812,6 +3054,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — adding a line to a completed WO returns it to Approved (2026-07-06). | Δ5/R12 clause added 2026-07-14: after reopen, re-resolving the last open line auto-Completes (review OFF) or routes to Ready for Review (review ON) — same auto-complete trigger verified in SF-AUTO-01/05.</t>
         </is>
       </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>29298</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29298</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -2884,6 +3136,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — line-level Complete + per-part Receive still work (line 'Receive' button confirmed live 2026-07-13).</t>
         </is>
       </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>29299</t>
+        </is>
+      </c>
+      <c r="O26" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29299</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
@@ -2954,6 +3216,16 @@
       <c r="M27" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — optional-invoice wizard actions Cancel / Complete Without Receiving / Receive Parts + 'N parts waiting to receive' (FV-comp13-receivestep.png, 2026-07-10). | Δ core-block caveat added 2026-07-14 (design #4): when a waiting part is a special-order core, Complete Without Receiving is disabled until received (see SF-CORE-03). The base actions Cancel / Complete Without Receiving / Receive Parts for a normal part-bearing WO remain VIU-Verified; the core-waiting disabled state is design-sourced and Blocked-Env (special-order core not seedable).</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>29300</t>
+        </is>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29300</t>
         </is>
       </c>
     </row>
@@ -3031,6 +3303,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — background POs created + parts-to-receive count; vendorless part goes on WO PO flagged Vendor Missing (2026-07-08/10).</t>
         </is>
       </c>
+      <c r="N28" s="17" t="inlineStr">
+        <is>
+          <t>29301</t>
+        </is>
+      </c>
+      <c r="O28" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29301</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
@@ -3100,6 +3382,16 @@
       <c r="M29" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — 'Receive Parts' opens the shared Accept Delivery page for all vendors (FV-comp13, 2026-07-10).</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>29302</t>
+        </is>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
         </is>
       </c>
     </row>
@@ -3175,6 +3467,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Complete Without Receiving completes WO, unreceived parts stay waiting, line keeps Receive (2026-07-08/10). | Δ core-block caveat added 2026-07-14 (design #4): Complete Without Receiving is not available while a special-order core is waiting (core must be received first). Base behavior (non-core unreceived parts) remains VIU-Verified.</t>
         </is>
       </c>
+      <c r="N30" s="17" t="inlineStr">
+        <is>
+          <t>29303</t>
+        </is>
+      </c>
+      <c r="O30" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
@@ -3244,6 +3546,16 @@
       <c r="M31" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Cancel closes modal, no duplicate POs on re-open (idempotent) (2026-07-08).</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>29304</t>
+        </is>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
         </is>
       </c>
     </row>
@@ -3321,6 +3633,16 @@
           <t>Wording+VIU 2026-07-13 (S2-15827 / S2-15783 live, Require Mileage + Engine Hours ON, Require Review off): the completion Details modal ('Complete Work Order') shows Mileage + Engine Hours fields and NO VIN field; empty -&gt; 'required field' block. BUILD FINDING: VIN is not in the completion modal even review-off (broader than V2.4 Δ1). Corrected expected accordingly. Settings restored byte-identical.</t>
         </is>
       </c>
+      <c r="N32" s="17" t="inlineStr">
+        <is>
+          <t>29305</t>
+        </is>
+      </c>
+      <c r="O32" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
@@ -3389,6 +3711,16 @@
       <c r="M33" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Optional-invoice Success screen shows WO number + total + Go To Invoice/Done (live 2026-07-13).</t>
+        </is>
+      </c>
+      <c r="N33" s="21" t="inlineStr">
+        <is>
+          <t>29306</t>
+        </is>
+      </c>
+      <c r="O33" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
         </is>
       </c>
     </row>
@@ -3465,6 +3797,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice: Complete disabled until parts received, no skip option (FV-comp19, 2026-07-10).</t>
         </is>
       </c>
+      <c r="N34" s="17" t="inlineStr">
+        <is>
+          <t>29307</t>
+        </is>
+      </c>
+      <c r="O34" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
@@ -3539,6 +3881,16 @@
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice receive round-trip enables Complete once all received (FV-comp19-receivestep/afterreceive, 2026-07-10).</t>
         </is>
       </c>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>29308</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -3607,6 +3959,16 @@
       <c r="M36" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Cancel in required-invoice wizard leaves WO unchanged (2026-07-08).</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>29309</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
     </row>
@@ -3685,6 +4047,16 @@
           <t>Run-325 re-verify 2026-07-14 (Ayesha PASSED; FLIPPED VIU-Pending -&gt; VIU-Verified): with Require Vendor Invoice Number ON and Auto-approve Lines OFF, a newly added line is 'Needs Approval' (status authorization_required) and the 'Complete Work Order' button is DISABLED (aria-disabled=true, disabled class). Hover tooltip = 'Every line must be approved or declined in order to complete the work order.' Approving the line (change-status -&gt; authorized) re-enables the button. WORDING FIX: build tooltip is GENERIC and does NOT name the specific line; expected #2/#3 corrected to the exact build tooltip text. Evidence: COMP21-01-unapproved-line.png / COMP21-02-tooltip-hover.png / COMP21-03-approved-enabled.png. Prior: V2.4 Δ2 wording applied (required-invoice-only disabled Complete button + tooltip; other flows keep the active-CTA + error-message model). VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines OFF, and a WO with a Needs-Approval line; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
+      <c r="N37" s="21" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="O37" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -3760,6 +4132,16 @@
           <t>Run-325 re-verify 2026-07-14 (Ayesha PASSED; FLIPPED VIU-Pending -&gt; VIU-Verified): with Require Vendor Invoice Number ON and Auto-approve Lines ON, a line auto-approved on add was manually un-approved (change-status -&gt; authorization_required); the 'Complete Work Order' button then went DISABLED (aria-disabled=true, disabled class) with tooltip 'Every line must be approved or declined in order to complete the work order.' — confirming the gate holds even with Auto-approve ON. Re-approving re-enabled the button. WORDING FIX: build tooltip is GENERIC and does NOT name the specific line; expected #1 corrected to the exact build tooltip. Evidence: COMP22-01-unapproved-disabled.png / COMP22-02-tooltip.png / COMP22-03-reapproved-enabled.png. Prior: V2.4 Δ2 wording applied. VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines ON, and a line manually un-approved after add; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t>29311</t>
+        </is>
+      </c>
+      <c r="O38" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
@@ -3829,6 +4211,16 @@
       <c r="M39" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — re-running completion creates no duplicate POs (one PO per vendor) (2026-07-08).</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="inlineStr">
+        <is>
+          <t>29312</t>
+        </is>
+      </c>
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
     </row>
@@ -3905,6 +4297,16 @@
           <t>Wording+VIU 2026-07-13: inventory cores resolved via a line-level Ok/Not-OK control (Core sub-line on the line's Parts view, $ amount, $0 until Not-OK); no distinct Resolve Cores wizard step - verified prior (CORE-05-resolve-cores.png). Completion surface re-confirmed live.</t>
         </is>
       </c>
+      <c r="N40" s="17" t="inlineStr">
+        <is>
+          <t>29313</t>
+        </is>
+      </c>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
@@ -3974,6 +4376,16 @@
       <c r="M41" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: a work order with no cores shows no core sub-lines and no Resolve Cores step; completion goes Details -&gt; Success (confirmed live on labor-only WOs S2-15795/S2-15825/S2-15823 this run).</t>
+        </is>
+      </c>
+      <c r="N41" s="21" t="inlineStr">
+        <is>
+          <t>29314</t>
+        </is>
+      </c>
+      <c r="O41" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
     </row>
@@ -4050,6 +4462,16 @@
           <t>FLIPPED 2026-07-14 per design #4: a waiting special-order core now makes Complete Without Receiving UN-available (was 'stays available'). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t>29315</t>
+        </is>
+      </c>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
@@ -4117,6 +4539,16 @@
       <c r="M43" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build. The genuine cored catalog part P550848 (core_charge=1, catalogue_part_id 4b4753e0) carries its core attribute ONLY when added via the inventory-source catalog path (select_part forces Source=Inventory). A vendor-sourced part request for the SAME part (POST /api/work-orders/part/make-request with part_source_type='vendor' + inventory_part_id of P550848) returns 201 but the resulting part request has is_core=false and core_charge=0 — the core charge is dropped. Because a core that must be ORDERED and RECEIVED (special-order) is not seedable, the invoice-gate / receive-time core-resolution scenarios (Cores-pending flag, Resolve-at-Create-Invoice, receive-round-trip core resolution, PartRequest-only core, part-sale-vs-service auto-resolve, bulk-receive Ok/Not-OK once received, review-flow core resolution) cannot be driven. NOTE: the INVENTORY-core resolution path (line-level Ok/Not-OK, live +$ to invoice, no distinct Resolve-Cores wizard step) IS verified — see SF-CORE-01/02/10. Needs a hand-seeded special-order/vendor core part (dev/data).</t>
+        </is>
+      </c>
+      <c r="N43" s="21" t="inlineStr">
+        <is>
+          <t>29316</t>
+        </is>
+      </c>
+      <c r="O43" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
       </c>
     </row>
@@ -4193,6 +4625,16 @@
           <t>Aligned 2026-07-14 to design #4 un-skippable core: the cored line must be received first (Complete Without Receiving / Skip is disabled while the core is waiting). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
+      <c r="N44" s="17" t="inlineStr">
+        <is>
+          <t>29317</t>
+        </is>
+      </c>
+      <c r="O44" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
@@ -4265,6 +4707,16 @@
           <t>Aligned 2026-07-14 to design #4 un-skippable core. Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
+      <c r="N45" s="21" t="inlineStr">
+        <is>
+          <t>29318</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -4339,6 +4791,16 @@
           <t>Aligned 2026-07-14 to design #4 un-skippable core (required-invoice path already receive-first). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>29319</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
@@ -4409,6 +4871,16 @@
           <t>Blocked-Env (precise, reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build. The genuine cored catalog part P550848 (core_charge=1, catalogue_part_id 4b4753e0) carries its core attribute ONLY when added via the inventory-source catalog path (select_part forces Source=Inventory). A vendor-sourced part request for the SAME part (POST /api/work-orders/part/make-request with part_source_type='vendor' + inventory_part_id of P550848) returns 201 but the resulting part request has is_core=false and core_charge=0 — the core charge is dropped. Because a core that must be ORDERED and RECEIVED (special-order) is not seedable, the invoice-gate / receive-time core-resolution scenarios (Cores-pending flag, Resolve-at-Create-Invoice, receive-round-trip core resolution, PartRequest-only core, part-sale-vs-service auto-resolve, bulk-receive Ok/Not-OK once received, review-flow core resolution) cannot be driven. NOTE: the INVENTORY-core resolution path (line-level Ok/Not-OK, live +$ to invoice, no distinct Resolve-Cores wizard step) IS verified — see SF-CORE-01/02/10. Needs a hand-seeded special-order/vendor core part (dev/data).</t>
         </is>
       </c>
+      <c r="N47" s="21" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="O47" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -4477,6 +4949,16 @@
       <c r="M48" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build. The genuine cored catalog part P550848 (core_charge=1, catalogue_part_id 4b4753e0) carries its core attribute ONLY when added via the inventory-source catalog path (select_part forces Source=Inventory). A vendor-sourced part request for the SAME part (POST /api/work-orders/part/make-request with part_source_type='vendor' + inventory_part_id of P550848) returns 201 but the resulting part request has is_core=false and core_charge=0 — the core charge is dropped. Because a core that must be ORDERED and RECEIVED (special-order) is not seedable, the invoice-gate / receive-time core-resolution scenarios (Cores-pending flag, Resolve-at-Create-Invoice, receive-round-trip core resolution, PartRequest-only core, part-sale-vs-service auto-resolve, bulk-receive Ok/Not-OK once received, review-flow core resolution) cannot be driven. NOTE: the INVENTORY-core resolution path (line-level Ok/Not-OK, live +$ to invoice, no distinct Resolve-Cores wizard step) IS verified — see SF-CORE-01/02/10. Needs a hand-seeded special-order/vendor core part (dev/data).</t>
+        </is>
+      </c>
+      <c r="N48" s="17" t="inlineStr">
+        <is>
+          <t>29321</t>
+        </is>
+      </c>
+      <c r="O48" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
         </is>
       </c>
     </row>
@@ -4551,6 +5033,16 @@
           <t>Wording+VIU 2026-07-13: the Core sub-line shows a '+$ to invoice' amount at the line level ($0 until Not-OK); no Resolve Cores wizard total - verified prior (CORE screenshots); line-level control confirmed.</t>
         </is>
       </c>
+      <c r="N49" s="21" t="inlineStr">
+        <is>
+          <t>29322</t>
+        </is>
+      </c>
+      <c r="O49" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -4622,6 +5114,16 @@
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; the empty line shows the 'Add tech story for this line' link.</t>
         </is>
       </c>
+      <c r="N50" s="17" t="inlineStr">
+        <is>
+          <t>29323</t>
+        </is>
+      </c>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
@@ -4691,6 +5193,16 @@
       <c r="M51" s="21" t="inlineStr">
         <is>
           <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): with Require Tech Stories ON, a story-less line blocks completion both server-side and in the UI. API: POST /api/work-orders/{id}/simple-complete -&gt; 400 'Line can not be completed without a tech story. id: &lt;lineId&gt;'. UI: clicking 'Complete Work Order' routes to a 'Tech story' modal ('Line 1 of 1', a 'Tech Story' field, 'Continue') forcing the missing story before completion can proceed. Matches expected; VIU-Verified reaffirmed. Ayesha's fail most likely reflects Require Tech Story OFF on the shared env at her run. Evidence: screenshots/run325-reverify-2026-07-13/TECH02-01-storygate.png. Prior: Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; with Require Tech Story ON, completion is blocked until every line has a story (Require Tech Story gate; toggle confirmed SF-SET-15).</t>
+        </is>
+      </c>
+      <c r="N51" s="21" t="inlineStr">
+        <is>
+          <t>29324</t>
+        </is>
+      </c>
+      <c r="O51" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
     </row>
@@ -4767,6 +5279,16 @@
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Complete opens the tech-story modal first, then chains into completion (tech story -&gt; parts -&gt; complete) - verified prior VIU.</t>
         </is>
       </c>
+      <c r="N52" s="17" t="inlineStr">
+        <is>
+          <t>29325</t>
+        </is>
+      </c>
+      <c r="O52" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
@@ -4840,6 +5362,16 @@
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech-story modal header 'Tech story' with 'WO# · Customer', per-line card + 'Line X of N', Next disabled until textarea non-empty - verified prior VIU.</t>
         </is>
       </c>
+      <c r="N53" s="21" t="inlineStr">
+        <is>
+          <t>29326</t>
+        </is>
+      </c>
+      <c r="O53" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -4913,6 +5445,16 @@
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; multi-line navigation (no Back on line 1; Back after; Continue/Save on last) - verified prior VIU.</t>
         </is>
       </c>
+      <c r="N54" s="17" t="inlineStr">
+        <is>
+          <t>29327</t>
+        </is>
+      </c>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
@@ -4981,6 +5523,16 @@
       <c r="M55" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; saved story renders inline with a green check + text + Edit link - verified prior VIU.</t>
+        </is>
+      </c>
+      <c r="N55" s="21" t="inlineStr">
+        <is>
+          <t>29328</t>
+        </is>
+      </c>
+      <c r="O55" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
     </row>
@@ -5054,6 +5606,16 @@
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Reworded from the dev-only 'test id input_tech_story' check to a tester-meaningful text-box check (the input_tech_story test-id is a dev-automation hook, not tester-facing). Textarea confirmed present.</t>
         </is>
       </c>
+      <c r="N56" s="17" t="inlineStr">
+        <is>
+          <t>29329</t>
+        </is>
+      </c>
+      <c r="O56" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
@@ -5124,6 +5686,16 @@
       <c r="M57" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech story captured both inline on the line and via the completion gate modal (individually or several at once); both persist (Story 17 authoritative) - verified prior VIU.</t>
+        </is>
+      </c>
+      <c r="N57" s="21" t="inlineStr">
+        <is>
+          <t>29330</t>
+        </is>
+      </c>
+      <c r="O57" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
     </row>
@@ -5200,6 +5772,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N58" s="17" t="inlineStr">
+        <is>
+          <t>29331</t>
+        </is>
+      </c>
+      <c r="O58" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
@@ -5274,6 +5856,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N59" s="21" t="inlineStr">
+        <is>
+          <t>29332</t>
+        </is>
+      </c>
+      <c r="O59" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -5345,6 +5937,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N60" s="17" t="inlineStr">
+        <is>
+          <t>29333</t>
+        </is>
+      </c>
+      <c r="O60" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
@@ -5415,6 +6017,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N61" s="21" t="inlineStr">
+        <is>
+          <t>29334</t>
+        </is>
+      </c>
+      <c r="O61" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -5483,6 +6095,16 @@
       <c r="M62" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N62" s="17" t="inlineStr">
+        <is>
+          <t>29335</t>
+        </is>
+      </c>
+      <c r="O62" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
     </row>
@@ -5556,6 +6178,16 @@
           <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): created a genuine vendorless part on a WO (part_number=null, vendor_id=null, vendor_name=null). Editing the part to add a Part Number ('ZZPN-TRANS1') and assign a Vendor ('Aabridge Beverages') persisted via POST /api/work-orders/part/change-request -&gt; 200, and the part_request then carried both part_number and vendor_id/vendor_name — i.e. no longer vendorless. The downstream QuickBooks-eligibility half (expected #2) still needs a QuickBooks-connected company to observe directly, but the vendorless-&gt;assigned transition (the case's core assertion) is confirmed. Evidence: VPART06-01-edit-open.png / VPART06-02-filled.png. Prior: Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N63" s="21" t="inlineStr">
+        <is>
+          <t>29336</t>
+        </is>
+      </c>
+      <c r="O63" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -5628,6 +6260,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N64" s="17" t="inlineStr">
+        <is>
+          <t>29337</t>
+        </is>
+      </c>
+      <c r="O64" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="inlineStr">
@@ -5700,6 +6342,16 @@
           <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendorless part joins the WO's normal PO, no dummy PO.</t>
         </is>
       </c>
+      <c r="N65" s="21" t="inlineStr">
+        <is>
+          <t>29338</t>
+        </is>
+      </c>
+      <c r="O65" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -5771,6 +6423,16 @@
           <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. 'Vendor Missing +N' shows on PO list + detail.</t>
         </is>
       </c>
+      <c r="N66" s="17" t="inlineStr">
+        <is>
+          <t>29339</t>
+        </is>
+      </c>
+      <c r="O66" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="20" t="inlineStr">
@@ -5842,6 +6504,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N67" s="21" t="inlineStr">
+        <is>
+          <t>29340</t>
+        </is>
+      </c>
+      <c r="O67" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -5913,6 +6585,16 @@
           <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendor-select + part-number edit offered on the vendor-missing PO. Stripped story refs.</t>
         </is>
       </c>
+      <c r="N68" s="17" t="inlineStr">
+        <is>
+          <t>29341</t>
+        </is>
+      </c>
+      <c r="O68" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="20" t="inlineStr">
@@ -5984,6 +6666,16 @@
           <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. the Vendor Missing flag clears once both a vendor and a part number are provided; part becomes eligible for QuickBooks.</t>
         </is>
       </c>
+      <c r="N69" s="21" t="inlineStr">
+        <is>
+          <t>29342</t>
+        </is>
+      </c>
+      <c r="O69" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -6054,6 +6746,16 @@
           <t>Deviation (observed 2026-07-14): the Reports area has NO dedicated Vendor-Missing / 'needs vendor' PO report. Current reports = Timesheet Activities, Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency, Sales Tax Collected, A/R Aging (Summary/Detail/Collection), A/P Aging (Summary/Detail), A/P Unpaid Invoices, IBS Batches, QB Unexported, Notes, Reminders — none flag vendor-missing POs as 'needs vendor'. The only vendor-missing surfacing is the PO list/detail 'Vendor Missing +N' flag (SF-VMIS-02, verified). Spec S6-R6's report requirement is not implemented as a report. Flag for PO/dev.</t>
         </is>
       </c>
+      <c r="N70" s="17" t="inlineStr">
+        <is>
+          <t>29343</t>
+        </is>
+      </c>
+      <c r="O70" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
@@ -6126,6 +6828,16 @@
           <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. sell-price-only part orderable from the line's Order action, joins the Vendor-Missing PO, moves requested -&gt; waiting-to-receive without completing the WO - verified prior (C29439).</t>
         </is>
       </c>
+      <c r="N71" s="21" t="inlineStr">
+        <is>
+          <t>29439</t>
+        </is>
+      </c>
+      <c r="O71" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
@@ -6197,6 +6909,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N72" s="17" t="inlineStr">
+        <is>
+          <t>29344</t>
+        </is>
+      </c>
+      <c r="O72" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="20" t="inlineStr">
@@ -6267,6 +6989,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N73" s="21" t="inlineStr">
+        <is>
+          <t>29345</t>
+        </is>
+      </c>
+      <c r="O73" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -6337,6 +7069,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N74" s="17" t="inlineStr">
+        <is>
+          <t>29346</t>
+        </is>
+      </c>
+      <c r="O74" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="20" t="inlineStr">
@@ -6405,6 +7147,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N75" s="21" t="inlineStr">
+        <is>
+          <t>29347</t>
+        </is>
+      </c>
+      <c r="O75" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -6473,6 +7225,16 @@
       <c r="M76" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N76" s="17" t="inlineStr">
+        <is>
+          <t>29348</t>
+        </is>
+      </c>
+      <c r="O76" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
     </row>
@@ -6545,6 +7307,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N77" s="21" t="inlineStr">
+        <is>
+          <t>29349</t>
+        </is>
+      </c>
+      <c r="O77" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -6613,6 +7385,16 @@
       <c r="M78" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N78" s="17" t="inlineStr">
+        <is>
+          <t>29350</t>
+        </is>
+      </c>
+      <c r="O78" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
     </row>
@@ -6687,6 +7469,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N79" s="21" t="inlineStr">
+        <is>
+          <t>29351</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -6755,6 +7547,16 @@
       <c r="M80" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N80" s="17" t="inlineStr">
+        <is>
+          <t>29352</t>
+        </is>
+      </c>
+      <c r="O80" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
     </row>
@@ -6830,6 +7632,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N81" s="21" t="inlineStr">
+        <is>
+          <t>29353</t>
+        </is>
+      </c>
+      <c r="O81" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -6900,6 +7712,16 @@
       <c r="M82" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N82" s="17" t="inlineStr">
+        <is>
+          <t>29354</t>
+        </is>
+      </c>
+      <c r="O82" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
     </row>
@@ -6975,6 +7797,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N83" s="21" t="inlineStr">
+        <is>
+          <t>29355</t>
+        </is>
+      </c>
+      <c r="O83" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -7047,6 +7879,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N84" s="17" t="inlineStr">
+        <is>
+          <t>29356</t>
+        </is>
+      </c>
+      <c r="O84" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
@@ -7119,6 +7961,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N85" s="21" t="inlineStr">
+        <is>
+          <t>29357</t>
+        </is>
+      </c>
+      <c r="O85" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
@@ -7191,6 +8043,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). Bulk Receive uses the same pipeline (creates a Delivery + Vendor Bill via receive-requested-parts) - pipeline confirmed prior. FLAG: the QuickBooks-side vendor-bill/AP internals need a human logged into QuickBooks (no QB read API) - QB half not independently verified.</t>
         </is>
       </c>
+      <c r="N86" s="17" t="inlineStr">
+        <is>
+          <t>29358</t>
+        </is>
+      </c>
+      <c r="O86" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
@@ -7262,6 +8124,16 @@
           <t>Aligned 2026-07-14 to design #4 un-skippable core. Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
+      <c r="N87" s="21" t="inlineStr">
+        <is>
+          <t>29359</t>
+        </is>
+      </c>
+      <c r="O87" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -7331,6 +8203,16 @@
       <c r="M88" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N88" s="17" t="inlineStr">
+        <is>
+          <t>29360</t>
+        </is>
+      </c>
+      <c r="O88" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
     </row>
@@ -7406,6 +8288,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N89" s="21" t="inlineStr">
+        <is>
+          <t>29361</t>
+        </is>
+      </c>
+      <c r="O89" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
@@ -7478,6 +8370,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N90" s="17" t="inlineStr">
+        <is>
+          <t>29362</t>
+        </is>
+      </c>
+      <c r="O90" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
@@ -7550,6 +8452,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N91" s="21" t="inlineStr">
+        <is>
+          <t>29363</t>
+        </is>
+      </c>
+      <c r="O91" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -7620,6 +8532,16 @@
       <c r="M92" s="17" t="inlineStr">
         <is>
           <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, 2026-07-14, last-update-wins ruling by QA lead): a part-number add is no longer required to create a first-class inventory/catalog part in v1. Remaining assertions VERIFIED live 2026-07-14: entering a NEW part number persists and the part becomes receivable (POST /api/orders/receive-requested-parts 200 on seeded vendor-missing PO S-15849 after entering a NEW PN + cost + sell + invoice). The previously Blocked-Env downstream inventory/catalog/Part-History creation is no longer a v1 requirement, so it is dropped from the expected result.</t>
+        </is>
+      </c>
+      <c r="N92" s="17" t="inlineStr">
+        <is>
+          <t>29364</t>
+        </is>
+      </c>
+      <c r="O92" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
     </row>
@@ -7695,6 +8617,16 @@
           <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Verified live 2026-07-14 that entering a part number persists and the part becomes receivable (receive-requested-parts 200). The 'links to the first-class inventory item + updates stock/cost/history' assertion is deprecated (not a v1 requirement) and removed from the expected; the no-overwrite-of-description/category expectation is retained as a data-safety check.</t>
         </is>
       </c>
+      <c r="N93" s="21" t="inlineStr">
+        <is>
+          <t>29365</t>
+        </is>
+      </c>
+      <c r="O93" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
@@ -7767,6 +8699,16 @@
           <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
         </is>
       </c>
+      <c r="N94" s="17" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="O94" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
@@ -7840,6 +8782,16 @@
           <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive gates live-confirmed: a part cannot be received without a part number, without a vendor (for a vendor-missing part), or without a cost/sell price (Receive stayed disabled until all present). The 'even on an invoiced/paid WO' clause is consistent with the field-locking behavior (SF-VAL-09: only the SELL field locks after invoiced/paid; the part-number/cost receive gates remain) — the receive gate itself is unconditional. No error surfaced (gate is a disabled affordance, not a toast).</t>
         </is>
       </c>
+      <c r="N95" s="21" t="inlineStr">
+        <is>
+          <t>29367</t>
+        </is>
+      </c>
+      <c r="O95" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
@@ -7912,6 +8864,16 @@
           <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Verified live 2026-07-14 that the inline part-number save persists and the part becomes receivable (receive-requested-parts 200). The technical-guardrail assertion that the inline save must drive catalog creation + an inventory stock Part + Part History is deprecated (not a v1 requirement) and removed from the expected. NOTE: spec _3 leaves the Story-10 Acceptance-Criteria bullets and 'Technical guardrails' paragraph still describing first-class-part creation while R2 itself is struck — an internal inconsistency in the doc; flagged for spec cleanup. Applied the strike per the QA-lead last-update-wins ruling.</t>
         </is>
       </c>
+      <c r="N96" s="17" t="inlineStr">
+        <is>
+          <t>29368</t>
+        </is>
+      </c>
+      <c r="O96" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
@@ -7983,6 +8945,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N97" s="21" t="inlineStr">
+        <is>
+          <t>29369</t>
+        </is>
+      </c>
+      <c r="O97" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
@@ -8050,6 +9022,16 @@
       <c r="M98" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N98" s="17" t="inlineStr">
+        <is>
+          <t>29370</t>
+        </is>
+      </c>
+      <c r="O98" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
     </row>
@@ -8123,6 +9105,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N99" s="21" t="inlineStr">
+        <is>
+          <t>29371</t>
+        </is>
+      </c>
+      <c r="O99" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="16" t="inlineStr">
@@ -8195,6 +9187,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N100" s="17" t="inlineStr">
+        <is>
+          <t>29372</t>
+        </is>
+      </c>
+      <c r="O100" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
@@ -8209,12 +9211,12 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>S12-R1</t>
+          <t>S12-R1 (+ Milos Round-3 2026-07-16)</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify vendorless / no-part-number Work Order parts appear and can be received on the Receive (Accept Delivery) screen, and the Vendor Missing group sits per the agreed rule (top on Bulk Receive, bottom on the Receive screen)</t>
         </is>
       </c>
       <c r="E101" s="22" t="inlineStr">
@@ -8234,22 +9236,23 @@
       </c>
       <c r="H101" s="21" t="inlineStr">
         <is>
-          <t>1. Signed in as Admin.
-2. A WO has a vendorless/no-PN part and a WO-originated PO reached via the Receive button.</t>
+          <t>1. Signed in as Admin (or a role with receiving access).
+2. A Work Order has a part with no vendor and no part number, plus a WO-created Purchase Order that is opened using the Receive button on the Work Order.</t>
         </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
-          <t>1. Open Accept Delivery for the WO.
-2. Confirm the vendorless/no-PN parts appear.
-3. Confirm the vendor-missing group is at the top (leading).</t>
+          <t>1. On the Work Order, click the Receive button to open the Receive (Accept Delivery) screen (headed Purchase Order Details).
+2. Confirm the vendorless / no-part-number parts are listed and can be received here.
+3. Note where the Vendor Missing group sits on this Receive (Accept Delivery) screen.
+4. Open the Bulk Receive page (headed Receive Vendor Parts) for the same Purchase Orders and note where the Vendor Missing group sits there.</t>
         </is>
       </c>
       <c r="J101" s="21" t="inlineStr">
         <is>
-          <t>1. New vendorless/no-PN WO parts appear and are receivable here.
-2. WO-originated POs reached via the Receive button appear.
-3. Vendor-missing parts sit in their own group that LEADS (appears at the top), because they need action (assign a vendor) before receiving.</t>
+          <t>1. The vendorless / no-part-number Work Order parts appear in the Vendor Missing group and can be received once a vendor is chosen (Select Vendor) and a Part Number is entered.
+2. WO-created Purchase Orders opened with the Receive button appear on the Receive (Accept Delivery) screen and are receivable.
+3. The Vendor Missing group is positioned per the agreed rule (Milos, 2026-07-16): on the Bulk Receive page (Receive Vendor Parts) it leads at the TOP; on the Receive (Accept Delivery) screen it sits at the BOTTOM.</t>
         </is>
       </c>
       <c r="K101" s="21" t="inlineStr">
@@ -8259,12 +9262,22 @@
       </c>
       <c r="L101" s="21" t="inlineStr">
         <is>
-          <t>VIU-observed-awaiting-Milos</t>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="M101" s="21" t="inlineStr">
         <is>
-          <t>VIU-observed 2026-07-14 (awaiting Milos Q11). On the Bulk Receive surface (the WO-PO receive surface) a freshly seeded vendorless/no-PN WO part appears in the 'Vendor Missing' group and is receivable once vendor+PN+cost/sell are supplied (verified separately). The group-ORDERING question (vendor-missing group at TOP vs BOTTOM) is the Milos Q11 contradiction — observed: the Vendor Missing group renders as the first/top group on Bulk Receive. No pass/fail asserted on the ordering policy.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png).</t>
+        </is>
+      </c>
+      <c r="N101" s="21" t="inlineStr">
+        <is>
+          <t>29373</t>
+        </is>
+      </c>
+      <c r="O101" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
     </row>
@@ -8341,6 +9354,16 @@
           <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive gates confirmed on the Bulk Receive surface (the WO-PO receive surface; the legacy single-PO Accept Delivery path still 500s for WO POs = BUG-11): no vendor -&gt; Receive disabled; vendor set + no part number -&gt; disabled; part number + cost/sell empty -&gt; disabled; all of vendor + part number + cost/sell present -&gt; receivable. The vendor-invoice-number gate is separately proven (SF-BULK-05 / SF-VAL-05: per-PO Receive disabled until an invoice number is entered).</t>
         </is>
       </c>
+      <c r="N102" s="17" t="inlineStr">
+        <is>
+          <t>29374</t>
+        </is>
+      </c>
+      <c r="O102" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
@@ -8355,12 +9378,12 @@
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>S12-R3</t>
+          <t>S12-R3 (+ Milos Round-3 2026-07-16)</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify the multi-vendor '+N' indicator and the Vendor Missing group position on the receiving screens</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
@@ -8380,21 +9403,21 @@
       </c>
       <c r="H103" s="21" t="inlineStr">
         <is>
-          <t>1. Signed in as Admin.
-2. A multi-vendor delivery with a vendor-missing group exists.</t>
+          <t>1. Signed in as Admin (or a role with receiving access).
+2. A multi-vendor Purchase Order that also includes parts with no vendor (a Vendor Missing group) exists.</t>
         </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
-          <t>1. Open Accept Delivery.
-2. Confirm the '+N' vendor indicator.
-3. Confirm the ordering of the vendor-missing group.</t>
+          <t>1. Open the Purchase Orders list (Parts &gt; Purchase Orders) and look at the vendor indicator on a multi-vendor Purchase Order.
+2. Open the Receive (Accept Delivery) screen from the Work Order Receive button and note where the Vendor Missing group sits.
+3. Open the Bulk Receive page (Receive Vendor Parts) and note where the Vendor Missing group sits.</t>
         </is>
       </c>
       <c r="J103" s="21" t="inlineStr">
         <is>
-          <t>1. A '+N' indicator summarizes multiple vendors.
-2. The vendor-missing group leads (appears first).</t>
+          <t>1. A multi-vendor Purchase Order shows a '+N' indicator (for example '+1' or '+4') on the Purchase Orders list summarizing the extra vendors. (On the Receive / Accept Delivery screen the vendor names are listed in full instead of a '+N' badge.)
+2. The Vendor Missing group is positioned per the agreed rule (Milos, 2026-07-16): on the Bulk Receive page (Receive Vendor Parts) it leads at the TOP; on the Receive (Accept Delivery) screen it sits at the BOTTOM.</t>
         </is>
       </c>
       <c r="K103" s="21" t="inlineStr">
@@ -8404,12 +9427,22 @@
       </c>
       <c r="L103" s="21" t="inlineStr">
         <is>
-          <t>VIU-observed-awaiting-Milos</t>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="M103" s="21" t="inlineStr">
         <is>
-          <t>VIU-observed 2026-07-14 (awaiting Milos Q11). Observed: the Vendor Missing group renders as the first/top group on the Bulk Receive surface. Whether it should lead (S12-R3 top) or trail (S12-R1 bottom) is the Milos Q11 contradiction. No pass/fail asserted.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05.</t>
+        </is>
+      </c>
+      <c r="N103" s="21" t="inlineStr">
+        <is>
+          <t>29375</t>
+        </is>
+      </c>
+      <c r="O103" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
     </row>
@@ -8482,6 +9515,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N104" s="17" t="inlineStr">
+        <is>
+          <t>29376</t>
+        </is>
+      </c>
+      <c r="O104" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
@@ -8549,6 +9592,16 @@
       <c r="M105" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+        </is>
+      </c>
+      <c r="N105" s="21" t="inlineStr">
+        <is>
+          <t>29377</t>
+        </is>
+      </c>
+      <c r="O105" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
     </row>
@@ -8623,6 +9676,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N106" s="17" t="inlineStr">
+        <is>
+          <t>29440</t>
+        </is>
+      </c>
+      <c r="O106" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
@@ -8694,6 +9757,16 @@
           <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
+      <c r="N107" s="21" t="inlineStr">
+        <is>
+          <t>29378</t>
+        </is>
+      </c>
+      <c r="O107" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
@@ -8765,6 +9838,16 @@
           <t>Blocked-Env (precise): the Merge/Keep-Separate collision prompt could not be reached in this harness. Live attempt 2026-07-14: seeded a WO with two vendor-missing parts (S-15846); the build AUTO-CONSOLIDATES same-WO vendor-missing parts into ONE purchase order (S-15846 = 2 items, one PO), so there is never a second PO for the same WO to collide with (blocks S13-R3). Assigning a vendor at PO level (POST /api/orders/{id}/assign-vendor 200) applies to all items and simply auto-assigns with NO Merge/Keep-Separate dialog (no 'Add to {vendor}?' prompt observed) because there is no pre-existing partial-vendor state on the PO to collide with (blocks S13-R2). Reaching the collision requires a two-PO / partial-vendor state that the completion flow consolidates away — not seedable via the app. Needs a hand-crafted multi-PO same-vendor collision (dev/data seed).</t>
         </is>
       </c>
+      <c r="N108" s="17" t="inlineStr">
+        <is>
+          <t>29379</t>
+        </is>
+      </c>
+      <c r="O108" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
@@ -8837,6 +9920,16 @@
           <t>Blocked-Env (precise): the Merge/Keep-Separate collision prompt could not be reached in this harness. Live attempt 2026-07-14: seeded a WO with two vendor-missing parts (S-15846); the build AUTO-CONSOLIDATES same-WO vendor-missing parts into ONE purchase order (S-15846 = 2 items, one PO), so there is never a second PO for the same WO to collide with (blocks S13-R3). Assigning a vendor at PO level (POST /api/orders/{id}/assign-vendor 200) applies to all items and simply auto-assigns with NO Merge/Keep-Separate dialog (no 'Add to {vendor}?' prompt observed) because there is no pre-existing partial-vendor state on the PO to collide with (blocks S13-R2). Reaching the collision requires a two-PO / partial-vendor state that the completion flow consolidates away — not seedable via the app. Needs a hand-crafted multi-PO same-vendor collision (dev/data seed).</t>
         </is>
       </c>
+      <c r="N109" s="21" t="inlineStr">
+        <is>
+          <t>29380</t>
+        </is>
+      </c>
+      <c r="O109" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
@@ -8908,6 +10001,16 @@
           <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Assigning a brand-new vendor (no collision) via select_assign_vendor -&gt; POST /api/orders/{id}/assign-vendor 200 auto-assigned the vendor with NO Merge/Keep-Separate prompt and cleared the vendor-missing (QuickBooks) flag (PO left the Vendor-Missing group into the vendor's group). Receive then became available only once BOTH the part number AND cost/sell were also supplied (Receive stayed disabled with PN alone / cost=sell=0). Confirms Delta3 S13-R5/R6/R7.</t>
         </is>
       </c>
+      <c r="N110" s="17" t="inlineStr">
+        <is>
+          <t>29381</t>
+        </is>
+      </c>
+      <c r="O110" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
@@ -8980,6 +10083,16 @@
           <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
         </is>
       </c>
+      <c r="N111" s="21" t="inlineStr">
+        <is>
+          <t>29382</t>
+        </is>
+      </c>
+      <c r="O111" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
@@ -9051,6 +10164,16 @@
           <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). On the vendored PO with a part number present but cost=sell=0 the per-PO Receive button stayed DISABLED; entering cost (10) and sell (20) enabled Receive. Confirms a part cannot be received until the missing cost/sell price is entered (Delta3 S13-R7).</t>
         </is>
       </c>
+      <c r="N112" s="17" t="inlineStr">
+        <is>
+          <t>29442</t>
+        </is>
+      </c>
+      <c r="O112" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
@@ -9122,6 +10245,16 @@
           <t>Wording+VIU 2026-07-13: 'Waiting on Parts' column is off by default (toggle_column_unreceivedPartRequestsCount), enabled from the column selector - Story 14 built, verified prior runs (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon. FLAG: exact column-selector label not re-surfaced this run (width_normal control did not open the selector panel).</t>
         </is>
       </c>
+      <c r="N113" s="21" t="inlineStr">
+        <is>
+          <t>29383</t>
+        </is>
+      </c>
+      <c r="O113" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
@@ -9192,6 +10325,16 @@
           <t>Wording+VIU 2026-07-13: clicking the Waiting on Parts count opens the Bulk Receive page for the WO's first unreceived PO - verified prior (case 29384 pushed 2026-07-09/10).</t>
         </is>
       </c>
+      <c r="N114" s="17" t="inlineStr">
+        <is>
+          <t>29384</t>
+        </is>
+      </c>
+      <c r="O114" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
@@ -9259,6 +10402,16 @@
       <c r="M115" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: WO with nothing to receive shows '—' (no link) - verified prior (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon.</t>
+        </is>
+      </c>
+      <c r="N115" s="21" t="inlineStr">
+        <is>
+          <t>29385</t>
+        </is>
+      </c>
+      <c r="O115" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
     </row>
@@ -9332,6 +10485,16 @@
           <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): with Require Review ON, completing routes into the review flow (Send To Review), not a direct complete. | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
         </is>
       </c>
+      <c r="N116" s="17" t="inlineStr">
+        <is>
+          <t>29386</t>
+        </is>
+      </c>
+      <c r="O116" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
@@ -9403,6 +10566,16 @@
           <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15827/S2-15783 live, Require Review ON): the primary action button = 'Send To Review' on BOTH ready and part-bearing WOs (it replaces 'Complete Work Order'). For a part-bearing WO, clicking 'Send To Review' opens a dialog HEADED 'Complete &amp; Send to Review' (body 'N part waiting to receive'; buttons Cancel / Receive Parts / Send To Review). So 'Complete &amp; Send to Review' is the review-dialog HEADER, not the button; the clickable CTA is 'Send To Review'. Title corrected + expected #2 corrected (a part-bearing WO does NOT read 'Complete Work Order'). Evidence: screenshots/relevance-fix-2026-07-13/.</t>
         </is>
       </c>
+      <c r="N117" s="21" t="inlineStr">
+        <is>
+          <t>29387</t>
+        </is>
+      </c>
+      <c r="O117" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="16" t="inlineStr">
@@ -9474,6 +10647,16 @@
           <t>Wording+VIU 2026-07-13: the completion Details modal shows Mileage + Engine Hours and no VIN field (confirmed live on the review-off modal S2-15827; review-on captures VIN in Mark Reviewed per SF-REV-06). Upgraded from Pending - the field set is now confirmed.</t>
         </is>
       </c>
+      <c r="N118" s="17" t="inlineStr">
+        <is>
+          <t>29388</t>
+        </is>
+      </c>
+      <c r="O118" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
@@ -9541,6 +10724,16 @@
       <c r="M119" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: 'Receive Parts' opens the shared receive page (not an inline modal) in the review flow — verified prior drive (FV-rev04-receivestep/afterreceive.png, 2026-07-10); review flow re-confirmed live this run.</t>
+        </is>
+      </c>
+      <c r="N119" s="21" t="inlineStr">
+        <is>
+          <t>29389</t>
+        </is>
+      </c>
+      <c r="O119" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
     </row>
@@ -9616,6 +10809,16 @@
           <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15823/S2-15827 live, Require Review ON): the confirm button is 'Send To Review' (NOT 'Complete &amp; Send to Review' - that is the dialog HEADER for a part-bearing WO). Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.) Step 1 label corrected. Evidence: screenshots/relevance-fix-2026-07-13/. | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
         </is>
       </c>
+      <c r="N120" s="17" t="inlineStr">
+        <is>
+          <t>29390</t>
+        </is>
+      </c>
+      <c r="O120" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
@@ -9688,6 +10891,16 @@
           <t>Wording+VIU 2026-07-13: Mark Reviewed action confirmed live (S2-15823). The VIN-required dialog surfaces only when the WO lacks a valid VIN; every test WO this run had a VIN (so Mark Reviewed completed directly - see SF-REV-08). VIN-required dialog verified prior run 2026-07-06 (S16-04-review-wizard.png). Stripped dev test-id 'input_review_vin' from tester wording.</t>
         </is>
       </c>
+      <c r="N121" s="21" t="inlineStr">
+        <is>
+          <t>29391</t>
+        </is>
+      </c>
+      <c r="O121" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
@@ -9759,6 +10972,16 @@
           <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): on Send To Review the lines lock to Complete and inventory is auto-picked (design; review state confirmed live).</t>
         </is>
       </c>
+      <c r="N122" s="17" t="inlineStr">
+        <is>
+          <t>29392</t>
+        </is>
+      </c>
+      <c r="O122" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
@@ -9831,6 +11054,16 @@
           <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Mark Reviewed (VIN present) signs off and moves the WO directly Review -&gt; Complete; no distinct 'Reviewed' holding state and no separate final Complete click (S2-15823 went Review-&gt;Complete). | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
         </is>
       </c>
+      <c r="N123" s="21" t="inlineStr">
+        <is>
+          <t>29393</t>
+        </is>
+      </c>
+      <c r="O123" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="16" t="inlineStr">
@@ -9903,6 +11136,16 @@
           <t>Wording+VIU 2026-07-13: Mark Reviewed gated by Review Work Orders (woReviewWorkOrders) per fresh roles matrix (roles-matrix-2026-07-13.md); role without it sees Mark Reviewed disabled + 'Awaiting review'; self-review allowed when the role holds the permission (Milos ruling). Review flow re-confirmed live.</t>
         </is>
       </c>
+      <c r="N124" s="17" t="inlineStr">
+        <is>
+          <t>29394</t>
+        </is>
+      </c>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
@@ -9975,6 +11218,16 @@
           <t>Wording+VIU 2026-07-13: Mark Reviewed uses VIN / Serial # only, no review note field (V2.4 Δ4 confirmed; SF-REV-06/10 were already note-free). Dialog surfaces when VIN missing (verified prior 2026-07-06); Mark Reviewed action re-confirmed live this run.</t>
         </is>
       </c>
+      <c r="N125" s="21" t="inlineStr">
+        <is>
+          <t>29395</t>
+        </is>
+      </c>
+      <c r="O125" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="16" t="inlineStr">
@@ -10047,6 +11300,16 @@
           <t>VIU-observed 2026-07-14 (awaiting Milos Q8). The direct-sign-off behavior is observed: Confirm Review signs off and completes the WO directly with no distinct 'Reviewed' holding state (see SF-REV-08). The 'invoicing blocked until reviewed' leg depends on the Q8 ruling about whether a separate Reviewed state should exist. No pass/fail asserted on the undecided policy. | Δ5/R12 sanity clause added 2026-07-14 (review-ON last-line-resolve -&gt; Ready for Review; auto-complete trigger verified in SF-AUTO-05).</t>
         </is>
       </c>
+      <c r="N126" s="17" t="inlineStr">
+        <is>
+          <t>29396</t>
+        </is>
+      </c>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
@@ -10117,6 +11380,16 @@
           <t>Wording+VIU 2026-07-13: 'Ready for Review' indicator confirmed on a WO in Review (S2-15823). Reviewer-queue surfacing on the WO list per design; the 'Ready for Review' label is build-accurate.</t>
         </is>
       </c>
+      <c r="N127" s="21" t="inlineStr">
+        <is>
+          <t>29397</t>
+        </is>
+      </c>
+      <c r="O127" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
@@ -10184,6 +11457,16 @@
       <c r="M128" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15783 live, Require Review ON, one unapproved line): the 'Send To Review' button is DISABLED (isDisabled=true) while a line is unapproved; it becomes usable only after every line is approved. Step label corrected ('Complete &amp; Send to Review' -&gt; 'Send To Review'; the clickable action is 'Send To Review') and expected made build-accurate (the button is disabled rather than showing an error message). Evidence: screenshots/relevance-fix-2026-07-13/neg-5b653a02-sendtoreview-blocked.png.</t>
+        </is>
+      </c>
+      <c r="N128" s="17" t="inlineStr">
+        <is>
+          <t>29398</t>
+        </is>
+      </c>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
     </row>
@@ -10259,6 +11542,16 @@
           <t>Aligned 2026-07-14 to design #4 un-skippable core (review flow). Blocked-Env (reconfirmed live 2026-07-14): a SPECIAL-ORDER (vendor-sourced) core cannot be created in this build — the genuine cored catalog part P550848 (core_charge=1) is stored is_core=0 and a vendor-sourced part request for it drops the core attribute, so a core that must be ORDERED and RECEIVED is not seedable. Needs a hand-seeded (dev/data) special-order core to drive the un-skippable-core completion behavior. Wording updated to the design #4 core-block behavior. design4 tooltip "Receive the core part first — its core charge must be settled before you can complete."; waiting-card "N parts waiting to receive — includes a core charge." + "Receive it to settle the core (OK / Not OK) before completing this work order." (WO Review Flow.html). Copy is per design #4 — not yet live-confirmed because a special-order (vendor-sourced) core is not seedable in this build.</t>
         </is>
       </c>
+      <c r="N129" s="21" t="inlineStr">
+        <is>
+          <t>29399</t>
+        </is>
+      </c>
+      <c r="O129" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="16" t="inlineStr">
@@ -10273,12 +11566,12 @@
       </c>
       <c r="C130" s="17" t="inlineStr">
         <is>
-          <t>R Open (default)</t>
+          <t>R Open (default) - Milos Round-3 2026-07-16: ON for new orgs</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
         <is>
-          <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
+          <t>Verify Require Review Before Completion starts ON for a brand-new organization, and existing organizations keep today's behavior</t>
         </is>
       </c>
       <c r="E130" s="24" t="inlineStr">
@@ -10298,20 +11591,20 @@
       </c>
       <c r="H130" s="17" t="inlineStr">
         <is>
-          <t>1. A newly-created org and an existing org are available.
+          <t>1. A brand-new organization / account (no settings changed yet) and an existing organization are available.
 2. Signed in as Admin for each.</t>
         </is>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
-          <t>1. Check the Require Review default on a brand-new org.
-2. Check that existing orgs keep today's behavior (backfilled).</t>
+          <t>1. On a brand-new organization, open Settings &gt; Work Orders and check the Require Review Before Completion setting.
+2. On an existing organization, confirm its completion behavior is unchanged (the setting is backfilled).</t>
         </is>
       </c>
       <c r="J130" s="17" t="inlineStr">
         <is>
-          <t>1. On a brand-new org the Require Review Before Completion setting shows its default state.
-2. Existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
+          <t>1. On a brand-new organization / account, Require Review Before Completion defaults to ON (Milos decision, 2026-07-16: it stays ON for every new organization).
+2. Existing organizations keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
         </is>
       </c>
       <c r="K130" s="17" t="inlineStr">
@@ -10321,12 +11614,22 @@
       </c>
       <c r="L130" s="17" t="inlineStr">
         <is>
-          <t>VIU-observed-awaiting-Milos</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M130" s="17" t="inlineStr">
         <is>
-          <t>VIU-observed 2026-07-14 (awaiting Milos Q1). The Require-Review default for NEW vs EXISTING orgs cannot be observed on the long-lived sv7301 org (Require Review is currently a normal toggle, default reflects prior toggling). The cohort default rule is a Milos product decision (Q1). No pass/fail asserted.</t>
+          <t>Reworded per Milos Round-3 (2026-07-16): the new-org default for Require Review Before Completion is ON (option A, 'Stays ON'; no cohort split). Build-accurate label confirmed live: 'Require Review Before Completion' - 'Work orders must be reviewed and signed off before they can be completed' (Settings &gt; Work Orders; API key requireReview). CHARACTERIZED BLOCKER (Standing Rule 14 self-serve attempted): the new-org ON default cannot be observed on the long-lived shared sv7301 org (its requireReview currently reads false from prior test toggling), and a brand-new organization cannot be provisioned in this shared QA env - org-creation is not exposed to us (POST /api/organizations -&gt; 405, POST /api/organizations/create -&gt; 404, GET /api/register -&gt; 405; GET /api/organizations lists only the existing org). Needs a freshly-provisioned org from backend/admin onboarding to observe the ON default. Evidence SETTINGS-workorders.png + observations.json.</t>
+        </is>
+      </c>
+      <c r="N130" s="17" t="inlineStr">
+        <is>
+          <t>29400</t>
+        </is>
+      </c>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29400</t>
         </is>
       </c>
     </row>
@@ -10396,6 +11699,16 @@
       <c r="M131" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (UX-workorders-list.png): the Work Orders create form's primary button reads 'Create Work Order' (confirmed on /workorders list Create Work Order button).</t>
+        </is>
+      </c>
+      <c r="N131" s="21" t="inlineStr">
+        <is>
+          <t>29401</t>
+        </is>
+      </c>
+      <c r="O131" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
     </row>
@@ -10469,6 +11782,16 @@
           <t>Wording+VIU 2026-07-13: required fields collected in the centralized 'Complete Work Order' modal (Mileage + Engine Hours; no VIN field in the modal - see SF-COMP-16/SF-VAL-02 build finding); tech story handled separately.</t>
         </is>
       </c>
+      <c r="N132" s="17" t="inlineStr">
+        <is>
+          <t>29402</t>
+        </is>
+      </c>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
@@ -10540,6 +11863,16 @@
           <t>Wording+VIU 2026-07-13: success screen shows WO number + total with 'Done' and 'Go To Invoice'; invoice number appears on the Finance step (confirmed live via SF-COMP drives S2-15825 'Invoice total $434.95').</t>
         </is>
       </c>
+      <c r="N133" s="21" t="inlineStr">
+        <is>
+          <t>29403</t>
+        </is>
+      </c>
+      <c r="O133" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="16" t="inlineStr">
@@ -10612,6 +11945,16 @@
           <t>VIU-observed 2026-07-14 (awaiting Milos Q10). The close-vs-cancel confirmation modal (Close = closes modal only; Cancel = closes modal + returns to previous screen) is per the design 'still to be added'; no distinct close/cancel confirmation modal behavior is defined/finalized. Milos Q10 decision. No pass/fail asserted.</t>
         </is>
       </c>
+      <c r="N134" s="17" t="inlineStr">
+        <is>
+          <t>29404</t>
+        </is>
+      </c>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
@@ -10684,6 +12027,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route.</t>
         </is>
       </c>
+      <c r="N135" s="21" t="inlineStr">
+        <is>
+          <t>29405</t>
+        </is>
+      </c>
+      <c r="O135" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
@@ -10755,6 +12108,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
         </is>
       </c>
+      <c r="N136" s="17" t="inlineStr">
+        <is>
+          <t>29406</t>
+        </is>
+      </c>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
@@ -10826,6 +12189,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT.</t>
         </is>
       </c>
+      <c r="N137" s="21" t="inlineStr">
+        <is>
+          <t>29407</t>
+        </is>
+      </c>
+      <c r="O137" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -10897,6 +12270,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Mark Reviewed gate = woReviewWorkOrders (not open-to-all). Self-review allowed when the role holds the permission (Milos ruling 2026-07-10; no reviewer!=completer identity block). Per-role has/lacks matches the matrix.</t>
         </is>
       </c>
+      <c r="N138" s="17" t="inlineStr">
+        <is>
+          <t>29408</t>
+        </is>
+      </c>
+      <c r="O138" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
@@ -10966,6 +12349,16 @@
       <c r="M139" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). PO Receive gate = woOrderParts (Order Parts); Office lacks it -&gt; no Receive on PO list/detail. FE confirmed (Technician redirected from /parts/orders, prior TECH-po-list.png).</t>
+        </is>
+      </c>
+      <c r="N139" s="21" t="inlineStr">
+        <is>
+          <t>29409</t>
+        </is>
+      </c>
+      <c r="O139" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
     </row>
@@ -11042,6 +12435,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
         </is>
       </c>
+      <c r="N140" s="17" t="inlineStr">
+        <is>
+          <t>29410</t>
+        </is>
+      </c>
+      <c r="O140" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
@@ -11112,6 +12515,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Review sign-off = Review Work Orders (woReviewWorkOrders), custom-role gated, not open-to-all for v1. Self-review allowed when the role holds the permission (Milos ruling 2026-07-10).</t>
         </is>
       </c>
+      <c r="N141" s="21" t="inlineStr">
+        <is>
+          <t>29411</t>
+        </is>
+      </c>
+      <c r="O141" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
@@ -11184,6 +12597,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Positive self-review: a role holding woReviewWorkOrders may Mark Reviewed a WO it completed (permission-gated only, no identity block). A role lacking it cannot. Matches matrix + Milos ruling.</t>
         </is>
       </c>
+      <c r="N142" s="17" t="inlineStr">
+        <is>
+          <t>29412</t>
+        </is>
+      </c>
+      <c r="O142" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
@@ -11252,6 +12675,16 @@
       <c r="M143" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session.</t>
+        </is>
+      </c>
+      <c r="N143" s="21" t="inlineStr">
+        <is>
+          <t>29413</t>
+        </is>
+      </c>
+      <c r="O143" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
     </row>
@@ -11327,6 +12760,16 @@
           <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
+      <c r="N144" s="17" t="inlineStr">
+        <is>
+          <t>29414</t>
+        </is>
+      </c>
+      <c r="O144" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
@@ -11394,6 +12837,16 @@
       <c r="M145" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
+        </is>
+      </c>
+      <c r="N145" s="21" t="inlineStr">
+        <is>
+          <t>29415</t>
+        </is>
+      </c>
+      <c r="O145" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
     </row>
@@ -11469,6 +12922,16 @@
           <t>Blocked-Env (precise, investigated live 2026-07-14): a VIN-less asset cannot be seeded. Asset/vehicle creation is not exposed via API (POST /api/assets 404, POST /api/vehicles 405 GET-only, POST /api/company-vehicles 404) and the new-asset UI flow requires a VIN; all existing assets already carry a VIN. So the non-review No-PO/Optional-invoice completion cannot be driven into a VIN-missing prompt. (Also note the Story-4 completion modal no longer carries a VIN field per Delta1 — SF-COMP-16.) Needs a VIN-less asset seeded by dev/data.</t>
         </is>
       </c>
+      <c r="N146" s="17" t="inlineStr">
+        <is>
+          <t>29416</t>
+        </is>
+      </c>
+      <c r="O146" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
@@ -11536,6 +12999,16 @@
       <c r="M147" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
+        </is>
+      </c>
+      <c r="N147" s="21" t="inlineStr">
+        <is>
+          <t>29417</t>
+        </is>
+      </c>
+      <c r="O147" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
     </row>
@@ -11609,6 +13082,16 @@
           <t>Wording+VIU 2026-07-13: tech-story modal Next/Continue disabled while the story textarea is empty (Require Tech Story gate) - behavior per prior VIU; tech-story requirement is a Work Orders setting toggle (see SF-SET-15).</t>
         </is>
       </c>
+      <c r="N148" s="17" t="inlineStr">
+        <is>
+          <t>29418</t>
+        </is>
+      </c>
+      <c r="O148" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
@@ -11677,6 +13160,16 @@
       <c r="M149" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
+        </is>
+      </c>
+      <c r="N149" s="21" t="inlineStr">
+        <is>
+          <t>29419</t>
+        </is>
+      </c>
+      <c r="O149" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
     </row>
@@ -11753,6 +13246,16 @@
           <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive-button gate progression confirmed: no vendor -&gt; Receive DISABLED; vendor assigned (POST /api/orders/{id}/assign-vendor 200, auto-assigned with NO merge prompt, vendor-missing flag cleared) but no part number -&gt; DISABLED; part number entered but cost/sell still 0 -&gt; DISABLED; part number + vendor invoice number + cost + sell all present -&gt; Receive ENABLED (receivable). Confirms a vendor-missing part cannot be received without a vendor, a part number, and a cost/sell price.</t>
         </is>
       </c>
+      <c r="N150" s="17" t="inlineStr">
+        <is>
+          <t>29420</t>
+        </is>
+      </c>
+      <c r="O150" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
@@ -11824,6 +13327,16 @@
           <t>Wording+VIU 2026-07-13: Confirm Review disabled until VIN entered in the Mark Reviewed dialog (surfaces when the WO lacks a valid VIN) - same gate as SF-REV-06; Mark Reviewed action confirmed live this run, VIN-required dialog per prior 2026-07-06.</t>
         </is>
       </c>
+      <c r="N151" s="21" t="inlineStr">
+        <is>
+          <t>29421</t>
+        </is>
+      </c>
+      <c r="O151" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="16" t="inlineStr">
@@ -11894,6 +13407,16 @@
           <t>Wording+VIU 2026-07-13: re-completing after cancel creates no duplicate POs (idempotent) - verified prior (2026-07-08); consistent with SF-COMP-15/23.</t>
         </is>
       </c>
+      <c r="N152" s="17" t="inlineStr">
+        <is>
+          <t>29422</t>
+        </is>
+      </c>
+      <c r="O152" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
@@ -11966,6 +13489,16 @@
           <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
         </is>
       </c>
+      <c r="N153" s="21" t="inlineStr">
+        <is>
+          <t>29423</t>
+        </is>
+      </c>
+      <c r="O153" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="16" t="inlineStr">
@@ -12034,6 +13567,16 @@
       <c r="M154" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: the same vendor invoice number can be reused across POs (uniqueness relaxed) - verified prior (2026-07-10, Story 9 apply-invoice).</t>
+        </is>
+      </c>
+      <c r="N154" s="17" t="inlineStr">
+        <is>
+          <t>29424</t>
+        </is>
+      </c>
+      <c r="O154" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
         </is>
       </c>
     </row>
@@ -12109,6 +13652,16 @@
           <t>VIU-Verified live 2026-07-14 (WO 4448308d). Build behavior: an unapproved (Needs Approval) line disables the 'Complete Work Order' button (aria-disabled) with the GENERIC tooltip 'Every line must be approved or declined in order to complete the work order.' — confirmed identical with Require Vendor Invoice Number ON and OFF. Approving the line (status-&gt;authorized) re-enables the button. BUILD-vs-SPEC observation: the build applies the disabled-button model UNIVERSALLY, not only the Story-4 required-invoice flow (spec Δ2 expected the other flows to keep an active button + 'you need to approve the line' error toast). Not an error/data-corruption (stricter, cleaner gate) — logged as OBS in bugs-log, case ruled Verified against the build. Wording corrected: dropped the 'names the line' claim and the 'button stays active/error toast' branch.</t>
         </is>
       </c>
+      <c r="N155" s="21" t="inlineStr">
+        <is>
+          <t>29425</t>
+        </is>
+      </c>
+      <c r="O155" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="16" t="inlineStr">
@@ -12180,6 +13733,16 @@
           <t>Blocked-Env (partial): the inventory-DECREMENT half is PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201 — prior run). The Part-History LOG half is OBS-6-blocked (GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} crashes). The QuickBooks-integrity leg is blocked: Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N156" s="17" t="inlineStr">
+        <is>
+          <t>29426</t>
+        </is>
+      </c>
+      <c r="O156" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
@@ -12252,6 +13815,16 @@
           <t>VIU-observed 2026-07-14 (awaiting Milos Q5) AND QB-blocked. The 'Create Purchase Orders' toggle is absent (POs always-on, SF-SET-03 Deviation) so the Create-POs-OFF scenario cannot be configured; and QuickBooks is not connected on sv7301 (no QB admin/API — see bugs-log) so QB integrity cannot be inspected regardless. Milos Q5 governs whether POs-always-on is intended. No pass/fail asserted.</t>
         </is>
       </c>
+      <c r="N157" s="21" t="inlineStr">
+        <is>
+          <t>29427</t>
+        </is>
+      </c>
+      <c r="O157" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29427</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="16" t="inlineStr">
@@ -12323,6 +13896,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N158" s="17" t="inlineStr">
+        <is>
+          <t>29428</t>
+        </is>
+      </c>
+      <c r="O158" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
@@ -12393,6 +13976,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N159" s="21" t="inlineStr">
+        <is>
+          <t>29429</t>
+        </is>
+      </c>
+      <c r="O159" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="16" t="inlineStr">
@@ -12463,6 +14056,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N160" s="17" t="inlineStr">
+        <is>
+          <t>29430</t>
+        </is>
+      </c>
+      <c r="O160" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
@@ -12533,6 +14136,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N161" s="21" t="inlineStr">
+        <is>
+          <t>29431</t>
+        </is>
+      </c>
+      <c r="O161" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="16" t="inlineStr">
@@ -12603,6 +14216,16 @@
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
+      <c r="N162" s="17" t="inlineStr">
+        <is>
+          <t>29432</t>
+        </is>
+      </c>
+      <c r="O162" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
@@ -12673,6 +14296,16 @@
           <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Previously Blocked-Env on QuickBooks; the QB dependency is not needed for this assertion. Part History for a genuinely inventory-tracked part is a native in-app feature (Parts &gt; Inventory clock icon) and inventory decrement + Part History on simple completion is verified elsewhere (SF-COMP-07 Passed). Since a plain part-number add no longer makes a part inventory-tracked (S10-R2 struck), the invariant now only claims Part History for parts that ARE inventory-tracked — which holds.</t>
         </is>
       </c>
+      <c r="N163" s="21" t="inlineStr">
+        <is>
+          <t>29433</t>
+        </is>
+      </c>
+      <c r="O163" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="16" t="inlineStr">
@@ -12740,6 +14373,8 @@
           <t>NEW V2.4 §8 open question (D9). Placeholder only — do NOT fabricate expected. The shared order/status logic (requested -&gt; orderable/waiting-to-receive; PO-on-order without vendor/cost) may touch Part Sales; confirm with dev and report. Excluded from the TestRail XML update batch until scoped. | 2026-07-13: NOT in testrail-id-map.csv (no C-ID) - Open-Question / dev-investigation case, not created in TestRail. Follow-up: assign a C-ID only if/when it is imported after dev confirmation. | 2026-07-14 grind: remains an Open-Question / dev BE-investigation. The claim (Part Sales unaffected by the shared requested-&gt;orderable/waiting-to-receive order-status logic) is a back-end code-path question that is NOT meaningfully UI-observable from the app; confirming it requires dev to trace whether the shared order/status logic touches the Part Sales flow. Still unmapped in testrail-id-map.csv (no C-ID) — assign a C-ID only if imported after dev confirmation. Kept Open-Question.</t>
         </is>
       </c>
+      <c r="N164" s="17" t="inlineStr"/>
+      <c r="O164" s="17" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
@@ -12814,6 +14449,16 @@
           <t>Wording+VIU 2026-07-14 (S-15838 live, Require Review OFF): two authorized lines; completing line 1 left the WO 'Approved'; completing the last line auto-flipped the WO to 'Complete' with no separate Complete Work Order step (WO status read via GET /api/work-orders/view/{id}).</t>
         </is>
       </c>
+      <c r="N165" s="21" t="inlineStr">
+        <is>
+          <t>29461</t>
+        </is>
+      </c>
+      <c r="O165" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29461</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="16" t="inlineStr">
@@ -12887,6 +14532,16 @@
           <t>Wording+VIU 2026-07-14 (S-15824 / 446c1cd6 live, Require Review OFF): 3 authorized labor lines resolved in one bulk call (POST /api/work-orders/lines/change-lines {field:'status',value:'complete',lines:[...]} -&gt; 201); the WO auto-flipped 'Approved' -&gt; 'Complete' with no separate Complete step.</t>
         </is>
       </c>
+      <c r="N166" s="17" t="inlineStr">
+        <is>
+          <t>29462</t>
+        </is>
+      </c>
+      <c r="O166" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29462</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
@@ -12960,6 +14615,16 @@
           <t>Wording+VIU 2026-07-14 (S-15822 / a8fb8d3f live, Require Review OFF): completed 2 of 3 lines (WO stayed 'Approved'), then split the still-open line to a new WO (POST /api/work-orders/split -&gt; 201, new WO id returned); the original WO, now fully resolved, auto-flipped to 'Complete'. New split WO cleaned up (deleted).</t>
         </is>
       </c>
+      <c r="N167" s="21" t="inlineStr">
+        <is>
+          <t>29463</t>
+        </is>
+      </c>
+      <c r="O167" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29463</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="16" t="inlineStr">
@@ -13033,6 +14698,16 @@
           <t>Wording per spec §16 R12(d)+design. VIU Blocked-Env 2026-07-14: the delete-a-line action could not be driven in this environment — POST /api/work-orders/lines/delete-lines returns HTTP 500 even for a delete that leaves the work order still open (requestId 768518b...), so it is a generic delete-lines failure in this env, not the auto-complete leg; and no browser (Chromium/Playwright) harness is available here to drive the UI 'Delete lines' bulk action. The auto-complete-on-last-line-resolve mechanism itself IS verified on the single, bulk and split paths (SF-AUTO-01/02/03) — the same backend recompute applies. Needs the delete-lines endpoint healthy (or a UI session) to confirm the delete-line trigger directly.</t>
         </is>
       </c>
+      <c r="N168" s="17" t="inlineStr">
+        <is>
+          <t>29464</t>
+        </is>
+      </c>
+      <c r="O168" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29464</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
@@ -13105,6 +14780,16 @@
           <t>Wording+VIU 2026-07-14 (S-15813 / 73d150d3 live): flipped Require Review ON (POST /api/organizations/settings/change requireReview:true); completing line 1 left the WO 'Approved'; resolving the last line routed the WO to 'Review' (Ready for Review), NOT 'Complete'. Settings restored byte-identical to baseline afterward.</t>
         </is>
       </c>
+      <c r="N169" s="21" t="inlineStr">
+        <is>
+          <t>29465</t>
+        </is>
+      </c>
+      <c r="O169" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29465</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="16" t="inlineStr">
@@ -13176,6 +14861,16 @@
           <t>Wording per spec §16 R13 (intentional clock-out exception). VIU Blocked-Env 2026-07-14: the per-line technician clock-out that finishes a line is not drivable through the available API (GET /api/technician-tasks returns 404; /api/technician-tasks/department-clock-* is a shop-time punch clock, not the per-line 'finish the line' timer), and no browser (Chromium/Playwright) harness is available here to drive the timer/clock-out UI. The auto-complete-vs-review routing is otherwise verified (SF-AUTO-01/05). Needs a technician time-clock UI session (or the per-line clock-out endpoint) to confirm the R13 exception directly.</t>
         </is>
       </c>
+      <c r="N170" s="17" t="inlineStr">
+        <is>
+          <t>29466</t>
+        </is>
+      </c>
+      <c r="O170" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29466</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
@@ -13244,6 +14939,16 @@
       <c r="M171" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-14: verified the backend status transition directly. Resolve action POST /api/work-orders/lines/change-status {status:'complete'} returns 200; GET /api/work-orders/view/{id} then shows work_order.status = 'Complete' when Require Review was OFF (S-15838/S-15824), and status = 'Review' (Ready for Review) when Require Review was ON (S-15813). Placed in an API-titled section per Standing Rule 4 (asserts a backend status transition).</t>
+        </is>
+      </c>
+      <c r="N171" s="21" t="inlineStr">
+        <is>
+          <t>29467</t>
+        </is>
+      </c>
+      <c r="O171" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29467</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -4447,17 +4447,17 @@
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Observe the screen shown right before the Receive parts / Complete without receiving choice.
-3. Leave the core undecided and try Complete Without Receiving.
-4. Mark the core OK or Not OK on the resolve screen and try again.</t>
+          <t>1. On a work order that has an un-received special-order (vendor) cored part, click Complete Work Order.
+2. Observe the completion wizard steps (Missing Details, Resolve cores, Receive parts &amp; invoice) and open the Resolve cores step.
+3. Leave the core undecided and try to move on with Continue.
+4. Set the core using OK · Returned or Not OK · Keep + Charge, then try Continue again.</t>
         </is>
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>1. A separate Resolve cores screen lists the un-received vendor core with its part info, core charge and an OK / Not OK choice, and explains that resolving now keeps the invoice accurate.
-2. While the core is still undecided, completing is blocked.
-3. Once every core is decided (OK or Not OK), Complete Without Receiving works — a decided core no longer blocks completing without receiving (no receive needed first).</t>
+          <t>1. The completion wizard shows a Resolve cores step (before Receive parts &amp; invoice) that lists the un-received vendor core under 'SPECIAL ORDER CORES' with its description, line and core charge, plus OK · Returned / Not OK · Keep + Charge buttons, and the message that resolving now decides whether the core charge is billed (invoice accuracy).
+2. While the core is undecided (shows '0 / 1 resolved'), the Continue button is disabled — completion is blocked.
+3. Once every core is set (shows '1 / 1 resolved'), Continue is enabled and the wizard proceeds — a decided core no longer blocks moving on (no receive needed first).</t>
         </is>
       </c>
       <c r="K42" s="17" t="inlineStr">
@@ -4465,14 +4465,14 @@
           <t>Resolve Cores Flow.html + Handoff; requirements-v4 S18 C-R1/C-R4</t>
         </is>
       </c>
-      <c r="L42" s="17" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R1/C-R4 (SV-8353, pre-resolve-before-receive): replaces the 2026-07-14 design-#4 'Complete Without Receiving DISABLED while a core waits' model — completion is now gated ONLY on undecided (NULL) cores; a DECIDED core does not block Complete Without Receiving. Screen labels from the Resolve Cores Flow design (wizard step 'Resolve cores'; Inventory / Special order groups; 'OK / Not OK'; 'N / M resolved' progress; '+$X to invoice' running total) — design-sourced, pending live confirm; state labels 'Core decision pending' / 'Core OK — return to vendor, no charge' / 'Core Not OK — customer charged' are spec-quoted (C-R9) — confirm exact on-screen text live. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R1/C-R4 (SV-8353, pre-resolve-before-receive): replaces the 2026-07-14 design-#4 'Complete Without Receiving DISABLED while a core waits' model — completion is now gated ONLY on undecided (NULL) cores; a DECIDED core does not block Complete Without Receiving. Screen labels from the Resolve Cores Flow design (wizard step 'Resolve cores'; Inventory / Special order groups; 'OK / Not OK'; 'N / M resolved' progress; '+$X to invoice' running total) — design-sourced, pending live confirm; state labels 'Core decision pending' / 'Core OK — return to vendor, no charge' / 'Core Not OK — customer charged' are spec-quoted (C-R9) — confirm exact on-screen text live. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU. || STAGING VIU 2026-07-20: Story-18 Resolve-cores wizard step OBSERVED LIVE (WO S3-25714, seeded undecided vendor core). Build labels: steps 'Missing Details -&gt; Resolve cores -&gt; Receive parts &amp; invoice'; buttons 'OK · Returned' / 'Not OK · Keep + Charge'; footnote 'Completion stays blocked until every core is set'. Gate: Continue disabled at 0/1, enabled at 1/1. Evidence: viu-staging-2026-07-20/CORE-step-resolve.png. Complete-to-Success not driven through.</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr">
@@ -4545,14 +4545,14 @@
           <t>requirements-v4 S18 C-R4</t>
         </is>
       </c>
-      <c r="L43" s="21" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M43" s="21" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R4: 'Cores pending' now reflects UNDECIDED (NULL) cores only — the old invoice-gate model (flag while cores unresolved until received) is replaced by the pre-resolve model; a decided-but-unreceived core no longer flags. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R4: 'Cores pending' now reflects UNDECIDED (NULL) cores only — the old invoice-gate model (flag while cores unresolved until received) is replaced by the pre-resolve model; a decided-but-unreceived core no longer flags. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU. || STAGING VIU 2026-07-20: 'cores pending' reflects only undecided cores — completion wizard Resolve-cores step shows '0 / 1 resolved' while undecided and gates Continue (and the following Receive parts &amp; invoice step) until resolved; API cores_pending went 1-&gt;0 after pre-resolve. Evidence: CORE-step-resolve.png + SF-CORE-18-api-evidence.json. Observed via the completion wizard gate (not a separate Finance-view indicator).</t>
         </is>
       </c>
       <c r="N43" s="21" t="inlineStr">
@@ -4863,9 +4863,9 @@
       </c>
       <c r="J47" s="21" t="inlineStr">
         <is>
-          <t>1. A separate, consolidated Resolve cores screen appears, listing EVERY un-received vendor core (both parts).
-2. Each core shows its part info, its core charge and an OK / Not OK choice.
-3. A message explains that resolving now is for invoice accuracy.</t>
+          <t>1. A consolidated Resolve cores step appears under a 'SPECIAL ORDER CORES · N' group, listing every un-received vendor core.
+2. Each core shows its description, line and core charge with OK · Returned / Not OK · Keep + Charge buttons.
+3. The message 'core part can now be resolved — mark whether each old unit was returned. This decides whether the core charge is billed.' explains the resolution is for invoice accuracy.</t>
         </is>
       </c>
       <c r="K47" s="21" t="inlineStr">
@@ -4873,14 +4873,14 @@
           <t>Resolve Cores Flow.html + Handoff; requirements-v4 S18 C-R1</t>
         </is>
       </c>
-      <c r="L47" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M47" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). Screen labels from the Resolve Cores Flow design (wizard step 'Resolve cores'; Inventory / Special order groups; OK / Not OK) are design-sourced pending live confirm; the C-R9 state texts are spec-quoted — confirm exact on-screen wording live, never invent.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). Screen labels from the Resolve Cores Flow design (wizard step 'Resolve cores'; Inventory / Special order groups; OK / Not OK) are design-sourced pending live confirm; the C-R9 state texts are spec-quoted — confirm exact on-screen wording live, never invent. || STAGING VIU 2026-07-20: Resolve-cores consolidated list OBSERVED LIVE (group 'SPECIAL ORDER CORES · N', count 'N / N resolved', per-core OK/Not-OK, intro + footnote messages). Evidence: CORE-step-resolve.png. One core seeded; consolidated-group + count mechanism confirms multi-core listing.</t>
         </is>
       </c>
       <c r="N47" s="21" t="inlineStr">
@@ -5422,16 +5422,16 @@
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>1. POST /api/work-orders/{id}/pre-resolve-cores with the core decision (ok / not_ok).
-2. Re-read the work order's lines / receive-view read models.
-3. Inspect for side-effect records (work-order part, statement item, vendor return).</t>
+          <t>1. POST /api/work-orders/{id}/pre-resolve-cores with body {cores:[{partRequestId, isCoreOk}]} (isCoreOk true = OK/Returned, false = Not OK).
+2. Re-read the work order lines read model and check the core part request's core_resolution and the pending-core count.
+3. Inspect for side-effect records (work-order part, statement item, vendor return, order).</t>
         </is>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t>1. The request succeeds (2xx) and core_resolution is persisted on the core work_order_part_request (ok | not_ok; NULL = undecided).
-2. NO WorkOrderPart, statement item, or vendor return is created at this point.
-3. cores_pending reflects only undecided (NULL) cores after the call.</t>
+          <t>1. The request succeeds (201) returning {data:{resolvedCount:N}} and core_resolution is persisted on the core part request (ok | not_ok; NULL = undecided; isCoreOk cannot be null).
+2. NO WorkOrderPart, statement item, vendor return or order is created — part request stays authorized_to_order with quantity_remaining and total_core_charge unchanged.
+3. cores_pending reflects only undecided (NULL) cores after the call (decided cores drop out).</t>
         </is>
       </c>
       <c r="K54" s="17" t="inlineStr">
@@ -5439,14 +5439,14 @@
           <t>requirements-v4 S18 C-R2 + technical plan (mirrors handle-cores)</t>
         </is>
       </c>
-      <c r="L54" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). Endpoint from the SV-8353 technical plan — existence on sv7301 unconfirmed; probe before re-VIU.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). Endpoint from the SV-8353 technical plan — existence on sv7301 unconfirmed; probe before re-VIU. || STAGING VIU 2026-07-20: pre-resolve-cores API OBSERVED LIVE (WO 316441e5, PR dcc299b8). Schema {cores:[{partRequestId,isCoreOk}]}; POST true-&gt;201 {resolvedCount:1} core_resolution 'ok', false-&gt;'not_ok'; pr_status/order_id/qty/total_core_charge unchanged; cores_pending 1-&gt;0; isCoreOk=null-&gt;400. Evidence: SF-CORE-18-api-evidence.json. Also discovered add-part endpoint POST /api/work-orders/part/make-request.</t>
         </is>
       </c>
       <c r="N54" s="17" t="inlineStr">
@@ -16121,7 +16121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16180,7 +16180,7 @@
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-11</t>
+          <t>SF-CORE-12</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Verify the Resolve cores screen lists every un-received vendor core with part info, core charge and OK / Not OK, plus an invoice-accuracy message</t>
+          <t>Verify marking a core Not OK immediately adds the core charge to the work order total and customer invoice, while OK adds no charge</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-12</t>
+          <t>SF-CORE-13</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify marking a core Not OK immediately adds the core charge to the work order total and customer invoice, while OK adds no charge</t>
+          <t>Verify completion and invoice creation are blocked only while a core is undecided — a decided core does not block</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -16238,7 +16238,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-13</t>
+          <t>SF-CORE-14</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify completion and invoice creation are blocked only while a core is undecided — a decided core does not block</t>
+          <t>Verify receiving a pre-resolved core auto-applies the saved decision: OK creates exactly one vendor return, Not OK creates none, the invoice never changes, retries create no duplicates</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -16267,7 +16267,7 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-14</t>
+          <t>SF-CORE-15</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify receiving a pre-resolved core auto-applies the saved decision: OK creates exactly one vendor return, Not OK creates none, the invoice never changes, retries create no duplicates</t>
+          <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -16296,7 +16296,7 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-15</t>
+          <t>SF-CORE-16</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
+          <t>Verify the Lines tab shows the core decision state before and after receive: 'Core decision pending', 'Core OK — return to vendor, no charge', 'Core Not OK — customer charged'</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -16325,7 +16325,7 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-16</t>
+          <t>SF-CORE-17</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify the Lines tab shows the core decision state before and after receive: 'Core decision pending', 'Core OK — return to vendor, no charge', 'Core Not OK — customer charged'</t>
+          <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -16354,17 +16354,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-17</t>
+          <t>SF-CORE-19</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>Core Pre-Resolve (Story 18)</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
+          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -16383,17 +16383,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-18</t>
+          <t>SF-POSEL-07</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Core Pre-Resolve (Story 18)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>API: Verify POST /api/work-orders/{id}/pre-resolve-cores persists the core decision on the part request with no side-effect records</t>
+          <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -16412,17 +16412,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-19</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Core Pre-Resolve (Story 18)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
+          <t>Verify Bulk Receive field editability: quantity editable (partial receive), cost editable ONLY when it is $0, sell locks after the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr"/>
@@ -16441,17 +16441,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-07</t>
+          <t>SF-BULK-11</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
+          <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -16470,17 +16470,17 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive field editability: quantity editable (partial receive), cost editable ONLY when it is $0, sell locks after the WO is invoiced/paid</t>
+          <t>Verify each vendor group has an invoice number field under the vendor name, available only when at least one PO of that vendor is selected (no Apply button)</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -16499,17 +16499,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-11</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
+          <t>Verify a typed invoice number fills only the selected POs of that vendor with no Apply click, still editable per PO</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an invoice number field under the vendor name, available only when at least one PO of that vendor is selected (no Apply button)</t>
+          <t>Verify the vendor invoice number field is scoped per vendor, absent for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -16557,17 +16557,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-RCV-11</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Verify a typed invoice number fills only the selected POs of that vendor with no Apply click, still editable per PO</t>
+          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -16586,17 +16586,17 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-RCV-12</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Verify the vendor invoice number field is scoped per vendor, absent for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr"/>
@@ -16615,17 +16615,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-11</t>
+          <t>SF-RCV-13</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
+          <t>Verify a vendorless part can be assigned a vendor / merged into the single-part receive on the spot, reusing the same invoice number</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -16644,17 +16644,17 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>SF-RCV-12</t>
+          <t>SF-VEND-07</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
+          <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -16673,17 +16673,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>SF-RCV-13</t>
+          <t>SF-VEND-08</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be assigned a vendor / merged into the single-part receive on the spot, reusing the same invoice number</t>
+          <t>Verify the part number stays editable via the edit icon after entry until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -16702,17 +16702,17 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SF-VEND-07</t>
+          <t>SF-WOP-04</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
+          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr"/>
@@ -16731,17 +16731,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>SF-VEND-08</t>
+          <t>SF-QB-09</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Verify the part number stays editable via the edit icon after entry until the part is received or the work order is invoiced/paid</t>
+          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -16751,69 +16751,11 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
       <c r="G22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>SF-WOP-04</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-09</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M4" s="17" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): NO 'Create Purchase Orders' toggle on the Work Orders tab and no createPurchaseOrders key in GET /api/organizations/settings (confirmed live). Build lags V2.4 spec S1-R2 (which retains the toggle + No-PO path). DEVIATION — tester will find the toggle absent. Do not record as passing.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): NO 'Create Purchase Orders' toggle on the Work Orders tab and no createPurchaseOrders key in GET /api/organizations/settings (confirmed live). Build lags V2.4 spec S1-R2 (which retains the toggle + No-PO path). DEVIATION — tester will find the toggle absent. Do not record as passing. || STAGING VIU 2026-07-20: API settings object has no createPurchaseOrders field (POs always-on); Deviation stands; UI toggle-absence not re-observed.</t>
         </is>
       </c>
       <c r="N4" s="17" t="inlineStr">
@@ -4628,14 +4628,14 @@
           <t>requirements-v4 S18 C-R6 (2026-07-16 change-log: both flows resolve-before-receive)</t>
         </is>
       </c>
-      <c r="L44" s="17" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R6: the required-invoice flow FLIPS from resolve-AFTER-the-receive-round-trip (old S4-C2) to resolve-FIRST-then-receive (unified with the optional flow, change-log 2026-07-16). NOTE the Resolve Cores Flow design still codes the required-flow branch as resolve-after-receive — spec (2026-07-16) wins; design flagged for cleanup. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R6: the required-invoice flow FLIPS from resolve-AFTER-the-receive-round-trip (old S4-C2) to resolve-FIRST-then-receive (unified with the optional flow, change-log 2026-07-16). NOTE the Resolve Cores Flow design still codes the required-flow branch as resolve-after-receive — spec (2026-07-16) wins; design flagged for cleanup. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU. || STAGING VIU 2026-07-20: required-invoice + review completion wizard ('Complete &amp; Send to Review') stepper pill order = Missing Details -&gt; Resolve cores -&gt; Receive parts &amp; invoice; the Resolve cores step PRECEDES the Receive step (asks to resolve cores FIRST, then receive). Evidence: W78-step2.png.</t>
         </is>
       </c>
       <c r="N44" s="17" t="inlineStr">
@@ -4708,14 +4708,14 @@
           <t>requirements-v4 S18 C-R2/C-R4</t>
         </is>
       </c>
-      <c r="L45" s="21" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R2/C-R4: detection now works off the decision saved on the core work_order_part_request (core_resolution = ok | not_ok | NULL; NULL = undecided blocks) instead of the old invoice-gate PartRequest scan — no WorkOrderPart needed. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R2/C-R4: detection now works off the decision saved on the core work_order_part_request (core_resolution = ok | not_ok | NULL; NULL = undecided blocks) instead of the old invoice-gate PartRequest scan — no WorkOrderPart needed. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU. || STAGING VIU 2026-07-20: the completion gate detects an undecided special-order core that exists only as a requested/authorized-to-order part (never received) — it is listed on the Resolve cores step and blocks Continue while undecided; API cores_pending also reflects it. Evidence: W78-step2.png + SF-CORE-18-api-evidence.json.</t>
         </is>
       </c>
       <c r="N45" s="21" t="inlineStr">
@@ -4955,14 +4955,14 @@
           <t>requirements-v4 S18 C-R3</t>
         </is>
       </c>
-      <c r="L48" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L48" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first).</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). || STAGING VIU 2026-07-20: WO estimate totalPrice includes core charge upfront regardless of OK/Not-OK; charge-follows-decision is at the customer invoice (not API-creatable, completion-&gt;invoice UI not driven). Still VIU-Pending. || STAGING VIU 2026-07-20: charge-follows-decision CONFIRMED at line level. Not OK (Keep + Charge) creates a separate 'Core for &lt;part&gt;' charge line (sell = core charge $25) billed to the customer; OK (Returned) creates NO such line (no charge). core_resolution persists not_ok/ok. (The work-order totalPrice aggregate field lags/inverts on recompute and is NOT reliable; line items are authoritative.) Evidence: CORE16-*.png + line-item dump.</t>
         </is>
       </c>
       <c r="N48" s="17" t="inlineStr">
@@ -5035,14 +5035,14 @@
           <t>requirements-v4 S18 C-R4</t>
         </is>
       </c>
-      <c r="L49" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M49" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first).</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). || STAGING VIU 2026-07-20: completion is blocked ONLY while a core is undecided — the completion wizard Resolve-cores step disables Continue at '0 / 1 resolved' and enables it at '1 / 1'; a decided core does not block. (Invoice creation is gated behind the same wizard step, before 'Receive parts &amp; invoice'.) Evidence: CORE-step-resolve.png.</t>
         </is>
       </c>
       <c r="N49" s="21" t="inlineStr">
@@ -5117,14 +5117,14 @@
           <t>requirements-v4 S18 C-R5 + AC (idempotency)</t>
         </is>
       </c>
-      <c r="L50" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L50" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first).</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). || STAGING VIU 2026-07-20: receiving a pre-resolved core auto-applies the decision at receive with NO re-prompt — the receive screen shows the core line with a read-only badge_core_resolution 'Not OK · Charged $25.00' (no OK/Not-OK asked again). Evidence: CORE14-receive.png.</t>
         </is>
       </c>
       <c r="N50" s="17" t="inlineStr">
@@ -5279,14 +5279,14 @@
           <t>requirements-v4 S18 C-R9</t>
         </is>
       </c>
-      <c r="L52" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L52" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). The three state texts are spec-quoted (C-R9) — confirm exact on-screen wording live.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). The three state texts are spec-quoted (C-R9) — confirm exact on-screen wording live. || STAGING VIU 2026-07-20: the Lines tab reflects the core decision state — a 'Core for &lt;part&gt;' line is PRESENT when Not OK and ABSENT when OK (observed both states live; undecided state not settable via the decision-only endpoint). Evidence: CORE16-NOTOK.png / CORE16-OK.png.</t>
         </is>
       </c>
       <c r="N52" s="17" t="inlineStr">
@@ -8366,14 +8366,14 @@
           <t>requirements-v4 S8-R7</t>
         </is>
       </c>
-      <c r="L90" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L90" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M90" s="17" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ14 (S8-R7: 'Cost is editable (if the cost is 0, if cost is not 0 cost filed should not be editable)'). The previous VIU-Verified was against the OLD 'qty and cost editable' build behavior (2026-07-13 labels). The $0-only rule has NOT been observed → re-VIU needed; if the build allows editing a non-zero cost on Bulk Receive it is a deviation until dev ships. SPEC INCONSISTENCY flagged for Milos (Rule 15.5): the surviving S8-R7 tail 'after it locks, only cost remains editable' contradicts the new only-if-$0 rule for a non-zero-cost part — cited, not silently resolved (this case asserts the $0-only rule per latest-wins; S10-R3/S12-R5 '$0/missing' parity aligns with it).</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ14 (S8-R7: 'Cost is editable (if the cost is 0, if cost is not 0 cost filed should not be editable)'). The previous VIU-Verified was against the OLD 'qty and cost editable' build behavior (2026-07-13 labels). The $0-only rule has NOT been observed → re-VIU needed; if the build allows editing a non-zero cost on Bulk Receive it is a deviation until dev ships. SPEC INCONSISTENCY flagged for Milos (Rule 15.5): the surviving S8-R7 tail 'after it locks, only cost remains editable' contradicts the new only-if-$0 rule for a non-zero-cost part — cited, not silently resolved (this case asserts the $0-only rule per latest-wins; S10-R3/S12-R5 '$0/missing' parity aligns with it). || STAGING VIU 2026-07-20: cost editable ONLY when $0 ($0 -&gt; input_cost_{id}; non-$0 -&gt; read-only currency_text_cost_{id}); sell shows icon_sell_locked on invoiced/paid POs; qty editable (partial) pre-invoice. Evidence: GRP-02-surface.png / BULK-02-receive-surface.png / INVOICED-*.png.</t>
         </is>
       </c>
       <c r="N90" s="17" t="inlineStr">
@@ -8694,14 +8694,14 @@
           <t>requirements-v4 S18 C-R5/C-R9</t>
         </is>
       </c>
-      <c r="L94" s="17" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
+      <c r="L94" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M94" s="17" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R5: receive no longer 'makes resolution available' (old S8-C1) — a pre-resolved decision AUTO-APPLIES at receive (OK → vendor core return created automatically; Not OK → core created already resolved, no return). Core-only partial receive (old S8-C2) retained. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Story 18 C-R5: receive no longer 'makes resolution available' (old S8-C1) — a pre-resolved decision AUTO-APPLIES at receive (OK → vendor core return created automatically; Not OK → core created already resolved, no return). Core-only partial receive (old S8-C2) retained. Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU. || STAGING VIU 2026-07-20: a pre-resolved core's decision is applied automatically at receive (badge_core_resolution shown, no re-prompt); the core is a separate selectable line (checkbox_item + editable input_qty) so core-only partial receive is supported. Evidence: CORE14-receive.png.</t>
         </is>
       </c>
       <c r="N94" s="17" t="inlineStr">
@@ -8858,14 +8858,14 @@
           <t>requirements-v4 S9-R1 (2026-07-16 change-log: Apply button removed)</t>
         </is>
       </c>
-      <c r="L96" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L96" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M96" s="17" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ13 (change-log 2026-07-16: 'Apply button removed from Bulk Invoice — invoice number is typed &amp; remembered, no button'). The previous VIU-Verified was against the OLD build behavior — the live label 'Apply to selected POs' was confirmed present 2026-07-13 (RCV-bulk-receive.png). The new no-button behavior has NOT been observed → re-VIU needed; the current build likely DEVIATES (button still present) until dev ships the removal.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ13 (change-log 2026-07-16: 'Apply button removed from Bulk Invoice — invoice number is typed &amp; remembered, no button'). The previous VIU-Verified was against the OLD build behavior — the live label 'Apply to selected POs' was confirmed present 2026-07-13 (RCV-bulk-receive.png). The new no-button behavior has NOT been observed → re-VIU needed; the current build likely DEVIATES (button still present) until dev ships the removal. || STAGING VIU 2026-07-20: grouped Bulk Receive page (/bulk-receive?ids=..., via 'Receive Selected'): per-vendor 'Apply to selected POs' invoice field (input_apply_invoice_{vendorId}), NO Apply button, Vendor Missing group has no invoice field, per-PO checkboxes + 'N of N selected'. Evidence: INV-grouped-detail.png.</t>
         </is>
       </c>
       <c r="N96" s="17" t="inlineStr">
@@ -8941,14 +8941,14 @@
           <t>requirements-v4 S9-R2</t>
         </is>
       </c>
-      <c r="L97" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M97" s="21" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ13: the fill happens as the number is typed — no Apply click. Previous VIU-Verified was against the OLD Apply-button build (2026-07-13). New behavior NOT observed → re-VIU needed; likely a build deviation until dev removes the button.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ13: the fill happens as the number is typed — no Apply click. Previous VIU-Verified was against the OLD Apply-button build (2026-07-13). New behavior NOT observed → re-VIU needed; likely a build deviation until dev removes the button. || STAGING VIU 2026-07-20: selected a PO then typed the vendor invoice field -&gt; per-PO input_invoice filled with NO Apply click; value remembered. Evidence: INV02-typed.png.</t>
         </is>
       </c>
       <c r="N97" s="21" t="inlineStr">
@@ -9023,14 +9023,14 @@
           <t>requirements-v4 S9-R3</t>
         </is>
       </c>
-      <c r="L98" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L98" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ13: per-vendor scoping retained; the vendorless group now explicitly shows NO invoice-number field (new AC). Previous VIU-Verified was against the OLD Apply-button build (2026-07-13). New behavior NOT observed → re-VIU needed; likely a build deviation until dev ships.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6) Δ13: per-vendor scoping retained; the vendorless group now explicitly shows NO invoice-number field (new AC). Previous VIU-Verified was against the OLD Apply-button build (2026-07-13). New behavior NOT observed → re-VIU needed; likely a build deviation until dev ships. || STAGING VIU 2026-07-20: invoice field scoped per vendor group; vendorless (Vendor Missing) group has no invoice field; reused/custom invoice string accepted. Evidence: RS-01-grouped.png.</t>
         </is>
       </c>
       <c r="N98" s="17" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M109" s="21" t="inlineStr">
         <is>
-          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png).</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png). || STAGING VIU 2026-07-20: Vendor Missing group + Select Vendor + Part Number entry confirmed; Bulk-Receive TOP position confirmed (matches Milos ruling). Accept-Delivery BOTTOM position not re-observed -&gt; Deviation UNCHANGED.</t>
         </is>
       </c>
       <c r="N109" s="21" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="M111" s="21" t="inlineStr">
         <is>
-          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05. || STAGING VIU 2026-07-20: '+N' indicator on PO list confirmed ('+1'); Vendor Missing leads at TOP on Bulk Receive (correct per Milos). Accept-Delivery BOTTOM not re-observed -&gt; Deviation UNCHANGED.</t>
         </is>
       </c>
       <c r="N111" s="21" t="inlineStr">
@@ -10570,14 +10570,14 @@
           <t>requirements-v4 S12-R6</t>
         </is>
       </c>
-      <c r="L117" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L117" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M117" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ10 — the assign/merge-on-the-spot leg of S12-R6 ('reusing the same invoice number... rather than going back'). Self-serviceable per Rule 14. Not yet observed — re-VIU; may not be built on sv7301 yet.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ10 — the assign/merge-on-the-spot leg of S12-R6 ('reusing the same invoice number... rather than going back'). Self-serviceable per Rule 14. Not yet observed — re-VIU; may not be built on sv7301 yet. || STAGING VIU 2026-07-20: vendorless part shows Select Vendor dropdown (select_assign_vendor_{poId}) to assign a vendor on the receive screen. Clauses 2/3 (reuse invoice #, both received) not driven to completion. Evidence: VEND-vm-receive.png.</t>
         </is>
       </c>
       <c r="N117" s="21" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="M124" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ11 — S13-R8 (from SV-8343, change-log 2026-07-16: 'Vendor + part number stay changeable until receive'). Prevents receiving against the wrong vendor. Self-serviceable per Rule 14 (the invoiced/paid leg may stay Blocked-Env — invoiced/paid WO not drivable in this env, see §0-ZZ). Not yet observed — re-VIU; may not be built yet.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ11 — S13-R8 (from SV-8343, change-log 2026-07-16: 'Vendor + part number stay changeable until receive'). Prevents receiving against the wrong vendor. Self-serviceable per Rule 14 (the invoiced/paid leg may stay Blocked-Env — invoiced/paid WO not drivable in this env, see §0-ZZ). Not yet observed — re-VIU; may not be built yet. || STAGING VIU 2026-07-20: assigned-vendor change affordance not located on the single-order receive view. Still VIU-Pending.</t>
         </is>
       </c>
       <c r="N124" s="17" t="inlineStr">
@@ -11218,14 +11218,14 @@
           <t>requirements-v4 S13-R8</t>
         </is>
       </c>
-      <c r="L125" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L125" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M125" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ11 — the part-number leg of S13-R8 ('likewise editable (edit icon) after entry, under the same condition'). Self-serviceable per Rule 14 (invoiced/paid leg may stay Blocked-Env). Not yet observed — re-VIU; may not be built yet.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ11 — the part-number leg of S13-R8 ('likewise editable (edit icon) after entry, under the same condition'). Self-serviceable per Rule 14 (invoiced/paid leg may stay Blocked-Env). Not yet observed — re-VIU; may not be built yet. || STAGING VIU 2026-07-20: part number editable via input_part_number_{id} on the receive screen before received ('Missing part number' -&gt; editable). Locked-after-received half not driven; lock pattern seen via icon_sell_locked. Evidence: VEND-vm-receive.png.</t>
         </is>
       </c>
       <c r="N125" s="21" t="inlineStr">
@@ -12677,14 +12677,14 @@
           <t>requirements-v4 Story 16 core paragraph + S18</t>
         </is>
       </c>
-      <c r="L143" s="21" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
+      <c r="L143" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M143" s="21" t="inlineStr">
         <is>
-          <t>REWORDED 2026-07-17 to spec `_4` (V2.6): the Story-16 core paragraph now reads 'Special-order cores (both required and optional) are pre-resolved before receiving on the resolve screen before Send to Review (no longer deferred to the invoice gate)' — the invoice-gate leg was dropped and the un-skippable/receive-first reading is replaced by gate-on-undecided (C-R4). Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU.</t>
+          <t>REWORDED 2026-07-17 to spec `_4` (V2.6): the Story-16 core paragraph now reads 'Special-order cores (both required and optional) are pre-resolved before receiving on the resolve screen before Send to Review (no longer deferred to the invoice gate)' — the invoice-gate leg was dropped and the un-skippable/receive-first reading is replaced by gate-on-undecided (C-R4). Blocked-Env: a special-order (vendor-sourced) core is still not seedable in this build (P550848 is_core=0; a vendor-sourced part request drops the core attribute) — needs a dev-seeded special-order core. ALSO: Story 18 / SV-8353 is a new dev plan, so the pre-resolve build is likely NOT deployed on sv7301 yet — probe the completion wizard for the resolve step + the pre-resolve endpoint before any re-VIU. || STAGING VIU 2026-07-20: with Require Review ON, cores are decided before receiving ahead of Send for Review — the 'Complete &amp; Send to Review' wizard stepper order is Missing Details -&gt; Resolve cores -&gt; Receive parts &amp; invoice (resolve precedes receive). Evidence: W78-step2.png.</t>
         </is>
       </c>
       <c r="N143" s="21" t="inlineStr">
@@ -16121,7 +16121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16180,7 +16180,7 @@
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-12</t>
+          <t>SF-CORE-15</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Verify marking a core Not OK immediately adds the core charge to the work order total and customer invoice, while OK adds no charge</t>
+          <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-13</t>
+          <t>SF-CORE-17</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify completion and invoice creation are blocked only while a core is undecided — a decided core does not block</t>
+          <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -16238,17 +16238,17 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-14</t>
+          <t>SF-CORE-19</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>Core Pre-Resolve (Story 18)</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Verify receiving a pre-resolved core auto-applies the saved decision: OK creates exactly one vendor return, Not OK creates none, the invoice never changes, retries create no duplicates</t>
+          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -16267,17 +16267,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-15</t>
+          <t>SF-POSEL-07</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
+          <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -16296,17 +16296,17 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-16</t>
+          <t>SF-BULK-11</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Verify the Lines tab shows the core decision state before and after receive: 'Core decision pending', 'Core OK — return to vendor, no charge', 'Core Not OK — customer charged'</t>
+          <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr"/>
@@ -16325,17 +16325,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-17</t>
+          <t>SF-RCV-11</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
+          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -16345,7 +16345,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -16354,17 +16354,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-19</t>
+          <t>SF-RCV-12</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Core Pre-Resolve (Story 18)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
+          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr"/>
@@ -16383,17 +16383,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-07</t>
+          <t>SF-VEND-07</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
+          <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -16412,17 +16412,17 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-WOP-04</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive field editability: quantity editable (partial receive), cost editable ONLY when it is $0, sell locks after the WO is invoiced/paid</t>
+          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
@@ -16441,17 +16441,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SF-BULK-11</t>
+          <t>SF-QB-09</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
+          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -16461,301 +16461,11 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
+          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
       <c r="G12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>SF-INV-01</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Verify each vendor group has an invoice number field under the vendor name, available only when at least one PO of that vendor is selected (no Apply button)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>SF-INV-02</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Verify a typed invoice number fills only the selected POs of that vendor with no Apply click, still editable per PO</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>SF-INV-03</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Verify the vendor invoice number field is scoped per vendor, absent for the vendorless group, and allows a reused invoice number</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>SF-RCV-11</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Receive Button on WO POs (Story 11)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>SF-RCV-12</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>SF-RCV-13</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Verify a vendorless part can be assigned a vendor / merged into the single-part receive on the spot, reusing the same invoice number</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>SF-VEND-07</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>SF-VEND-08</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>Verify the part number stays editable via the edit icon after entry until the part is received or the work order is invoiced/paid</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>SF-WOP-04</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-09</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -5198,14 +5198,14 @@
           <t>requirements-v4 S18 C-R8 (FE-only lock)</t>
         </is>
       </c>
-      <c r="L51" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L51" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M51" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). Tooltip text is spec-quoted (C-R8) — confirm exact on-screen wording live.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). Tooltip text is spec-quoted (C-R8) — confirm exact on-screen wording live. || STAGING VIU 2026-07-20: needs an INVOICED/paid WO with an un-received core; invoice is not API-creatable and completion-&gt;invoice UI not driven to an invoiced+un-received-core state. Blocked-Env.</t>
         </is>
       </c>
       <c r="N51" s="21" t="inlineStr">
@@ -5357,14 +5357,14 @@
           <t>requirements-v4 S18 AC</t>
         </is>
       </c>
-      <c r="L53" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L53" s="21" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M53" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first).</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). || STAGING VIU 2026-07-20: needs an INVOICED/paid WO to test decision-immutability after invoicing; same invoiced-state blocker as SF-CORE-15. Blocked-Env.</t>
         </is>
       </c>
       <c r="N53" s="21" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="M55" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first).</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ8 — Story 18 Core Parts (SV-8353), pre-resolve-before-receive model. Not yet observed — expected Blocked-Env at re-VIU until (a) a special-order vendor-sourced core is seedable (P550848 is_core=0; a vendor-sourced part request drops the core attribute — needs a dev-seeded core) and (b) the SV-8353 pre-resolve build is deployed on sv7301 (probe the completion wizard for the resolve step + the pre-resolve endpoint first). || STAGING VIU 2026-07-20: needs a RECEIVED core resolved via the existing handle-core(s) endpoint; a received-core state was not reachable this run (completing without receiving leaves the core un-ordered; cannot order on a completed WO). Still VIU-Pending.</t>
         </is>
       </c>
       <c r="N55" s="21" t="inlineStr">
@@ -7875,14 +7875,14 @@
           <t>requirements-v4 Story 7 AC</t>
         </is>
       </c>
-      <c r="L84" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L84" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ15 — part-sale POs CONFIRMED in scope for Stories 7/8 (§8 'Part Sales — confirmed (Jul 14)'; new S7 AC bullet). Seeding self-serviceable per Rule 14 (create a Part Sale with a vendor part). Not yet observed — re-VIU at the next live pass.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ15 — part-sale POs CONFIRMED in scope for Stories 7/8 (§8 'Part Sales — confirmed (Jul 14)'; new S7 AC bullet). Seeding self-serviceable per Rule 14 (create a Part Sale with a vendor part). Not yet observed — re-VIU at the next live pass. || STAGING VIU 2026-07-20: created a Part Sale (7dc7db6f) with a vendor part, authorized + ordered -&gt; part-sale PO 60e64e95 (type 2, number 'P-1110'). It appears in the PO list with a selectable checkbox_select_order and joins the Receive Selected flow like a work-order PO. Evidence: PS-verify / PS-bulk11.png.</t>
         </is>
       </c>
       <c r="N84" s="17" t="inlineStr">
@@ -8776,14 +8776,14 @@
           <t>requirements-v4 Story 8 AC</t>
         </is>
       </c>
-      <c r="L95" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M95" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ15 — part-sale POs receivable on Bulk Receive (new S8 AC bullet). Seeding self-serviceable per Rule 14. Not yet observed — re-VIU at the next live pass.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ15 — part-sale POs receivable on Bulk Receive (new S8 AC bullet). Seeding self-serviceable per Rule 14. Not yet observed — re-VIU at the next live pass. || STAGING VIU 2026-07-20: the part-sale PO (P-1110) is included on the grouped Bulk Receive page (/bulk-receive?ids=...,60e64e95) under its vendor group like a work-order PO. Actual receive not executed to keep data clean; same pipeline. Evidence: PS-bulk11.png.</t>
         </is>
       </c>
       <c r="N95" s="21" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M109" s="21" t="inlineStr">
         <is>
-          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png). || STAGING VIU 2026-07-20: Vendor Missing group + Select Vendor + Part Number entry confirmed; Bulk-Receive TOP position confirmed (matches Milos ruling). Accept-Delivery BOTTOM position not re-observed -&gt; Deviation UNCHANGED.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png). || STAGING VIU 2026-07-20: Vendor Missing group + Select Vendor + Part Number entry confirmed; Bulk-Receive TOP position confirmed (matches Milos ruling). Accept-Delivery BOTTOM position not re-observed -&gt; Deviation UNCHANGED. || STAGING VIU 2026-07-20 (definitive): seeded a WO with a real-vendor group + a true vendor_id=null part, ordered into one PO, opened Accept-Delivery — Vendor Missing group renders at the TOP (y=406, before the vendor group). Milos ruled BOTTOM for that screen -&gt; DEVIATION PERSISTS. Bug draft #5 stays OPEN. Evidence: DEV-accept-delivery.png.</t>
         </is>
       </c>
       <c r="N109" s="21" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="M111" s="21" t="inlineStr">
         <is>
-          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05. || STAGING VIU 2026-07-20: '+N' indicator on PO list confirmed ('+1'); Vendor Missing leads at TOP on Bulk Receive (correct per Milos). Accept-Delivery BOTTOM not re-observed -&gt; Deviation UNCHANGED.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05. || STAGING VIU 2026-07-20: '+N' indicator on PO list confirmed ('+1'); Vendor Missing leads at TOP on Bulk Receive (correct per Milos). Accept-Delivery BOTTOM not re-observed -&gt; Deviation UNCHANGED. || STAGING VIU 2026-07-20 (definitive): '+N' PO-list indicator confirmed; on Accept-Delivery the Vendor Missing group is still at the TOP (should be BOTTOM per Milos) -&gt; DEVIATION PERSISTS, bug #5 stays open. Evidence: DEV-accept-delivery.png.</t>
         </is>
       </c>
       <c r="N111" s="21" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="M115" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ9 — S11-R4 return-to-originating-line (change-log 2026-07-15 'Jul 14 SU follow-ups'). Self-serviceable per Rule 14 (seed a multi-line WO with an orderable part). Not yet observed — re-VIU at the next live pass; new requirement, may not be built on sv7301 yet.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ9 — S11-R4 return-to-originating-line (change-log 2026-07-15 'Jul 14 SU follow-ups'). Self-serviceable per Rule 14 (seed a multi-line WO with an orderable part). Not yet observed — re-VIU at the next live pass; new requirement, may not be built on sv7301 yet. || STAGING VIU 2026-07-20: return-to-originating-line scroll/focus not driven (needs a many-line WO receive round-trip with reliable scroll observation). Still VIU-Pending.</t>
         </is>
       </c>
       <c r="N115" s="21" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="M116" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ10 — S12-R6 vendorless group surfaced on single-part receive (change-log 2026-07-15). Covers the CONTENT of the single-part receive view; the vendor-missing group POSITION deviation stays with SF-RCV-05/07 (Milos Round-3 ruling — unaffected by S12-R6). Self-serviceable per Rule 14. Not yet observed — re-VIU; may not be built on sv7301 yet.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ10 — S12-R6 vendorless group surfaced on single-part receive (change-log 2026-07-15). Covers the CONTENT of the single-part receive view; the vendor-missing group POSITION deviation stays with SF-RCV-05/07 (Milos Round-3 ruling — unaffected by S12-R6). Self-serviceable per Rule 14. Not yet observed — re-VIU; may not be built on sv7301 yet. || STAGING VIU 2026-07-20: the Accept-Delivery/Receive screen shows the vendor group AND the vendorless group together (clause 2 observed). Clause 1 'only that vendor's parts, other vendors excluded' not isolated (test WO had a single real vendor). Still VIU-Pending.</t>
         </is>
       </c>
       <c r="N116" s="17" t="inlineStr">
@@ -11138,14 +11138,14 @@
           <t>requirements-v4 S13-R8</t>
         </is>
       </c>
-      <c r="L124" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L124" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="M124" s="17" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ11 — S13-R8 (from SV-8343, change-log 2026-07-16: 'Vendor + part number stay changeable until receive'). Prevents receiving against the wrong vendor. Self-serviceable per Rule 14 (the invoiced/paid leg may stay Blocked-Env — invoiced/paid WO not drivable in this env, see §0-ZZ). Not yet observed — re-VIU; may not be built yet. || STAGING VIU 2026-07-20: assigned-vendor change affordance not located on the single-order receive view. Still VIU-Pending.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ11 — S13-R8 (from SV-8343, change-log 2026-07-16: 'Vendor + part number stay changeable until receive'). Prevents receiving against the wrong vendor. Self-serviceable per Rule 14 (the invoiced/paid leg may stay Blocked-Env — invoiced/paid WO not drivable in this env, see §0-ZZ). Not yet observed — re-VIU; may not be built yet. || STAGING VIU 2026-07-20: assigned-vendor change affordance not located on the single-order receive view. Still VIU-Pending. || STAGING VIU 2026-07-20: assigned vendor is changeable before receive — on the WO Parts tab each waiting-to-receive part has an editable select_vendor_{id}; changed a part's vendor 7d54f3e1-&gt;5f3a23dd and it persisted (CHANGED:true). Clause 2 (locked once received/invoiced) not driven to a received state. Evidence: VEND07-changed.png.</t>
         </is>
       </c>
       <c r="N124" s="17" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="M129" s="21" t="inlineStr">
         <is>
-          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ15 — the spec's remaining check: 'verify part-sale POs behave in Bulk Receive + Waiting-on-Parts'. Whether part sales surface on the list carrying the Waiting on Parts column is NOT specified — VIU-confirm the surface live (expected #1 allows either counted-consistently or cleanly-excluded; only errors/broken links fail). Seeding self-serviceable per Rule 14.</t>
+          <t>NEW 2026-07-17 per spec `_4` (V2.6) Δ15 — the spec's remaining check: 'verify part-sale POs behave in Bulk Receive + Waiting-on-Parts'. Whether part sales surface on the list carrying the Waiting on Parts column is NOT specified — VIU-confirm the surface live (expected #1 allows either counted-consistently or cleanly-excluded; only errors/broken links fail). Seeding self-serviceable per Rule 14. || STAGING VIU 2026-07-20: a Part Sale with an unreceived vendor part was created; the Waiting-on-Parts column consistency/clean-exclusion was not specifically observed (needs the WOP column enabled + WO-list observation). Still VIU-Pending.</t>
         </is>
       </c>
       <c r="N129" s="21" t="inlineStr">
@@ -15513,14 +15513,14 @@
           <t>requirements-v4 §8 'Part Sales — confirmed (Jul 14)'</t>
         </is>
       </c>
-      <c r="L178" s="25" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="L178" s="17" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="M178" s="17" t="inlineStr">
         <is>
-          <t>RESCOPED 2026-07-17 per spec `_4` (V2.6) Δ15 — the §8 'Part Sales impact (investigation — BE)' open question is now CONFIRMED in-spec ('Part Sales — confirmed (Jul 14)': adding a part on a Part Sale already creates a PO received via the same PO/receive pipeline; part-sale POs in scope for PO multi-select + Bulk Receive + Accept Delivery). This case now covers the spec's residual check ('the new order/status logic does not regress part-sale status transitions'); the in-scope part-sale PO behaviors are covered by the new cases SF-POSEL-07 (PO list / multi-select), SF-BULK-11 (Bulk Receive) and SF-WOP-04 (Waiting on Parts). Open-Question RESOLVED → VIU-Pending (seedable per Rule 14: create a Part Sale with a vendor part). ADDED TO TESTRAIL 2026-07-17 (was deliberately unmapped while an open question).</t>
+          <t>RESCOPED 2026-07-17 per spec `_4` (V2.6) Δ15 — the §8 'Part Sales impact (investigation — BE)' open question is now CONFIRMED in-spec ('Part Sales — confirmed (Jul 14)': adding a part on a Part Sale already creates a PO received via the same PO/receive pipeline; part-sale POs in scope for PO multi-select + Bulk Receive + Accept Delivery). This case now covers the spec's residual check ('the new order/status logic does not regress part-sale status transitions'); the in-scope part-sale PO behaviors are covered by the new cases SF-POSEL-07 (PO list / multi-select), SF-BULK-11 (Bulk Receive) and SF-WOP-04 (Waiting on Parts). Open-Question RESOLVED → VIU-Pending (seedable per Rule 14: create a Part Sale with a vendor part). ADDED TO TESTRAIL 2026-07-17 (was deliberately unmapped while an open question). || STAGING VIU 2026-07-20: QuickBooks NOT connected on staging (/api/quickbooks/status 404, no QB in Admin) — part-sale QB status transitions cannot be observed. External dependency -&gt; Blocked-Env.</t>
         </is>
       </c>
       <c r="N178" s="17" t="inlineStr">
@@ -16121,7 +16121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16180,17 +16180,17 @@
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-15</t>
+          <t>SF-CORE-19</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>Core Pre-Resolve (Story 18)</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
+          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -16209,17 +16209,17 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>SF-CORE-17</t>
+          <t>SF-RCV-11</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Core parts — Pre-Resolve (Story 18)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
+          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr"/>
@@ -16238,17 +16238,17 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>SF-CORE-19</t>
+          <t>SF-RCV-12</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Core Pre-Resolve (Story 18)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
+          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>Needs a cored part + a live receive/resolve round-trip walk.</t>
+          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr"/>
@@ -16267,17 +16267,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>SF-POSEL-07</t>
+          <t>SF-WOP-04</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
+          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -16292,180 +16292,6 @@
       </c>
       <c r="F6" s="21" t="inlineStr"/>
       <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>SF-BULK-11</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>SF-RCV-11</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Receive Button on WO POs (Story 11)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>SF-RCV-12</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>SF-VEND-07</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>Not driven in the VIU run - needs a targeted live walk on sv7301.</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>SF-WOP-04</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>NOT BUILT - needs dev to complete the feature, then live verification.</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>SF-QB-09</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Needs QuickBooks / inventory inspection after a live receive/invoice.</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M109" s="21" t="inlineStr">
         <is>
-          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png). || STAGING VIU 2026-07-20: Vendor Missing group + Select Vendor + Part Number entry confirmed; Bulk-Receive TOP position confirmed (matches Milos ruling). Accept-Delivery BOTTOM position not re-observed -&gt; Deviation UNCHANGED. || STAGING VIU 2026-07-20 (definitive): seeded a WO with a real-vendor group + a true vendor_id=null part, ordered into one PO, opened Accept-Delivery — Vendor Missing group renders at the TOP (y=406, before the vendor group). Milos ruled BOTTOM for that screen -&gt; DEVIATION PERSISTS. Bug draft #5 stays OPEN. Evidence: DEV-accept-delivery.png.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16): Bulk Receive = top, Receive/Accept-Delivery = bottom. LIVE VIU 2026-07-16 (Admin, sv7301): (a) Bulk Receive page (Receive Vendor Parts) shows the Vendor Missing group at the TOP (leads), above Aabridge Beverages and Aeland Design - MATCHES the ruling (evidence BULK-groups-full.png). (b) Vendorless/no-PN parts (Cab shock, Miscellaneous hardware) appear in the Vendor Missing group and are receivable after Select Vendor + Part Number - VERIFIED. (c) WO-created PO reached via the WO Receive button opens the grouped Receive (Accept Delivery) surface at /order/{id}?receive=1 - VERIFIED. DEVIATION: on that Receive (Accept Delivery) screen the Vendor Missing group is currently at the TOP (leads), NOT the bottom as ruled - observed on two orders (S-15884 above Aeland Design; S-15878 above Aeboro Motors); evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Dev bug: move the Vendor Missing group to the BOTTOM on the Receive/Accept-Delivery screen. Note: the legacy single-PO /accept-delivery/{orderId} route renders a flat one-table PO with a PO-level 'Vendor Missing' badge and no vendor groups (evidence AD-*.png). || STAGING VIU 2026-07-20: Vendor Missing group + Select Vendor + Part Number entry confirmed; Bulk-Receive TOP position confirmed (matches Milos ruling). Accept-Delivery BOTTOM position not re-observed -&gt; Deviation UNCHANGED. || STAGING VIU 2026-07-20 (definitive): seeded a WO with a real-vendor group + a true vendor_id=null part, ordered into one PO, opened Accept-Delivery — Vendor Missing group renders at the TOP (y=406, before the vendor group). Milos ruled BOTTOM for that screen -&gt; DEVIATION PERSISTS. Bug draft #5 stays OPEN. Evidence: DEV-accept-delivery.png. || ACCEPTED COSMETIC DEVIATION — WON'T FIX/WON'T FILE (user decision 2026-07-20): Milos's bottom-placement ruling for the Vendor Missing group on the Accept-Delivery / 'Purchase Order Details' screen is not implemented on the build (group renders at TOP), but this is deemed PURELY VISUAL — the group still appears and functions; only its position differs. No functional/data/workflow impact. Bug draft #5 DROPPED (won't-file). viu_status stays Deviation because the build genuinely deviates from the ruling, but this is an ACCEPTED/won't-file cosmetic deviation, not an open actionable bug. No TestRail change needed — case wording already reflects the intended behavior.</t>
         </is>
       </c>
       <c r="N109" s="21" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="M111" s="21" t="inlineStr">
         <is>
-          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05. || STAGING VIU 2026-07-20: '+N' indicator on PO list confirmed ('+1'); Vendor Missing leads at TOP on Bulk Receive (correct per Milos). Accept-Delivery BOTTOM not re-observed -&gt; Deviation UNCHANGED. || STAGING VIU 2026-07-20 (definitive): '+N' PO-list indicator confirmed; on Accept-Delivery the Vendor Missing group is still at the TOP (should be BOTTOM per Milos) -&gt; DEVIATION PERSISTS, bug #5 stays open. Evidence: DEV-accept-delivery.png.</t>
+          <t>Reworded per Milos Round-3 split ruling (2026-07-16). LIVE VIU 2026-07-16 (Admin, sv7301): '+N' indicator VERIFIED on the Purchase Orders list (/parts/orders shows '+1', '+4'); on the Receive/Accept-Delivery surface the header lists vendor names in full ('Vendor(s) Aeland Design Vendor Missing') rather than a '+N' badge (evidence PO-LIST.png, ORDER-RECV-5vendor.png). Group ordering: Bulk Receive shows Vendor Missing at the TOP (matches ruling). DEVIATION: the Receive (Accept Delivery) screen also shows the Vendor Missing group at the TOP (leads), NOT the bottom as ruled - evidence ORDER-RECV-S15884-allgroups-full.png, ORDER-RECV-S15878-full.png. Same dev bug as SF-RCV-05. || STAGING VIU 2026-07-20: '+N' indicator on PO list confirmed ('+1'); Vendor Missing leads at TOP on Bulk Receive (correct per Milos). Accept-Delivery BOTTOM not re-observed -&gt; Deviation UNCHANGED. || STAGING VIU 2026-07-20 (definitive): '+N' PO-list indicator confirmed; on Accept-Delivery the Vendor Missing group is still at the TOP (should be BOTTOM per Milos) -&gt; DEVIATION PERSISTS, bug #5 stays open. Evidence: DEV-accept-delivery.png. || ACCEPTED COSMETIC DEVIATION — WON'T FIX/WON'T FILE (user decision 2026-07-20): Milos's bottom-placement ruling for the Vendor Missing group on the Accept-Delivery / 'Purchase Order Details' screen is not implemented on the build (group renders at TOP), but this is deemed PURELY VISUAL — the group still appears and functions; only its position differs. No functional/data/workflow impact. Bug draft #5 DROPPED (won't-file). viu_status stays Deviation because the build genuinely deviates from the ruling, but this is an ACCEPTED/won't-file cosmetic deviation, not an open actionable bug. No TestRail change needed — case wording already reflects the intended behavior.</t>
         </is>
       </c>
       <c r="N111" s="21" t="inlineStr">
@@ -13152,9 +13152,9 @@
       </c>
       <c r="J149" s="21" t="inlineStr">
         <is>
-          <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
-2. A role without App Settings cannot open or change the Work Order settings.
-3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
+          <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can open and change the Work Order settings page.
+2. A role without App Settings cannot reach the Work Order settings page (it is redirected away) and so cannot change those settings from the screen.
+3. A role that cannot open the Work Order settings page cannot save changes to it.</t>
         </is>
       </c>
       <c r="K149" s="21" t="inlineStr">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -586,7 +586,7 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Simple Flow V1 (Simple Mode) - Manual Test Cases
-This workbook contains 184 manual test cases covering the ShopView "Simple Mode - Streamlined Work Order Completion &amp; Receiving" feature (Epic SV-7301): the Work Order settings page; the four settings-driven completion flows (No-PO/skip, PO+Optional invoice, PO+Required invoice, and Review-ON); the tech-story and line-approval gates; core-part resolution; vendorless / Vendor-Missing part handling; PO multi-select, Bulk Receive, apply-invoice, part-number fix, the WO-PO Receive button, Accept Delivery and assign-vendor / merge; the Waiting-on-Parts column; UX refinements; permissions; validation / edge cases; and QuickBooks / inventory integrity.
+This workbook contains 186 manual test cases covering the ShopView "Simple Mode - Streamlined Work Order Completion &amp; Receiving" feature (Epic SV-7301): the Work Order settings page; the four settings-driven completion flows (No-PO/skip, PO+Optional invoice, PO+Required invoice, and Review-ON); the tech-story and line-approval gates; core-part resolution; vendorless / Vendor-Missing part handling; PO multi-select, Bulk Receive, apply-invoice, part-number fix, the WO-PO Receive button, Accept Delivery and assign-vendor / merge; the Waiting-on-Parts column; UX refinements; permissions; validation / edge cases; and QuickBooks / inventory integrity.
 Authored from the COMPLETE spec (build/simple-flow/requirements.md, 17 stories) plus the design mockups / dev handoffs (design-notes.md) and the live VIU findings (viu-findings.md).
 VIU (Verify-in-UI on QA env sv7301) is PARTIAL because the feature is still under development. Each case carries a VIU Status: VIU-Verified (tested live and passed - screenshot cited in Notes), VIU-Pending (not yet verifiable - either a not-built story or a cookie/role-dependent check), or Open-Question (the expected result depends on an unresolved decision or a VIU deviation - see the Open Questions tab).
 NOT-BUILT stories (all cases VIU-Pending until dev completes): Story 7 (PO multi-select), Story 8 (Bulk Receive page), Story 9 (apply-invoice), Story 14 (Waiting-on-Parts column).
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" ht="160" customHeight="1">
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O185"/>
+  <dimension ref="A1:O187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="M149" s="21" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route. REFINED 2026-07-23 (BE driver, metadata-only): POST /api/organizations/settings/change gates on the settings atom-FAMILY, not settingsApp specifically — a clean Parts Manager (settingsParts/settingsFinance, no settingsApp) gets HTTP 200; no-settings roles get 403. The FE settings route stays settingsApp-gated (page-reachability). Tester-facing Expected reworded to the page-reachability truth (Rules 7/9/20). TestRail C29405 update_case PUSHED 2026-07-23 (HTTP 200 + re-GET MATCH); status unchanged VIU-Verified. Audit: build/simple-flow/sv8183/testrail-execution-log-2026-07-23.md.</t>
         </is>
       </c>
       <c r="N149" s="21" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="M150" s="17" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06). LIVE RE-OBSERVED 2026-07-23 (Technician cell, clean baseline): as genuine Technician (role 50bf6a0d re-read at template = canonical 6 atoms, view_mode=tech, verified before+after = no drift this window) on WO S3-25842, the WO-level 'Send To Review' completion control is ABSENT (no Parts/Finance tabs, no Rate/Margin/Total); only line-level New Line/Complete show (line-edit, not WO completion). Technician cannot complete/send-to-review the WO — clean this run, no carried-evidence caveat. Evidence: viu-sv8183-2026-07-23/element-reobserve/complete-Tech-reset-2026-07-23.png.</t>
         </is>
       </c>
       <c r="N150" s="17" t="inlineStr">
@@ -13308,14 +13308,15 @@
       </c>
       <c r="I151" s="21" t="inlineStr">
         <is>
-          <t>1. For each role, attempt to reach and use Bulk Receive.
-2. Record the outcomes.</t>
+          <t>1. For each role, attempt to reach and use Bulk Receive by BOTH entry points: (a) the per-purchase-order Receive button on the Purchase Orders list, and (b) multi-selecting purchase orders with the checkboxes and using 'Receive Selected'.
+2. Where a receive screen opens, attempt to actually complete the receive (enter invoice details and submit).
+3. Record the outcomes for each role and each entry point.</t>
         </is>
       </c>
       <c r="J151" s="21" t="inlineStr">
         <is>
-          <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
-2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
+          <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive by both entry points: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
+2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot complete a receive by any path — neither the per-purchase-order Receive button nor the multi-select 'Receive Selected' route may lead to a usable receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
@@ -13331,7 +13332,7 @@
       </c>
       <c r="M151" s="21" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT. TIGHTENED 2026-07-24: steps + expected now explicitly drive BOTH Bulk-Receive entry points — the per-PO Receive button AND the multi-select 'Receive Selected' path — so the SV-8515 coverage gap cannot recur. See the dedicated View-only negative SF-PERM-11 (driver SV-8515): live re-verify 2026-07-24 showed the per-PO Receive button is correctly hidden for a Vendor &amp; Order Mgmt View-only (Office) user, but the multi-select 'Receive Selected' route currently EXPOSES the editable /bulk-receive screen (FE-exposure defect, SV-8515 dev Ready-to-Fix) while the backend still blocks the actual receive (POST /api/inventory/orders/accept -&gt; 403).</t>
         </is>
       </c>
       <c r="N151" s="21" t="inlineStr">
@@ -13819,7 +13820,7 @@
       </c>
       <c r="M157" s="21" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session. LIVE RE-OBSERVED 2026-07-23 (clean baseline): as genuine Technician (6 atoms, no seeFinancialData, verified before+after) opened the New Part Request dialog live (New Line -&gt; Save &amp; Add Part -&gt; 'New Part Request'); it shows only Part Number, Description, Quantity — the sell-price field (input_workorder_part_sell_price) is ABSENT, so a vendorless add is prevented. seeFinancialData gate corroborated live for Admin (Parts tab Cost/Sell Price/Margin columns). Clean this run, carried-evidence caveat removed. Evidence: viu-sv8183-2026-07-23/element-reobserve/tech-newpartrequest-dialog-2026-07-23.png.</t>
         </is>
       </c>
       <c r="N157" s="21" t="inlineStr">
@@ -13902,7 +13903,7 @@
       </c>
       <c r="M158" s="17" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock. LIVE RE-OBSERVED 2026-07-23 (Technician cell, clean baseline): Technician (canonical 6 atoms, view_mode=tech, no drift before+after) has NO 'Complete Work Order'/Send-To-Review control on WO S3-25842 = cannot complete, matching the per-role matrix. Clean this run, no carried-evidence caveat. Evidence: viu-sv8183-2026-07-23/element-reobserve/complete-Tech-reset-2026-07-23.png.</t>
         </is>
       </c>
       <c r="N158" s="17" t="inlineStr">
@@ -13919,119 +13920,266 @@
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
+          <t>SF-PERM-11</t>
+        </is>
+      </c>
+      <c r="B159" s="21" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C159" s="21" t="inlineStr">
+        <is>
+          <t>§9.1 Bulk Receive gate / §9.2 Office footnote-4</t>
+        </is>
+      </c>
+      <c r="D159" s="21" t="inlineStr">
+        <is>
+          <t>Verify a Vendor &amp; Order Management View-only user cannot receive purchase orders by any path on the Bulk Receive screen</t>
+        </is>
+      </c>
+      <c r="E159" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F159" s="21" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="G159" s="21" t="inlineStr">
+        <is>
+          <t>Vendor &amp; Order Management: Create &amp; Edit plus See Financial Data are required to receive. A View-only user (for example, Office) has Vendor &amp; Order Management: View only and cannot receive.</t>
+        </is>
+      </c>
+      <c r="H159" s="21" t="inlineStr">
+        <is>
+          <t>1. A user whose role has Vendor &amp; Order Management set to View only exists (for example, Office).
+2. At least one purchase order that can be received exists on the Purchase Orders list.</t>
+        </is>
+      </c>
+      <c r="I159" s="21" t="inlineStr">
+        <is>
+          <t>1. Sign in as the View-only user and open the Purchase Orders list.
+2. Confirm no per-purchase-order Receive button is shown on the list.
+3. Tick the checkboxes to multi-select one or more purchase orders, then use 'Receive Selected'.
+4. If a receive screen opens, try to complete the receive (enter the invoice number, date and cost and use Receive All / Receive Parts).</t>
+        </is>
+      </c>
+      <c r="J159" s="21" t="inlineStr">
+        <is>
+          <t>1. The View-only user must not be able to reach an editable receive screen or complete a receive by any path — neither the per-purchase-order Receive button nor the multi-select 'Receive Selected' route may lead to a usable receive.
+2. No purchase order is received and no inventory is changed.</t>
+        </is>
+      </c>
+      <c r="K159" s="21" t="inlineStr">
+        <is>
+          <t>requirements §9.1 (Bulk Receive gate = Vendor &amp; Order Mgmt: Create &amp; Edit) / §9.2 Office row = 'No (4)', footnote 4 ('Office has Vendor &amp; Order Mgmt: View only — can open Bulk Receive but cannot receive')</t>
+        </is>
+      </c>
+      <c r="L159" s="21" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="M159" s="21" t="inlineStr">
+        <is>
+          <t>Authored 2026-07-24 as a corrective case for the SV-8515 coverage gap (our SV-8183 report missed the multi-select entry point). LIVE re-verify 2026-07-24 on a CLEAN template Office role (drift ruled out, Rule 26; role d704c465 = 25/25 == template; impersonated via switch-user on henry.hess, restored after): (1) the per-PO Receive button IS correctly hidden for Office on /parts/orders; (2) BUILD DEVIATION — after multi-select, the 'Receive Selected' button IS shown and opens the full editable /bulk-receive 'Receive Vendor Parts' screen (invoice #, date, cost, tax inputs + Receive All/Receive Parts), none FE-gated for a View-only user; (3) the backend blocks the actual receive — POST /api/inventory/orders/accept -&gt; HTTP 403 {"errors":[{"error":"Access denied."}]}, so no PO is received and no inventory mutates (receive-view read = 200, which is why the editable screen loads). Net: a REAL front-end exposure defect (misleading dead-end), NOT a data-layer bypass. SV-8515 = dev Ready-to-Fix (FE route guard should require Vendor &amp; Order Mgmt: Create &amp; Edit / hasPartsPermissions to reach Bulk Receive). Deviation from spec wording: requirements §9.1 'Bulk Receive page ... Vendor &amp; Order Mgmt: Create &amp; Edit (route gate hasPartsPermissions)' and §9.2 Office footnote 4 'can open Bulk Receive but cannot receive' — BE matches spec, the FE deviates by exposing the Receive Selected entry point. Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8515-office-parts-orders.png, sv8515-office-after-select.png, sv8515-bulk-receive-screen.png, sv8515-recv5-after.png, sv8515-recv5-net.json, LOG-SV-8515.md).</t>
+        </is>
+      </c>
+      <c r="N159" s="21" t="inlineStr"/>
+      <c r="O159" s="21" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>SF-PERM-12</t>
+        </is>
+      </c>
+      <c r="B160" s="17" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C160" s="17" t="inlineStr">
+        <is>
+          <t>§9.2 Time Clock part-actions</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>Verify a no-access role (Time Clock) cannot edit, cancel or change the vendor of a work order part from the part menu</t>
+        </is>
+      </c>
+      <c r="E160" s="22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F160" s="17" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="G160" s="17" t="inlineStr">
+        <is>
+          <t>Managing a part request (edit / cancel / change vendor) requires WO Lines: Create &amp; Edit. A no-access role such as Time Clock does not have it.</t>
+        </is>
+      </c>
+      <c r="H160" s="17" t="inlineStr">
+        <is>
+          <t>1. A user with a no-access role exists (for example, Time Clock).
+2. A work order with at least one part on a line exists.</t>
+        </is>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>1. Sign in as the no-access (Time Clock) user and open the work order's parts.
+2. On a part row, open the three-dot (⋮) menu.
+3. Review the actions offered in the menu.</t>
+        </is>
+      </c>
+      <c r="J160" s="17" t="inlineStr">
+        <is>
+          <t>1. The part menu must not offer Edit, Cancel or Change Vendor for a no-access user (only Return may appear).
+2. The actions being hidden in the interface is the pass condition.</t>
+        </is>
+      </c>
+      <c r="K160" s="17" t="inlineStr">
+        <is>
+          <t>requirements §9.2 (Time Clock = 'No' across every column) / §9.1 (part-request management maps to WO Lines: Create &amp; Edit)</t>
+        </is>
+      </c>
+      <c r="L160" s="19" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="M160" s="17" t="inlineStr">
+        <is>
+          <t>Authored 2026-07-24 as a corrective case for the SV-8516 coverage gap (no per-role part edit/cancel/return negative existed). LIVE re-verify 2026-07-24 on a CLEAN Time Clock template role (drift ruled out, Rule 26; role e35b0211 = 3/3 == template scheduleView/timesheetsView/workOrdersView, before &amp; after; impersonated via switch-user on henry.hess, restored to Technician after): the Time Clock part-row ⋮ menu shows ONLY 'Return' — no Edit / Cancel / Change Vendor items (sv8516-tc-menus.json: MENU=['Return']; Cancel/Change Vendor keywords = false). The original over-grant's Edit/Cancel/Change-Vendor controls have been removed from the Time Clock UI, so the front-end gating holds and this case PASSES. FLAG (Standing Rule 24): the same edit can still succeed through the API (POST /api/work-orders/part/change-request {id,line,work_order,description,quantity,part_source_type,part_category_id,cost} -&gt; HTTP 200 and the change persisted, confirmed live on Time Clock at 3 perms); per the product ruling 2026-07-24 this front-end-only gating is ACCEPTED for now and is NOT a defect. Editing an already-received part is blocked by state ('Part requests can't be modified once received') for Admin and Time Clock alike, not by permission. Deviation from spec wording noted only as a flag (not a bug): requirements §9.2 'Time Clock = No across every column' and §9.4 atom-collapse (the FE gate is a convenience, not a BE-enforceable boundary — so the residual API-possibility is spec-anticipated). Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8516-tc-wo-lines.png, sv8516-tc-menus.json, LOG-SV-8516.md).</t>
+        </is>
+      </c>
+      <c r="N160" s="17" t="inlineStr"/>
+      <c r="O160" s="17" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="20" t="inlineStr">
+        <is>
           <t>SF-VAL-01</t>
         </is>
       </c>
-      <c r="B159" s="21" t="inlineStr">
+      <c r="B161" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C159" s="21" t="inlineStr">
+      <c r="C161" s="21" t="inlineStr">
         <is>
           <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D159" s="21" t="inlineStr">
+      <c r="D161" s="21" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="E159" s="22" t="inlineStr">
+      <c r="E161" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F159" s="21" t="inlineStr">
+      <c r="F161" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G159" s="21" t="inlineStr">
+      <c r="G161" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H159" s="21" t="inlineStr">
+      <c r="H161" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="I159" s="21" t="inlineStr">
+      <c r="I161" s="21" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J159" s="21" t="inlineStr">
+      <c r="J161" s="21" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="K159" s="21" t="inlineStr">
+      <c r="K161" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html (Details step)</t>
         </is>
       </c>
-      <c r="L159" s="19" t="inlineStr">
+      <c r="L161" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M159" s="21" t="inlineStr">
+      <c r="M161" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
         </is>
       </c>
-      <c r="N159" s="21" t="inlineStr">
+      <c r="N161" s="21" t="inlineStr">
         <is>
           <t>29415</t>
         </is>
       </c>
-      <c r="O159" s="21" t="inlineStr">
+      <c r="O161" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="16" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-02</t>
         </is>
       </c>
-      <c r="B160" s="17" t="inlineStr">
+      <c r="B162" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C160" s="17" t="inlineStr">
+      <c r="C162" s="17" t="inlineStr">
         <is>
           <t>S15-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D160" s="17" t="inlineStr">
+      <c r="D162" s="17" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
-      <c r="E160" s="23" t="inlineStr">
+      <c r="E162" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F160" s="17" t="inlineStr">
+      <c r="F162" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G160" s="17" t="inlineStr">
+      <c r="G162" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H160" s="17" t="inlineStr">
+      <c r="H162" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
@@ -14039,328 +14187,328 @@
 4. You are completing via the No-PO (Skip) or Optional-invoice flow (Story 2 / Story 3).</t>
         </is>
       </c>
-      <c r="I160" s="17" t="inlineStr">
+      <c r="I162" s="17" t="inlineStr">
         <is>
           <t>1. Start completion on a work order whose vehicle has no valid VIN (Require Review off).
 2. Watch the work order header 'Valid VIN Required' chip and try to proceed through completion.</t>
         </is>
       </c>
-      <c r="J160" s="17" t="inlineStr">
+      <c r="J162" s="17" t="inlineStr">
         <is>
           <t>1. The completion Details modal collects Mileage and Engine Hours only — there is no VIN field in the modal.
 2. VIN validity is shown by the 'Valid VIN Required' chip on the work order header; a work order without a valid VIN cannot be completed.
 3. For a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog, not at completion.</t>
         </is>
       </c>
-      <c r="K160" s="17" t="inlineStr">
+      <c r="K162" s="17" t="inlineStr">
         <is>
           <t>requirements S15-R2 / S3-R3</t>
         </is>
       </c>
-      <c r="L160" s="17" t="inlineStr">
+      <c r="L162" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M160" s="17" t="inlineStr">
+      <c r="M162" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, investigated live 2026-07-14): a VIN-less asset cannot be seeded. Asset/vehicle creation is not exposed via API (POST /api/assets 404, POST /api/vehicles 405 GET-only, POST /api/company-vehicles 404) and the new-asset UI flow requires a VIN; all existing assets already carry a VIN. So the non-review No-PO/Optional-invoice completion cannot be driven into a VIN-missing prompt. (Also note the Story-4 completion modal no longer carries a VIN field per Delta1 — SF-COMP-16.) Needs a VIN-less asset seeded by dev/data.</t>
         </is>
       </c>
-      <c r="N160" s="17" t="inlineStr">
+      <c r="N162" s="17" t="inlineStr">
         <is>
           <t>29416</t>
         </is>
       </c>
-      <c r="O160" s="17" t="inlineStr">
+      <c r="O162" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="20" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-03</t>
         </is>
       </c>
-      <c r="B161" s="21" t="inlineStr">
+      <c r="B163" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C161" s="21" t="inlineStr">
+      <c r="C163" s="21" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="D161" s="21" t="inlineStr">
+      <c r="D163" s="21" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="E161" s="23" t="inlineStr">
+      <c r="E163" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F161" s="21" t="inlineStr">
+      <c r="F163" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G161" s="21" t="inlineStr">
+      <c r="G163" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H161" s="21" t="inlineStr">
+      <c r="H163" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="I161" s="21" t="inlineStr">
+      <c r="I163" s="21" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="J161" s="21" t="inlineStr">
+      <c r="J163" s="21" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="K161" s="21" t="inlineStr">
+      <c r="K163" s="21" t="inlineStr">
         <is>
           <t>requirements S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="L161" s="19" t="inlineStr">
+      <c r="L163" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M161" s="21" t="inlineStr">
+      <c r="M163" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
         </is>
       </c>
-      <c r="N161" s="21" t="inlineStr">
+      <c r="N163" s="21" t="inlineStr">
         <is>
           <t>29417</t>
         </is>
       </c>
-      <c r="O161" s="21" t="inlineStr">
+      <c r="O163" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="16" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-04</t>
         </is>
       </c>
-      <c r="B162" s="17" t="inlineStr">
+      <c r="B164" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C162" s="17" t="inlineStr">
+      <c r="C164" s="17" t="inlineStr">
         <is>
           <t>TS-R4</t>
         </is>
       </c>
-      <c r="D162" s="17" t="inlineStr">
+      <c r="D164" s="17" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="E162" s="23" t="inlineStr">
+      <c r="E164" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F162" s="17" t="inlineStr">
+      <c r="F164" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G162" s="17" t="inlineStr">
+      <c r="G164" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H162" s="17" t="inlineStr">
+      <c r="H164" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="I162" s="17" t="inlineStr">
+      <c r="I164" s="17" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="J162" s="17" t="inlineStr">
+      <c r="J164" s="17" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="K162" s="17" t="inlineStr">
+      <c r="K164" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html</t>
         </is>
       </c>
-      <c r="L162" s="19" t="inlineStr">
+      <c r="L164" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M162" s="17" t="inlineStr">
+      <c r="M164" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: tech-story modal Next/Continue disabled while the story textarea is empty (Require Tech Story gate) - behavior per prior VIU; tech-story requirement is a Work Orders setting toggle (see SF-SET-15).</t>
         </is>
       </c>
-      <c r="N162" s="17" t="inlineStr">
+      <c r="N164" s="17" t="inlineStr">
         <is>
           <t>29418</t>
         </is>
       </c>
-      <c r="O162" s="17" t="inlineStr">
+      <c r="O164" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="20" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-05</t>
         </is>
       </c>
-      <c r="B163" s="21" t="inlineStr">
+      <c r="B165" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C163" s="21" t="inlineStr">
+      <c r="C165" s="21" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
-      <c r="D163" s="21" t="inlineStr">
+      <c r="D165" s="21" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="E163" s="22" t="inlineStr">
+      <c r="E165" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F163" s="21" t="inlineStr">
+      <c r="F165" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G163" s="21" t="inlineStr">
+      <c r="G165" s="21" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H163" s="21" t="inlineStr">
+      <c r="H165" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="I163" s="21" t="inlineStr">
+      <c r="I165" s="21" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="J163" s="21" t="inlineStr">
+      <c r="J165" s="21" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="K163" s="21" t="inlineStr">
+      <c r="K165" s="21" t="inlineStr">
         <is>
           <t>requirements §4 / S4-R5</t>
         </is>
       </c>
-      <c r="L163" s="19" t="inlineStr">
+      <c r="L165" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M163" s="21" t="inlineStr">
+      <c r="M165" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
         </is>
       </c>
-      <c r="N163" s="21" t="inlineStr">
+      <c r="N165" s="21" t="inlineStr">
         <is>
           <t>29419</t>
         </is>
       </c>
-      <c r="O163" s="21" t="inlineStr">
+      <c r="O165" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="16" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-06</t>
         </is>
       </c>
-      <c r="B164" s="17" t="inlineStr">
+      <c r="B166" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C164" s="17" t="inlineStr">
+      <c r="C166" s="17" t="inlineStr">
         <is>
           <t>S10 / S12-R2 / S13-R6 / S13-R7</t>
         </is>
       </c>
-      <c r="D164" s="17" t="inlineStr">
+      <c r="D166" s="17" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
-      <c r="E164" s="22" t="inlineStr">
+      <c r="E166" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F164" s="17" t="inlineStr">
+      <c r="F166" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G164" s="17" t="inlineStr">
+      <c r="G166" s="17" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H164" s="17" t="inlineStr">
+      <c r="H166" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="I164" s="17" t="inlineStr">
+      <c r="I166" s="17" t="inlineStr">
         <is>
           <t>1. On a receive surface with a vendor-missing part, try to receive with no vendor selected.
 2. Select a vendor but leave the part number empty and try to receive.
@@ -14368,7 +14516,7 @@
 4. Provide vendor, part number and cost / sell price, then receive.</t>
         </is>
       </c>
-      <c r="J164" s="17" t="inlineStr">
+      <c r="J166" s="17" t="inlineStr">
         <is>
           <t>1. Receiving is blocked while no vendor is selected.
 2. Receiving is blocked while the part number is empty.
@@ -14376,1208 +14524,1208 @@
 4. Receiving succeeds only once vendor, part number and cost / sell price are all present.</t>
         </is>
       </c>
-      <c r="K164" s="17" t="inlineStr">
+      <c r="K166" s="17" t="inlineStr">
         <is>
           <t>requirements S12-R2 / S10 / S13-R6 / S13-R7</t>
         </is>
       </c>
-      <c r="L164" s="19" t="inlineStr">
+      <c r="L166" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M164" s="17" t="inlineStr">
+      <c r="M166" s="17" t="inlineStr">
         <is>
           <t>VIU-Verified live 2026-07-14 on the Bulk Receive page (/bulk-receive) with a freshly seeded vendor-missing WO PO (S-15845, order 0ee75c5f, part 'Gear oil' no PN/no vendor/cost=sell=0). Receive-button gate progression confirmed: no vendor -&gt; Receive DISABLED; vendor assigned (POST /api/orders/{id}/assign-vendor 200, auto-assigned with NO merge prompt, vendor-missing flag cleared) but no part number -&gt; DISABLED; part number entered but cost/sell still 0 -&gt; DISABLED; part number + vendor invoice number + cost + sell all present -&gt; Receive ENABLED (receivable). Confirms a vendor-missing part cannot be received without a vendor, a part number, and a cost/sell price.</t>
         </is>
       </c>
-      <c r="N164" s="17" t="inlineStr">
+      <c r="N166" s="17" t="inlineStr">
         <is>
           <t>29420</t>
         </is>
       </c>
-      <c r="O164" s="17" t="inlineStr">
+      <c r="O166" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="20" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-07</t>
         </is>
       </c>
-      <c r="B165" s="21" t="inlineStr">
+      <c r="B167" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C165" s="21" t="inlineStr">
+      <c r="C167" s="21" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="D165" s="21" t="inlineStr">
+      <c r="D167" s="21" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="E165" s="23" t="inlineStr">
+      <c r="E167" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F165" s="21" t="inlineStr">
+      <c r="F167" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G165" s="21" t="inlineStr">
+      <c r="G167" s="21" t="inlineStr">
         <is>
           <t>Reviewer role (matrix TBD).</t>
         </is>
       </c>
-      <c r="H165" s="21" t="inlineStr">
+      <c r="H167" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="I165" s="21" t="inlineStr">
+      <c r="I167" s="21" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="J165" s="21" t="inlineStr">
+      <c r="J167" s="21" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="K165" s="21" t="inlineStr">
+      <c r="K167" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; requirements R7</t>
         </is>
       </c>
-      <c r="L165" s="19" t="inlineStr">
+      <c r="L167" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M165" s="21" t="inlineStr">
+      <c r="M167" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: Confirm Review disabled until VIN entered in the Mark Reviewed dialog (surfaces when the WO lacks a valid VIN) - same gate as SF-REV-06; Mark Reviewed action confirmed live this run, VIN-required dialog per prior 2026-07-06.</t>
         </is>
       </c>
-      <c r="N165" s="21" t="inlineStr">
+      <c r="N167" s="21" t="inlineStr">
         <is>
           <t>29421</t>
         </is>
       </c>
-      <c r="O165" s="21" t="inlineStr">
+      <c r="O167" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="16" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-08</t>
         </is>
       </c>
-      <c r="B166" s="17" t="inlineStr">
+      <c r="B168" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C166" s="17" t="inlineStr">
+      <c r="C168" s="17" t="inlineStr">
         <is>
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
-      <c r="D166" s="17" t="inlineStr">
+      <c r="D168" s="17" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="E166" s="23" t="inlineStr">
+      <c r="E168" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F166" s="17" t="inlineStr">
+      <c r="F168" s="17" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G166" s="17" t="inlineStr">
+      <c r="G168" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H166" s="17" t="inlineStr">
+      <c r="H168" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="I166" s="17" t="inlineStr">
+      <c r="I168" s="17" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="J166" s="17" t="inlineStr">
+      <c r="J168" s="17" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="K166" s="17" t="inlineStr">
+      <c r="K168" s="17" t="inlineStr">
         <is>
           <t>requirements S3-R9</t>
         </is>
       </c>
-      <c r="L166" s="19" t="inlineStr">
+      <c r="L168" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M166" s="17" t="inlineStr">
+      <c r="M168" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: re-completing after cancel creates no duplicate POs (idempotent) - verified prior (2026-07-08); consistent with SF-COMP-15/23.</t>
         </is>
       </c>
-      <c r="N166" s="17" t="inlineStr">
+      <c r="N168" s="17" t="inlineStr">
         <is>
           <t>29422</t>
         </is>
       </c>
-      <c r="O166" s="17" t="inlineStr">
+      <c r="O168" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="20" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-09</t>
         </is>
       </c>
-      <c r="B167" s="21" t="inlineStr">
+      <c r="B169" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C167" s="21" t="inlineStr">
+      <c r="C169" s="21" t="inlineStr">
         <is>
           <t>S8-R7 / §4 field locking</t>
         </is>
       </c>
-      <c r="D167" s="21" t="inlineStr">
+      <c r="D169" s="21" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="E167" s="23" t="inlineStr">
+      <c r="E169" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F167" s="21" t="inlineStr">
+      <c r="F169" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G167" s="21" t="inlineStr">
+      <c r="G169" s="21" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H167" s="21" t="inlineStr">
+      <c r="H169" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="I167" s="21" t="inlineStr">
+      <c r="I169" s="21" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="J167" s="21" t="inlineStr">
+      <c r="J169" s="21" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="K167" s="21" t="inlineStr">
+      <c r="K169" s="21" t="inlineStr">
         <is>
           <t>requirements S8-R7 / §4</t>
         </is>
       </c>
-      <c r="L167" s="21" t="inlineStr">
+      <c r="L169" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M167" s="21" t="inlineStr">
+      <c r="M169" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, investigated live 2026-07-14): a true invoiced/paid WO state is not drivable in this harness. On WO S-15845 (29f0c308, Complete, valid VIN set) the finance page 'Create Invoice' action and the Estimate/Invoice toggle only fire POST /api/work-orders/invoices/estimate (a recompute) — no invoice is persisted (is_invoice_created stays false, invoice_status=null, invoice_id empty); no confirm dialog renders headless. Direct invoice-create API endpoints all 404 (/api/work-orders/invoices/create, /{id}/create-invoice, /{id}/invoice, /api/work-orders/invoices). Marking the WO PAID would additionally require a payment step. So the sell-field-lock / receive-blocked-when-invoiced-or-paid behavior cannot be exercised here. Needs an invoiced+paid WO seeded by dev, or an interactive (non-headless) session that can complete the finance invoice flow.</t>
         </is>
       </c>
-      <c r="N167" s="21" t="inlineStr">
+      <c r="N169" s="21" t="inlineStr">
         <is>
           <t>29423</t>
         </is>
       </c>
-      <c r="O167" s="21" t="inlineStr">
+      <c r="O169" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="16" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="16" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="B168" s="17" t="inlineStr">
+      <c r="B170" s="17" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C168" s="17" t="inlineStr">
+      <c r="C170" s="17" t="inlineStr">
         <is>
           <t>S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="D168" s="17" t="inlineStr">
+      <c r="D170" s="17" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="E168" s="24" t="inlineStr">
+      <c r="E170" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F168" s="17" t="inlineStr">
+      <c r="F170" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G168" s="17" t="inlineStr">
+      <c r="G170" s="17" t="inlineStr">
         <is>
           <t>receive access.</t>
         </is>
       </c>
-      <c r="H168" s="17" t="inlineStr">
+      <c r="H170" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="I168" s="17" t="inlineStr">
+      <c r="I170" s="17" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="J168" s="17" t="inlineStr">
+      <c r="J170" s="17" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="K168" s="17" t="inlineStr">
+      <c r="K170" s="17" t="inlineStr">
         <is>
           <t>requirements S9-R3 / §4</t>
         </is>
       </c>
-      <c r="L168" s="19" t="inlineStr">
+      <c r="L170" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M168" s="17" t="inlineStr">
+      <c r="M170" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: the same vendor invoice number can be reused across POs (uniqueness relaxed) - verified prior (2026-07-10, Story 9 apply-invoice).</t>
         </is>
       </c>
-      <c r="N168" s="17" t="inlineStr">
+      <c r="N170" s="17" t="inlineStr">
         <is>
           <t>29424</t>
         </is>
       </c>
-      <c r="O168" s="17" t="inlineStr">
+      <c r="O170" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="20" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="20" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="B169" s="21" t="inlineStr">
+      <c r="B171" s="21" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C169" s="21" t="inlineStr">
+      <c r="C171" s="21" t="inlineStr">
         <is>
           <t>S4-R8 / S3-R9 / Key Decision (line approval)</t>
         </is>
       </c>
-      <c r="D169" s="21" t="inlineStr">
+      <c r="D171" s="21" t="inlineStr">
         <is>
           <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
         </is>
       </c>
-      <c r="E169" s="23" t="inlineStr">
+      <c r="E171" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F169" s="21" t="inlineStr">
+      <c r="F171" s="21" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G169" s="21" t="inlineStr">
+      <c r="G171" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access.</t>
         </is>
       </c>
-      <c r="H169" s="21" t="inlineStr">
+      <c r="H171" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Auto-approve Lines is OFF so a newly added line lands in Needs Approval.
 3. A work order has one line still in Needs Approval and all other completion gates satisfied.</t>
         </is>
       </c>
-      <c r="I169" s="21" t="inlineStr">
+      <c r="I171" s="21" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still in Needs Approval; look at the Complete Work Order button, then hover it.
 2. Turn Require Vendor Invoice Number OFF and reopen the same work order; look at the Complete Work Order button again and hover it.
 3. Approve the pending line, then look at the Complete Work Order button again.</t>
         </is>
       </c>
-      <c r="J169" s="21" t="inlineStr">
+      <c r="J171" s="21" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled; hovering it shows the tooltip 'Every line must be approved or declined in order to complete the work order.' (the tooltip is generic and does not name the specific line).
 2. With Require Vendor Invoice Number OFF the Complete Work Order button is still disabled with the same generic tooltip — the unapproved-line gate applies in every completion flow, not only the required-invoice flow.
 3. Once the pending line is approved the Complete Work Order button becomes enabled and completion can proceed.</t>
         </is>
       </c>
-      <c r="K169" s="21" t="inlineStr">
+      <c r="K171" s="21" t="inlineStr">
         <is>
           <t>requirements S4-R8 / S3-R9 / §4 Key Decision</t>
         </is>
       </c>
-      <c r="L169" s="19" t="inlineStr">
+      <c r="L171" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M169" s="21" t="inlineStr">
+      <c r="M171" s="21" t="inlineStr">
         <is>
           <t>VIU-Verified live 2026-07-14 (WO 4448308d). Build behavior: an unapproved (Needs Approval) line disables the 'Complete Work Order' button (aria-disabled) with the GENERIC tooltip 'Every line must be approved or declined in order to complete the work order.' — confirmed identical with Require Vendor Invoice Number ON and OFF. Approving the line (status-&gt;authorized) re-enables the button. BUILD-vs-SPEC observation: the build applies the disabled-button model UNIVERSALLY, not only the Story-4 required-invoice flow (spec Δ2 expected the other flows to keep an active button + 'you need to approve the line' error toast). Not an error/data-corruption (stricter, cleaner gate) — logged as OBS in bugs-log, case ruled Verified against the build. Wording corrected: dropped the 'names the line' claim and the 'button stays active/error toast' branch.</t>
         </is>
       </c>
-      <c r="N169" s="21" t="inlineStr">
+      <c r="N171" s="21" t="inlineStr">
         <is>
           <t>29425</t>
         </is>
       </c>
-      <c r="O169" s="21" t="inlineStr">
+      <c r="O171" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="16" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
         <is>
           <t>SF-QB-01</t>
         </is>
       </c>
-      <c r="B170" s="17" t="inlineStr">
+      <c r="B172" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C170" s="17" t="inlineStr">
+      <c r="C172" s="17" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="D170" s="17" t="inlineStr">
+      <c r="D172" s="17" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="E170" s="22" t="inlineStr">
+      <c r="E172" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F170" s="17" t="inlineStr">
+      <c r="F172" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G170" s="17" t="inlineStr">
+      <c r="G172" s="17" t="inlineStr">
         <is>
           <t>Work Order edit access + Inventory visibility.</t>
         </is>
       </c>
-      <c r="H170" s="17" t="inlineStr">
+      <c r="H172" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="I170" s="17" t="inlineStr">
+      <c r="I172" s="17" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="J170" s="17" t="inlineStr">
+      <c r="J172" s="17" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="K170" s="17" t="inlineStr">
+      <c r="K172" s="17" t="inlineStr">
         <is>
           <t>requirements §5 invariant 1</t>
         </is>
       </c>
-      <c r="L170" s="17" t="inlineStr">
+      <c r="L172" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M170" s="17" t="inlineStr">
+      <c r="M172" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env (partial): the inventory-DECREMENT half is PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201 — prior run). The Part-History LOG half is OBS-6-blocked (GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} crashes). The QuickBooks-integrity leg is blocked: Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
-      <c r="N170" s="17" t="inlineStr">
+      <c r="N172" s="17" t="inlineStr">
         <is>
           <t>29426</t>
         </is>
       </c>
-      <c r="O170" s="17" t="inlineStr">
+      <c r="O172" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="20" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="20" t="inlineStr">
         <is>
           <t>SF-QB-02</t>
         </is>
       </c>
-      <c r="B171" s="21" t="inlineStr">
+      <c r="B173" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C171" s="21" t="inlineStr">
+      <c r="C173" s="21" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="D171" s="21" t="inlineStr">
+      <c r="D173" s="21" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="E171" s="22" t="inlineStr">
+      <c r="E173" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F171" s="21" t="inlineStr">
+      <c r="F173" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G171" s="21" t="inlineStr">
+      <c r="G173" s="21" t="inlineStr">
         <is>
           <t>Admin / owner (settings) + Work Order edit access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H171" s="21" t="inlineStr">
+      <c r="H173" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF (see SF-SET-03).
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="I171" s="21" t="inlineStr">
+      <c r="I173" s="21" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="J171" s="21" t="inlineStr">
+      <c r="J173" s="21" t="inlineStr">
         <is>
           <t>1. No purchase order, vendor bill or accounts-payable sync is produced.
 2. No catalog or inventory sync happens (the part is received at request time only).</t>
         </is>
       </c>
-      <c r="K171" s="21" t="inlineStr">
+      <c r="K173" s="21" t="inlineStr">
         <is>
           <t>requirements §4 / §5</t>
         </is>
       </c>
-      <c r="L171" s="21" t="inlineStr">
+      <c r="L173" s="21" t="inlineStr">
         <is>
           <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
-      <c r="M171" s="21" t="inlineStr">
+      <c r="M173" s="21" t="inlineStr">
         <is>
           <t>VIU-observed 2026-07-14 (awaiting Milos Q5) AND QB-blocked. The 'Create Purchase Orders' toggle is absent (POs always-on, SF-SET-03 Deviation) so the Create-POs-OFF scenario cannot be configured; and QuickBooks is not connected on sv7301 (no QB admin/API — see bugs-log) so QB integrity cannot be inspected regardless. Milos Q5 governs whether POs-always-on is intended. No pass/fail asserted.</t>
         </is>
       </c>
-      <c r="N171" s="21" t="inlineStr">
+      <c r="N173" s="21" t="inlineStr">
         <is>
           <t>29427</t>
         </is>
       </c>
-      <c r="O171" s="21" t="inlineStr">
+      <c r="O173" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29427</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="16" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="16" t="inlineStr">
         <is>
           <t>SF-QB-03</t>
         </is>
       </c>
-      <c r="B172" s="17" t="inlineStr">
+      <c r="B174" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C172" s="17" t="inlineStr">
+      <c r="C174" s="17" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="D172" s="17" t="inlineStr">
+      <c r="D174" s="17" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="E172" s="22" t="inlineStr">
+      <c r="E174" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F172" s="17" t="inlineStr">
+      <c r="F174" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G172" s="17" t="inlineStr">
+      <c r="G174" s="17" t="inlineStr">
         <is>
           <t>receive access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H172" s="17" t="inlineStr">
+      <c r="H174" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="I172" s="17" t="inlineStr">
+      <c r="I174" s="17" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="J172" s="17" t="inlineStr">
+      <c r="J174" s="17" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="K172" s="17" t="inlineStr">
+      <c r="K174" s="17" t="inlineStr">
         <is>
           <t>requirements §5 invariant 2</t>
         </is>
       </c>
-      <c r="L172" s="17" t="inlineStr">
+      <c r="L174" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M172" s="17" t="inlineStr">
+      <c r="M174" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
-      <c r="N172" s="17" t="inlineStr">
+      <c r="N174" s="17" t="inlineStr">
         <is>
           <t>29428</t>
         </is>
       </c>
-      <c r="O172" s="17" t="inlineStr">
+      <c r="O174" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="20" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="20" t="inlineStr">
         <is>
           <t>SF-QB-04</t>
         </is>
       </c>
-      <c r="B173" s="21" t="inlineStr">
+      <c r="B175" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C173" s="21" t="inlineStr">
+      <c r="C175" s="21" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="D173" s="21" t="inlineStr">
+      <c r="D175" s="21" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="E173" s="23" t="inlineStr">
+      <c r="E175" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F173" s="21" t="inlineStr">
+      <c r="F175" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G173" s="21" t="inlineStr">
+      <c r="G175" s="21" t="inlineStr">
         <is>
           <t>Inventory visibility.</t>
         </is>
       </c>
-      <c r="H173" s="21" t="inlineStr">
+      <c r="H175" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="I173" s="21" t="inlineStr">
+      <c r="I175" s="21" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="J173" s="21" t="inlineStr">
+      <c r="J175" s="21" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="K173" s="21" t="inlineStr">
+      <c r="K175" s="21" t="inlineStr">
         <is>
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L173" s="21" t="inlineStr">
+      <c r="L175" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M173" s="21" t="inlineStr">
+      <c r="M175" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
-      <c r="N173" s="21" t="inlineStr">
+      <c r="N175" s="21" t="inlineStr">
         <is>
           <t>29429</t>
         </is>
       </c>
-      <c r="O173" s="21" t="inlineStr">
+      <c r="O175" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="16" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="16" t="inlineStr">
         <is>
           <t>SF-QB-05</t>
         </is>
       </c>
-      <c r="B174" s="17" t="inlineStr">
+      <c r="B176" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C174" s="17" t="inlineStr">
+      <c r="C176" s="17" t="inlineStr">
         <is>
           <t>§5 / S6-R3</t>
         </is>
       </c>
-      <c r="D174" s="17" t="inlineStr">
+      <c r="D176" s="17" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="E174" s="23" t="inlineStr">
+      <c r="E176" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F174" s="17" t="inlineStr">
+      <c r="F176" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G174" s="17" t="inlineStr">
+      <c r="G176" s="17" t="inlineStr">
         <is>
           <t>QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H174" s="17" t="inlineStr">
+      <c r="H176" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="I174" s="17" t="inlineStr">
+      <c r="I176" s="17" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="J174" s="17" t="inlineStr">
+      <c r="J176" s="17" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="K174" s="17" t="inlineStr">
+      <c r="K176" s="17" t="inlineStr">
         <is>
           <t>requirements §5 / S6-R3</t>
         </is>
       </c>
-      <c r="L174" s="17" t="inlineStr">
+      <c r="L176" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M174" s="17" t="inlineStr">
+      <c r="M176" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
-      <c r="N174" s="17" t="inlineStr">
+      <c r="N176" s="17" t="inlineStr">
         <is>
           <t>29430</t>
         </is>
       </c>
-      <c r="O174" s="17" t="inlineStr">
+      <c r="O176" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="20" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="20" t="inlineStr">
         <is>
           <t>SF-QB-06</t>
         </is>
       </c>
-      <c r="B175" s="21" t="inlineStr">
+      <c r="B177" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C175" s="21" t="inlineStr">
+      <c r="C177" s="21" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="D175" s="21" t="inlineStr">
+      <c r="D177" s="21" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="E175" s="23" t="inlineStr">
+      <c r="E177" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F175" s="21" t="inlineStr">
+      <c r="F177" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G175" s="21" t="inlineStr">
+      <c r="G177" s="21" t="inlineStr">
         <is>
           <t>Work Order edit access + See Financial Data + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H175" s="21" t="inlineStr">
+      <c r="H177" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="I175" s="21" t="inlineStr">
+      <c r="I177" s="21" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="J175" s="21" t="inlineStr">
+      <c r="J177" s="21" t="inlineStr">
         <is>
           <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
 2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
         </is>
       </c>
-      <c r="K175" s="21" t="inlineStr">
+      <c r="K177" s="21" t="inlineStr">
         <is>
           <t>requirements §9 (See Financial Data gate on vendorless sell)</t>
         </is>
       </c>
-      <c r="L175" s="21" t="inlineStr">
+      <c r="L177" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M175" s="21" t="inlineStr">
+      <c r="M177" s="21" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
-      <c r="N175" s="21" t="inlineStr">
+      <c r="N177" s="21" t="inlineStr">
         <is>
           <t>29431</t>
         </is>
       </c>
-      <c r="O175" s="21" t="inlineStr">
+      <c r="O177" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="16" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="16" t="inlineStr">
         <is>
           <t>SF-QB-07</t>
         </is>
       </c>
-      <c r="B176" s="17" t="inlineStr">
+      <c r="B178" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C176" s="17" t="inlineStr">
+      <c r="C178" s="17" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="D176" s="17" t="inlineStr">
+      <c r="D178" s="17" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="E176" s="23" t="inlineStr">
+      <c r="E178" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F176" s="17" t="inlineStr">
+      <c r="F178" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G176" s="17" t="inlineStr">
+      <c r="G178" s="17" t="inlineStr">
         <is>
           <t>Finance access + QuickBooks visibility.</t>
         </is>
       </c>
-      <c r="H176" s="17" t="inlineStr">
+      <c r="H178" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="I176" s="17" t="inlineStr">
+      <c r="I178" s="17" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="J176" s="17" t="inlineStr">
+      <c r="J178" s="17" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="K176" s="17" t="inlineStr">
+      <c r="K178" s="17" t="inlineStr">
         <is>
           <t>requirements §5</t>
         </is>
       </c>
-      <c r="L176" s="17" t="inlineStr">
+      <c r="L178" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M176" s="17" t="inlineStr">
+      <c r="M178" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env (precise, confirmed live 2026-07-14): QuickBooks is NOT connected on the sv7301 QA org. There is NO QuickBooks/accounting/integrations option in the Admin menu (menu = Work Orders, Schedule, Customers, Parts, Reports, Feature Flags, Settings, Staff, Locations, Departments, Taxes, Labor Rates, Canned Lines, Asset Types, Pricing, Bin Locations, Categories, IBS, Payment Methods, Contacts, Assets, Vendors, Inventory, Invoices — no QuickBooks); /administration/integrations does not exist; all QB API endpoints 404 (/api/quickbooks*, /api/integrations/quickbooks, /api/organizations/integrations); the WO finance object has invoice_shop_id=null. So QuickBooks sync/vendor-bill/AP/Journal-Entry side-effects cannot be inspected here. Needs a QB-connected company + a human in QuickBooks.</t>
         </is>
       </c>
-      <c r="N176" s="17" t="inlineStr">
+      <c r="N178" s="17" t="inlineStr">
         <is>
           <t>29432</t>
         </is>
       </c>
-      <c r="O176" s="17" t="inlineStr">
+      <c r="O178" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="20" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="20" t="inlineStr">
         <is>
           <t>SF-QB-08</t>
         </is>
       </c>
-      <c r="B177" s="21" t="inlineStr">
+      <c r="B179" s="21" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C177" s="21" t="inlineStr">
+      <c r="C179" s="21" t="inlineStr">
         <is>
           <t>§5 invariant 3 (rescoped after S10-R2 strike)</t>
         </is>
       </c>
-      <c r="D177" s="21" t="inlineStr">
+      <c r="D179" s="21" t="inlineStr">
         <is>
           <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
         </is>
       </c>
-      <c r="E177" s="23" t="inlineStr">
+      <c r="E179" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F177" s="21" t="inlineStr">
+      <c r="F179" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G177" s="21" t="inlineStr">
+      <c r="G179" s="21" t="inlineStr">
         <is>
           <t>Inventory visibility.</t>
         </is>
       </c>
-      <c r="H177" s="21" t="inlineStr">
+      <c r="H179" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
         </is>
       </c>
-      <c r="I177" s="21" t="inlineStr">
+      <c r="I179" s="21" t="inlineStr">
         <is>
           <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
 2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
         </is>
       </c>
-      <c r="J177" s="21" t="inlineStr">
+      <c r="J179" s="21" t="inlineStr">
         <is>
           <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
 2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
         </is>
       </c>
-      <c r="K177" s="21" t="inlineStr">
+      <c r="K179" s="21" t="inlineStr">
         <is>
           <t>requirements §5 invariant 3</t>
         </is>
       </c>
-      <c r="L177" s="19" t="inlineStr">
+      <c r="L179" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M177" s="21" t="inlineStr">
+      <c r="M179" s="21" t="inlineStr">
         <is>
           <t>Rescoped 2026-07-14 for the S10-R2 deprecation (spec _3, last-update-wins). Previously Blocked-Env on QuickBooks; the QB dependency is not needed for this assertion. Part History for a genuinely inventory-tracked part is a native in-app feature (Parts &gt; Inventory clock icon) and inventory decrement + Part History on simple completion is verified elsewhere (SF-COMP-07 Passed). Since a plain part-number add no longer makes a part inventory-tracked (S10-R2 struck), the invariant now only claims Part History for parts that ARE inventory-tracked — which holds.</t>
         </is>
       </c>
-      <c r="N177" s="21" t="inlineStr">
+      <c r="N179" s="21" t="inlineStr">
         <is>
           <t>29433</t>
         </is>
       </c>
-      <c r="O177" s="21" t="inlineStr">
+      <c r="O179" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="16" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="16" t="inlineStr">
         <is>
           <t>SF-QB-09</t>
         </is>
       </c>
-      <c r="B178" s="17" t="inlineStr">
+      <c r="B180" s="17" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C178" s="17" t="inlineStr">
+      <c r="C180" s="17" t="inlineStr">
         <is>
           <t>§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC</t>
         </is>
       </c>
-      <c r="D178" s="17" t="inlineStr">
+      <c r="D180" s="17" t="inlineStr">
         <is>
           <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
         </is>
       </c>
-      <c r="E178" s="24" t="inlineStr">
+      <c r="E180" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F178" s="17" t="inlineStr">
+      <c r="F180" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G178" s="17" t="inlineStr">
+      <c r="G180" s="17" t="inlineStr">
         <is>
           <t>Inventory / Part Sales visibility.</t>
         </is>
       </c>
-      <c r="H178" s="17" t="inlineStr">
+      <c r="H180" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Part Sale exists (or can be created) to which a vendor part can be added.</t>
         </is>
       </c>
-      <c r="I178" s="17" t="inlineStr">
+      <c r="I180" s="17" t="inlineStr">
         <is>
           <t>1. Add a vendor part to the Part Sale so a purchase order is created.
 2. Follow the order's status as it is ordered and then received (same PO/receive pipeline as work orders).
 3. Confirm the part sale itself progresses normally after receiving.</t>
         </is>
       </c>
-      <c r="J178" s="17" t="inlineStr">
+      <c r="J180" s="17" t="inlineStr">
         <is>
           <t>1. The part-sale purchase order moves through the normal statuses (requested, then waiting to receive, then received) with no errors.
 2. Receiving the part-sale PO behaves like receiving a work-order PO (same pipeline).
 3. The part sale is not broken by the shared order/status logic.</t>
         </is>
       </c>
-      <c r="K178" s="17" t="inlineStr">
+      <c r="K180" s="17" t="inlineStr">
         <is>
           <t>requirements-v4 §8 'Part Sales — confirmed (Jul 14)'</t>
         </is>
       </c>
-      <c r="L178" s="17" t="inlineStr">
+      <c r="L180" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M178" s="17" t="inlineStr">
+      <c r="M180" s="17" t="inlineStr">
         <is>
           <t>RESCOPED 2026-07-17 per spec `_4` (V2.6) Δ15 — the §8 'Part Sales impact (investigation — BE)' open question is now CONFIRMED in-spec ('Part Sales — confirmed (Jul 14)': adding a part on a Part Sale already creates a PO received via the same PO/receive pipeline; part-sale POs in scope for PO multi-select + Bulk Receive + Accept Delivery). This case now covers the spec's residual check ('the new order/status logic does not regress part-sale status transitions'); the in-scope part-sale PO behaviors are covered by the new cases SF-POSEL-07 (PO list / multi-select), SF-BULK-11 (Bulk Receive) and SF-WOP-04 (Waiting on Parts). Open-Question RESOLVED → VIU-Pending (seedable per Rule 14: create a Part Sale with a vendor part). ADDED TO TESTRAIL 2026-07-17 (was deliberately unmapped while an open question). || STAGING VIU 2026-07-20: QuickBooks NOT connected on staging (/api/quickbooks/status 404, no QB in Admin) — part-sale QB status transitions cannot be observed. External dependency -&gt; Blocked-Env.</t>
         </is>
       </c>
-      <c r="N178" s="17" t="inlineStr">
+      <c r="N180" s="17" t="inlineStr">
         <is>
           <t>29909</t>
         </is>
       </c>
-      <c r="O178" s="17" t="inlineStr">
+      <c r="O180" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29909</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="20" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="20" t="inlineStr">
         <is>
           <t>SF-AUTO-01</t>
         </is>
       </c>
-      <c r="B179" s="21" t="inlineStr">
+      <c r="B181" s="21" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C179" s="21" t="inlineStr">
+      <c r="C181" s="21" t="inlineStr">
         <is>
           <t>S16-R12 (a) single line</t>
         </is>
       </c>
-      <c r="D179" s="21" t="inlineStr">
+      <c r="D181" s="21" t="inlineStr">
         <is>
           <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="E179" s="18" t="inlineStr">
+      <c r="E181" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F179" s="21" t="inlineStr">
+      <c r="F181" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G179" s="21" t="inlineStr">
+      <c r="G181" s="21" t="inlineStr">
         <is>
           <t>Admin / a role that can complete work orders.</t>
         </is>
       </c>
-      <c r="H179" s="21" t="inlineStr">
+      <c r="H181" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is OFF (in the Work Orders settings tab).
 3. A work order is in Approved status with two or more open (not-yet-completed) lines.</t>
         </is>
       </c>
-      <c r="I179" s="21" t="inlineStr">
+      <c r="I181" s="21" t="inlineStr">
         <is>
           <t>1. Open the work order and complete one line at a time using the per-line Complete action.
 2. After completing the first line (while at least one other line is still open), check the work order status.
@@ -15585,526 +15733,526 @@
 4. Check the work order status again.</t>
         </is>
       </c>
-      <c r="J179" s="21" t="inlineStr">
+      <c r="J181" s="21" t="inlineStr">
         <is>
           <t>1. While at least one line is still open, the work order stays in Approved.
 2. The moment the last open line is completed, the work order moves to Complete on its own (invoice-ready).
 3. You do not have to click Complete Work Order separately for the work order to reach Complete.</t>
         </is>
       </c>
-      <c r="K179" s="21" t="inlineStr">
+      <c r="K181" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L179" s="19" t="inlineStr">
+      <c r="L181" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M179" s="21" t="inlineStr">
+      <c r="M181" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-14 (S-15838 live, Require Review OFF): two authorized lines; completing line 1 left the WO 'Approved'; completing the last line auto-flipped the WO to 'Complete' with no separate Complete Work Order step (WO status read via GET /api/work-orders/view/{id}).</t>
         </is>
       </c>
-      <c r="N179" s="21" t="inlineStr">
+      <c r="N181" s="21" t="inlineStr">
         <is>
           <t>29461</t>
         </is>
       </c>
-      <c r="O179" s="21" t="inlineStr">
+      <c r="O181" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29461</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="16" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="16" t="inlineStr">
         <is>
           <t>SF-AUTO-02</t>
         </is>
       </c>
-      <c r="B180" s="17" t="inlineStr">
+      <c r="B182" s="17" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C180" s="17" t="inlineStr">
+      <c r="C182" s="17" t="inlineStr">
         <is>
           <t>S16-R12 (b) bulk</t>
         </is>
       </c>
-      <c r="D180" s="17" t="inlineStr">
+      <c r="D182" s="17" t="inlineStr">
         <is>
           <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="E180" s="18" t="inlineStr">
+      <c r="E182" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F180" s="17" t="inlineStr">
+      <c r="F182" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G180" s="17" t="inlineStr">
+      <c r="G182" s="17" t="inlineStr">
         <is>
           <t>Admin / a role that can complete work orders.</t>
         </is>
       </c>
-      <c r="H180" s="17" t="inlineStr">
+      <c r="H182" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order is in Approved status with several open lines and nothing left to receive on those lines.</t>
         </is>
       </c>
-      <c r="I180" s="17" t="inlineStr">
+      <c r="I182" s="17" t="inlineStr">
         <is>
           <t>1. Open the work order and select all the open lines.
 2. From the bulk actions menu choose Set line status and set the selected lines to Complete (resolving them all at once).
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="J180" s="17" t="inlineStr">
+      <c r="J182" s="17" t="inlineStr">
         <is>
           <t>1. All selected lines become Complete in one action.
 2. Because that resolves the last open lines, the work order moves to Complete on its own (invoice-ready).
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="K180" s="17" t="inlineStr">
+      <c r="K182" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L180" s="19" t="inlineStr">
+      <c r="L182" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M180" s="17" t="inlineStr">
+      <c r="M182" s="17" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-14 (S-15824 / 446c1cd6 live, Require Review OFF): 3 authorized labor lines resolved in one bulk call (POST /api/work-orders/lines/change-lines {field:'status',value:'complete',lines:[...]} -&gt; 201); the WO auto-flipped 'Approved' -&gt; 'Complete' with no separate Complete step.</t>
         </is>
       </c>
-      <c r="N180" s="17" t="inlineStr">
+      <c r="N182" s="17" t="inlineStr">
         <is>
           <t>29462</t>
         </is>
       </c>
-      <c r="O180" s="17" t="inlineStr">
+      <c r="O182" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29462</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="20" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="20" t="inlineStr">
         <is>
           <t>SF-AUTO-03</t>
         </is>
       </c>
-      <c r="B181" s="21" t="inlineStr">
+      <c r="B183" s="21" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C181" s="21" t="inlineStr">
+      <c r="C183" s="21" t="inlineStr">
         <is>
           <t>S16-R12 (c) split</t>
         </is>
       </c>
-      <c r="D181" s="21" t="inlineStr">
+      <c r="D183" s="21" t="inlineStr">
         <is>
           <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
         </is>
       </c>
-      <c r="E181" s="22" t="inlineStr">
+      <c r="E183" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F181" s="21" t="inlineStr">
+      <c r="F183" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G181" s="21" t="inlineStr">
+      <c r="G183" s="21" t="inlineStr">
         <is>
           <t>Admin / a role that can complete work orders and split.</t>
         </is>
       </c>
-      <c r="H181" s="21" t="inlineStr">
+      <c r="H183" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has several lines; some are already completed and at least one line is still open.</t>
         </is>
       </c>
-      <c r="I181" s="21" t="inlineStr">
+      <c r="I183" s="21" t="inlineStr">
         <is>
           <t>1. Open the work order and complete all but one line, leaving one line still open (the work order stays Approved).
 2. Select the remaining open line and use the bulk actions menu Split work order to move it to a new work order.
 3. Check the status of the original work order after the split.</t>
         </is>
       </c>
-      <c r="J181" s="21" t="inlineStr">
+      <c r="J183" s="21" t="inlineStr">
         <is>
           <t>1. The open line moves to a new work order.
 2. The original work order is now fully resolved (all its remaining lines are complete), so it moves to Complete on its own.
 3. No separate Complete Work Order step is needed on the original work order.</t>
         </is>
       </c>
-      <c r="K181" s="21" t="inlineStr">
+      <c r="K183" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L181" s="19" t="inlineStr">
+      <c r="L183" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M181" s="21" t="inlineStr">
+      <c r="M183" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-14 (S-15822 / a8fb8d3f live, Require Review OFF): completed 2 of 3 lines (WO stayed 'Approved'), then split the still-open line to a new WO (POST /api/work-orders/split -&gt; 201, new WO id returned); the original WO, now fully resolved, auto-flipped to 'Complete'. New split WO cleaned up (deleted).</t>
         </is>
       </c>
-      <c r="N181" s="21" t="inlineStr">
+      <c r="N183" s="21" t="inlineStr">
         <is>
           <t>29463</t>
         </is>
       </c>
-      <c r="O181" s="21" t="inlineStr">
+      <c r="O183" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29463</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="16" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="16" t="inlineStr">
         <is>
           <t>SF-AUTO-04</t>
         </is>
       </c>
-      <c r="B182" s="17" t="inlineStr">
+      <c r="B184" s="17" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C182" s="17" t="inlineStr">
+      <c r="C184" s="17" t="inlineStr">
         <is>
           <t>S16-R12 (d) delete line</t>
         </is>
       </c>
-      <c r="D182" s="17" t="inlineStr">
+      <c r="D184" s="17" t="inlineStr">
         <is>
           <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="E182" s="22" t="inlineStr">
+      <c r="E184" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F182" s="17" t="inlineStr">
+      <c r="F184" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G182" s="17" t="inlineStr">
+      <c r="G184" s="17" t="inlineStr">
         <is>
           <t>Admin / a role that can complete work orders and delete lines.</t>
         </is>
       </c>
-      <c r="H182" s="17" t="inlineStr">
+      <c r="H184" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has some completed lines and one remaining open line.</t>
         </is>
       </c>
-      <c r="I182" s="17" t="inlineStr">
+      <c r="I184" s="17" t="inlineStr">
         <is>
           <t>1. Open the work order (its other lines are already complete; one line is still open).
 2. Select the open line and use the bulk actions menu Delete lines to remove it.
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="J182" s="17" t="inlineStr">
+      <c r="J184" s="17" t="inlineStr">
         <is>
           <t>1. The open line is removed.
 2. Because the remaining lines are all complete, the work order moves to Complete on its own.
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="K182" s="17" t="inlineStr">
+      <c r="K184" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L182" s="17" t="inlineStr">
+      <c r="L184" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M182" s="17" t="inlineStr">
+      <c r="M184" s="17" t="inlineStr">
         <is>
           <t>Wording per spec §16 R12(d)+design. VIU Blocked-Env 2026-07-14: the delete-a-line action could not be driven in this environment — POST /api/work-orders/lines/delete-lines returns HTTP 500 even for a delete that leaves the work order still open (requestId 768518b...), so it is a generic delete-lines failure in this env, not the auto-complete leg; and no browser (Chromium/Playwright) harness is available here to drive the UI 'Delete lines' bulk action. The auto-complete-on-last-line-resolve mechanism itself IS verified on the single, bulk and split paths (SF-AUTO-01/02/03) — the same backend recompute applies. Needs the delete-lines endpoint healthy (or a UI session) to confirm the delete-line trigger directly.</t>
         </is>
       </c>
-      <c r="N182" s="17" t="inlineStr">
+      <c r="N184" s="17" t="inlineStr">
         <is>
           <t>29464</t>
         </is>
       </c>
-      <c r="O182" s="17" t="inlineStr">
+      <c r="O184" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29464</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="20" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="20" t="inlineStr">
         <is>
           <t>SF-AUTO-05</t>
         </is>
       </c>
-      <c r="B183" s="21" t="inlineStr">
+      <c r="B185" s="21" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C183" s="21" t="inlineStr">
+      <c r="C185" s="21" t="inlineStr">
         <is>
           <t>S16-R12 review ON</t>
         </is>
       </c>
-      <c r="D183" s="21" t="inlineStr">
+      <c r="D185" s="21" t="inlineStr">
         <is>
           <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
         </is>
       </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="E185" s="18" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F183" s="21" t="inlineStr">
+      <c r="F185" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G183" s="21" t="inlineStr">
+      <c r="G185" s="21" t="inlineStr">
         <is>
           <t>Admin / a role that can complete work orders.</t>
         </is>
       </c>
-      <c r="H183" s="21" t="inlineStr">
+      <c r="H185" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is ON and saved.
 3. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="I183" s="21" t="inlineStr">
+      <c r="I185" s="21" t="inlineStr">
         <is>
           <t>1. Open the work order and complete the lines one at a time (or in bulk).
 2. After the last open line is resolved, check the work order status.
 3. Confirm whether the work order went straight to Complete or to review.</t>
         </is>
       </c>
-      <c r="J183" s="21" t="inlineStr">
+      <c r="J185" s="21" t="inlineStr">
         <is>
           <t>1. When the last open line is resolved, the work order moves to Ready for Review (Review) — it does NOT auto-complete.
 2. The work order must be signed off in the review step before it can reach Complete.</t>
         </is>
       </c>
-      <c r="K183" s="21" t="inlineStr">
+      <c r="K185" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L183" s="19" t="inlineStr">
+      <c r="L185" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M183" s="21" t="inlineStr">
+      <c r="M185" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-14 (S-15813 / 73d150d3 live): flipped Require Review ON (POST /api/organizations/settings/change requireReview:true); completing line 1 left the WO 'Approved'; resolving the last line routed the WO to 'Review' (Ready for Review), NOT 'Complete'. Settings restored byte-identical to baseline afterward.</t>
         </is>
       </c>
-      <c r="N183" s="21" t="inlineStr">
+      <c r="N185" s="21" t="inlineStr">
         <is>
           <t>29465</t>
         </is>
       </c>
-      <c r="O183" s="21" t="inlineStr">
+      <c r="O185" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29465</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="16" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="16" t="inlineStr">
         <is>
           <t>SF-AUTO-06</t>
         </is>
       </c>
-      <c r="B184" s="17" t="inlineStr">
+      <c r="B186" s="17" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C184" s="17" t="inlineStr">
+      <c r="C186" s="17" t="inlineStr">
         <is>
           <t>S16-R13 clock-out exception</t>
         </is>
       </c>
-      <c r="D184" s="17" t="inlineStr">
+      <c r="D186" s="17" t="inlineStr">
         <is>
           <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
         </is>
       </c>
-      <c r="E184" s="23" t="inlineStr">
+      <c r="E186" s="23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F184" s="17" t="inlineStr">
+      <c r="F186" s="17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G184" s="17" t="inlineStr">
+      <c r="G186" s="17" t="inlineStr">
         <is>
           <t>Technician (clocked into the line) / Admin to observe.</t>
         </is>
       </c>
-      <c r="H184" s="17" t="inlineStr">
+      <c r="H186" s="17" t="inlineStr">
         <is>
           <t>1. Signed in as a Technician who is clocked into the work on the work order.
 2. Require Review Before Completion is OFF.
 3. The work order has one remaining open line that the technician is working on.</t>
         </is>
       </c>
-      <c r="I184" s="17" t="inlineStr">
+      <c r="I186" s="17" t="inlineStr">
         <is>
           <t>1. As the technician, finish the last open line by clocking out of it.
 2. Check the work order status.</t>
         </is>
       </c>
-      <c r="J184" s="17" t="inlineStr">
+      <c r="J186" s="17" t="inlineStr">
         <is>
           <t>1. Even though Require Review is off, the work order routes to Ready for Review (not straight to Complete).
 2. This is the one path that does not auto-complete when review is off (a technician may not be allowed to complete a work order).</t>
         </is>
       </c>
-      <c r="K184" s="17" t="inlineStr">
+      <c r="K186" s="17" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L184" s="17" t="inlineStr">
+      <c r="L186" s="17" t="inlineStr">
         <is>
           <t>Blocked-Env</t>
         </is>
       </c>
-      <c r="M184" s="17" t="inlineStr">
+      <c r="M186" s="17" t="inlineStr">
         <is>
           <t>Wording per spec §16 R13 (intentional clock-out exception). VIU Blocked-Env 2026-07-14: the per-line technician clock-out that finishes a line is not drivable through the available API (GET /api/technician-tasks returns 404; /api/technician-tasks/department-clock-* is a shop-time punch clock, not the per-line 'finish the line' timer), and no browser (Chromium/Playwright) harness is available here to drive the timer/clock-out UI. The auto-complete-vs-review routing is otherwise verified (SF-AUTO-01/05). Needs a technician time-clock UI session (or the per-line clock-out endpoint) to confirm the R13 exception directly.</t>
         </is>
       </c>
-      <c r="N184" s="17" t="inlineStr">
+      <c r="N186" s="17" t="inlineStr">
         <is>
           <t>29466</t>
         </is>
       </c>
-      <c r="O184" s="17" t="inlineStr">
+      <c r="O186" s="17" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29466</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="20" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="20" t="inlineStr">
         <is>
           <t>SF-AUTO-07</t>
         </is>
       </c>
-      <c r="B185" s="21" t="inlineStr">
+      <c r="B187" s="21" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C185" s="21" t="inlineStr">
+      <c r="C187" s="21" t="inlineStr">
         <is>
           <t>S16-R12 backend status transition</t>
         </is>
       </c>
-      <c r="D185" s="21" t="inlineStr">
+      <c r="D187" s="21" t="inlineStr">
         <is>
           <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
         </is>
       </c>
-      <c r="E185" s="22" t="inlineStr">
+      <c r="E187" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F185" s="21" t="inlineStr">
+      <c r="F187" s="21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G185" s="21" t="inlineStr">
+      <c r="G187" s="21" t="inlineStr">
         <is>
           <t>Admin.</t>
         </is>
       </c>
-      <c r="H185" s="21" t="inlineStr">
+      <c r="H187" s="21" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="I185" s="21" t="inlineStr">
+      <c r="I187" s="21" t="inlineStr">
         <is>
           <t>1. With Require Review off, resolve the last open line and read the work order record.
 2. Turn Require Review on, and on another work order resolve the last open line and read the work order record.</t>
         </is>
       </c>
-      <c r="J185" s="21" t="inlineStr">
+      <c r="J187" s="21" t="inlineStr">
         <is>
           <t>1. With Require Review off, after the last open line resolves the work order record status becomes Complete (the resolve action returns success).
 2. With Require Review on, after the last open line resolves the work order record status becomes Ready for Review (Review), not Complete.</t>
         </is>
       </c>
-      <c r="K185" s="21" t="inlineStr">
+      <c r="K187" s="21" t="inlineStr">
         <is>
           <t>WO Review Flow.html; Simple Mode spec §16 R12/R13</t>
         </is>
       </c>
-      <c r="L185" s="19" t="inlineStr">
+      <c r="L187" s="19" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="M185" s="21" t="inlineStr">
+      <c r="M187" s="21" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-14: verified the backend status transition directly. Resolve action POST /api/work-orders/lines/change-status {status:'complete'} returns 200; GET /api/work-orders/view/{id} then shows work_order.status = 'Complete' when Require Review was OFF (S-15838/S-15824), and status = 'Review' (Ready for Review) when Require Review was ON (S-15813). Placed in an API-titled section per Standing Rule 4 (asserts a backend status transition).</t>
         </is>
       </c>
-      <c r="N185" s="21" t="inlineStr">
+      <c r="N187" s="21" t="inlineStr">
         <is>
           <t>29467</t>
         </is>
       </c>
-      <c r="O185" s="21" t="inlineStr">
+      <c r="O187" s="21" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29467</t>
         </is>

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -13988,8 +13988,16 @@
           <t>Authored 2026-07-24 as a corrective case for the SV-8515 coverage gap (our SV-8183 report missed the multi-select entry point). LIVE re-verify 2026-07-24 on a CLEAN template Office role (drift ruled out, Rule 26; role d704c465 = 25/25 == template; impersonated via switch-user on henry.hess, restored after): (1) the per-PO Receive button IS correctly hidden for Office on /parts/orders; (2) BUILD DEVIATION — after multi-select, the 'Receive Selected' button IS shown and opens the full editable /bulk-receive 'Receive Vendor Parts' screen (invoice #, date, cost, tax inputs + Receive All/Receive Parts), none FE-gated for a View-only user; (3) the backend blocks the actual receive — POST /api/inventory/orders/accept -&gt; HTTP 403 {"errors":[{"error":"Access denied."}]}, so no PO is received and no inventory mutates (receive-view read = 200, which is why the editable screen loads). Net: a REAL front-end exposure defect (misleading dead-end), NOT a data-layer bypass. SV-8515 = dev Ready-to-Fix (FE route guard should require Vendor &amp; Order Mgmt: Create &amp; Edit / hasPartsPermissions to reach Bulk Receive). Deviation from spec wording: requirements §9.1 'Bulk Receive page ... Vendor &amp; Order Mgmt: Create &amp; Edit (route gate hasPartsPermissions)' and §9.2 Office footnote 4 'can open Bulk Receive but cannot receive' — BE matches spec, the FE deviates by exposing the Receive Selected entry point. Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8515-office-parts-orders.png, sv8515-office-after-select.png, sv8515-bulk-receive-screen.png, sv8515-recv5-after.png, sv8515-recv5-net.json, LOG-SV-8515.md).</t>
         </is>
       </c>
-      <c r="N159" s="21" t="inlineStr"/>
-      <c r="O159" s="21" t="inlineStr"/>
+      <c r="N159" s="21" t="inlineStr">
+        <is>
+          <t>30646</t>
+        </is>
+      </c>
+      <c r="O159" s="21" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30646</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="16" t="inlineStr">
@@ -14058,11 +14066,19 @@
       </c>
       <c r="M160" s="17" t="inlineStr">
         <is>
-          <t>Authored 2026-07-24 as a corrective case for the SV-8516 coverage gap (no per-role part edit/cancel/return negative existed). LIVE re-verify 2026-07-24 on a CLEAN Time Clock template role (drift ruled out, Rule 26; role e35b0211 = 3/3 == template scheduleView/timesheetsView/workOrdersView, before &amp; after; impersonated via switch-user on henry.hess, restored to Technician after): the Time Clock part-row ⋮ menu shows ONLY 'Return' — no Edit / Cancel / Change Vendor items (sv8516-tc-menus.json: MENU=['Return']; Cancel/Change Vendor keywords = false). The original over-grant's Edit/Cancel/Change-Vendor controls have been removed from the Time Clock UI, so the front-end gating holds and this case PASSES. FLAG (Standing Rule 24): the same edit can still succeed through the API (POST /api/work-orders/part/change-request {id,line,work_order,description,quantity,part_source_type,part_category_id,cost} -&gt; HTTP 200 and the change persisted, confirmed live on Time Clock at 3 perms); per the product ruling 2026-07-24 this front-end-only gating is ACCEPTED for now and is NOT a defect. Editing an already-received part is blocked by state ('Part requests can't be modified once received') for Admin and Time Clock alike, not by permission. Deviation from spec wording noted only as a flag (not a bug): requirements §9.2 'Time Clock = No across every column' and §9.4 atom-collapse (the FE gate is a convenience, not a BE-enforceable boundary — so the residual API-possibility is spec-anticipated). Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8516-tc-wo-lines.png, sv8516-tc-menus.json, LOG-SV-8516.md).</t>
-        </is>
-      </c>
-      <c r="N160" s="17" t="inlineStr"/>
-      <c r="O160" s="17" t="inlineStr"/>
+          <t>Authored 2026-07-24 as a corrective case for the SV-8516 coverage gap (no per-role part edit/cancel/return negative existed). LIVE re-verify 2026-07-24 on a CLEAN Time Clock template role (drift ruled out, Rule 26; role e35b0211 = 3/3 == template scheduleView/timesheetsView/workOrdersView, before &amp; after; impersonated via switch-user on henry.hess, restored to Technician after): the Time Clock part-row ⋮ menu shows ONLY 'Return' — no Edit / Cancel / Change Vendor items (sv8516-tc-menus.json: MENU=['Return']; Cancel/Change Vendor keywords = false). The original over-grant's Edit/Cancel/Change-Vendor controls have been removed from the Time Clock UI, so the front-end gating holds and this case PASSES. PASS per Rule 24 (FE gating is the pass criterion; API-possible accepted): the same edit can still succeed through the API (POST /api/work-orders/part/change-request {id,line,work_order,description,quantity,part_source_type,part_category_id,cost} -&gt; HTTP 200 and the change persisted, confirmed live on Time Clock at 3 perms); per the strengthened Standing Rule 24 (user ruling 2026-07-24) FE-blocks + BE/API-allows = a PASSED test case, so this front-end-only gating is ACCEPTED and is NOT a defect. Editing an already-received part is blocked by state ('Part requests can't be modified once received') for Admin and Time Clock alike, not by permission. Deviation from spec wording noted only as a flag (not a bug): requirements §9.2 'Time Clock = No across every column' and §9.4 atom-collapse (the FE gate is a convenience, not a BE-enforceable boundary — so the residual API-possibility is spec-anticipated). Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8516-tc-wo-lines.png, sv8516-tc-menus.json, LOG-SV-8516.md).</t>
+        </is>
+      </c>
+      <c r="N160" s="17" t="inlineStr">
+        <is>
+          <t>30647</t>
+        </is>
+      </c>
+      <c r="O160" s="17" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30647</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">

--- a/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
+++ b/build/simple-flow/SimpleFlow_V1_TestCases.xlsx
@@ -13555,7 +13555,8 @@
           <t>1. As a role that lacks the mapped permission, confirm the gated setting or action is hidden or unavailable in the app.
 2. As that same role, try the same setting change directly through the API (bypassing the app) and note the response.
 3. As a role that lacks the completion or review sign-off permission, try to complete a work order and to sign off a review directly through the API and note the responses.
-4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.</t>
+4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.
+5. For each of the eleven roles in turn, call the Bulk Receive 'accept' action directly through the API (the 'Receive Selected' / Bulk Receive submit) and note the response for each role.</t>
         </is>
       </c>
       <c r="J154" s="17" t="inlineStr">
@@ -13563,7 +13564,8 @@
           <t>1. In the app, a role without the mapped permission does not see or cannot use the gated setting or action (this is the v1 pass criterion).
 2. The Work Order settings save is also blocked at the backend: the unauthorized API request is rejected with HTTP 403.
 3. Work order completion and review sign-off are NOT blocked at the backend today: a direct API call from a role lacking the permission still succeeds (HTTP 200). This still passes v1 on the app-level restriction, but the backend gap is a known issue to fix later — note it as 'app blocks / backend allows'.
-4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.</t>
+4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.
+5. Unlike work order completion and review sign-off, the Bulk Receive 'accept' action IS enforced at the backend per role: the direct API call is rejected with HTTP 403 for the four roles that should not have it — Office, Sales Representative, Technician, Time Clock — and is allowed for the seven roles that should (Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager, Parts Technician). This matches the permission matrix exactly, so Bulk Receive is genuinely backend-enforced.</t>
         </is>
       </c>
       <c r="K154" s="17" t="inlineStr">
@@ -13578,7 +13580,7 @@
       </c>
       <c r="M154" s="17" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing. | OPTIONAL REGRESSION EDIT 2026-07-24 (user-authorized): added the per-role Bulk Receive 'accept' backend-enforcement matrix (step 5 + expected 5) — POST /api/inventory/orders/accept returns 403 for the 4 No roles (Office, Sales Rep, Technician, Time Clock) and is allowed for the 7 Yes roles (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager, Parts Tech), matching §9.2 exactly (source: rerun2-2026-07-24 be-matrix-11roles.json; recommendation Finding 5). This is the single feature endpoint that genuinely BE-enforces per role — pure regression insurance, no status change.</t>
         </is>
       </c>
       <c r="N154" s="17" t="inlineStr">
@@ -14051,7 +14053,8 @@
       <c r="J160" s="17" t="inlineStr">
         <is>
           <t>1. The part menu must not offer Edit, Cancel or Change Vendor for a no-access user (only Return may appear).
-2. The actions being hidden in the interface is the pass condition.</t>
+2. The actions being hidden in the interface is the pass condition.
+3. QA note: for a no-access role, editing a part or changing its vendor is hidden on screen but can still be done through the API. Per the product ruling (2026-07-24), this front-end-only gating is accepted — it counts as a PASS, not a defect. (The same applies to adding or deleting a work-order part, which the backend also does not block for any role.)</t>
         </is>
       </c>
       <c r="K160" s="17" t="inlineStr">
@@ -14066,7 +14069,7 @@
       </c>
       <c r="M160" s="17" t="inlineStr">
         <is>
-          <t>Authored 2026-07-24 as a corrective case for the SV-8516 coverage gap (no per-role part edit/cancel/return negative existed). LIVE re-verify 2026-07-24 on a CLEAN Time Clock template role (drift ruled out, Rule 26; role e35b0211 = 3/3 == template scheduleView/timesheetsView/workOrdersView, before &amp; after; impersonated via switch-user on henry.hess, restored to Technician after): the Time Clock part-row ⋮ menu shows ONLY 'Return' — no Edit / Cancel / Change Vendor items (sv8516-tc-menus.json: MENU=['Return']; Cancel/Change Vendor keywords = false). The original over-grant's Edit/Cancel/Change-Vendor controls have been removed from the Time Clock UI, so the front-end gating holds and this case PASSES. PASS per Rule 24 (FE gating is the pass criterion; API-possible accepted): the same edit can still succeed through the API (POST /api/work-orders/part/change-request {id,line,work_order,description,quantity,part_source_type,part_category_id,cost} -&gt; HTTP 200 and the change persisted, confirmed live on Time Clock at 3 perms); per the strengthened Standing Rule 24 (user ruling 2026-07-24) FE-blocks + BE/API-allows = a PASSED test case, so this front-end-only gating is ACCEPTED and is NOT a defect. Editing an already-received part is blocked by state ('Part requests can't be modified once received') for Admin and Time Clock alike, not by permission. Deviation from spec wording noted only as a flag (not a bug): requirements §9.2 'Time Clock = No across every column' and §9.4 atom-collapse (the FE gate is a convenience, not a BE-enforceable boundary — so the residual API-possibility is spec-anticipated). Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8516-tc-wo-lines.png, sv8516-tc-menus.json, LOG-SV-8516.md).</t>
+          <t>Authored 2026-07-24 as a corrective case for the SV-8516 coverage gap (no per-role part edit/cancel/return negative existed). LIVE re-verify 2026-07-24 on a CLEAN Time Clock template role (drift ruled out, Rule 26; role e35b0211 = 3/3 == template scheduleView/timesheetsView/workOrdersView, before &amp; after; impersonated via switch-user on henry.hess, restored to Technician after): the Time Clock part-row ⋮ menu shows ONLY 'Return' — no Edit / Cancel / Change Vendor items (sv8516-tc-menus.json: MENU=['Return']; Cancel/Change Vendor keywords = false). The original over-grant's Edit/Cancel/Change-Vendor controls have been removed from the Time Clock UI, so the front-end gating holds and this case PASSES. PASS per Rule 24 (FE gating is the pass criterion; API-possible accepted): the same edit can still succeed through the API (POST /api/work-orders/part/change-request {id,line,work_order,description,quantity,part_source_type,part_category_id,cost} -&gt; HTTP 200 and the change persisted, confirmed live on Time Clock at 3 perms); per the strengthened Standing Rule 24 (user ruling 2026-07-24) FE-blocks + BE/API-allows = a PASSED test case, so this front-end-only gating is ACCEPTED and is NOT a defect. Editing an already-received part is blocked by state ('Part requests can't be modified once received') for Admin and Time Clock alike, not by permission. Deviation from spec wording noted only as a flag (not a bug): requirements §9.2 'Time Clock = No across every column' and §9.4 atom-collapse (the FE gate is a convenience, not a BE-enforceable boundary — so the residual API-possibility is spec-anticipated). Evidence: build/simple-flow/sv8183/ayesha-issues/reverify-2026-07-24/ (sv8516-tc-wo-lines.png, sv8516-tc-menus.json, LOG-SV-8516.md). | OPTIONAL TRACEABILITY EDIT 2026-07-24 (user-authorized): appended a plain QA note to Expected recording the two accepted Rule-24 API behaviors — NEW-1 (a no-access role can still change a part's vendor via the API even though the control is FE-hidden; BE applies the See-Financial-Data gate rather than Vendor &amp; Order Mgmt: Create &amp; Edit per §9.1, a spec-conformance flag not a defect) and NEW-2 (part add/delete via POST /api/work-orders/part/make-request and /parts/delete is not BE-enforced for ANY role, §9.4 / SV-7864 atom-collapse). Both are FE-blocks + BE/API-allows = PASS per the strengthened Standing Rule 24; no status change (source: rerun-2026-07-24 / rerun2-2026-07-24 FINDINGS + recommendation Findings 1 &amp; 2).</t>
         </is>
       </c>
       <c r="N160" s="17" t="inlineStr">
